--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BF6150-1A36-420D-BFF4-D2FF0FE13FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F25545E-9824-4536-B679-D08F69A5DFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4972,30 +4972,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5005,6 +5005,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5014,16 +5023,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5393,7 +5393,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.29</v>
+        <v>10.73</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12696.223889999997</v>
+        <v>13239.11393</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.22761913967028624</v>
+        <v>0.21077952890145579</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0900000000000001</v>
+        <v>1.0924437000000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>16.839117152521428</v>
+        <v>16.876615244077868</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>8.8370124591368651</v>
+        <v>8.8567073541407026</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>10.964982587634889</v>
+        <v>10.989418574505121</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>13.489670428191051</v>
+        <v>13.519731241292133</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>15.187479505223905</v>
+        <v>15.22132284821037</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>11574595.608524427</v>
+        <v>11576404.690875448</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-2582327.2209755722</v>
+        <v>-2580518.1386245508</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-389566992.56364924</v>
+        <v>-389567444.83423698</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>1207881403.2915702</v>
+        <v>1207889974.6580667</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>1109895499.6909478</v>
+        <v>1109896856.5027108</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.5287079461161994E-2</v>
+        <v>9.1584666084687946E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5894,14 +5894,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.7201166180758024E-2</v>
+        <v>5.4978527306616974E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.72703422459564127</v>
+        <v>0.72866329119929796</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5921,11 +5921,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095589410589849</v>
+        <v>0.10095601131136619</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.8884951666389239E-2</v>
+        <v>8.8885506981639828E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5935,11 +5935,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>0.1263954426223067</v>
+        <v>0.12639558936200029</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128278252432619</v>
+        <v>0.11128347777166675</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25013021749406933</v>
+        <v>-0.25069099108351001</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>6705419480.0925961</v>
+        <v>6705117966.3674259</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9237026758722804</v>
+        <v>5.9367162220374494</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.51552737642662227</v>
+        <v>0.51668315096769923</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.1890998348048338</v>
+        <v>6.2027083819216378</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7008492751797555</v>
+        <v>1.7046624544217344</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>16.789143593241125</v>
+        <v>16.826529647745442</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.38 HKD</v>
+        <v>17.42 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.3635532053681615E-2</v>
+        <v>2.3635880103361234E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.08 HKD</v>
+        <v>17.12 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.980975358546533E-2</v>
+        <v>2.9810197792355522E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>16.79 HKD</v>
+        <v>16.83 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.6015658262164192E-2</v>
+        <v>3.6016201355065697E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.5 HKD</v>
+        <v>16.54 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.2252185932175432E-2</v>
+        <v>4.2252830682570734E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.22 HKD</v>
+        <v>16.25 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,17 +6445,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.8518211535007863E-2</v>
+        <v>4.851896075547317E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>16.839117152521428</v>
+        <v>16.876615244077868</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.58860000000000001</v>
+        <v>0.58991959800000016</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,15 +6566,15 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>1.0770506376984164</v>
+        <v>1.0794653061785484</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>7.7599618214384485</v>
+        <v>7.7772420479621536</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>8.8370124591368651</v>
+        <v>8.8567073541407026</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,15 +6587,15 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>1.2384167233625794</v>
+        <v>1.2411931627633881</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>9.7265658642723096</v>
+        <v>9.7482254117417337</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>10.964982587634889</v>
+        <v>10.989418574505121</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,15 +6634,15 @@
       </c>
       <c r="C144" s="337">
         <f>Scenarios!C66</f>
-        <v>1.4200581999274888</v>
+        <v>1.4232418661872714</v>
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>12.069612228263562</v>
+        <v>12.096489375104861</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>13.489670428191051</v>
+        <v>13.519731241292133</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,15 +6655,15 @@
       </c>
       <c r="C145" s="337">
         <f>Scenarios!C67</f>
-        <v>1.5376440587140374</v>
+        <v>1.5410913438390648</v>
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>13.649835446509867</v>
+        <v>13.680231504371305</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>15.187479505223905</v>
+        <v>15.22132284821037</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,6 +6777,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6793,18 +6805,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.65400000000000003</v>
+        <v>0.6554662200000001</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.65400000000000003</v>
+        <v>0.6554662200000001</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10216,11 +10216,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.239200554281467</v>
+        <v>13.268881870239724</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7008492751797555</v>
+        <v>1.7046624544217344</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6705419480.0925961</v>
+        <v>6705117966.3674259</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10478,11 +10478,11 @@
       </c>
       <c r="C73" s="289">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-983824392.20499992</v>
+        <v>-983975149.06758499</v>
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-964549634.04370224</v>
+        <v>-964700390.90628731</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10494,11 +10494,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7764837064344938</v>
+        <v>8.7751390432594469</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9518656618854546</v>
+        <v>8.9504667247706884</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10511,7 +10511,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1929099268.0874045</v>
+        <v>1929400781.8125746</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10626,11 +10626,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>308620917.68309999</v>
+        <v>309312823.12946904</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.25013021749406933</v>
+        <v>0.25069099108351001</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10643,11 +10643,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7308907233.30093</v>
+        <v>7324963880.1149082</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.9237026758722804</v>
+        <v>5.9367162220374494</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10660,11 +10660,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>636078813.65760005</v>
+        <v>637504855.67313695</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.51552737642662227</v>
+        <v>0.51668315096769923</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10677,11 +10677,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>8253606964.6416302</v>
+        <v>8271781558.9175138</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.6893602697929717</v>
+        <v>6.7040903640886587</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11162,36 +11162,36 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-2582327.2209755722</v>
+        <v>-2580518.1386245508</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>42398130.75156936</v>
+        <v>42406702.118065715</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40864718.496472761</v>
+        <v>40873899.449171297</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>17656081.432377532</v>
+        <v>17662119.878446877</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>5033237.4418803789</v>
+        <v>5037070.0296748653</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
-        <v>-4723118.4306187667</v>
+        <v>-4720392.4684606194</v>
       </c>
       <c r="L10" s="270">
         <f t="shared" si="6"/>
-        <v>-6438957.324082097</v>
+        <v>-6436925.2410469837</v>
       </c>
       <c r="M10" s="270">
         <f t="shared" si="6"/>
-        <v>7526252.7046930669</v>
+        <v>7527509.7544652186</v>
       </c>
       <c r="N10" s="270">
         <f t="shared" si="6"/>
@@ -11217,36 +11217,36 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>1558267970.2545969</v>
+        <v>1558269779.3369479</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1371951330.2915702</v>
+        <v>1371959901.6580667</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>1481849386.8164725</v>
+        <v>1481858567.769171</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>1407183580.4323776</v>
+        <v>1407189618.8784468</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>1240487555.4418805</v>
+        <v>1240491388.0296748</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
-        <v>1157432572.5693812</v>
+        <v>1157435298.5315394</v>
       </c>
       <c r="L11" s="271">
         <f t="shared" si="7"/>
-        <v>999246857.25591993</v>
+        <v>999248889.33895504</v>
       </c>
       <c r="M11" s="271">
         <f t="shared" si="7"/>
-        <v>939473559.47469211</v>
+        <v>939474816.52446425</v>
       </c>
       <c r="N11" s="271">
         <f t="shared" si="7"/>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-389566992.56364924</v>
+        <v>-389567444.83423698</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11384,38 +11384,38 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>1109895499.6909478</v>
+        <v>1109896856.5027108</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207881403.2915702</v>
+        <v>1207889974.6580667</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>1497823329.8164725</v>
+        <v>1497832510.769171</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>1418619057.4323776</v>
+        <v>1418625095.8784468</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>1235034743.4418805</v>
+        <v>1235038576.0296748</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
-        <v>1149262021.5693812</v>
+        <v>1149264747.5315394</v>
       </c>
       <c r="L14" s="271">
         <f t="shared" si="8"/>
-        <v>975074782.13591993</v>
+        <v>975076814.21895504</v>
       </c>
       <c r="M14" s="271">
         <f t="shared" si="8"/>
-        <v>950269405.84469211</v>
+        <v>950270662.89446425</v>
       </c>
       <c r="N14" s="271">
         <f t="shared" si="8"/>
@@ -11602,38 +11602,38 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>1109895499.6909478</v>
+        <v>1109896856.5027108</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207881403.2915702</v>
+        <v>1207889974.6580667</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>1497823329.8164725</v>
+        <v>1497832510.769171</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>1418619057.4323776</v>
+        <v>1418625095.8784468</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>1235034743.4418805</v>
+        <v>1235038576.0296748</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
-        <v>1149262021.5693812</v>
+        <v>1149264747.5315394</v>
       </c>
       <c r="L19" s="275">
         <f t="shared" si="9"/>
-        <v>975074782.13591993</v>
+        <v>975076814.21895504</v>
       </c>
       <c r="M19" s="275">
         <f t="shared" si="9"/>
-        <v>950269405.84469211</v>
+        <v>950270662.89446425</v>
       </c>
       <c r="N19" s="275">
         <f t="shared" si="9"/>
@@ -12341,31 +12341,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.672608107579805E-2</v>
+        <v>7.6725601726977469E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.3984391787633373E-2</v>
+        <v>-4.3984119279426949E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.1264997396333204E-3</v>
+        <v>-8.1264648676944214E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3957006872653599E-3</v>
+        <v>4.3956871064304067E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.0592025778764955E-3</v>
+        <v>7.059185952222242E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4190293864301063E-2</v>
+        <v>2.4190244670665422E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491378614249145E-2</v>
+        <v>-1.1491363238387425E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12479,36 +12479,36 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>11574595.608524427</v>
+        <v>11576404.690875448</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54840013.75156936</v>
+        <v>54848585.118065715</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>58740175.496472761</v>
+        <v>58749356.449171297</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>38634267.432377532</v>
+        <v>38640305.878446877</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>24521080.441880379</v>
+        <v>24524913.029674865</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
-        <v>17440836.569381233</v>
+        <v>17443562.531539381</v>
       </c>
       <c r="L46" s="278">
         <f t="shared" si="17"/>
-        <v>13001364.675917903</v>
+        <v>13003396.758953016</v>
       </c>
       <c r="M46" s="278">
         <f t="shared" si="17"/>
-        <v>8042664.7046930669</v>
+        <v>8043921.7544652186</v>
       </c>
       <c r="N46" s="278">
         <f t="shared" si="17"/>
@@ -12591,36 +12591,36 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-2582327.2209755722</v>
+        <v>-2580518.1386245508</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42398130.75156936</v>
+        <v>42406702.118065715</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40864718.496472761</v>
+        <v>40873899.449171297</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>17656081.432377532</v>
+        <v>17662119.878446877</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>5033237.4418803789</v>
+        <v>5037070.0296748653</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
-        <v>-4723118.4306187667</v>
+        <v>-4720392.4684606194</v>
       </c>
       <c r="L48" s="271">
         <f t="shared" si="18"/>
-        <v>-6438957.324082097</v>
+        <v>-6436925.2410469837</v>
       </c>
       <c r="M48" s="271">
         <f t="shared" si="18"/>
-        <v>7526252.7046930669</v>
+        <v>7527509.7544652186</v>
       </c>
       <c r="N48" s="271">
         <f t="shared" si="18"/>
@@ -13556,38 +13556,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0945973242170331E-4</v>
+        <v>2.0931299272810609E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.439030131529608E-3</v>
+        <v>3.4397253788701586E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4431268875100233E-3</v>
+        <v>3.4439004444131991E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.6153332859156337E-3</v>
+        <v>1.6158857359577553E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8117230428875476E-4</v>
+        <v>4.8153869572602681E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2432157838990033E-4</v>
+        <v>5.2401896459725755E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.2818638496382538E-4</v>
+        <v>7.279565752097289E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.1933994137474782E-4</v>
+        <v>9.1949349136956988E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13613,38 +13613,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.1263954426223067</v>
+        <v>0.12639558936200029</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.11128278252432619</v>
+        <v>0.11128347777166675</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12485575955768381</v>
+        <v>0.12485653311458698</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12874150391592704</v>
+        <v>0.12874205636596917</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11858932990661795</v>
+        <v>0.1185896962980552</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12848859969195317</v>
+        <v>0.12848890230574583</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300555665282036</v>
+        <v>0.11300578646257446</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.1147577155563782</v>
+        <v>0.11475786910637302</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1598860655576676E-2</v>
+        <v>3.1598897340500073E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13785,38 +13785,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.0026706334099316E-2</v>
+        <v>9.0026816388869488E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.7974615097393622E-2</v>
+        <v>9.7975310344734182E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12620167149997702</v>
+        <v>0.12620244505688019</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12978772171397981</v>
+        <v>0.12978827416402194</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11806804670764509</v>
+        <v>0.11806841309908234</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758157263778</v>
+        <v>0.12758187525157266</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11027191902908971</v>
+        <v>0.11027214883884381</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607643991474285</v>
+        <v>0.11607659346473768</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14008,38 +14008,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.0026706334099316E-2</v>
+        <v>9.0026816388869488E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.7974615097393622E-2</v>
+        <v>9.7975310344734182E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12620167149997702</v>
+        <v>0.12620244505688019</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12978772171397981</v>
+        <v>0.12978827416402194</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11806804670764509</v>
+        <v>0.11806841309908234</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758157263778</v>
+        <v>0.12758187525157266</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11027191902908971</v>
+        <v>0.11027214883884381</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607643991474285</v>
+        <v>0.11607659346473768</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14077,12 +14077,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.65400000000000003</v>
+        <v>0.6554662200000001</v>
       </c>
       <c r="E88" s="238"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.65400000000000003</v>
+        <v>0.6554662200000001</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14133,12 +14133,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>806932014</v>
+        <v>808741096.3510201</v>
       </c>
       <c r="E89" s="238"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>806932014</v>
+        <v>808741096.3510201</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.72703422459564127</v>
+        <v>0.72866329119929796</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.66805566490306745</v>
+        <v>0.66954864542191528</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14264,12 +14264,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.7201166180758024E-2</v>
+        <v>5.4978527306616974E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.7201166180758024E-2</v>
+        <v>5.4978527306616974E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14401,38 +14401,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.13580411771854206</v>
+        <v>0.13579834035507776</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162770860945249E-2</v>
+        <v>-7.4162722746576648E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.3060458793267706E-2</v>
+        <v>5.3062464282700228E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.13437944158264248</v>
+        <v>0.13438080462093804</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1757944990372691E-2</v>
+        <v>7.1758732089396426E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830494153152785</v>
+        <v>0.15830531400163106</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.362424698216107E-2</v>
+        <v>6.3624986815103535E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35101965277048275</v>
+        <v>0.35102146048388727</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -15012,31 +15012,31 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4674278676448351</v>
+        <v>1.4674174545589376</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5709651226278571</v>
+        <v>1.5709554934093843</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.427008268635569</v>
+        <v>1.4270021945061211</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.6577101072431046</v>
+        <v>1.6577049630155098</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.5825853946833814</v>
+        <v>1.5825816409200233</v>
       </c>
       <c r="L113" s="254">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3992880798652516</v>
+        <v>1.3992851637159525</v>
       </c>
       <c r="M113" s="254">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.0454406569965542</v>
+        <v>1.045439274052735</v>
       </c>
       <c r="N113" s="254">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15120,36 +15120,36 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.1263954426223067</v>
+        <v>0.12639558936200029</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.11128278252432619</v>
+        <v>0.11128347777166675</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12485575955768381</v>
+        <v>0.12485653311458698</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12874150391592704</v>
+        <v>0.12874205636596917</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11858932990661795</v>
+        <v>0.1185896962980552</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12848859969195317</v>
+        <v>0.12848890230574583</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300555665282036</v>
+        <v>0.11300578646257446</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.1147577155563782</v>
+        <v>0.11475786910637302</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15285,38 +15285,38 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.10095589410589849</v>
+        <v>0.10095601131136619</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.8884951666389239E-2</v>
+        <v>8.8885506981639828E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11046907221939727</v>
+        <v>0.11046975664207592</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11113409200750815</v>
+        <v>0.11113456890137642</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11165817555137104</v>
+        <v>0.11165852052843984</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11541835439311031</v>
+        <v>0.11541862622412138</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.10956694591986318</v>
+        <v>0.10956716873680816</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176186985763205</v>
+        <v>0.11176201939907643</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15406,50 +15406,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.98050404765535681</v>
+        <v>0.9827034670887016</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.06706676920917</v>
+        <v>1.0694666436829097</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3232073091265044</v>
+        <v>1.3261819716194903</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2532366590195103</v>
+        <v>1.2560516700728095</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0910545770092337</v>
+        <v>1.0935040346694505</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0152812262768263</v>
+        <v>1.0175598258389218</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.86140070927141577</v>
+        <v>0.86333370564729817</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.8394871400534708</v>
+        <v>0.84137032160049918</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.61381907885513609</v>
+        <v>0.61519521617898787</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.50546897581908834</v>
+        <v>0.50660220016423441</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.47653321225344275</v>
+        <v>0.47760156474040039</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15463,50 +15463,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.5287079461161994E-2</v>
+        <v>9.1584666084687946E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.1036993944809689</v>
+        <v>9.9670703045937517E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.12859157523095283</v>
+        <v>0.12359571030936535</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12179170641589022</v>
+        <v>0.11705980149793191</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10603057113792359</v>
+        <v>0.10191090723853219</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.8666785838369908E-2</v>
+        <v>9.4833161774363628E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.371241100791213E-2</v>
+        <v>8.0459804813354907E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.1582812444457808E-2</v>
+        <v>7.8412891109086599E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.9651999888740148E-2</v>
+        <v>5.7334130119197378E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.9122349447919184E-2</v>
+        <v>4.721362536479351E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.6310321890519222E-2</v>
+        <v>4.4510863442721378E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15520,43 +15520,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12631012873545036</v>
+        <v>0.12113058943968164</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12825469360874669</v>
+        <v>0.12299541446728829</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10957865425607269</v>
+        <v>0.10508521456616848</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1026510932141415</v>
+        <v>9.8441728720737739E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7902727438433673E-2</v>
+        <v>9.3888076919057081E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8582655272472513E-2</v>
+        <v>8.4950188513862268E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2991503205131342E-2</v>
+        <v>6.99983753942965E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2185271671355203E-2</v>
+        <v>6.9225204613070357E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9624045664966622E-2</v>
+        <v>4.7589136057083543E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8433282630147449E-2</v>
+        <v>4.6447202074950344E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>1109895499.6909478</v>
+        <v>1109896856.5027108</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>6705419480.0925961</v>
+        <v>6705117966.3674259</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>11998870266.929165</v>
+        <v>11998884935.164442</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-2582327.2209755722</v>
+        <v>-2580518.1386245508</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16404,14 +16404,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>7005839568.1425962</v>
+        <v>7005538054.4174261</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>7005839568.1425962</v>
+        <v>7005538054.4174261</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>19004709835.071762</v>
+        <v>19004422989.581867</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.1890998348048338</v>
+        <v>6.2027083819216378</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-2582327.2209755722</v>
+        <v>-2580518.1386245508</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0900000000000001</v>
+        <v>1.0924437000000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>20715133720.228222</v>
+        <v>20761262167.103882</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>16.789143593241125</v>
+        <v>16.826529647745442</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>16.840420150876522</v>
+        <v>16.877921163659639</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>1561001146.7179101</v>
+        <v>1561002955.800261</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16723,11 +16723,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>1111842408.8393734</v>
+        <v>1111843765.6511366</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>1.754137348036533E-3</v>
+        <v>1.7541352036625213E-3</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>1017704722.0497696</v>
+        <v>1017705963.9827337</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>1563739109.1966355</v>
+        <v>1563740918.2789865</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16772,11 +16772,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>1113792727.1848693</v>
+        <v>1113794083.9966326</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>1.7541319974760938E-3</v>
+        <v>1.7541298568632957E-3</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>933171542.76128101</v>
+        <v>933172679.54202616</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>1566481866.0714772</v>
+        <v>1566483675.1538281</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16821,11 +16821,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>1115746460.6972177</v>
+        <v>1115747817.508981</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>1.7541266563003699E-3</v>
+        <v>1.754124519442346E-3</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>855659902.82777059</v>
+        <v>855660943.35934508</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>1566481866.0714772</v>
+        <v>1566483675.1538281</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>12062123899.42938</v>
+        <v>12062138567.66466</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18285,7 +18285,7 @@
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>9250377327.8677902</v>
+        <v>9250388576.8577843</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18298,7 +18298,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>12056913495.506611</v>
+        <v>12056928163.74189</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18322,7 +18322,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>12056913495.506611</v>
+        <v>12056928163.74189</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18357,19 +18357,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>11758474105.825018</v>
+        <v>11758488774.060295</v>
       </c>
       <c r="C56" s="118">
-        <v>11878672186.37709</v>
+        <v>11878686854.612366</v>
       </c>
       <c r="D56" s="118">
-        <v>11998870266.929165</v>
+        <v>11998884935.164442</v>
       </c>
       <c r="E56" s="118">
-        <v>12119068347.481236</v>
+        <v>12119083015.716515</v>
       </c>
       <c r="F56" s="118">
-        <v>12239266428.033314</v>
+        <v>12239281096.268593</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18383,19 +18383,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>11542832698.152647</v>
+        <v>11542847366.387926</v>
       </c>
       <c r="C57" s="118">
-        <v>11769751271.277269</v>
+        <v>11769765939.51255</v>
       </c>
       <c r="D57" s="118">
-        <v>11998870266.929163</v>
+        <v>11998884935.16444</v>
       </c>
       <c r="E57" s="118">
-        <v>12230189685.108326</v>
+        <v>12230204353.343605</v>
       </c>
       <c r="F57" s="118">
-        <v>12463709525.81476</v>
+        <v>12463724194.050035</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18409,19 +18409,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>11349396927.425943</v>
+        <v>11349411595.661221</v>
       </c>
       <c r="C58" s="118">
-        <v>11671049480.935095</v>
+        <v>11671064149.170372</v>
       </c>
       <c r="D58" s="118">
-        <v>11998870266.929163</v>
+        <v>11998884935.16444</v>
       </c>
       <c r="E58" s="118">
-        <v>12332919708.910025</v>
+        <v>12332934377.145306</v>
       </c>
       <c r="F58" s="118">
-        <v>12673258230.379583</v>
+        <v>12673272898.614862</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18435,19 +18435,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>11175880171.991465</v>
+        <v>11175894840.226742</v>
       </c>
       <c r="C59" s="118">
-        <v>11581608041.631893</v>
+        <v>11581622709.867172</v>
       </c>
       <c r="D59" s="118">
-        <v>11998870266.929165</v>
+        <v>11998884935.16444</v>
       </c>
       <c r="E59" s="118">
-        <v>12427892087.893751</v>
+        <v>12427906756.129032</v>
       </c>
       <c r="F59" s="118">
-        <v>12868900956.838282</v>
+        <v>12868915625.073555</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18461,19 +18461,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>11020231274.668089</v>
+        <v>11020245942.903366</v>
       </c>
       <c r="C60" s="118">
-        <v>11500558133.247301</v>
+        <v>11500572801.482576</v>
       </c>
       <c r="D60" s="118">
-        <v>11998870266.929165</v>
+        <v>11998884935.16444</v>
       </c>
       <c r="E60" s="118">
-        <v>12515692639.631565</v>
+        <v>12515707307.866844</v>
       </c>
       <c r="F60" s="118">
-        <v>13051560527.536558</v>
+        <v>13051575195.771837</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18487,19 +18487,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>10880610295.833385</v>
+        <v>10880624964.068665</v>
       </c>
       <c r="C61" s="118">
-        <v>11427112449.676819</v>
+        <v>11427127117.912098</v>
       </c>
       <c r="D61" s="118">
-        <v>11998870266.929161</v>
+        <v>11998884935.16444</v>
       </c>
       <c r="E61" s="118">
-        <v>12596862943.75531</v>
+        <v>12596877611.990589</v>
       </c>
       <c r="F61" s="118">
-        <v>13222098524.893299</v>
+        <v>13222113193.128578</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18513,19 +18513,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>10755366763.331779</v>
+        <v>10755381431.567059</v>
       </c>
       <c r="C62" s="118">
-        <v>11360557551.063751</v>
+        <v>11360572219.29903</v>
       </c>
       <c r="D62" s="118">
-        <v>11998870266.929163</v>
+        <v>11998884935.16444</v>
       </c>
       <c r="E62" s="118">
-        <v>12671903682.579094</v>
+        <v>12671918350.814373</v>
       </c>
       <c r="F62" s="118">
-        <v>13381319355.377401</v>
+        <v>13381334023.61268</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18539,19 +18539,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>10643020162.094639</v>
+        <v>10643034830.329918</v>
       </c>
       <c r="C63" s="118">
-        <v>11300246933.556259</v>
+        <v>11300261601.791538</v>
       </c>
       <c r="D63" s="118">
-        <v>11998870266.929161</v>
+        <v>11998884935.164438</v>
       </c>
       <c r="E63" s="118">
-        <v>12741277729.455082</v>
+        <v>12741292397.690361</v>
       </c>
       <c r="F63" s="118">
-        <v>13529974043.792763</v>
+        <v>13529988712.028042</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18565,19 +18565,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>10542242432.838442</v>
+        <v>10542257101.073719</v>
       </c>
       <c r="C64" s="118">
-        <v>11245594749.27029</v>
+        <v>11245609417.505573</v>
       </c>
       <c r="D64" s="118">
-        <v>11998870266.929161</v>
+        <v>11998884935.164436</v>
       </c>
       <c r="E64" s="118">
-        <v>12805413003.912521</v>
+        <v>12805427672.1478</v>
       </c>
       <c r="F64" s="118">
-        <v>13668763775.768658</v>
+        <v>13668778444.003937</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18591,19 +18591,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>10451842272.956451</v>
+        <v>10451856941.19173</v>
       </c>
       <c r="C65" s="118">
-        <v>11196070115.455091</v>
+        <v>11196084783.690372</v>
       </c>
       <c r="D65" s="118">
-        <v>11998870266.929161</v>
+        <v>11998884935.164436</v>
       </c>
       <c r="E65" s="118">
-        <v>12864705111.19125</v>
+        <v>12864719779.426529</v>
       </c>
       <c r="F65" s="118">
-        <v>13798343205.164921</v>
+        <v>13798357873.4002</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18617,19 +18617,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>10121724568.857693</v>
+        <v>10121739237.092968</v>
       </c>
       <c r="C66" s="281">
-        <v>11010016141.023438</v>
+        <v>11010030809.258718</v>
       </c>
       <c r="D66" s="118">
-        <v>11998870266.929161</v>
+        <v>11998884935.164436</v>
       </c>
       <c r="E66" s="118">
-        <v>13100394802.152721</v>
+        <v>13100409470.387997</v>
       </c>
       <c r="F66" s="118">
-        <v>14328113820.962217</v>
+        <v>14328128489.197496</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18652,19 +18652,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>9929993732.7027645</v>
+        <v>9930008400.9380398</v>
       </c>
       <c r="C67" s="281">
-        <v>10896329955.101215</v>
+        <v>10896344623.336493</v>
       </c>
       <c r="D67" s="118">
-        <v>11998870266.929161</v>
+        <v>11998884935.164436</v>
       </c>
       <c r="E67" s="118">
-        <v>13259557109.955845</v>
+        <v>13259571778.191122</v>
       </c>
       <c r="F67" s="118">
-        <v>14703935212.874456</v>
+        <v>14703949881.109735</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18687,19 +18687,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>9818637349.5817032</v>
+        <v>9818652017.8169785</v>
       </c>
       <c r="C68" s="281">
-        <v>10826863291.413843</v>
+        <v>10826877959.64912</v>
       </c>
       <c r="D68" s="118">
-        <v>11998870266.929163</v>
+        <v>11998884935.164436</v>
       </c>
       <c r="E68" s="118">
-        <v>13367040131.898279</v>
+        <v>13367054800.133556</v>
       </c>
       <c r="F68" s="118">
-        <v>14970544410.151831</v>
+        <v>14970559078.38711</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18722,19 +18722,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>9753962077.1503792</v>
+        <v>9753976745.3856564</v>
       </c>
       <c r="C69" s="281">
-        <v>10784416468.831938</v>
+        <v>10784431137.067213</v>
       </c>
       <c r="D69" s="118">
-        <v>11998870266.929165</v>
+        <v>11998884935.164434</v>
       </c>
       <c r="E69" s="118">
-        <v>13439623899.78488</v>
+        <v>13439638568.020159</v>
       </c>
       <c r="F69" s="118">
-        <v>15159678040.122215</v>
+        <v>15159692708.357494</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18831,23 +18831,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>16.789143593241125</v>
+        <v>16.826529647745442</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>16.789143593241125</v>
+        <v>16.826529647745442</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>16.789143593241125</v>
+        <v>16.826529647745442</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>16.789143593241125</v>
+        <v>16.826529647745442</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>16.789143593241125</v>
+        <v>16.826529647745442</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18862,23 +18862,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>16.576772780791611</v>
+        <v>16.613682715521264</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>16.682958187016368</v>
+        <v>16.720106181633351</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>16.789143593241125</v>
+        <v>16.826529647745438</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>16.895328999465878</v>
+        <v>16.932953113857529</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>17.001514405690639</v>
+        <v>17.03937657996962</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>16.386270816306006</v>
+        <v>16.422753659613079</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>16.586735255975167</v>
+        <v>16.623667525842993</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>16.789143593241121</v>
+        <v>16.826529647745438</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>16.993495828103871</v>
+        <v>17.031340025320421</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>17.19979196056341</v>
+        <v>17.238098658567932</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18924,23 +18924,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>16.215385758918458</v>
+        <v>16.251485490468891</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>16.499540105649498</v>
+        <v>16.536276890389939</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>16.789143593241121</v>
+        <v>16.826529647745438</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>17.084249601032351</v>
+        <v>17.122297261546983</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>17.38491150836224</v>
+        <v>17.423633230806175</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18955,23 +18955,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>16.062097560987297</v>
+        <v>16.09785363164848</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>16.420525736018007</v>
+        <v>16.457085376340956</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>16.789143593241125</v>
+        <v>16.826529647745438</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>17.168150114220243</v>
+        <v>17.206385873527609</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>17.557746234911271</v>
+        <v>17.596855440127008</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18986,23 +18986,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>15.924594188930053</v>
+        <v>15.960041987123075</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>16.348924613880548</v>
+        <v>16.385323729742787</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>16.789143593241125</v>
+        <v>16.826529647745438</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>17.245714890714314</v>
+        <v>17.284124544557745</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>17.719111380064597</v>
+        <v>17.758582354092454</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -19017,23 +19017,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>15.801250203011428</v>
+        <v>15.836421473040788</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>16.284041217161015</v>
+        <v>16.320294869209896</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>16.789143593241121</v>
+        <v>16.826529647745438</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>17.317422372873587</v>
+        <v>17.355992789629088</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>17.869768083091039</v>
+        <v>17.909576818389713</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19049,23 +19049,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>15.690607542873899</v>
+        <v>15.725530760179792</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>16.22524527871494</v>
+        <v>16.261367114585124</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>16.789143593241121</v>
+        <v>16.826529647745438</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>17.383714873542576</v>
+        <v>17.42243391321907</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>18.010426972873162</v>
+        <v>18.05055105507914</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19080,23 +19080,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>15.591358291675013</v>
+        <v>15.626058999444068</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>16.171965664013236</v>
+        <v>16.207968050897687</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>16.789143593241121</v>
+        <v>16.826529647745435</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>17.44500130436699</v>
+        <v>17.483857743723309</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>18.141751519855106</v>
+        <v>18.182170022056919</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19112,23 +19112,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>15.502329215084709</v>
+        <v>15.536830326198293</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>16.12368482323091</v>
+        <v>16.159578968013879</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>16.789143593241121</v>
+        <v>16.826529647745435</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>17.501659698081099</v>
+        <v>17.540643161397707</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>18.264361165549914</v>
+        <v>18.305054549578497</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19144,23 +19144,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>15.422467892376703</v>
+        <v>15.456789960266157</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>16.079933763849215</v>
+        <v>16.115729821968138</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>16.789143593241121</v>
+        <v>16.826529647745435</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>17.554039540324805</v>
+        <v>17.593140435403331</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>18.378834244367948</v>
+        <v>18.419784268637553</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19176,23 +19176,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>15.130835261050912</v>
+        <v>15.16450350998516</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>15.915569934044159</v>
+        <v>15.950997500520057</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>16.789143593241121</v>
+        <v>16.826529647745435</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>17.762252562219849</v>
+        <v>17.801820255611773</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>18.846844280684664</v>
+        <v>18.888843549106326</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19208,23 +19208,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>14.961456377216711</v>
+        <v>14.994744891124881</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>15.815137266743248</v>
+        <v>15.850339670550259</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>16.789143593241121</v>
+        <v>16.826529647745435</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>17.902859751886428</v>
+        <v>17.942742676277792</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>19.178852470706182</v>
+        <v>19.221596077122303</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19240,23 +19240,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>14.863081904653427</v>
+        <v>14.896149870214256</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>15.753769016361524</v>
+        <v>15.788833837055273</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>16.789143593241121</v>
+        <v>16.826529647745435</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>17.997812419140352</v>
+        <v>18.037908220442702</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>19.414380407476266</v>
+        <v>19.457652050240171</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19272,23 +19272,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>14.805946465848796</v>
+        <v>14.838886337949251</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>15.716270638033784</v>
+        <v>15.751251390115494</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>16.789143593241125</v>
+        <v>16.826529647745435</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>18.061934382178052</v>
+        <v>18.10217394021533</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>19.581464867036065</v>
+        <v>19.625111100895221</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>17.38491150836224</v>
+        <v>17.423633230806175</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>17.084249601032351</v>
+        <v>17.122297261546983</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>16.789143593241121</v>
+        <v>16.826529647745438</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>16.499540105649498</v>
+        <v>16.536276890389939</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>16.215385758918458</v>
+        <v>16.251485490468891</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>1207881403.2915702</v>
+        <v>1207889974.6580667</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>1109895499.6909478</v>
+        <v>1109896856.5027108</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C14" s="252">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7260201366300074E-2</v>
+        <v>-7.725889125187102E-2</v>
       </c>
       <c r="D14" s="465"/>
       <c r="E14" s="465"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>17.084249601032351</v>
+        <v>17.122297261546983</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>16.789143593241121</v>
+        <v>16.826529647745438</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>16.499540105649498</v>
+        <v>16.536276890389939</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>16.775763922901461</v>
+        <v>16.813119981166871</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19917,7 +19917,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>17.38491150836224</v>
+        <v>17.423633230806175</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19940,7 +19940,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>16.215385758918458</v>
+        <v>16.251485490468891</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.58860000000000001</v>
+        <v>0.58991959800000016</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.29</v>
+        <v>10.73</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22761913967028624</v>
+        <v>0.21077952890145579</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20005,7 +20005,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>16.789143593241125</v>
+        <v>16.826529647745442</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20016,7 +20016,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.6015658262164074E-2</v>
+        <v>3.6016201355065634E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>16.839117152521428</v>
+        <v>16.876615244077868</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>16.840420150876522</v>
+        <v>16.877921163659639</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.3972512459651919</v>
+        <v>0.39724140576358608</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.58860000000000001</v>
+        <v>0.58991959800000016</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20265,15 +20265,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.0770506376984164</v>
+        <v>1.0794653061785484</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>7.7599618214384485</v>
+        <v>7.7772420479621536</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>8.8370124591368651</v>
+        <v>8.8567073541407026</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.47520927735729646</v>
+        <v>0.47520831481605363</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20290,15 +20290,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2384167233625794</v>
+        <v>1.2411931627633881</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>9.7265658642723096</v>
+        <v>9.7482254117417337</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>10.964982587634889</v>
+        <v>10.989418574505121</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34883863041519181</v>
+        <v>0.34883752366391174</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20336,15 +20336,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4200581999274888</v>
+        <v>1.4232418661872714</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>12.069612228263562</v>
+        <v>12.096489375104861</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>13.489670428191051</v>
+        <v>13.519731241292133</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19890868945162266</v>
+        <v>0.19890742037054443</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20361,15 +20361,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5376440587140374</v>
+        <v>1.5410913438390648</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>13.649835446509867</v>
+        <v>13.680231504371305</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>15.187479505223905</v>
+        <v>15.22132284821037</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>9.8083387171530756E-2</v>
+        <v>9.8082013006035251E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20488,7 +20488,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>10.29</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20506,14 +20506,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12696.223889999997</v>
+        <v>13239.11393</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.22761913967028624</v>
+        <v>0.21077952890145579</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20521,13 +20521,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0900000000000001</v>
+        <v>1.0924437000000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>16.839117152521428</v>
+        <v>16.876615244077868</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20643,7 +20643,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>8.8370124591368651</v>
+        <v>8.8567073541407026</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>10.964982587634889</v>
+        <v>10.989418574505121</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>13.489670428191051</v>
+        <v>13.519731241292133</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>15.187479505223905</v>
+        <v>15.22132284821037</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20712,22 +20712,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>11574595.608524427</v>
+        <v>11576404.690875448</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-2582327.2209755722</v>
+        <v>-2580518.1386245508</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-389566992.56364924</v>
+        <v>-389567444.83423698</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20917,10 +20917,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20936,22 +20936,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>1207881403.2915702</v>
+        <v>1207889974.6580667</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>1109895499.6909478</v>
+        <v>1109896856.5027108</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.5287079461161994E-2</v>
+        <v>9.1584666084687946E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20995,14 +20995,14 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.7201166180758024E-2</v>
+        <v>5.4978527306616974E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>0.72703422459564127</v>
+        <v>0.72866329119929796</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21022,11 +21022,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095589410589849</v>
+        <v>0.10095601131136619</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>8.8884951666389239E-2</v>
+        <v>8.8885506981639828E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21036,11 +21036,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>0.1263954426223067</v>
+        <v>0.12639558936200029</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128278252432619</v>
+        <v>0.11128347777166675</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21086,22 +21086,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21109,13 +21109,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25013021749406933</v>
+        <v>-0.25069099108351001</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>6705419480.0925961</v>
+        <v>6705117966.3674259</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9237026758722804</v>
+        <v>5.9367162220374494</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.51552737642662227</v>
+        <v>0.51668315096769923</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>6.1890998348048338</v>
+        <v>6.2027083819216378</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21264,33 +21264,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21353,23 +21353,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.7008492751797555</v>
+        <v>1.7046624544217344</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>16.789143593241125</v>
+        <v>16.826529647745442</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21413,13 +21413,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21464,7 +21464,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.38 HKD</v>
+        <v>17.42 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.08 HKD</v>
+        <v>17.12 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>16.79 HKD</v>
+        <v>16.83 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.5 HKD</v>
+        <v>16.54 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.22 HKD</v>
+        <v>16.25 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>16.839117152521428</v>
+        <v>16.876615244077868</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21583,13 +21583,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21602,22 +21602,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C136" s="410">
         <f>Scenarios!C58</f>
-        <v>0.58860000000000001</v>
+        <v>0.58991959800000016</v>
       </c>
       <c r="D136" s="347" t="str">
         <f>Market_currency</f>
@@ -21678,15 +21678,15 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>1.0770506376984164</v>
+        <v>1.0794653061785484</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>7.7599618214384485</v>
+        <v>7.7772420479621536</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>8.8370124591368651</v>
+        <v>8.8567073541407026</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21699,15 +21699,15 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>1.2384167233625794</v>
+        <v>1.2411931627633881</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>9.7265658642723096</v>
+        <v>9.7482254117417337</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>10.964982587634889</v>
+        <v>10.989418574505121</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21739,15 +21739,15 @@
       </c>
       <c r="C144" s="413">
         <f>Scenarios!C66</f>
-        <v>1.4200581999274888</v>
+        <v>1.4232418661872714</v>
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>12.069612228263562</v>
+        <v>12.096489375104861</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>13.489670428191051</v>
+        <v>13.519731241292133</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21760,15 +21760,15 @@
       </c>
       <c r="C145" s="413">
         <f>Scenarios!C67</f>
-        <v>1.5376440587140374</v>
+        <v>1.5410913438390648</v>
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>13.649835446509867</v>
+        <v>13.680231504371305</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>15.187479505223905</v>
+        <v>15.22132284821037</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21786,13 +21786,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21800,13 +21800,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21843,22 +21843,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21882,12 +21882,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21902,15 +21905,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F25545E-9824-4536-B679-D08F69A5DFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE804A41-FCF4-4D28-A1BB-294E525701B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4972,30 +4972,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5005,25 +5005,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5393,7 +5393,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.73</v>
+        <v>10.42</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>13239.11393</v>
+        <v>12856.623219999999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.21077952890145579</v>
+        <v>0.22438656215485436</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0924437000000002</v>
+        <v>1.0954849</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>16.876615244077868</v>
+        <v>16.923280267644014</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>8.8567073541407026</v>
+        <v>8.881217043386771</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>10.989418574505121</v>
+        <v>11.01982839702711</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>13.519731241292133</v>
+        <v>13.557140974581815</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>15.22132284821037</v>
+        <v>15.263439814781965</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>11576404.690875448</v>
+        <v>11578656.105224969</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-2580518.1386245508</v>
+        <v>-2578266.7242750302</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-389567444.83423698</v>
+        <v>-389568007.68782437</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>1207889974.6580667</v>
+        <v>1207900641.7775121</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>1109896856.5027108</v>
+        <v>1109898545.0634732</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.1584666084687946E-2</v>
+        <v>9.4572040872875823E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5894,14 +5894,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.4978527306616974E-2</v>
+        <v>5.6771770249520161E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.72866329119929796</v>
+        <v>0.7306906692576669</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5921,11 +5921,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095601131136619</v>
+        <v>0.10095615717430696</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.8885506981639828E-2</v>
+        <v>8.8886198074957332E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5935,11 +5935,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639558936200029</v>
+        <v>0.12639577198047069</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128347777166675</v>
+        <v>0.11128434301134923</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25069099108351001</v>
+        <v>-0.25138887733804471</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>6705117966.3674259</v>
+        <v>6704742730.6425056</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9367162220374494</v>
+        <v>5.9529099939162595</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.51668315096769923</v>
+        <v>0.51812151964401887</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.2027083819216378</v>
+        <v>6.2196426362222343</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7046624544217344</v>
+        <v>1.7094079799407034</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>16.826529647745442</v>
+        <v>16.873055240496466</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.42 HKD</v>
+        <v>17.47 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.3635880103361234E-2</v>
+        <v>2.3636313267688221E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.12 HKD</v>
+        <v>17.17 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.9810197792355522E-2</v>
+        <v>2.981075062910921E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>16.83 HKD</v>
+        <v>16.87 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.6016201355065697E-2</v>
+        <v>3.6016877260469662E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.54 HKD</v>
+        <v>16.58 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.2252830682570734E-2</v>
+        <v>4.2253633105975415E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.25 HKD</v>
+        <v>16.3 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,17 +6445,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.851896075547317E-2</v>
+        <v>4.8519893197378393E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>16.876615244077868</v>
+        <v>16.923280267644014</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.58991959800000016</v>
+        <v>0.59156184600000006</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,15 +6566,15 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>1.0794653061785484</v>
+        <v>1.0824703762697119</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>7.7772420479621536</v>
+        <v>7.7987466671170589</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>8.8567073541407026</v>
+        <v>8.881217043386771</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,15 +6587,15 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>1.2411931627633881</v>
+        <v>1.2446484590377829</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>9.7482254117417337</v>
+        <v>9.7751799379893267</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>10.989418574505121</v>
+        <v>11.01982839702711</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,15 +6634,15 @@
       </c>
       <c r="C144" s="337">
         <f>Scenarios!C66</f>
-        <v>1.4232418661872714</v>
+        <v>1.4272039588456378</v>
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>12.096489375104861</v>
+        <v>12.129937015736177</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>13.519731241292133</v>
+        <v>13.557140974581815</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,15 +6655,15 @@
       </c>
       <c r="C145" s="337">
         <f>Scenarios!C67</f>
-        <v>1.5410913438390648</v>
+        <v>1.5453815118311389</v>
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>13.680231504371305</v>
+        <v>13.718058302950826</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>15.22132284821037</v>
+        <v>15.263439814781965</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,18 +6777,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6805,6 +6793,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.6554662200000001</v>
+        <v>0.65729093999999999</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.6554662200000001</v>
+        <v>0.65729093999999999</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10216,11 +10216,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.268881870239724</v>
+        <v>13.305820454391721</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7046624544217344</v>
+        <v>1.7094079799407034</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6705117966.3674259</v>
+        <v>6704742730.6425056</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10478,11 +10478,11 @@
       </c>
       <c r="C73" s="289">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-983975149.06758499</v>
+        <v>-984162766.93004501</v>
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-964700390.90628731</v>
+        <v>-964888008.76874733</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10494,11 +10494,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7751390432594469</v>
+        <v>8.7734661768542068</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9504667247706884</v>
+        <v>8.9487263492870461</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10511,7 +10511,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1929400781.8125746</v>
+        <v>1929776017.5374947</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10626,11 +10626,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>309312823.12946904</v>
+        <v>310173903.80365044</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.25069099108351001</v>
+        <v>0.25138887733804471</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10643,11 +10643,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7324963880.1149082</v>
+        <v>7344944419.8036318</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.9367162220374494</v>
+        <v>5.9529099939162595</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10660,11 +10660,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>637504855.67313695</v>
+        <v>639279573.91909587</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.51668315096769923</v>
+        <v>0.51812151964401887</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10677,11 +10677,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>8271781558.9175138</v>
+        <v>8294397897.5263786</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.7040903640886587</v>
+        <v>6.7224203908983231</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11162,36 +11162,36 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-2580518.1386245508</v>
+        <v>-2578266.7242750302</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>42406702.118065715</v>
+        <v>42417369.237511106</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40873899.449171297</v>
+        <v>40885325.2024744</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>17662119.878446877</v>
+        <v>17669634.762510419</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>5037070.0296748653</v>
+        <v>5041839.7092593461</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
-        <v>-4720392.4684606194</v>
+        <v>-4716999.9914317839</v>
       </c>
       <c r="L10" s="270">
         <f t="shared" si="6"/>
-        <v>-6436925.2410469837</v>
+        <v>-6434396.3009453397</v>
       </c>
       <c r="M10" s="270">
         <f t="shared" si="6"/>
-        <v>7527509.7544652186</v>
+        <v>7529074.1608027667</v>
       </c>
       <c r="N10" s="270">
         <f t="shared" si="6"/>
@@ -11217,36 +11217,36 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>1558269779.3369479</v>
+        <v>1558272030.7512975</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1371959901.6580667</v>
+        <v>1371970568.7775121</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>1481858567.769171</v>
+        <v>1481869993.5224741</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>1407189618.8784468</v>
+        <v>1407197133.7625103</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>1240491388.0296748</v>
+        <v>1240496157.7092593</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
-        <v>1157435298.5315394</v>
+        <v>1157438691.0085683</v>
       </c>
       <c r="L11" s="271">
         <f t="shared" si="7"/>
-        <v>999248889.33895504</v>
+        <v>999251418.27905679</v>
       </c>
       <c r="M11" s="271">
         <f t="shared" si="7"/>
-        <v>939474816.52446425</v>
+        <v>939476380.93080175</v>
       </c>
       <c r="N11" s="271">
         <f t="shared" si="7"/>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-389567444.83423698</v>
+        <v>-389568007.68782437</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11384,38 +11384,38 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>1109896856.5027108</v>
+        <v>1109898545.0634732</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207889974.6580667</v>
+        <v>1207900641.7775121</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>1497832510.769171</v>
+        <v>1497843936.5224741</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>1418625095.8784468</v>
+        <v>1418632610.7625103</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>1235038576.0296748</v>
+        <v>1235043345.7092593</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
-        <v>1149264747.5315394</v>
+        <v>1149268140.0085683</v>
       </c>
       <c r="L14" s="271">
         <f t="shared" si="8"/>
-        <v>975076814.21895504</v>
+        <v>975079343.15905678</v>
       </c>
       <c r="M14" s="271">
         <f t="shared" si="8"/>
-        <v>950270662.89446425</v>
+        <v>950272227.30080175</v>
       </c>
       <c r="N14" s="271">
         <f t="shared" si="8"/>
@@ -11602,38 +11602,38 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>1109896856.5027108</v>
+        <v>1109898545.0634732</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207889974.6580667</v>
+        <v>1207900641.7775121</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>1497832510.769171</v>
+        <v>1497843936.5224741</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>1418625095.8784468</v>
+        <v>1418632610.7625103</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>1235038576.0296748</v>
+        <v>1235043345.7092593</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
-        <v>1149264747.5315394</v>
+        <v>1149268140.0085683</v>
       </c>
       <c r="L19" s="275">
         <f t="shared" si="9"/>
-        <v>975076814.21895504</v>
+        <v>975079343.15905678</v>
       </c>
       <c r="M19" s="275">
         <f t="shared" si="9"/>
-        <v>950270662.89446425</v>
+        <v>950272227.30080175</v>
       </c>
       <c r="N19" s="275">
         <f t="shared" si="9"/>
@@ -12341,31 +12341,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.6725601726977469E-2</v>
+        <v>7.6725005182724432E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.3984119279426949E-2</v>
+        <v>-4.3983780145968321E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.1264648676944214E-3</v>
+        <v>-8.1264214697654019E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3956871064304067E-3</v>
+        <v>4.3956702051132033E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.059185952222242E-3</v>
+        <v>7.0591652616004653E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4190244670665422E-2</v>
+        <v>2.4190183449156303E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491363238387425E-2</v>
+        <v>-1.1491344103088399E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12479,36 +12479,36 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>11576404.690875448</v>
+        <v>11578656.105224969</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54848585.118065715</v>
+        <v>54859252.237511106</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>58749356.449171297</v>
+        <v>58760782.2024744</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>38640305.878446877</v>
+        <v>38647820.762510419</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>24524913.029674865</v>
+        <v>24529682.709259346</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
-        <v>17443562.531539381</v>
+        <v>17446955.008568216</v>
       </c>
       <c r="L46" s="278">
         <f t="shared" si="17"/>
-        <v>13003396.758953016</v>
+        <v>13005925.69905466</v>
       </c>
       <c r="M46" s="278">
         <f t="shared" si="17"/>
-        <v>8043921.7544652186</v>
+        <v>8045486.1608027667</v>
       </c>
       <c r="N46" s="278">
         <f t="shared" si="17"/>
@@ -12591,36 +12591,36 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-2580518.1386245508</v>
+        <v>-2578266.7242750302</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42406702.118065715</v>
+        <v>42417369.237511106</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40873899.449171297</v>
+        <v>40885325.2024744</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>17662119.878446877</v>
+        <v>17669634.762510419</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>5037070.0296748653</v>
+        <v>5041839.7092593461</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
-        <v>-4720392.4684606194</v>
+        <v>-4716999.9914317839</v>
       </c>
       <c r="L48" s="271">
         <f t="shared" si="18"/>
-        <v>-6436925.2410469837</v>
+        <v>-6434396.3009453397</v>
       </c>
       <c r="M48" s="271">
         <f t="shared" si="18"/>
-        <v>7527509.7544652186</v>
+        <v>7529074.1608027667</v>
       </c>
       <c r="N48" s="271">
         <f t="shared" si="18"/>
@@ -13556,38 +13556,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0931299272810609E-4</v>
+        <v>2.0913037425768512E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.4397253788701586E-3</v>
+        <v>3.4405906185526408E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4439004444131991E-3</v>
+        <v>3.4448631408382671E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.6158857359577553E-3</v>
+        <v>1.6165732635053669E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8153869572602681E-4</v>
+        <v>4.8199467217118456E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2401896459725755E-4</v>
+        <v>5.2364235983145711E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.279565752097289E-4</v>
+        <v>7.2767057552721522E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.1949349136956988E-4</v>
+        <v>9.1968458530264374E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13613,38 +13613,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639558936200029</v>
+        <v>0.12639577198047069</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.11128347777166675</v>
+        <v>0.11128434301134923</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12485653311458698</v>
+        <v>0.12485749581101205</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12874205636596917</v>
+        <v>0.12874274389351675</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.1185896962980552</v>
+        <v>0.11859015227450036</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12848890230574583</v>
+        <v>0.12848927891051162</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300578646257446</v>
+        <v>0.11300607246225698</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11475786910637302</v>
+        <v>0.1147580602003061</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1598897340500073E-2</v>
+        <v>3.1598942995117674E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13785,38 +13785,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.0026816388869488E-2</v>
+        <v>9.002695335272233E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.7975310344734182E-2</v>
+        <v>9.7976175584416667E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12620244505688019</v>
+        <v>0.12620340775330524</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12978827416402194</v>
+        <v>0.12978896169156953</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11806841309908234</v>
+        <v>0.11806886907552751</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758187525157266</v>
+        <v>0.12758225185633845</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11027214883884381</v>
+        <v>0.11027243483852633</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607659346473768</v>
+        <v>0.11607678455867075</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14008,38 +14008,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.0026816388869488E-2</v>
+        <v>9.002695335272233E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.7975310344734182E-2</v>
+        <v>9.7976175584416667E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12620244505688019</v>
+        <v>0.12620340775330524</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12978827416402194</v>
+        <v>0.12978896169156953</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11806841309908234</v>
+        <v>0.11806886907552751</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758187525157266</v>
+        <v>0.12758225185633845</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11027214883884381</v>
+        <v>0.11027243483852633</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607659346473768</v>
+        <v>0.11607678455867075</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14077,12 +14077,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.6554662200000001</v>
+        <v>0.65729093999999999</v>
       </c>
       <c r="E88" s="238"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.6554662200000001</v>
+        <v>0.65729093999999999</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14133,12 +14133,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>808741096.3510201</v>
+        <v>810992510.70053995</v>
       </c>
       <c r="E89" s="238"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>808741096.3510201</v>
+        <v>810992510.70053995</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.72866329119929796</v>
+        <v>0.7306906692576669</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.66954864542191528</v>
+        <v>0.67140663946258572</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14264,12 +14264,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.4978527306616974E-2</v>
+        <v>5.6771770249520161E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.4978527306616974E-2</v>
+        <v>5.6771770249520161E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14401,38 +14401,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.13579834035507776</v>
+        <v>0.13579115049077806</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162722746576648E-2</v>
+        <v>-7.4162662868775597E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.3062464282700228E-2</v>
+        <v>5.3064960102858105E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.13438080462093804</v>
+        <v>0.1343825009188957</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1758732089396426E-2</v>
+        <v>7.1759711633897716E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830531400163106</v>
+        <v>0.15830577754089825</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3624986815103535E-2</v>
+        <v>6.3625907539082593E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35102146048388727</v>
+        <v>0.35102371019457435</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -15012,31 +15012,31 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4674174545589376</v>
+        <v>1.4674044956145322</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5709554934093843</v>
+        <v>1.5709435099513751</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.4270021945061211</v>
+        <v>1.4269946352860885</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.6577049630155098</v>
+        <v>1.6576985610365456</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.5825816409200233</v>
+        <v>1.5825769693628156</v>
       </c>
       <c r="L113" s="254">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3992851637159525</v>
+        <v>1.3992815345668077</v>
       </c>
       <c r="M113" s="254">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.045439274052735</v>
+        <v>1.0454375529755755</v>
       </c>
       <c r="N113" s="254">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15120,36 +15120,36 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639558936200029</v>
+        <v>0.12639577198047069</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.11128347777166675</v>
+        <v>0.11128434301134923</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12485653311458698</v>
+        <v>0.12485749581101205</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12874205636596917</v>
+        <v>0.12874274389351675</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.1185896962980552</v>
+        <v>0.11859015227450036</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12848890230574583</v>
+        <v>0.12848927891051162</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300578646257446</v>
+        <v>0.11300607246225698</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11475786910637302</v>
+        <v>0.1147580602003061</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15285,38 +15285,38 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.10095601131136619</v>
+        <v>0.10095615717430696</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.8885506981639828E-2</v>
+        <v>8.8886198074957332E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11046975664207592</v>
+        <v>0.11047060841039869</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11113456890137642</v>
+        <v>0.11113516239879108</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11165852052843984</v>
+        <v>0.11165894985456894</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11541862622412138</v>
+        <v>0.11541896451952213</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.10956716873680816</v>
+        <v>0.1095674460338958</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176201939907643</v>
+        <v>0.11176220550434329</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15406,50 +15406,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.9827034670887016</v>
+        <v>0.98544066589536605</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0694666436829097</v>
+        <v>1.0724533499596574</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3261819716194903</v>
+        <v>1.3298840085691179</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2560516700728095</v>
+        <v>1.2595550024175783</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0935040346694505</v>
+        <v>1.0965524213168254</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0175598258389218</v>
+        <v>1.0203955723877489</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.86333370564729817</v>
+        <v>0.86573934302123612</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.84137032160049918</v>
+        <v>0.84371395981929276</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.61519521617898787</v>
+        <v>0.6169078277226705</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.50660220016423441</v>
+        <v>0.50801250498007011</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.47760156474040039</v>
+        <v>0.47893113612123073</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15463,50 +15463,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.1584666084687946E-2</v>
+        <v>9.4572040872875823E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>9.9670703045937517E-2</v>
+        <v>0.10292258636848919</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.12359571030936535</v>
+        <v>0.12762802385500172</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.11705980149793191</v>
+        <v>0.1208785990803818</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10191090723853219</v>
+        <v>0.10523535713213296</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.4833161774363628E-2</v>
+        <v>9.7926638424927923E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.0459804813354907E-2</v>
+        <v>8.3084389925262583E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>7.8412891109086599E-2</v>
+        <v>8.0970629541198921E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.7334130119197378E-2</v>
+        <v>5.9204206115419433E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.721362536479351E-2</v>
+        <v>4.8753599326302313E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.4510863442721378E-2</v>
+        <v>4.596268100971504E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15520,43 +15520,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12113058943968164</v>
+        <v>0.12473428259959539</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12299541446728829</v>
+        <v>0.12665458706660301</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10508521456616848</v>
+        <v>0.10821155012427906</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8441728720737739E-2</v>
+        <v>0.10137041738709365</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3888076919057081E-2</v>
+        <v>9.6681292259259352E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4950188513862268E-2</v>
+        <v>8.7477497385195974E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.99983753942965E-2</v>
+        <v>7.2080860650748702E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9225204613070357E-2</v>
+        <v>7.1284687667777832E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7589136057083543E-2</v>
+        <v>4.9004935690259738E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6447202074950344E-2</v>
+        <v>4.7829028624205107E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>1109896856.5027108</v>
+        <v>1109898545.0634732</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>6705117966.3674259</v>
+        <v>6704742730.6425056</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>11998884935.164442</v>
+        <v>11998903189.875387</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-2580518.1386245508</v>
+        <v>-2578266.7242750302</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16404,14 +16404,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>7005538054.4174261</v>
+        <v>7005162818.6925058</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>7005538054.4174261</v>
+        <v>7005162818.6925058</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>19004422989.581867</v>
+        <v>19004066008.567894</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.2027083819216378</v>
+        <v>6.2196426362222343</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-2580518.1386245508</v>
+        <v>-2578266.7242750302</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0924437000000002</v>
+        <v>1.0954849</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>20761262167.103882</v>
+        <v>20818667350.989399</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>16.826529647745442</v>
+        <v>16.873055240496466</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>16.877921163659639</v>
+        <v>16.924589822710733</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>1561002955.800261</v>
+        <v>1561005207.2146106</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16723,11 +16723,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>1111843765.6511366</v>
+        <v>1111845454.2118986</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>1.7541352036625213E-3</v>
+        <v>1.7541325349823556E-3</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>1017705963.9827337</v>
+        <v>1017707509.5761085</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>1563740918.2789865</v>
+        <v>1563743169.693336</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16772,11 +16772,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>1113794083.9966326</v>
+        <v>1113795772.5573945</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>1.7541298568632957E-3</v>
+        <v>1.7541271928644964E-3</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>933172679.54202616</v>
+        <v>933174094.27280402</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>1566483675.1538281</v>
+        <v>1566485926.5681777</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16821,11 +16821,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>1115747817.508981</v>
+        <v>1115749506.0697429</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>1.754124519442346E-3</v>
+        <v>1.7541218601166975E-3</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>855660943.35934508</v>
+        <v>855662238.3074255</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>1566483675.1538281</v>
+        <v>1566485926.5681777</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>12062138567.66466</v>
+        <v>12062156822.375599</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18285,7 +18285,7 @@
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>9250388576.8577843</v>
+        <v>9250402576.2964916</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18298,7 +18298,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>12056928163.74189</v>
+        <v>12056946418.452829</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18322,7 +18322,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>12056928163.74189</v>
+        <v>12056946418.452829</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18357,19 +18357,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>11758488774.060295</v>
+        <v>11758507028.771236</v>
       </c>
       <c r="C56" s="118">
-        <v>11878686854.612366</v>
+        <v>11878705109.323309</v>
       </c>
       <c r="D56" s="118">
-        <v>11998884935.164442</v>
+        <v>11998903189.875385</v>
       </c>
       <c r="E56" s="118">
-        <v>12119083015.716515</v>
+        <v>12119101270.427456</v>
       </c>
       <c r="F56" s="118">
-        <v>12239281096.268593</v>
+        <v>12239299350.979532</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18383,19 +18383,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>11542847366.387926</v>
+        <v>11542865621.098866</v>
       </c>
       <c r="C57" s="118">
-        <v>11769765939.51255</v>
+        <v>11769784194.223488</v>
       </c>
       <c r="D57" s="118">
-        <v>11998884935.16444</v>
+        <v>11998903189.875387</v>
       </c>
       <c r="E57" s="118">
-        <v>12230204353.343605</v>
+        <v>12230222608.054546</v>
       </c>
       <c r="F57" s="118">
-        <v>12463724194.050035</v>
+        <v>12463742448.760979</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18409,19 +18409,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>11349411595.661221</v>
+        <v>11349429850.372166</v>
       </c>
       <c r="C58" s="118">
-        <v>11671064149.170372</v>
+        <v>11671082403.881315</v>
       </c>
       <c r="D58" s="118">
-        <v>11998884935.16444</v>
+        <v>11998903189.875385</v>
       </c>
       <c r="E58" s="118">
-        <v>12332934377.145306</v>
+        <v>12332952631.856245</v>
       </c>
       <c r="F58" s="118">
-        <v>12673272898.614862</v>
+        <v>12673291153.325806</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18435,19 +18435,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>11175894840.226742</v>
+        <v>11175913094.937683</v>
       </c>
       <c r="C59" s="118">
-        <v>11581622709.867172</v>
+        <v>11581640964.578114</v>
       </c>
       <c r="D59" s="118">
-        <v>11998884935.16444</v>
+        <v>11998903189.875385</v>
       </c>
       <c r="E59" s="118">
-        <v>12427906756.129032</v>
+        <v>12427925010.839973</v>
       </c>
       <c r="F59" s="118">
-        <v>12868915625.073555</v>
+        <v>12868933879.7845</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18461,19 +18461,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>11020245942.903366</v>
+        <v>11020264197.614309</v>
       </c>
       <c r="C60" s="118">
-        <v>11500572801.482576</v>
+        <v>11500591056.193521</v>
       </c>
       <c r="D60" s="118">
-        <v>11998884935.16444</v>
+        <v>11998903189.875385</v>
       </c>
       <c r="E60" s="118">
-        <v>12515707307.866844</v>
+        <v>12515725562.577787</v>
       </c>
       <c r="F60" s="118">
-        <v>13051575195.771837</v>
+        <v>13051593450.482777</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18487,19 +18487,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>10880624964.068665</v>
+        <v>10880643218.779606</v>
       </c>
       <c r="C61" s="118">
-        <v>11427127117.912098</v>
+        <v>11427145372.623041</v>
       </c>
       <c r="D61" s="118">
-        <v>11998884935.16444</v>
+        <v>11998903189.875385</v>
       </c>
       <c r="E61" s="118">
-        <v>12596877611.990589</v>
+        <v>12596895866.70153</v>
       </c>
       <c r="F61" s="118">
-        <v>13222113193.128578</v>
+        <v>13222131447.83952</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18513,19 +18513,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>10755381431.567059</v>
+        <v>10755399686.278</v>
       </c>
       <c r="C62" s="118">
-        <v>11360572219.29903</v>
+        <v>11360590474.009972</v>
       </c>
       <c r="D62" s="118">
-        <v>11998884935.16444</v>
+        <v>11998903189.875385</v>
       </c>
       <c r="E62" s="118">
-        <v>12671918350.814373</v>
+        <v>12671936605.525314</v>
       </c>
       <c r="F62" s="118">
-        <v>13381334023.61268</v>
+        <v>13381352278.323622</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18539,19 +18539,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>10643034830.329918</v>
+        <v>10643053085.040859</v>
       </c>
       <c r="C63" s="118">
-        <v>11300261601.791538</v>
+        <v>11300279856.50248</v>
       </c>
       <c r="D63" s="118">
-        <v>11998884935.164438</v>
+        <v>11998903189.875385</v>
       </c>
       <c r="E63" s="118">
-        <v>12741292397.690361</v>
+        <v>12741310652.401302</v>
       </c>
       <c r="F63" s="118">
-        <v>13529988712.028042</v>
+        <v>13530006966.738983</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18565,19 +18565,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>10542257101.073719</v>
+        <v>10542275355.784662</v>
       </c>
       <c r="C64" s="118">
-        <v>11245609417.505573</v>
+        <v>11245627672.216515</v>
       </c>
       <c r="D64" s="118">
-        <v>11998884935.164436</v>
+        <v>11998903189.875381</v>
       </c>
       <c r="E64" s="118">
-        <v>12805427672.1478</v>
+        <v>12805445926.858742</v>
       </c>
       <c r="F64" s="118">
-        <v>13668778444.003937</v>
+        <v>13668796698.714878</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18591,19 +18591,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>10451856941.19173</v>
+        <v>10451875195.90267</v>
       </c>
       <c r="C65" s="118">
-        <v>11196084783.690372</v>
+        <v>11196103038.401314</v>
       </c>
       <c r="D65" s="118">
-        <v>11998884935.164436</v>
+        <v>11998903189.875381</v>
       </c>
       <c r="E65" s="118">
-        <v>12864719779.426529</v>
+        <v>12864738034.13747</v>
       </c>
       <c r="F65" s="118">
-        <v>13798357873.4002</v>
+        <v>13798376128.111139</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18617,19 +18617,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>10121739237.092968</v>
+        <v>10121757491.803911</v>
       </c>
       <c r="C66" s="281">
-        <v>11010030809.258718</v>
+        <v>11010049063.969662</v>
       </c>
       <c r="D66" s="118">
-        <v>11998884935.164436</v>
+        <v>11998903189.875381</v>
       </c>
       <c r="E66" s="118">
-        <v>13100409470.387997</v>
+        <v>13100427725.098942</v>
       </c>
       <c r="F66" s="118">
-        <v>14328128489.197496</v>
+        <v>14328146743.908438</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18652,19 +18652,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>9930008400.9380398</v>
+        <v>9930026655.648983</v>
       </c>
       <c r="C67" s="281">
-        <v>10896344623.336493</v>
+        <v>10896362878.047438</v>
       </c>
       <c r="D67" s="118">
-        <v>11998884935.164436</v>
+        <v>11998903189.875381</v>
       </c>
       <c r="E67" s="118">
-        <v>13259571778.191122</v>
+        <v>13259590032.902067</v>
       </c>
       <c r="F67" s="118">
-        <v>14703949881.109735</v>
+        <v>14703968135.820679</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18687,19 +18687,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>9818652017.8169785</v>
+        <v>9818670272.5279217</v>
       </c>
       <c r="C68" s="281">
-        <v>10826877959.64912</v>
+        <v>10826896214.360067</v>
       </c>
       <c r="D68" s="118">
-        <v>11998884935.164436</v>
+        <v>11998903189.87538</v>
       </c>
       <c r="E68" s="118">
-        <v>13367054800.133556</v>
+        <v>13367073054.8445</v>
       </c>
       <c r="F68" s="118">
-        <v>14970559078.38711</v>
+        <v>14970577333.098053</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18722,19 +18722,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>9753976745.3856564</v>
+        <v>9753995000.0965958</v>
       </c>
       <c r="C69" s="281">
-        <v>10784431137.067213</v>
+        <v>10784449391.778162</v>
       </c>
       <c r="D69" s="118">
-        <v>11998884935.164434</v>
+        <v>11998903189.87538</v>
       </c>
       <c r="E69" s="118">
-        <v>13439638568.020159</v>
+        <v>13439656822.7311</v>
       </c>
       <c r="F69" s="118">
-        <v>15159692708.357494</v>
+        <v>15159710963.068438</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18831,23 +18831,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>16.826529647745442</v>
+        <v>16.873055240496466</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>16.826529647745442</v>
+        <v>16.873055240496466</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>16.826529647745442</v>
+        <v>16.873055240496466</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>16.826529647745442</v>
+        <v>16.873055240496466</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>16.826529647745442</v>
+        <v>16.873055240496466</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18862,23 +18862,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>16.613682715521264</v>
+        <v>16.659615774221987</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>16.720106181633351</v>
+        <v>16.766335507359223</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>16.826529647745438</v>
+        <v>16.873055240496463</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>16.932953113857529</v>
+        <v>16.979774973633695</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>17.03937657996962</v>
+        <v>17.086494706770935</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>16.422753659613079</v>
+        <v>16.468155200355643</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>16.623667525842993</v>
+        <v>16.669628380763466</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>16.826529647745438</v>
+        <v>16.873055240496463</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>17.031340025320421</v>
+        <v>17.078435779554617</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>17.238098658567932</v>
+        <v>17.285769997937944</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18924,23 +18924,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>16.251485490468891</v>
+        <v>16.296410246223818</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>16.536276890389939</v>
+        <v>16.581994462841454</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>16.826529647745438</v>
+        <v>16.873055240496463</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>17.122297261546983</v>
+        <v>17.169646227133686</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>17.423633230806175</v>
+        <v>17.471821070697992</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18955,23 +18955,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>16.09785363164848</v>
+        <v>16.142350699268039</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>16.457085376340956</v>
+        <v>16.50258249145217</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>16.826529647745438</v>
+        <v>16.873055240496463</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>17.206385873527609</v>
+        <v>17.253968929243399</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>17.596855440127008</v>
+        <v>17.645525504762293</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18986,23 +18986,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>15.960041987123075</v>
+        <v>16.004155407719612</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>16.385323729742787</v>
+        <v>16.430621071154331</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>16.826529647745438</v>
+        <v>16.873055240496463</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>17.284124544557745</v>
+        <v>17.331924013115994</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>17.758582354092454</v>
+        <v>17.807702642286856</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -19017,23 +19017,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>15.836421473040788</v>
+        <v>15.880190752600644</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>16.320294869209896</v>
+        <v>16.365411179991987</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>16.826529647745438</v>
+        <v>16.873055240496463</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>17.355992789629088</v>
+        <v>17.403992328641223</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>17.909576818389713</v>
+        <v>17.95911745260727</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19049,23 +19049,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>15.725530760179792</v>
+        <v>15.768991336567161</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>16.261367114585124</v>
+        <v>16.306319379304824</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>16.826529647745438</v>
+        <v>16.873055240496463</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>17.42243391321907</v>
+        <v>17.470618414389953</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>18.05055105507914</v>
+        <v>18.100484140503681</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19080,23 +19080,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>15.626058999444068</v>
+        <v>15.669242661315156</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>16.207968050897687</v>
+        <v>16.252771660604331</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>16.826529647745435</v>
+        <v>16.873055240496463</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>17.483857743723309</v>
+        <v>17.532213239658798</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>18.182170022056919</v>
+        <v>18.232469515015659</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19112,23 +19112,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>15.536830326198293</v>
+        <v>15.579765588777892</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>16.159578968013879</v>
+        <v>16.204247869745306</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>16.826529647745435</v>
+        <v>16.873055240496459</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>17.540643161397707</v>
+        <v>17.589156739449681</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>18.305054549578497</v>
+        <v>18.355696134697318</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19144,23 +19144,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>15.456789960266157</v>
+        <v>15.499502402428671</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>16.115729821968138</v>
+        <v>16.160276654230032</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>16.826529647745435</v>
+        <v>16.873055240496459</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>17.593140435403331</v>
+        <v>17.641800158020654</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>18.419784268637553</v>
+        <v>18.470745244148393</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19176,23 +19176,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>15.16450350998516</v>
+        <v>15.206402270350992</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>15.950997500520057</v>
+        <v>15.995085742617546</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>16.826529647745435</v>
+        <v>16.873055240496459</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>17.801820255611773</v>
+        <v>17.851060911662298</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>18.888843549106326</v>
+        <v>18.941110315555196</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19208,23 +19208,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>14.994744891124881</v>
+        <v>15.036171068865468</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>15.850339670550259</v>
+        <v>15.894147696291975</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>16.826529647745435</v>
+        <v>16.873055240496459</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>17.942742676277792</v>
+        <v>17.992375639287232</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>19.221596077122303</v>
+        <v>19.274789176880798</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19240,23 +19240,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>14.896149870214256</v>
+        <v>14.937301574151208</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>15.788833837055273</v>
+        <v>15.832470639748312</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>16.826529647745435</v>
+        <v>16.873055240496459</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>18.037908220442702</v>
+        <v>18.087806110105028</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>19.457652050240171</v>
+        <v>19.511502294550322</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19272,23 +19272,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>14.838886337949251</v>
+        <v>14.879878628770154</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>15.751251390115494</v>
+        <v>15.794783568892782</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>16.826529647745435</v>
+        <v>16.873055240496459</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>18.10217394021533</v>
+        <v>18.152250736037285</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>19.625111100895221</v>
+        <v>19.679427526176397</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>17.423633230806175</v>
+        <v>17.471821070697992</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>17.122297261546983</v>
+        <v>17.169646227133686</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>16.826529647745438</v>
+        <v>16.873055240496463</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>16.536276890389939</v>
+        <v>16.581994462841454</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>16.251485490468891</v>
+        <v>16.296410246223818</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>1207889974.6580667</v>
+        <v>1207900641.7775121</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>1109896856.5027108</v>
+        <v>1109898545.0634732</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C14" s="252">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.725889125187102E-2</v>
+        <v>-7.7257260824409646E-2</v>
       </c>
       <c r="D14" s="465"/>
       <c r="E14" s="465"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>17.122297261546983</v>
+        <v>17.169646227133686</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>16.826529647745438</v>
+        <v>16.873055240496463</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>16.536276890389939</v>
+        <v>16.581994462841454</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>16.813119981166871</v>
+        <v>16.859608243410154</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19917,7 +19917,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>17.423633230806175</v>
+        <v>17.471821070697992</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19940,7 +19940,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>16.251485490468891</v>
+        <v>16.296410246223818</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.58991959800000016</v>
+        <v>0.59156184600000006</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.73</v>
+        <v>10.42</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.21077952890145579</v>
+        <v>0.22438656215485436</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20005,7 +20005,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>16.826529647745442</v>
+        <v>16.873055240496466</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20016,7 +20016,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.6016201355065634E-2</v>
+        <v>3.6016877260469607E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>16.876615244077868</v>
+        <v>16.923280267644014</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>16.877921163659639</v>
+        <v>16.924589822710733</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.39724140576358608</v>
+        <v>0.39722915915722701</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.58991959800000016</v>
+        <v>0.59156184600000006</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20265,15 +20265,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.0794653061785484</v>
+        <v>1.0824703762697119</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>7.7772420479621536</v>
+        <v>7.7987466671170589</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>8.8567073541407026</v>
+        <v>8.881217043386771</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.47520831481605363</v>
+        <v>0.47520711688696893</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20290,15 +20290,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2411931627633881</v>
+        <v>1.2446484590377829</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>9.7482254117417337</v>
+        <v>9.7751799379893267</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>10.989418574505121</v>
+        <v>11.01982839702711</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34883752366391174</v>
+        <v>0.34883614625846748</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20336,15 +20336,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4232418661872714</v>
+        <v>1.4272039588456378</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>12.096489375104861</v>
+        <v>12.129937015736177</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>13.519731241292133</v>
+        <v>13.557140974581815</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19890742037054443</v>
+        <v>0.19890584093782304</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20361,15 +20361,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5410913438390648</v>
+        <v>1.5453815118311389</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>13.680231504371305</v>
+        <v>13.718058302950826</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>15.22132284821037</v>
+        <v>15.263439814781965</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>9.8082013006035251E-2</v>
+        <v>9.808030279067903E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20488,7 +20488,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>10.73</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20506,14 +20506,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>13239.11393</v>
+        <v>12856.623219999999</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.21077952890145579</v>
+        <v>0.22438656215485436</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20521,13 +20521,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0924437000000002</v>
+        <v>1.0954849</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>16.876615244077868</v>
+        <v>16.923280267644014</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20643,7 +20643,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>8.8567073541407026</v>
+        <v>8.881217043386771</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>10.989418574505121</v>
+        <v>11.01982839702711</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>13.519731241292133</v>
+        <v>13.557140974581815</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>15.22132284821037</v>
+        <v>15.263439814781965</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20712,22 +20712,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>11576404.690875448</v>
+        <v>11578656.105224969</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-2580518.1386245508</v>
+        <v>-2578266.7242750302</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-389567444.83423698</v>
+        <v>-389568007.68782437</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20917,10 +20917,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20936,22 +20936,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>1207889974.6580667</v>
+        <v>1207900641.7775121</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>1109896856.5027108</v>
+        <v>1109898545.0634732</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.1584666084687946E-2</v>
+        <v>9.4572040872875823E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20995,14 +20995,14 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.4978527306616974E-2</v>
+        <v>5.6771770249520161E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>0.72866329119929796</v>
+        <v>0.7306906692576669</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21022,11 +21022,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095601131136619</v>
+        <v>0.10095615717430696</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>8.8885506981639828E-2</v>
+        <v>8.8886198074957332E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21036,11 +21036,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639558936200029</v>
+        <v>0.12639577198047069</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128347777166675</v>
+        <v>0.11128434301134923</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21086,22 +21086,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21109,13 +21109,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25069099108351001</v>
+        <v>-0.25138887733804471</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>6705117966.3674259</v>
+        <v>6704742730.6425056</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9367162220374494</v>
+        <v>5.9529099939162595</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.51668315096769923</v>
+        <v>0.51812151964401887</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>6.2027083819216378</v>
+        <v>6.2196426362222343</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21264,33 +21264,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21353,23 +21353,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.7046624544217344</v>
+        <v>1.7094079799407034</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>16.826529647745442</v>
+        <v>16.873055240496466</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21413,13 +21413,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21464,7 +21464,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.42 HKD</v>
+        <v>17.47 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.12 HKD</v>
+        <v>17.17 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>16.83 HKD</v>
+        <v>16.87 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.54 HKD</v>
+        <v>16.58 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.25 HKD</v>
+        <v>16.3 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>16.876615244077868</v>
+        <v>16.923280267644014</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21583,13 +21583,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21602,22 +21602,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C136" s="410">
         <f>Scenarios!C58</f>
-        <v>0.58991959800000016</v>
+        <v>0.59156184600000006</v>
       </c>
       <c r="D136" s="347" t="str">
         <f>Market_currency</f>
@@ -21678,15 +21678,15 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>1.0794653061785484</v>
+        <v>1.0824703762697119</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>7.7772420479621536</v>
+        <v>7.7987466671170589</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>8.8567073541407026</v>
+        <v>8.881217043386771</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21699,15 +21699,15 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>1.2411931627633881</v>
+        <v>1.2446484590377829</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>9.7482254117417337</v>
+        <v>9.7751799379893267</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>10.989418574505121</v>
+        <v>11.01982839702711</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21739,15 +21739,15 @@
       </c>
       <c r="C144" s="413">
         <f>Scenarios!C66</f>
-        <v>1.4232418661872714</v>
+        <v>1.4272039588456378</v>
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>12.096489375104861</v>
+        <v>12.129937015736177</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>13.519731241292133</v>
+        <v>13.557140974581815</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21760,15 +21760,15 @@
       </c>
       <c r="C145" s="413">
         <f>Scenarios!C67</f>
-        <v>1.5410913438390648</v>
+        <v>1.5453815118311389</v>
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>13.680231504371305</v>
+        <v>13.718058302950826</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>15.22132284821037</v>
+        <v>15.263439814781965</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21786,13 +21786,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21800,13 +21800,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21843,22 +21843,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21882,15 +21882,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21905,12 +21902,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE804A41-FCF4-4D28-A1BB-294E525701B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E0E6AA-BA39-4518-83DF-BA6BF50EC956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4972,30 +4972,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5005,6 +5005,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5014,16 +5023,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5393,7 +5393,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.42</v>
+        <v>10.51</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12856.623219999999</v>
+        <v>12967.66891</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.22438656215485436</v>
+        <v>0.21998237366068735</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0954849</v>
+        <v>1.0935677000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>16.923280267644014</v>
+        <v>16.893862419523156</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>8.881217043386771</v>
+        <v>8.8657660079709828</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>11.01982839702711</v>
+        <v>11.000657888146176</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>13.557140974581815</v>
+        <v>13.533557687136012</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>15.263439814781965</v>
+        <v>15.236889064117824</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>11578656.105224969</v>
+        <v>11577236.793245848</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-2578266.7242750302</v>
+        <v>-2579686.0362541508</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-389568007.68782437</v>
+        <v>-389567652.8598296</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>1207900641.7775121</v>
+        <v>1207893917.1288862</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>1109898545.0634732</v>
+        <v>1109897480.5794888</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.4572040872875823E-2</v>
+        <v>9.3598012371917214E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5894,14 +5894,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6771770249520161E-2</v>
+        <v>5.6187113035204579E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.7306906692576669</v>
+        <v>0.72941259250244783</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5921,11 +5921,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095615717430696</v>
+        <v>0.10095606522098918</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.8886198074957332E-2</v>
+        <v>8.8885762403476218E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5935,11 +5935,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639577198047069</v>
+        <v>0.12639565685613444</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128434301134923</v>
+        <v>0.11128379755642379</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25138887733804471</v>
+        <v>-0.25094892352797171</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>6704742730.6425056</v>
+        <v>6704979282.6390257</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9529099939162595</v>
+        <v>5.9427015090787307</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.51812151964401887</v>
+        <v>0.51721475901458314</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.2196426362222343</v>
+        <v>6.2089673445653419</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7094079799407034</v>
+        <v>1.7064163577110023</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>16.873055240496466</v>
+        <v>16.84372529082318</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.47 HKD</v>
+        <v>17.44 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.3636313267688221E-2</v>
+        <v>2.3636040195127318E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.17 HKD</v>
+        <v>17.14 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.981075062910921E-2</v>
+        <v>2.981040211342852E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>16.87 HKD</v>
+        <v>16.84 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.6016877260469662E-2</v>
+        <v>3.6016451160631256E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.58 HKD</v>
+        <v>16.55 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.2253633105975415E-2</v>
+        <v>4.2253127247448757E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.3 HKD</v>
+        <v>16.27 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,17 +6445,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.8519893197378393E-2</v>
+        <v>4.8519305373386744E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>16.923280267644014</v>
+        <v>16.893862419523156</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.59156184600000006</v>
+        <v>0.59052655800000009</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,15 +6566,15 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>1.0824703762697119</v>
+        <v>1.0805759528911842</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>7.7987466671170589</v>
+        <v>7.7851900550797977</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>8.881217043386771</v>
+        <v>8.8657660079709828</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,15 +6587,15 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>1.2446484590377829</v>
+        <v>1.2424702089992223</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>9.7751799379893267</v>
+        <v>9.7581876791469533</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>11.01982839702711</v>
+        <v>11.000657888146176</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,15 +6634,15 @@
       </c>
       <c r="C144" s="337">
         <f>Scenarios!C66</f>
-        <v>1.4272039588456378</v>
+        <v>1.4247062197805911</v>
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>12.129937015736177</v>
+        <v>12.108851467355422</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>13.557140974581815</v>
+        <v>13.533557687136012</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,15 +6655,15 @@
       </c>
       <c r="C145" s="337">
         <f>Scenarios!C67</f>
-        <v>1.5453815118311389</v>
+        <v>1.5426769511069494</v>
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>13.718058302950826</v>
+        <v>13.694212113010874</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>15.263439814781965</v>
+        <v>15.236889064117824</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,6 +6777,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6793,18 +6805,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.65729093999999999</v>
+        <v>0.65614062000000006</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.65729093999999999</v>
+        <v>0.65614062000000006</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10216,11 +10216,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.305820454391721</v>
+        <v>13.282534036682854</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7094079799407034</v>
+        <v>1.7064163577110023</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6704742730.6425056</v>
+        <v>6704979282.6390257</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10478,11 +10478,11 @@
       </c>
       <c r="C73" s="289">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-984162766.93004501</v>
+        <v>-984044490.93178499</v>
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-964888008.76874733</v>
+        <v>-964769732.77048731</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10494,11 +10494,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7734661768542068</v>
+        <v>8.7745206926609924</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9487263492870461</v>
+        <v>8.9498234188842432</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10511,7 +10511,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1929776017.5374947</v>
+        <v>1929539465.5409746</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10626,11 +10626,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>310173903.80365044</v>
+        <v>309631070.75467616</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.25138887733804471</v>
+        <v>0.25094892352797171</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10643,11 +10643,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7344944419.8036318</v>
+        <v>7332348772.6632099</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.9529099939162595</v>
+        <v>5.9427015090787307</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10660,11 +10660,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>639279573.91909587</v>
+        <v>638160775.47731221</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.51812151964401887</v>
+        <v>0.51721475901458314</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10677,11 +10677,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>8294397897.5263786</v>
+        <v>8280140618.8951979</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.7224203908983231</v>
+        <v>6.7108651916212851</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11162,36 +11162,36 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-2578266.7242750302</v>
+        <v>-2579686.0362541508</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>42417369.237511106</v>
+        <v>42410644.588885337</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40885325.2024744</v>
+        <v>40878122.304199807</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>17669634.762510419</v>
+        <v>17664897.311594129</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>5041839.7092593461</v>
+        <v>5038832.860088177</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
-        <v>-4716999.9914317839</v>
+        <v>-4719138.639649488</v>
       </c>
       <c r="L10" s="270">
         <f t="shared" si="6"/>
-        <v>-6434396.3009453397</v>
+        <v>-6435990.5676699448</v>
       </c>
       <c r="M10" s="270">
         <f t="shared" si="6"/>
-        <v>7529074.1608027667</v>
+        <v>7528087.9448911706</v>
       </c>
       <c r="N10" s="270">
         <f t="shared" si="6"/>
@@ -11217,36 +11217,36 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>1558272030.7512975</v>
+        <v>1558270611.4393184</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1371970568.7775121</v>
+        <v>1371963844.1288862</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>1481869993.5224741</v>
+        <v>1481862790.6241994</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>1407197133.7625103</v>
+        <v>1407192396.311594</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>1240496157.7092593</v>
+        <v>1240493150.8600881</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
-        <v>1157438691.0085683</v>
+        <v>1157436552.3603506</v>
       </c>
       <c r="L11" s="271">
         <f t="shared" si="7"/>
-        <v>999251418.27905679</v>
+        <v>999249824.01233208</v>
       </c>
       <c r="M11" s="271">
         <f t="shared" si="7"/>
-        <v>939476380.93080175</v>
+        <v>939475394.71489024</v>
       </c>
       <c r="N11" s="271">
         <f t="shared" si="7"/>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-389568007.68782437</v>
+        <v>-389567652.8598296</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11384,38 +11384,38 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>1109898545.0634732</v>
+        <v>1109897480.5794888</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207900641.7775121</v>
+        <v>1207893917.1288862</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>1497843936.5224741</v>
+        <v>1497836733.6241994</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>1418632610.7625103</v>
+        <v>1418627873.311594</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>1235043345.7092593</v>
+        <v>1235040338.8600881</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
-        <v>1149268140.0085683</v>
+        <v>1149266001.3603506</v>
       </c>
       <c r="L14" s="271">
         <f t="shared" si="8"/>
-        <v>975079343.15905678</v>
+        <v>975077748.89233208</v>
       </c>
       <c r="M14" s="271">
         <f t="shared" si="8"/>
-        <v>950272227.30080175</v>
+        <v>950271241.08489025</v>
       </c>
       <c r="N14" s="271">
         <f t="shared" si="8"/>
@@ -11602,38 +11602,38 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>1109898545.0634732</v>
+        <v>1109897480.5794888</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207900641.7775121</v>
+        <v>1207893917.1288862</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>1497843936.5224741</v>
+        <v>1497836733.6241994</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>1418632610.7625103</v>
+        <v>1418627873.311594</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>1235043345.7092593</v>
+        <v>1235040338.8600881</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
-        <v>1149268140.0085683</v>
+        <v>1149266001.3603506</v>
       </c>
       <c r="L19" s="275">
         <f t="shared" si="9"/>
-        <v>975079343.15905678</v>
+        <v>975077748.89233208</v>
       </c>
       <c r="M19" s="275">
         <f t="shared" si="9"/>
-        <v>950272227.30080175</v>
+        <v>950271241.08489025</v>
       </c>
       <c r="N19" s="275">
         <f t="shared" si="9"/>
@@ -12341,31 +12341,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.6725005182724432E-2</v>
+        <v>7.6725381248539046E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.3983780145968321E-2</v>
+        <v>-4.3983993938160236E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.1264214697654019E-3</v>
+        <v>-8.1264488281585674E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3956702051132033E-3</v>
+        <v>4.3956808598413681E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.0591652616004653E-3</v>
+        <v>7.0591783051415337E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4190183449156303E-2</v>
+        <v>2.4190222043713551E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491344103088399E-2</v>
+        <v>-1.1491356166146636E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12479,36 +12479,36 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>11578656.105224969</v>
+        <v>11577236.793245848</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54859252.237511106</v>
+        <v>54852527.588885337</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>58760782.2024744</v>
+        <v>58753579.304199807</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>38647820.762510419</v>
+        <v>38643083.311594129</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>24529682.709259346</v>
+        <v>24526675.860088177</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
-        <v>17446955.008568216</v>
+        <v>17444816.360350512</v>
       </c>
       <c r="L46" s="278">
         <f t="shared" si="17"/>
-        <v>13005925.69905466</v>
+        <v>13004331.432330055</v>
       </c>
       <c r="M46" s="278">
         <f t="shared" si="17"/>
-        <v>8045486.1608027667</v>
+        <v>8044499.9448911706</v>
       </c>
       <c r="N46" s="278">
         <f t="shared" si="17"/>
@@ -12591,36 +12591,36 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-2578266.7242750302</v>
+        <v>-2579686.0362541508</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42417369.237511106</v>
+        <v>42410644.588885337</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40885325.2024744</v>
+        <v>40878122.304199807</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>17669634.762510419</v>
+        <v>17664897.311594129</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>5041839.7092593461</v>
+        <v>5038832.860088177</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
-        <v>-4716999.9914317839</v>
+        <v>-4719138.639649488</v>
       </c>
       <c r="L48" s="271">
         <f t="shared" si="18"/>
-        <v>-6434396.3009453397</v>
+        <v>-6435990.5676699448</v>
       </c>
       <c r="M48" s="271">
         <f t="shared" si="18"/>
-        <v>7529074.1608027667</v>
+        <v>7528087.9448911706</v>
       </c>
       <c r="N48" s="271">
         <f t="shared" si="18"/>
@@ -13556,38 +13556,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0913037425768512E-4</v>
+        <v>2.0924549859396393E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.4405906185526408E-3</v>
+        <v>3.4400451636271991E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4448631408382671E-3</v>
+        <v>3.4442562483004073E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.6165732635053669E-3</v>
+        <v>1.6161398399178748E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8199467217118456E-4</v>
+        <v>4.8170722049399931E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2364235983145711E-4</v>
+        <v>5.2387977488373659E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.2767057552721522E-4</v>
+        <v>7.2785087231509987E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.1968458530264374E-4</v>
+        <v>9.1956411795801368E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13613,38 +13613,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639577198047069</v>
+        <v>0.12639565685613444</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.11128434301134923</v>
+        <v>0.11128379755642379</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12485749581101205</v>
+        <v>0.12485688891847418</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12874274389351675</v>
+        <v>0.12874231046992926</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11859015227450036</v>
+        <v>0.11858986482282317</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12848927891051162</v>
+        <v>0.12848904149545937</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300607246225698</v>
+        <v>0.11300589216546909</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.1147580602003061</v>
+        <v>0.11475793973296147</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1598942995117674E-2</v>
+        <v>3.1598914214033609E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13785,38 +13785,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.002695335272233E-2</v>
+        <v>9.0026867009470116E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.7976175584416667E-2</v>
+        <v>9.7975630129491217E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12620340775330524</v>
+        <v>0.12620280086076738</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12978896169156953</v>
+        <v>0.12978852826798204</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11806886907552751</v>
+        <v>0.11806858162385032</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758225185633845</v>
+        <v>0.12758201444128617</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11027243483852633</v>
+        <v>0.11027225454173845</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607678455867075</v>
+        <v>0.11607666409132612</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14008,38 +14008,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.002695335272233E-2</v>
+        <v>9.0026867009470116E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.7976175584416667E-2</v>
+        <v>9.7975630129491217E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12620340775330524</v>
+        <v>0.12620280086076738</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12978896169156953</v>
+        <v>0.12978852826798204</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11806886907552751</v>
+        <v>0.11806858162385032</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758225185633845</v>
+        <v>0.12758201444128617</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11027243483852633</v>
+        <v>0.11027225454173845</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607678455867075</v>
+        <v>0.11607666409132612</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14077,12 +14077,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.65729093999999999</v>
+        <v>0.65614062000000006</v>
       </c>
       <c r="E88" s="238"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.65729093999999999</v>
+        <v>0.65614062000000006</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14133,12 +14133,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>810992510.70053995</v>
+        <v>809573198.72142005</v>
       </c>
       <c r="E89" s="238"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>810992510.70053995</v>
+        <v>809573198.72142005</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.7306906692576669</v>
+        <v>0.72941259250244783</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.67140663946258572</v>
+        <v>0.67023534702926735</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14264,12 +14264,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6771770249520161E-2</v>
+        <v>5.6187113035204579E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.6771770249520161E-2</v>
+        <v>5.6187113035204579E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14401,38 +14401,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.13579115049077806</v>
+        <v>0.13579568303326961</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162662868775597E-2</v>
+        <v>-7.4162700616175692E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.3064960102858105E-2</v>
+        <v>5.3063386718351202E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.1343825009188957</v>
+        <v>0.13438143155883298</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1759711633897716E-2</v>
+        <v>7.1759094120849021E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830577754089825</v>
+        <v>0.15830548532182309</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3625907539082593E-2</v>
+        <v>6.3625327106711538E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35102371019457435</v>
+        <v>0.35102229195659951</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -15012,31 +15012,31 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4674044956145322</v>
+        <v>1.4674126650236874</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5709435099513751</v>
+        <v>1.570951064410445</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.4269946352860885</v>
+        <v>1.4269994006774711</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.6576985610365456</v>
+        <v>1.657702596896256</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.5825769693628156</v>
+        <v>1.5825799143515396</v>
       </c>
       <c r="L113" s="254">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3992815345668077</v>
+        <v>1.3992838224130759</v>
       </c>
       <c r="M113" s="254">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.0454375529755755</v>
+        <v>1.0454386379575309</v>
       </c>
       <c r="N113" s="254">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15120,36 +15120,36 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639577198047069</v>
+        <v>0.12639565685613444</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.11128434301134923</v>
+        <v>0.11128379755642379</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12485749581101205</v>
+        <v>0.12485688891847418</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12874274389351675</v>
+        <v>0.12874231046992926</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11859015227450036</v>
+        <v>0.11858986482282317</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12848927891051162</v>
+        <v>0.12848904149545937</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300607246225698</v>
+        <v>0.11300589216546909</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.1147580602003061</v>
+        <v>0.11475793973296147</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15285,38 +15285,38 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.10095615717430696</v>
+        <v>0.10095606522098918</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.8886198074957332E-2</v>
+        <v>8.8885762403476218E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11047060841039869</v>
+        <v>0.11047007144794031</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11113516239879108</v>
+        <v>0.11113478825265029</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11165894985456894</v>
+        <v>0.11165867920349216</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11541896451952213</v>
+        <v>0.11541875125504024</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.1095674460338958</v>
+        <v>0.10956727122330247</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176220550434329</v>
+        <v>0.11176208818189899</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15406,50 +15406,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.98544066589536605</v>
+        <v>0.98371511002885004</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0724533499596574</v>
+        <v>1.0705704971699164</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3298840085691179</v>
+        <v>1.3275502044144492</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2595550024175783</v>
+        <v>1.2573464656898672</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0965524213168254</v>
+        <v>1.0946306880501193</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0203955723877489</v>
+        <v>1.0186078901542708</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.86573934302123612</v>
+        <v>0.86422280599961043</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.84371395981929276</v>
+        <v>0.84223650818002405</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.6169078277226705</v>
+        <v>0.61582818190800903</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.50801250498007011</v>
+        <v>0.50712343606223498</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.47893113612123073</v>
+        <v>0.47809296229138465</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15463,50 +15463,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.4572040872875823E-2</v>
+        <v>9.3598012371917214E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10292258636848919</v>
+        <v>0.10186208346050585</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.12762802385500172</v>
+        <v>0.12631305465408652</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.1208785990803818</v>
+        <v>0.11963334592672381</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10523535713213296</v>
+        <v>0.10415134995719499</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.7926638424927923E-2</v>
+        <v>9.6917972421909693E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.3084389925262583E-2</v>
+        <v>8.2228620932408222E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.0970629541198921E-2</v>
+        <v>8.0136680131305815E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.9204206115419433E-2</v>
+        <v>5.8594498754330072E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.8753599326302313E-2</v>
+        <v>4.8251516276140341E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.596268100971504E-2</v>
+        <v>4.5489339894518047E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15520,43 +15520,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12473428259959539</v>
+        <v>0.12366614887609742</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12665458706660301</v>
+        <v>0.12557000925157025</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10821155012427906</v>
+        <v>0.1072849050708837</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10137041738709365</v>
+        <v>0.10050235482145727</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6681292259259352E-2</v>
+        <v>9.5853383952567303E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7477497385195974E-2</v>
+        <v>8.6728403687320849E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2080860650748702E-2</v>
+        <v>7.1463612557640471E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1284687667777832E-2</v>
+        <v>7.0674257421336345E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9004935690259738E-2</v>
+        <v>4.8585293044006321E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7829028624205107E-2</v>
+        <v>4.7419455591267097E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>1109898545.0634732</v>
+        <v>1109897480.5794888</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>6704742730.6425056</v>
+        <v>6704979282.6390257</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>11998903189.875387</v>
+        <v>11998891681.940418</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-2578266.7242750302</v>
+        <v>-2579686.0362541508</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16404,14 +16404,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>7005162818.6925058</v>
+        <v>7005399370.6890259</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>7005162818.6925058</v>
+        <v>7005399370.6890259</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>19004066008.567894</v>
+        <v>19004291052.629444</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.2196426362222343</v>
+        <v>6.2089673445653419</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-2578266.7242750302</v>
+        <v>-2579686.0362541508</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0954849</v>
+        <v>1.0935677000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>20818667350.989399</v>
+        <v>20782478856.554562</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>16.873055240496466</v>
+        <v>16.84372529082318</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>16.924589822710733</v>
+        <v>16.895169682747269</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>1561005207.2146106</v>
+        <v>1561003787.9026315</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16723,11 +16723,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>1111845454.2118986</v>
+        <v>1111844389.7279143</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>1.7541325349823556E-3</v>
+        <v>1.7541342173414964E-3</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>1017707509.5761085</v>
+        <v>1017706535.2200588</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>1563743169.693336</v>
+        <v>1563741750.381357</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16772,11 +16772,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>1113795772.5573945</v>
+        <v>1113794708.0734103</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>1.7541271928644964E-3</v>
+        <v>1.7541288722724424E-3</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>933174094.27280402</v>
+        <v>933173202.41371965</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>1566485926.5681777</v>
+        <v>1566484507.2561986</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16821,11 +16821,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>1115749506.0697429</v>
+        <v>1115748441.5857587</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>1.7541218601166975E-3</v>
+        <v>1.7541235365787777E-3</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>855662238.3074255</v>
+        <v>855661421.96043754</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>1566485926.5681777</v>
+        <v>1566484507.2561986</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>12062156822.375599</v>
+        <v>12062145314.440634</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18285,7 +18285,7 @@
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>9250402576.2964916</v>
+        <v>9250393750.9236488</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18298,7 +18298,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>12056946418.452829</v>
+        <v>12056934910.517864</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18322,7 +18322,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>12056946418.452829</v>
+        <v>12056934910.517864</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18357,19 +18357,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>11758507028.771236</v>
+        <v>11758495520.836269</v>
       </c>
       <c r="C56" s="118">
-        <v>11878705109.323309</v>
+        <v>11878693601.388342</v>
       </c>
       <c r="D56" s="118">
-        <v>11998903189.875385</v>
+        <v>11998891681.940416</v>
       </c>
       <c r="E56" s="118">
-        <v>12119101270.427456</v>
+        <v>12119089762.492491</v>
       </c>
       <c r="F56" s="118">
-        <v>12239299350.979532</v>
+        <v>12239287843.044565</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18383,19 +18383,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>11542865621.098866</v>
+        <v>11542854113.163902</v>
       </c>
       <c r="C57" s="118">
-        <v>11769784194.223488</v>
+        <v>11769772686.288527</v>
       </c>
       <c r="D57" s="118">
-        <v>11998903189.875387</v>
+        <v>11998891681.940418</v>
       </c>
       <c r="E57" s="118">
-        <v>12230222608.054546</v>
+        <v>12230211100.119581</v>
       </c>
       <c r="F57" s="118">
-        <v>12463742448.760979</v>
+        <v>12463730940.826014</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18409,19 +18409,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>11349429850.372166</v>
+        <v>11349418342.437199</v>
       </c>
       <c r="C58" s="118">
-        <v>11671082403.881315</v>
+        <v>11671070895.94635</v>
       </c>
       <c r="D58" s="118">
-        <v>11998903189.875385</v>
+        <v>11998891681.940416</v>
       </c>
       <c r="E58" s="118">
-        <v>12332952631.856245</v>
+        <v>12332941123.92128</v>
       </c>
       <c r="F58" s="118">
-        <v>12673291153.325806</v>
+        <v>12673279645.390841</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18435,19 +18435,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>11175913094.937683</v>
+        <v>11175901587.00272</v>
       </c>
       <c r="C59" s="118">
-        <v>11581640964.578114</v>
+        <v>11581629456.64315</v>
       </c>
       <c r="D59" s="118">
-        <v>11998903189.875385</v>
+        <v>11998891681.940418</v>
       </c>
       <c r="E59" s="118">
-        <v>12427925010.839973</v>
+        <v>12427913502.905006</v>
       </c>
       <c r="F59" s="118">
-        <v>12868933879.7845</v>
+        <v>12868922371.849535</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18461,19 +18461,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>11020264197.614309</v>
+        <v>11020252689.679344</v>
       </c>
       <c r="C60" s="118">
-        <v>11500591056.193521</v>
+        <v>11500579548.258554</v>
       </c>
       <c r="D60" s="118">
-        <v>11998903189.875385</v>
+        <v>11998891681.940418</v>
       </c>
       <c r="E60" s="118">
-        <v>12515725562.577787</v>
+        <v>12515714054.642822</v>
       </c>
       <c r="F60" s="118">
-        <v>13051593450.482777</v>
+        <v>13051581942.547813</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18487,19 +18487,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>10880643218.779606</v>
+        <v>10880631710.844641</v>
       </c>
       <c r="C61" s="118">
-        <v>11427145372.623041</v>
+        <v>11427133864.688074</v>
       </c>
       <c r="D61" s="118">
-        <v>11998903189.875385</v>
+        <v>11998891681.940416</v>
       </c>
       <c r="E61" s="118">
-        <v>12596895866.70153</v>
+        <v>12596884358.766565</v>
       </c>
       <c r="F61" s="118">
-        <v>13222131447.83952</v>
+        <v>13222119939.904552</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18513,19 +18513,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>10755399686.278</v>
+        <v>10755388178.343037</v>
       </c>
       <c r="C62" s="118">
-        <v>11360590474.009972</v>
+        <v>11360578966.075008</v>
       </c>
       <c r="D62" s="118">
-        <v>11998903189.875385</v>
+        <v>11998891681.940416</v>
       </c>
       <c r="E62" s="118">
-        <v>12671936605.525314</v>
+        <v>12671925097.590347</v>
       </c>
       <c r="F62" s="118">
-        <v>13381352278.323622</v>
+        <v>13381340770.388657</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18539,19 +18539,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>10643053085.040859</v>
+        <v>10643041577.105896</v>
       </c>
       <c r="C63" s="118">
-        <v>11300279856.50248</v>
+        <v>11300268348.567514</v>
       </c>
       <c r="D63" s="118">
-        <v>11998903189.875385</v>
+        <v>11998891681.940414</v>
       </c>
       <c r="E63" s="118">
-        <v>12741310652.401302</v>
+        <v>12741299144.466337</v>
       </c>
       <c r="F63" s="118">
-        <v>13530006966.738983</v>
+        <v>13529995458.804016</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18565,19 +18565,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>10542275355.784662</v>
+        <v>10542263847.849697</v>
       </c>
       <c r="C64" s="118">
-        <v>11245627672.216515</v>
+        <v>11245616164.281548</v>
       </c>
       <c r="D64" s="118">
-        <v>11998903189.875381</v>
+        <v>11998891681.940414</v>
       </c>
       <c r="E64" s="118">
-        <v>12805445926.858742</v>
+        <v>12805434418.923777</v>
       </c>
       <c r="F64" s="118">
-        <v>13668796698.714878</v>
+        <v>13668785190.779915</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18591,19 +18591,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>10451875195.90267</v>
+        <v>10451863687.967707</v>
       </c>
       <c r="C65" s="118">
-        <v>11196103038.401314</v>
+        <v>11196091530.466347</v>
       </c>
       <c r="D65" s="118">
-        <v>11998903189.875381</v>
+        <v>11998891681.940414</v>
       </c>
       <c r="E65" s="118">
-        <v>12864738034.13747</v>
+        <v>12864726526.202505</v>
       </c>
       <c r="F65" s="118">
-        <v>13798376128.111139</v>
+        <v>13798364620.176178</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18617,19 +18617,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>10121757491.803911</v>
+        <v>10121745983.86895</v>
       </c>
       <c r="C66" s="281">
-        <v>11010049063.969662</v>
+        <v>11010037556.034693</v>
       </c>
       <c r="D66" s="118">
-        <v>11998903189.875381</v>
+        <v>11998891681.940414</v>
       </c>
       <c r="E66" s="118">
-        <v>13100427725.098942</v>
+        <v>13100416217.163977</v>
       </c>
       <c r="F66" s="118">
-        <v>14328146743.908438</v>
+        <v>14328135235.973475</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18652,19 +18652,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>9930026655.648983</v>
+        <v>9930015147.7140217</v>
       </c>
       <c r="C67" s="281">
-        <v>10896362878.047438</v>
+        <v>10896351370.112473</v>
       </c>
       <c r="D67" s="118">
-        <v>11998903189.875381</v>
+        <v>11998891681.940414</v>
       </c>
       <c r="E67" s="118">
-        <v>13259590032.902067</v>
+        <v>13259578524.967102</v>
       </c>
       <c r="F67" s="118">
-        <v>14703968135.820679</v>
+        <v>14703956627.885715</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18687,19 +18687,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>9818670272.5279217</v>
+        <v>9818658764.5929585</v>
       </c>
       <c r="C68" s="281">
-        <v>10826896214.360067</v>
+        <v>10826884706.425098</v>
       </c>
       <c r="D68" s="118">
-        <v>11998903189.87538</v>
+        <v>11998891681.940414</v>
       </c>
       <c r="E68" s="118">
-        <v>13367073054.8445</v>
+        <v>13367061546.909534</v>
       </c>
       <c r="F68" s="118">
-        <v>14970577333.098053</v>
+        <v>14970565825.163088</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18722,19 +18722,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>9753995000.0965958</v>
+        <v>9753983492.1616364</v>
       </c>
       <c r="C69" s="281">
-        <v>10784449391.778162</v>
+        <v>10784437883.843193</v>
       </c>
       <c r="D69" s="118">
-        <v>11998903189.87538</v>
+        <v>11998891681.940414</v>
       </c>
       <c r="E69" s="118">
-        <v>13439656822.7311</v>
+        <v>13439645314.796135</v>
       </c>
       <c r="F69" s="118">
-        <v>15159710963.068438</v>
+        <v>15159699455.133474</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18831,23 +18831,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>16.873055240496466</v>
+        <v>16.84372529082318</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>16.873055240496466</v>
+        <v>16.84372529082318</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>16.873055240496466</v>
+        <v>16.84372529082318</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>16.873055240496466</v>
+        <v>16.84372529082318</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>16.873055240496466</v>
+        <v>16.84372529082318</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18862,23 +18862,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>16.659615774221987</v>
+        <v>16.630659363375887</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>16.766335507359223</v>
+        <v>16.737192327099532</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>16.873055240496463</v>
+        <v>16.843725290823176</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>16.979774973633695</v>
+        <v>16.950258254546828</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>17.086494706770935</v>
+        <v>17.056791218270469</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>16.468155200355643</v>
+        <v>16.439533863240108</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>16.669628380763466</v>
+        <v>16.640654446928909</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>16.873055240496463</v>
+        <v>16.84372529082318</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>17.078435779554617</v>
+        <v>17.048746394922919</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>17.285769997937944</v>
+        <v>17.255717759228123</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18924,23 +18924,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>16.296410246223818</v>
+        <v>16.268089478678945</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>16.581994462841454</v>
+        <v>16.553173896476803</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>16.873055240496463</v>
+        <v>16.843725290823176</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>17.169646227133686</v>
+        <v>17.139797215774038</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>17.471821070697992</v>
+        <v>17.441443225385381</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18955,23 +18955,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>16.142350699268039</v>
+        <v>16.114299550193877</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>16.50258249145217</v>
+        <v>16.473900903389779</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>16.873055240496463</v>
+        <v>16.84372529082318</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>17.253968929243399</v>
+        <v>17.223972345348081</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>17.645525504762293</v>
+        <v>17.614843660607718</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18986,23 +18986,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>16.004155407719612</v>
+        <v>15.976346113200407</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>16.430621071154331</v>
+        <v>16.402065422239975</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>16.873055240496463</v>
+        <v>16.84372529082318</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>17.331924013115994</v>
+        <v>17.30179100060646</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>17.807702642286856</v>
+        <v>17.776736973126518</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -19017,23 +19017,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>15.880190752600644</v>
+        <v>15.852598407705116</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>16.365411179991987</v>
+        <v>16.336969654424593</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>16.873055240496463</v>
+        <v>16.843725290823176</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>17.403992328641223</v>
+        <v>17.373733189907107</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>17.95911745260727</v>
+        <v>17.92788679351019</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19049,23 +19049,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>15.768991336567161</v>
+        <v>15.741593600945043</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>16.306319379304824</v>
+        <v>16.277981269859627</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>16.873055240496463</v>
+        <v>16.843725290823176</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>17.470618414389953</v>
+        <v>17.440242673837229</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>18.100484140503681</v>
+        <v>18.069006076614407</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19080,23 +19080,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>15.669242661315156</v>
+        <v>15.642019495109919</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>16.252771660604331</v>
+        <v>16.224527264624552</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>16.873055240496463</v>
+        <v>16.843725290823176</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>17.532213239658798</v>
+        <v>17.501729702459127</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>18.232469515015659</v>
+        <v>18.20076046450118</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19112,23 +19112,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>15.579765588777892</v>
+        <v>15.552699015733786</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>16.204247869745306</v>
+        <v>16.176088394892083</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>16.873055240496459</v>
+        <v>16.843725290823176</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>17.589156739449681</v>
+        <v>17.558573545853278</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>18.355696134697318</v>
+        <v>18.32377142618952</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19144,23 +19144,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>15.499502402428671</v>
+        <v>15.472576297391809</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>16.160276654230032</v>
+        <v>16.132194133075014</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>16.873055240496459</v>
+        <v>16.843725290823176</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>17.641800158020654</v>
+        <v>17.611124833567789</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>18.470745244148393</v>
+        <v>18.43861918904728</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19176,23 +19176,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>15.206402270350992</v>
+        <v>15.179989117681819</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>15.995085742617546</v>
+        <v>15.967292320851978</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>16.873055240496459</v>
+        <v>16.843725290823176</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>17.851060911662298</v>
+        <v>17.820019361516241</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>18.941110315555196</v>
+        <v>18.908161078030567</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19208,23 +19208,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>15.036171068865468</v>
+        <v>15.01005583655968</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>15.894147696291975</v>
+        <v>15.866530925452787</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>16.873055240496459</v>
+        <v>16.843725290823176</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>17.992375639287232</v>
+        <v>17.961086775284265</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>19.274789176880798</v>
+        <v>19.241255970455338</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19240,23 +19240,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>14.937301574151208</v>
+        <v>14.911359372614957</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>15.832470639748312</v>
+        <v>15.804961809468415</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>16.873055240496459</v>
+        <v>16.843725290823176</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>18.087806110105028</v>
+        <v>18.056350233942744</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>19.511502294550322</v>
+        <v>19.477554818252955</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19272,23 +19272,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>14.879878628770154</v>
+        <v>14.854036922704802</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>15.794783568892782</v>
+        <v>15.767340694476124</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>16.873055240496459</v>
+        <v>16.843725290823176</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>18.152250736037285</v>
+        <v>18.120682075813036</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>19.679427526176397</v>
+        <v>19.645186165176401</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>17.471821070697992</v>
+        <v>17.441443225385381</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>17.169646227133686</v>
+        <v>17.139797215774038</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>16.873055240496463</v>
+        <v>16.843725290823176</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>16.581994462841454</v>
+        <v>16.553173896476803</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>16.296410246223818</v>
+        <v>16.268089478678945</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>1207900641.7775121</v>
+        <v>1207893917.1288862</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>1109898545.0634732</v>
+        <v>1109897480.5794888</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C14" s="252">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7257260824409646E-2</v>
+        <v>-7.7258288658287211E-2</v>
       </c>
       <c r="D14" s="465"/>
       <c r="E14" s="465"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>17.169646227133686</v>
+        <v>17.139797215774038</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>16.873055240496463</v>
+        <v>16.843725290823176</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>16.581994462841454</v>
+        <v>16.553173896476803</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>16.859608243410154</v>
+        <v>16.830301827226759</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19917,7 +19917,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>17.471821070697992</v>
+        <v>17.441443225385381</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19940,7 +19940,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>16.296410246223818</v>
+        <v>16.268089478678945</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.59156184600000006</v>
+        <v>0.59052655800000009</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.42</v>
+        <v>10.51</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22438656215485436</v>
+        <v>0.21998237366068735</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20005,7 +20005,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>16.873055240496466</v>
+        <v>16.84372529082318</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20016,7 +20016,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.6016877260469607E-2</v>
+        <v>3.6016451160631194E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>16.923280267644014</v>
+        <v>16.893862419523156</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>16.924589822710733</v>
+        <v>16.895169682747269</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.39722915915722701</v>
+        <v>0.39723687958213555</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.59156184600000006</v>
+        <v>0.59052655800000009</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20265,15 +20265,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.0824703762697119</v>
+        <v>1.0805759528911842</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>7.7987466671170589</v>
+        <v>7.7851900550797977</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>8.881217043386771</v>
+        <v>8.8657660079709828</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.47520711688696893</v>
+        <v>0.47520787207753135</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20290,15 +20290,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2446484590377829</v>
+        <v>1.2424702089992223</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>9.7751799379893267</v>
+        <v>9.7581876791469533</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>11.01982839702711</v>
+        <v>11.000657888146176</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34883614625846748</v>
+        <v>0.34883701459333427</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20336,15 +20336,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4272039588456378</v>
+        <v>1.4247062197805911</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>12.129937015736177</v>
+        <v>12.108851467355422</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>13.557140974581815</v>
+        <v>13.533557687136012</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19890584093782304</v>
+        <v>0.19890683663339503</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20361,15 +20361,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5453815118311389</v>
+        <v>1.5426769511069494</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>13.718058302950826</v>
+        <v>13.694212113010874</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>15.263439814781965</v>
+        <v>15.236889064117824</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>9.808030279067903E-2</v>
+        <v>9.8081380933378148E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20488,7 +20488,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>10.42</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20506,14 +20506,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12856.623219999999</v>
+        <v>12967.66891</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.22438656215485436</v>
+        <v>0.21998237366068735</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20521,13 +20521,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0954849</v>
+        <v>1.0935677000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>16.923280267644014</v>
+        <v>16.893862419523156</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20643,7 +20643,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>8.881217043386771</v>
+        <v>8.8657660079709828</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>11.01982839702711</v>
+        <v>11.000657888146176</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>13.557140974581815</v>
+        <v>13.533557687136012</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>15.263439814781965</v>
+        <v>15.236889064117824</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20712,22 +20712,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>11578656.105224969</v>
+        <v>11577236.793245848</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-2578266.7242750302</v>
+        <v>-2579686.0362541508</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-389568007.68782437</v>
+        <v>-389567652.8598296</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20917,10 +20917,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20936,22 +20936,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>1207900641.7775121</v>
+        <v>1207893917.1288862</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>1109898545.0634732</v>
+        <v>1109897480.5794888</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.4572040872875823E-2</v>
+        <v>9.3598012371917214E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20995,14 +20995,14 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.6771770249520161E-2</v>
+        <v>5.6187113035204579E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>0.7306906692576669</v>
+        <v>0.72941259250244783</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21022,11 +21022,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095615717430696</v>
+        <v>0.10095606522098918</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>8.8886198074957332E-2</v>
+        <v>8.8885762403476218E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21036,11 +21036,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639577198047069</v>
+        <v>0.12639565685613444</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128434301134923</v>
+        <v>0.11128379755642379</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21086,22 +21086,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21109,13 +21109,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25138887733804471</v>
+        <v>-0.25094892352797171</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>6704742730.6425056</v>
+        <v>6704979282.6390257</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9529099939162595</v>
+        <v>5.9427015090787307</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.51812151964401887</v>
+        <v>0.51721475901458314</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>6.2196426362222343</v>
+        <v>6.2089673445653419</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21264,33 +21264,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21353,23 +21353,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.7094079799407034</v>
+        <v>1.7064163577110023</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>16.873055240496466</v>
+        <v>16.84372529082318</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21413,13 +21413,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21464,7 +21464,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.47 HKD</v>
+        <v>17.44 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.17 HKD</v>
+        <v>17.14 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>16.87 HKD</v>
+        <v>16.84 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.58 HKD</v>
+        <v>16.55 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.3 HKD</v>
+        <v>16.27 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>16.923280267644014</v>
+        <v>16.893862419523156</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21583,13 +21583,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21602,22 +21602,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C136" s="410">
         <f>Scenarios!C58</f>
-        <v>0.59156184600000006</v>
+        <v>0.59052655800000009</v>
       </c>
       <c r="D136" s="347" t="str">
         <f>Market_currency</f>
@@ -21678,15 +21678,15 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>1.0824703762697119</v>
+        <v>1.0805759528911842</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>7.7987466671170589</v>
+        <v>7.7851900550797977</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>8.881217043386771</v>
+        <v>8.8657660079709828</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21699,15 +21699,15 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>1.2446484590377829</v>
+        <v>1.2424702089992223</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>9.7751799379893267</v>
+        <v>9.7581876791469533</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>11.01982839702711</v>
+        <v>11.000657888146176</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21739,15 +21739,15 @@
       </c>
       <c r="C144" s="413">
         <f>Scenarios!C66</f>
-        <v>1.4272039588456378</v>
+        <v>1.4247062197805911</v>
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>12.129937015736177</v>
+        <v>12.108851467355422</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>13.557140974581815</v>
+        <v>13.533557687136012</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21760,15 +21760,15 @@
       </c>
       <c r="C145" s="413">
         <f>Scenarios!C67</f>
-        <v>1.5453815118311389</v>
+        <v>1.5426769511069494</v>
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>13.718058302950826</v>
+        <v>13.694212113010874</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>15.263439814781965</v>
+        <v>15.236889064117824</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21786,13 +21786,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21800,13 +21800,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21843,22 +21843,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21882,12 +21882,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21902,15 +21905,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E0E6AA-BA39-4518-83DF-BA6BF50EC956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0C2BC7-D78C-4417-B940-8429A333C3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5393,7 +5393,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.51</v>
+        <v>10.4</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12967.66891</v>
+        <v>12831.946400000001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.21998237366068735</v>
+        <v>0.22497970185102439</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0935677000000001</v>
+        <v>1.0948992599999998</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>16.893862419523156</v>
+        <v>16.914294180464442</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>8.8657660079709828</v>
+        <v>8.8764973068773703</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>11.000657888146176</v>
+        <v>11.013972495365891</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>13.533557687136012</v>
+        <v>13.549937128080195</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>15.236889064117824</v>
+        <v>15.255329515217692</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>11577236.793245848</v>
+        <v>11578222.553239023</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-2579686.0362541508</v>
+        <v>-2578700.2762609757</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-389567652.8598296</v>
+        <v>-389567899.29982787</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>1207893917.1288862</v>
+        <v>1207898587.6239438</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>1109897480.5794888</v>
+        <v>1109898219.8994837</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.3598012371917214E-2</v>
+        <v>9.4703227535556239E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5894,14 +5894,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6187113035204579E-2</v>
+        <v>5.6850538499999985E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.72941259250244783</v>
+        <v>0.73030026013376526</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5921,11 +5921,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095606522098918</v>
+        <v>0.10095612908566674</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.8885762403476218E-2</v>
+        <v>8.8886064991999802E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5935,11 +5935,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639565685613444</v>
+        <v>0.12639573681386509</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128379755642379</v>
+        <v>0.1112841763932486</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25094892352797171</v>
+        <v>-0.25125448627329861</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>6704979282.6390257</v>
+        <v>6704814989.3068295</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9427015090787307</v>
+        <v>5.9497917237544824</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.51721475901458314</v>
+        <v>0.51784453482500004</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.2089673445653419</v>
+        <v>6.2163817723061836</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7064163577110023</v>
+        <v>1.7084941401521563</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>16.84372529082318</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.44 HKD</v>
+        <v>17.46 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.3636040195127318E-2</v>
+        <v>2.3636229852552898E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.14 HKD</v>
+        <v>17.16 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.981040211342852E-2</v>
+        <v>2.981064416844759E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>16.84 HKD</v>
+        <v>16.86 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.6016451160631256E-2</v>
+        <v>3.6016747100256985E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.55 HKD</v>
+        <v>16.57 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.2253127247448757E-2</v>
+        <v>4.2253478581955356E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.27 HKD</v>
+        <v>16.29 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.8519305373386744E-2</v>
+        <v>4.8519713635444148E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>16.893862419523156</v>
+        <v>16.914294180464442</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.59052655800000009</v>
+        <v>0.59124560039999985</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,15 +6566,15 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>1.0805759528911842</v>
+        <v>1.0818916937601135</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>7.7851900550797977</v>
+        <v>7.7946056131172563</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>8.8657660079709828</v>
+        <v>8.8764973068773703</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,15 +6587,15 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>1.2424702089992223</v>
+        <v>1.2439830770470757</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>9.7581876791469533</v>
+        <v>9.769989418318815</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>11.000657888146176</v>
+        <v>11.013972495365891</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,15 +6634,15 @@
       </c>
       <c r="C144" s="337">
         <f>Scenarios!C66</f>
-        <v>1.4247062197805911</v>
+        <v>1.4264409837225129</v>
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>12.108851467355422</v>
+        <v>12.123496144357683</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>13.533557687136012</v>
+        <v>13.549937128080195</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,15 +6655,15 @@
       </c>
       <c r="C145" s="337">
         <f>Scenarios!C67</f>
-        <v>1.5426769511069494</v>
+        <v>1.5445553596599959</v>
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>13.694212113010874</v>
+        <v>13.710774155557695</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>15.236889064117824</v>
+        <v>15.255329515217692</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.65614062000000006</v>
+        <v>0.65693955599999987</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.65614062000000006</v>
+        <v>0.65693955599999987</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10216,11 +10216,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.282534036682854</v>
+        <v>13.298707238416849</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7064163577110023</v>
+        <v>1.7084941401521563</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6704979282.6390257</v>
+        <v>6704814989.3068295</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10478,11 +10478,11 @@
       </c>
       <c r="C73" s="289">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-984044490.93178499</v>
+        <v>-984126637.59788287</v>
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-964769732.77048731</v>
+        <v>-964851879.43658531</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10494,11 +10494,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7745206926609924</v>
+        <v>8.7737882690134956</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9498234188842432</v>
+        <v>8.9490614385516185</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10511,7 +10511,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1929539465.5409746</v>
+        <v>1929703758.8731706</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10626,11 +10626,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>309631070.75467616</v>
+        <v>310008086.59793305</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.25094892352797171</v>
+        <v>0.25125448627329861</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10643,11 +10643,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7332348772.6632099</v>
+        <v>7341096970.2289543</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.9427015090787307</v>
+        <v>5.9497917237544824</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10660,11 +10660,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>638160775.47731221</v>
+        <v>638937818.69301283</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.51721475901458314</v>
+        <v>0.51784453482500004</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10677,11 +10677,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>8280140618.8951979</v>
+        <v>8290042875.5199003</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.7108651916212851</v>
+        <v>6.7188907448527804</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11162,36 +11162,36 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-2579686.0362541508</v>
+        <v>-2578700.2762609757</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>42410644.588885337</v>
+        <v>42415315.083942771</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40878122.304199807</v>
+        <v>40883124.959752962</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>17664897.311594129</v>
+        <v>17668187.630883768</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>5038832.860088177</v>
+        <v>5040921.2181532532</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
-        <v>-4719138.639649488</v>
+        <v>-4717653.2764006034</v>
       </c>
       <c r="L10" s="270">
         <f t="shared" si="6"/>
-        <v>-6435990.5676699448</v>
+        <v>-6434883.2957109343</v>
       </c>
       <c r="M10" s="270">
         <f t="shared" si="6"/>
-        <v>7528087.9448911706</v>
+        <v>7528772.9050722905</v>
       </c>
       <c r="N10" s="270">
         <f t="shared" si="6"/>
@@ -11217,36 +11217,36 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>1558270611.4393184</v>
+        <v>1558271597.1993115</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1371963844.1288862</v>
+        <v>1371968514.6239438</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>1481862790.6241994</v>
+        <v>1481867793.2797527</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>1407192396.311594</v>
+        <v>1407195686.6308837</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>1240493150.8600881</v>
+        <v>1240495239.2181532</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
-        <v>1157436552.3603506</v>
+        <v>1157438037.7235994</v>
       </c>
       <c r="L11" s="271">
         <f t="shared" si="7"/>
-        <v>999249824.01233208</v>
+        <v>999250931.28429115</v>
       </c>
       <c r="M11" s="271">
         <f t="shared" si="7"/>
-        <v>939475394.71489024</v>
+        <v>939476079.67507136</v>
       </c>
       <c r="N11" s="271">
         <f t="shared" si="7"/>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-389567652.8598296</v>
+        <v>-389567899.29982787</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11384,38 +11384,38 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>1109897480.5794888</v>
+        <v>1109898219.8994837</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207893917.1288862</v>
+        <v>1207898587.6239438</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>1497836733.6241994</v>
+        <v>1497841736.2797527</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>1418627873.311594</v>
+        <v>1418631163.6308837</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>1235040338.8600881</v>
+        <v>1235042427.2181532</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
-        <v>1149266001.3603506</v>
+        <v>1149267486.7235994</v>
       </c>
       <c r="L14" s="271">
         <f t="shared" si="8"/>
-        <v>975077748.89233208</v>
+        <v>975078856.16429114</v>
       </c>
       <c r="M14" s="271">
         <f t="shared" si="8"/>
-        <v>950271241.08489025</v>
+        <v>950271926.04507136</v>
       </c>
       <c r="N14" s="271">
         <f t="shared" si="8"/>
@@ -11602,38 +11602,38 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>1109897480.5794888</v>
+        <v>1109898219.8994837</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207893917.1288862</v>
+        <v>1207898587.6239438</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>1497836733.6241994</v>
+        <v>1497841736.2797527</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>1418627873.311594</v>
+        <v>1418631163.6308837</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>1235040338.8600881</v>
+        <v>1235042427.2181532</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
-        <v>1149266001.3603506</v>
+        <v>1149267486.7235994</v>
       </c>
       <c r="L19" s="275">
         <f t="shared" si="9"/>
-        <v>975077748.89233208</v>
+        <v>975078856.16429114</v>
       </c>
       <c r="M19" s="275">
         <f t="shared" si="9"/>
-        <v>950271241.08489025</v>
+        <v>950271926.04507136</v>
       </c>
       <c r="N19" s="275">
         <f t="shared" si="9"/>
@@ -12341,31 +12341,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.6725381248539046E-2</v>
+        <v>7.6725120057768201E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.3983993938160236E-2</v>
+        <v>-4.3983845452058759E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.1264488281585674E-3</v>
+        <v>-8.1264298268131328E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3956808598413681E-3</v>
+        <v>4.3956734597681672E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.0591783051415337E-3</v>
+        <v>7.0591692459576472E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4190222043713551E-2</v>
+        <v>2.4190195238480035E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491356166146636E-2</v>
+        <v>-1.1491347787943539E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12479,36 +12479,36 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>11577236.793245848</v>
+        <v>11578222.553239023</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54852527.588885337</v>
+        <v>54857198.083942771</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>58753579.304199807</v>
+        <v>58758581.959752962</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>38643083.311594129</v>
+        <v>38646373.630883768</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>24526675.860088177</v>
+        <v>24528764.218153253</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
-        <v>17444816.360350512</v>
+        <v>17446301.723599397</v>
       </c>
       <c r="L46" s="278">
         <f t="shared" si="17"/>
-        <v>13004331.432330055</v>
+        <v>13005438.704289066</v>
       </c>
       <c r="M46" s="278">
         <f t="shared" si="17"/>
-        <v>8044499.9448911706</v>
+        <v>8045184.9050722905</v>
       </c>
       <c r="N46" s="278">
         <f t="shared" si="17"/>
@@ -12591,36 +12591,36 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-2579686.0362541508</v>
+        <v>-2578700.2762609757</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42410644.588885337</v>
+        <v>42415315.083942771</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40878122.304199807</v>
+        <v>40883124.959752962</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>17664897.311594129</v>
+        <v>17668187.630883768</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>5038832.860088177</v>
+        <v>5040921.2181532532</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
-        <v>-4719138.639649488</v>
+        <v>-4717653.2764006034</v>
       </c>
       <c r="L48" s="271">
         <f t="shared" si="18"/>
-        <v>-6435990.5676699448</v>
+        <v>-6434883.2957109343</v>
       </c>
       <c r="M48" s="271">
         <f t="shared" si="18"/>
-        <v>7528087.9448911706</v>
+        <v>7528772.9050722905</v>
       </c>
       <c r="N48" s="271">
         <f t="shared" si="18"/>
@@ -13556,38 +13556,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0924549859396393E-4</v>
+        <v>2.0916554086330714E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.4400451636271991E-3</v>
+        <v>3.4404240004520061E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4442562483004073E-3</v>
+        <v>3.4446777556171775E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.6161398399178748E-3</v>
+        <v>1.6164408672035837E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8170722049399931E-4</v>
+        <v>4.8190686536948076E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2387977488373659E-4</v>
+        <v>5.2371488213023528E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.2785087231509987E-4</v>
+        <v>7.2772565012081886E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.1956411795801368E-4</v>
+        <v>9.1964778658800296E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13613,38 +13613,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639565685613444</v>
+        <v>0.12639573681386509</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.11128379755642379</v>
+        <v>0.1112841763932486</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12485688891847418</v>
+        <v>0.12485731042579097</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12874231046992926</v>
+        <v>0.12874261149721497</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11858986482282317</v>
+        <v>0.11859006446769867</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12848904149545937</v>
+        <v>0.12848920638821285</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300589216546909</v>
+        <v>0.11300601738766337</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11475793973296147</v>
+        <v>0.11475802340159147</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1598914214033609E-2</v>
+        <v>3.1598934203466274E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13785,38 +13785,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.0026867009470116E-2</v>
+        <v>9.002692697776811E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.7975630129491217E-2</v>
+        <v>9.7976008966316031E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12620280086076738</v>
+        <v>0.12620322236808418</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12978852826798204</v>
+        <v>0.12978882929526778</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11806858162385032</v>
+        <v>0.1180687812687258</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758201444128617</v>
+        <v>0.12758217933403967</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11027225454173845</v>
+        <v>0.11027237976393273</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607666409132612</v>
+        <v>0.11607674775995612</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14008,38 +14008,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.0026867009470116E-2</v>
+        <v>9.002692697776811E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.7975630129491217E-2</v>
+        <v>9.7976008966316031E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12620280086076738</v>
+        <v>0.12620322236808418</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12978852826798204</v>
+        <v>0.12978882929526778</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11806858162385032</v>
+        <v>0.1180687812687258</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758201444128617</v>
+        <v>0.12758217933403967</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11027225454173845</v>
+        <v>0.11027237976393273</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607666409132612</v>
+        <v>0.11607674775995612</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14077,12 +14077,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.65614062000000006</v>
+        <v>0.65693955599999987</v>
       </c>
       <c r="E88" s="238"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.65614062000000006</v>
+        <v>0.65693955599999987</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14133,12 +14133,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>809573198.72142005</v>
+        <v>810558958.71459579</v>
       </c>
       <c r="E89" s="238"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>809573198.72142005</v>
+        <v>810558958.71459579</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.72941259250244783</v>
+        <v>0.73030026013376526</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.67023534702926735</v>
+        <v>0.67104885047431473</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14264,12 +14264,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6187113035204579E-2</v>
+        <v>5.6850538499999985E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.6187113035204579E-2</v>
+        <v>5.6850538499999985E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14401,38 +14401,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.13579568303326961</v>
+        <v>0.13579253502507194</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162700616175692E-2</v>
+        <v>-7.4162674399295581E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.3063386718351202E-2</v>
+        <v>5.306447948803017E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.13438143155883298</v>
+        <v>0.13438217426597832</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1759094120849021E-2</v>
+        <v>7.1759523004710557E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830548532182309</v>
+        <v>0.15830568827791613</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3625327106711538E-2</v>
+        <v>6.3625730236680056E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35102229195659951</v>
+        <v>0.35102327697066049</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -15012,31 +15012,31 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4674126650236874</v>
+        <v>1.4674069910841121</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.570951064410445</v>
+        <v>1.5709458175763662</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.4269994006774711</v>
+        <v>1.4269960909492099</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.657702596896256</v>
+        <v>1.6576997938536142</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.5825799143515396</v>
+        <v>1.5825778689564769</v>
       </c>
       <c r="L113" s="254">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3992838224130759</v>
+        <v>1.3992822334259603</v>
       </c>
       <c r="M113" s="254">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.0454386379575309</v>
+        <v>1.0454378844007655</v>
       </c>
       <c r="N113" s="254">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15120,36 +15120,36 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639565685613444</v>
+        <v>0.12639573681386509</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.11128379755642379</v>
+        <v>0.1112841763932486</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12485688891847418</v>
+        <v>0.12485731042579097</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12874231046992926</v>
+        <v>0.12874261149721497</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11858986482282317</v>
+        <v>0.11859006446769867</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12848904149545937</v>
+        <v>0.12848920638821285</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300589216546909</v>
+        <v>0.11300601738766337</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11475793973296147</v>
+        <v>0.11475802340159147</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15285,38 +15285,38 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.10095606522098918</v>
+        <v>0.10095612908566674</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.8885762403476218E-2</v>
+        <v>8.8886064991999802E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11047007144794031</v>
+        <v>0.1104704443864606</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11113478825265029</v>
+        <v>0.11113504810975192</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11165867920349216</v>
+        <v>0.11165886717978457</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11541875125504024</v>
+        <v>0.11541889937440886</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.10956727122330247</v>
+        <v>0.10956739263514978</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176208818189899</v>
+        <v>0.11176216966628974</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15406,50 +15406,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.98371511002885004</v>
+        <v>0.98491356636978489</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0705704971699164</v>
+        <v>1.0718781996582225</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3275502044144492</v>
+        <v>1.3291711076628319</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2573464656898672</v>
+        <v>1.2588803673021025</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0946306880501193</v>
+        <v>1.0959653955653603</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0186078901542708</v>
+        <v>1.0198494949962991</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.86422280599961043</v>
+        <v>0.86527609153523721</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.84223650818002405</v>
+        <v>0.84326264780107263</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.61582818190800903</v>
+        <v>0.61657803230492669</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.50712343606223498</v>
+        <v>0.50774092438282348</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.47809296229138465</v>
+        <v>0.47867510225845622</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15463,50 +15463,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.3598012371917214E-2</v>
+        <v>9.4703227535556239E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10186208346050585</v>
+        <v>0.10306521150559832</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.12631305465408652</v>
+        <v>0.12780491419834922</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.11963334592672381</v>
+        <v>0.12104618916366369</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10415134995719499</v>
+        <v>0.10538128803513079</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.6917972421909693E-2</v>
+        <v>9.8062451441951831E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.2228620932408222E-2</v>
+        <v>8.3199624186080498E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.0136680131305815E-2</v>
+        <v>8.1082946903949293E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.8594498754330072E-2</v>
+        <v>5.9286349260089105E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.8251516276140341E-2</v>
+        <v>4.8821242729117642E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.5489339894518047E-2</v>
+        <v>4.6026452140236172E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15520,43 +15520,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12366614887609742</v>
+        <v>0.12497415621997922</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12557000925157025</v>
+        <v>0.12689815358019263</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1072849050708837</v>
+        <v>0.10841964925913344</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10050235482145727</v>
+        <v>0.10156536049745345</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5853383952567303E-2</v>
+        <v>9.6867217821296384E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6728403687320849E-2</v>
+        <v>8.7645723341705964E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1463612557640471E-2</v>
+        <v>7.2219477690461678E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0674257421336345E-2</v>
+        <v>7.142177360560048E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8585293044006321E-2</v>
+        <v>4.9099175951202542E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7419455591267097E-2</v>
+        <v>4.7921007525405498E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>1109897480.5794888</v>
+        <v>1109898219.8994837</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>6704979282.6390257</v>
+        <v>6704814989.3068295</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>11998891681.940418</v>
+        <v>11998899674.589012</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-2579686.0362541508</v>
+        <v>-2578700.2762609757</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16404,14 +16404,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>7005399370.6890259</v>
+        <v>7005235077.3568296</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>7005399370.6890259</v>
+        <v>7005235077.3568296</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>19004291052.629444</v>
+        <v>19004134751.945843</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.2089673445653419</v>
+        <v>6.2163817723061836</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-2579686.0362541508</v>
+        <v>-2578700.2762609757</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0935677000000001</v>
+        <v>1.0948992599999998</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>20782478856.554562</v>
+        <v>20807613076.845783</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>16.84372529082318</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>16.895169682747269</v>
+        <v>16.915603035450467</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>1561003787.9026315</v>
+        <v>1561004773.6626246</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16723,11 +16723,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>1111844389.7279143</v>
+        <v>1111845129.0479093</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>1.7541342173414964E-3</v>
+        <v>1.7541330488861639E-3</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>1017706535.2200588</v>
+        <v>1017707211.9431663</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>1563741750.381357</v>
+        <v>1563742736.14135</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16772,11 +16772,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>1113794708.0734103</v>
+        <v>1113795447.3934052</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>1.7541288722724424E-3</v>
+        <v>1.7541277058668037E-3</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>933173202.41371965</v>
+        <v>933173821.83990502</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>1566484507.2561986</v>
+        <v>1566485493.0161917</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16821,11 +16821,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>1115748441.5857587</v>
+        <v>1115749180.9057536</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>1.7541235365787777E-3</v>
+        <v>1.754122372219058E-3</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>855661421.96043754</v>
+        <v>855661988.94092751</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>1566484507.2561986</v>
+        <v>1566485493.0161917</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>12062145314.440634</v>
+        <v>12062153307.089228</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18285,7 +18285,7 @@
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>9250393750.9236488</v>
+        <v>9250399880.4424591</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18298,7 +18298,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>12056934910.517864</v>
+        <v>12056942903.166458</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18322,7 +18322,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>12056934910.517864</v>
+        <v>12056942903.166458</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18357,19 +18357,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>11758495520.836269</v>
+        <v>11758503513.484865</v>
       </c>
       <c r="C56" s="118">
-        <v>11878693601.388342</v>
+        <v>11878701594.036936</v>
       </c>
       <c r="D56" s="118">
-        <v>11998891681.940416</v>
+        <v>11998899674.589012</v>
       </c>
       <c r="E56" s="118">
-        <v>12119089762.492491</v>
+        <v>12119097755.141087</v>
       </c>
       <c r="F56" s="118">
-        <v>12239287843.044565</v>
+        <v>12239295835.693161</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18383,19 +18383,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>11542854113.163902</v>
+        <v>11542862105.812494</v>
       </c>
       <c r="C57" s="118">
-        <v>11769772686.288527</v>
+        <v>11769780678.937115</v>
       </c>
       <c r="D57" s="118">
-        <v>11998891681.940418</v>
+        <v>11998899674.589012</v>
       </c>
       <c r="E57" s="118">
-        <v>12230211100.119581</v>
+        <v>12230219092.768173</v>
       </c>
       <c r="F57" s="118">
-        <v>12463730940.826014</v>
+        <v>12463738933.474606</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18409,19 +18409,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>11349418342.437199</v>
+        <v>11349426335.085793</v>
       </c>
       <c r="C58" s="118">
-        <v>11671070895.94635</v>
+        <v>11671078888.594944</v>
       </c>
       <c r="D58" s="118">
-        <v>11998891681.940416</v>
+        <v>11998899674.589012</v>
       </c>
       <c r="E58" s="118">
-        <v>12332941123.92128</v>
+        <v>12332949116.569874</v>
       </c>
       <c r="F58" s="118">
-        <v>12673279645.390841</v>
+        <v>12673287638.039433</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18435,19 +18435,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>11175901587.00272</v>
+        <v>11175909579.651312</v>
       </c>
       <c r="C59" s="118">
-        <v>11581629456.64315</v>
+        <v>11581637449.29174</v>
       </c>
       <c r="D59" s="118">
-        <v>11998891681.940418</v>
+        <v>11998899674.589012</v>
       </c>
       <c r="E59" s="118">
-        <v>12427913502.905006</v>
+        <v>12427921495.5536</v>
       </c>
       <c r="F59" s="118">
-        <v>12868922371.849535</v>
+        <v>12868930364.498127</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18461,19 +18461,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>11020252689.679344</v>
+        <v>11020260682.327938</v>
       </c>
       <c r="C60" s="118">
-        <v>11500579548.258554</v>
+        <v>11500587540.907148</v>
       </c>
       <c r="D60" s="118">
-        <v>11998891681.940418</v>
+        <v>11998899674.589012</v>
       </c>
       <c r="E60" s="118">
-        <v>12515714054.642822</v>
+        <v>12515722047.291412</v>
       </c>
       <c r="F60" s="118">
-        <v>13051581942.547813</v>
+        <v>13051589935.196405</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18487,19 +18487,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>10880631710.844641</v>
+        <v>10880639703.493235</v>
       </c>
       <c r="C61" s="118">
-        <v>11427133864.688074</v>
+        <v>11427141857.336666</v>
       </c>
       <c r="D61" s="118">
-        <v>11998891681.940416</v>
+        <v>11998899674.58901</v>
       </c>
       <c r="E61" s="118">
-        <v>12596884358.766565</v>
+        <v>12596892351.415157</v>
       </c>
       <c r="F61" s="118">
-        <v>13222119939.904552</v>
+        <v>13222127932.553146</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18513,19 +18513,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>10755388178.343037</v>
+        <v>10755396170.991627</v>
       </c>
       <c r="C62" s="118">
-        <v>11360578966.075008</v>
+        <v>11360586958.723598</v>
       </c>
       <c r="D62" s="118">
-        <v>11998891681.940416</v>
+        <v>11998899674.589012</v>
       </c>
       <c r="E62" s="118">
-        <v>12671925097.590347</v>
+        <v>12671933090.238941</v>
       </c>
       <c r="F62" s="118">
-        <v>13381340770.388657</v>
+        <v>13381348763.037249</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18539,19 +18539,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>10643041577.105896</v>
+        <v>10643049569.75449</v>
       </c>
       <c r="C63" s="118">
-        <v>11300268348.567514</v>
+        <v>11300276341.216106</v>
       </c>
       <c r="D63" s="118">
-        <v>11998891681.940414</v>
+        <v>11998899674.58901</v>
       </c>
       <c r="E63" s="118">
-        <v>12741299144.466337</v>
+        <v>12741307137.114931</v>
       </c>
       <c r="F63" s="118">
-        <v>13529995458.804016</v>
+        <v>13530003451.45261</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18565,19 +18565,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>10542263847.849697</v>
+        <v>10542271840.498291</v>
       </c>
       <c r="C64" s="118">
-        <v>11245616164.281548</v>
+        <v>11245624156.930141</v>
       </c>
       <c r="D64" s="118">
-        <v>11998891681.940414</v>
+        <v>11998899674.589008</v>
       </c>
       <c r="E64" s="118">
-        <v>12805434418.923777</v>
+        <v>12805442411.572369</v>
       </c>
       <c r="F64" s="118">
-        <v>13668785190.779915</v>
+        <v>13668793183.428505</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18591,19 +18591,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>10451863687.967707</v>
+        <v>10451871680.616301</v>
       </c>
       <c r="C65" s="118">
-        <v>11196091530.466347</v>
+        <v>11196099523.114941</v>
       </c>
       <c r="D65" s="118">
-        <v>11998891681.940414</v>
+        <v>11998899674.589008</v>
       </c>
       <c r="E65" s="118">
-        <v>12864726526.202505</v>
+        <v>12864734518.851097</v>
       </c>
       <c r="F65" s="118">
-        <v>13798364620.176178</v>
+        <v>13798372612.82477</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18617,19 +18617,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>10121745983.86895</v>
+        <v>10121753976.51754</v>
       </c>
       <c r="C66" s="281">
-        <v>11010037556.034693</v>
+        <v>11010045548.683287</v>
       </c>
       <c r="D66" s="118">
-        <v>11998891681.940414</v>
+        <v>11998899674.589012</v>
       </c>
       <c r="E66" s="118">
-        <v>13100416217.163977</v>
+        <v>13100424209.812569</v>
       </c>
       <c r="F66" s="118">
-        <v>14328135235.973475</v>
+        <v>14328143228.622068</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18652,19 +18652,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>9930015147.7140217</v>
+        <v>9930023140.3626118</v>
       </c>
       <c r="C67" s="281">
-        <v>10896351370.112473</v>
+        <v>10896359362.761065</v>
       </c>
       <c r="D67" s="118">
-        <v>11998891681.940414</v>
+        <v>11998899674.58901</v>
       </c>
       <c r="E67" s="118">
-        <v>13259578524.967102</v>
+        <v>13259586517.615696</v>
       </c>
       <c r="F67" s="118">
-        <v>14703956627.885715</v>
+        <v>14703964620.534307</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18687,19 +18687,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>9818658764.5929585</v>
+        <v>9818666757.2415466</v>
       </c>
       <c r="C68" s="281">
-        <v>10826884706.425098</v>
+        <v>10826892699.073692</v>
       </c>
       <c r="D68" s="118">
-        <v>11998891681.940414</v>
+        <v>11998899674.589008</v>
       </c>
       <c r="E68" s="118">
-        <v>13367061546.909534</v>
+        <v>13367069539.558128</v>
       </c>
       <c r="F68" s="118">
-        <v>14970565825.163088</v>
+        <v>14970573817.811684</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18722,19 +18722,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>9753983492.1616364</v>
+        <v>9753991484.8102226</v>
       </c>
       <c r="C69" s="281">
-        <v>10784437883.843193</v>
+        <v>10784445876.491787</v>
       </c>
       <c r="D69" s="118">
-        <v>11998891681.940414</v>
+        <v>11998899674.58901</v>
       </c>
       <c r="E69" s="118">
-        <v>13439645314.796135</v>
+        <v>13439653307.444729</v>
       </c>
       <c r="F69" s="118">
-        <v>15159699455.133474</v>
+        <v>15159707447.782068</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18831,23 +18831,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>16.84372529082318</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>16.84372529082318</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>16.84372529082318</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>16.84372529082318</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>16.84372529082318</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18862,23 +18862,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>16.630659363375887</v>
+        <v>16.650770640581737</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>16.737192327099532</v>
+        <v>16.757433321956306</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>16.843725290823176</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>16.950258254546828</v>
+        <v>16.970758684705459</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>17.056791218270469</v>
+        <v>17.077421366080035</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>16.439533863240108</v>
+        <v>16.459412420449777</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>16.640654446928909</v>
+        <v>16.660777894440677</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>16.84372529082318</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>17.048746394922919</v>
+        <v>17.069366747120398</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>17.255717759228123</v>
+        <v>17.276590125809214</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18924,23 +18924,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>16.268089478678945</v>
+        <v>16.287759280194109</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>16.553173896476803</v>
+        <v>16.573190825113009</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>16.843725290823176</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>17.139797215774038</v>
+        <v>17.160528434112695</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>17.441443225385381</v>
+        <v>17.462541736723416</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18955,23 +18955,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>16.114299550193877</v>
+        <v>16.133782092596341</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>16.473900903389779</v>
+        <v>16.493821306912192</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>16.84372529082318</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>17.223972345348081</v>
+        <v>17.244806057785212</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>17.614843660607718</v>
+        <v>17.636153309384728</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18986,23 +18986,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>15.976346113200407</v>
+        <v>15.995660679465171</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>16.402065422239975</v>
+        <v>16.421898356780563</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>16.84372529082318</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>17.30179100060646</v>
+        <v>17.322719467313117</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>17.776736973126518</v>
+        <v>17.798243747933505</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -19017,23 +19017,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>15.852598407705116</v>
+        <v>15.871762295146127</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>16.336969654424593</v>
+        <v>16.356723326455334</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>16.843725290823176</v>
+        <v>16.864096003330882</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>17.373733189907107</v>
+        <v>17.394749255526563</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>17.92788679351019</v>
+        <v>17.949577612757075</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19049,23 +19049,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>15.741593600945043</v>
+        <v>15.760622325688319</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>16.277981269859627</v>
+        <v>16.297663115908897</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>16.843725290823176</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>17.440242673837229</v>
+        <v>17.461339723348601</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>18.069006076614407</v>
+        <v>18.090868726825764</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19080,23 +19080,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>15.642019495109919</v>
+        <v>15.66092697551106</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>16.224527264624552</v>
+        <v>16.244144023514419</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>16.843725290823176</v>
+        <v>16.864096003330882</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>17.501729702459127</v>
+        <v>17.522901620374007</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>18.20076046450118</v>
+        <v>18.222783542706832</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19112,23 +19112,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>15.552699015733786</v>
+        <v>15.571497736908119</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>16.176088394892083</v>
+        <v>16.195646173198142</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>16.843725290823176</v>
+        <v>16.864096003330882</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>17.558573545853278</v>
+        <v>17.579814678493609</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>18.32377142618952</v>
+        <v>18.345944286138124</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19144,23 +19144,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>15.472576297391809</v>
+        <v>15.491277458802045</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>16.132194133075014</v>
+        <v>16.151698464444717</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>16.843725290823176</v>
+        <v>16.864096003330882</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>17.611124833567789</v>
+        <v>17.632429954192279</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>18.43861918904728</v>
+        <v>18.460931890989308</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19176,23 +19176,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>15.179989117681819</v>
+        <v>15.198334016388777</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>15.967292320851978</v>
+        <v>15.986595862954511</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>16.843725290823176</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>17.820019361516241</v>
+        <v>17.841578838224617</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>18.908161078030567</v>
+        <v>18.931045507902834</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19208,23 +19208,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>15.01005583655968</v>
+        <v>15.028193819535849</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>15.866530925452787</v>
+        <v>15.8857117775347</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>16.843725290823176</v>
+        <v>16.864096003330882</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>17.961086775284265</v>
+        <v>17.982818019799499</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>19.241255970455338</v>
+        <v>19.264545986406048</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19240,23 +19240,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>14.911359372614957</v>
+        <v>14.929377179891414</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>15.804961809468415</v>
+        <v>15.824067693194847</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>16.843725290823176</v>
+        <v>16.864096003330882</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>18.056350233942744</v>
+        <v>18.078197474030095</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>19.477554818252955</v>
+        <v>19.50113255858852</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19272,23 +19272,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>14.854036922704802</v>
+        <v>14.87198493249053</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>15.767340694476124</v>
+        <v>15.786400769633156</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>16.843725290823176</v>
+        <v>16.864096003330882</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>18.120682075813036</v>
+        <v>18.142607648231674</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>19.645186165176401</v>
+        <v>19.668968018340372</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>17.441443225385381</v>
+        <v>17.462541736723416</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>17.139797215774038</v>
+        <v>17.160528434112695</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>16.843725290823176</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>16.553173896476803</v>
+        <v>16.573190825113009</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>16.268089478678945</v>
+        <v>16.287759280194109</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>1207893917.1288862</v>
+        <v>1207898587.6239438</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>1109897480.5794888</v>
+        <v>1109898219.8994837</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C14" s="252">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7258288658287211E-2</v>
+        <v>-7.7257574792176764E-2</v>
       </c>
       <c r="D14" s="465"/>
       <c r="E14" s="465"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>17.139797215774038</v>
+        <v>17.160528434112695</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>16.843725290823176</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>16.553173896476803</v>
+        <v>16.573190825113009</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>16.830301827226759</v>
+        <v>16.850656194932778</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19917,7 +19917,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>17.441443225385381</v>
+        <v>17.462541736723416</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19940,7 +19940,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>16.268089478678945</v>
+        <v>16.287759280194109</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.59052655800000009</v>
+        <v>0.59124560039999985</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.51</v>
+        <v>10.4</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.21998237366068735</v>
+        <v>0.22497970185102439</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20005,7 +20005,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>16.84372529082318</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20016,7 +20016,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.6016451160631194E-2</v>
+        <v>3.6016747100256985E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>16.893862419523156</v>
+        <v>16.914294180464442</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>16.895169682747269</v>
+        <v>16.915603035450467</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.39723687958213555</v>
+        <v>0.39723151750623564</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.59052655800000009</v>
+        <v>0.59124560039999985</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20265,15 +20265,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.0805759528911842</v>
+        <v>1.0818916937601135</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>7.7851900550797977</v>
+        <v>7.7946056131172563</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>8.8657660079709828</v>
+        <v>8.8764973068773703</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.47520787207753135</v>
+        <v>0.4752073475741313</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20290,15 +20290,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2424702089992223</v>
+        <v>1.2439830770470757</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>9.7581876791469533</v>
+        <v>9.769989418318815</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>11.000657888146176</v>
+        <v>11.013972495365891</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34883701459333427</v>
+        <v>0.34883641150768585</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20336,15 +20336,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4247062197805911</v>
+        <v>1.4264409837225129</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>12.108851467355422</v>
+        <v>12.123496144357683</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>13.533557687136012</v>
+        <v>13.549937128080195</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19890683663339503</v>
+        <v>0.19890614509176441</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20361,15 +20361,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5426769511069494</v>
+        <v>1.5445553596599959</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>13.694212113010874</v>
+        <v>13.710774155557695</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>15.236889064117824</v>
+        <v>15.255329515217692</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>9.8081380933378148E-2</v>
+        <v>9.8080632129646239E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20488,7 +20488,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>10.51</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20506,14 +20506,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12967.66891</v>
+        <v>12831.946400000001</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.21998237366068735</v>
+        <v>0.22497970185102439</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0935677000000001</v>
+        <v>1.0948992599999998</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>16.893862419523156</v>
+        <v>16.914294180464442</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20643,7 +20643,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>8.8657660079709828</v>
+        <v>8.8764973068773703</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>11.000657888146176</v>
+        <v>11.013972495365891</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>13.533557687136012</v>
+        <v>13.549937128080195</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>15.236889064117824</v>
+        <v>15.255329515217692</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>11577236.793245848</v>
+        <v>11578222.553239023</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-2579686.0362541508</v>
+        <v>-2578700.2762609757</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-389567652.8598296</v>
+        <v>-389567899.29982787</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20959,7 +20959,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>1207893917.1288862</v>
+        <v>1207898587.6239438</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>1109897480.5794888</v>
+        <v>1109898219.8994837</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.3598012371917214E-2</v>
+        <v>9.4703227535556239E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20995,14 +20995,14 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.6187113035204579E-2</v>
+        <v>5.6850538499999985E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>0.72941259250244783</v>
+        <v>0.73030026013376526</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21022,11 +21022,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095606522098918</v>
+        <v>0.10095612908566674</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>8.8885762403476218E-2</v>
+        <v>8.8886064991999802E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21036,11 +21036,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639565685613444</v>
+        <v>0.12639573681386509</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128379755642379</v>
+        <v>0.1112841763932486</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25094892352797171</v>
+        <v>-0.25125448627329861</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>6704979282.6390257</v>
+        <v>6704814989.3068295</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9427015090787307</v>
+        <v>5.9497917237544824</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.51721475901458314</v>
+        <v>0.51784453482500004</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>6.2089673445653419</v>
+        <v>6.2163817723061836</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.7064163577110023</v>
+        <v>1.7084941401521563</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>16.84372529082318</v>
+        <v>16.864096003330886</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21464,7 +21464,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.44 HKD</v>
+        <v>17.46 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.14 HKD</v>
+        <v>17.16 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>16.84 HKD</v>
+        <v>16.86 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.55 HKD</v>
+        <v>16.57 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.27 HKD</v>
+        <v>16.29 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>16.893862419523156</v>
+        <v>16.914294180464442</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C136" s="410">
         <f>Scenarios!C58</f>
-        <v>0.59052655800000009</v>
+        <v>0.59124560039999985</v>
       </c>
       <c r="D136" s="347" t="str">
         <f>Market_currency</f>
@@ -21678,15 +21678,15 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>1.0805759528911842</v>
+        <v>1.0818916937601135</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>7.7851900550797977</v>
+        <v>7.7946056131172563</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>8.8657660079709828</v>
+        <v>8.8764973068773703</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21699,15 +21699,15 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>1.2424702089992223</v>
+        <v>1.2439830770470757</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>9.7581876791469533</v>
+        <v>9.769989418318815</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>11.000657888146176</v>
+        <v>11.013972495365891</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21739,15 +21739,15 @@
       </c>
       <c r="C144" s="413">
         <f>Scenarios!C66</f>
-        <v>1.4247062197805911</v>
+        <v>1.4264409837225129</v>
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>12.108851467355422</v>
+        <v>12.123496144357683</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>13.533557687136012</v>
+        <v>13.549937128080195</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21760,15 +21760,15 @@
       </c>
       <c r="C145" s="413">
         <f>Scenarios!C67</f>
-        <v>1.5426769511069494</v>
+        <v>1.5445553596599959</v>
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>13.694212113010874</v>
+        <v>13.710774155557695</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>15.236889064117824</v>
+        <v>15.255329515217692</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0C2BC7-D78C-4417-B940-8429A333C3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B363DE7-7AFE-4E37-8250-08F66E05AB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4972,30 +4972,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5005,25 +5005,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5393,7 +5393,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12831.946400000001</v>
+        <v>13078.714599999999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.22497970185102439</v>
+        <v>0.21934387142409759</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0948992599999998</v>
+        <v>1.1013227999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>16.914294180464442</v>
+        <v>17.012853707020131</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>8.8764973068773703</v>
+        <v>8.9282636709273095</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>11.013972495365891</v>
+        <v>11.078200368693507</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>13.549937128080195</v>
+        <v>13.628949317518744</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>15.255329515217692</v>
+        <v>15.34428371927317</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>11578222.553239023</v>
+        <v>11582977.929449307</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-2578700.2762609757</v>
+        <v>-2573944.9000506923</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-389567899.29982787</v>
+        <v>-389569088.14388049</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>1207898587.6239438</v>
+        <v>1207921118.4237735</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>1109898219.8994837</v>
+        <v>1109901786.4316416</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.4703227535556239E-2</v>
+        <v>9.3461795026699143E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5894,14 +5894,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6850538499999985E-2</v>
+        <v>5.6105123773584897E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.73030026013376526</v>
+        <v>0.73458241521182999</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5921,11 +5921,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095612908566674</v>
+        <v>0.10095643717340666</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.8886064991999802E-2</v>
+        <v>8.8887524700525647E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5935,11 +5935,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639573681386509</v>
+        <v>0.12639612253563595</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>0.1112841763932486</v>
+        <v>0.11128600392899436</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25125448627329861</v>
+        <v>-0.25272854265612604</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>6704814989.3068295</v>
+        <v>6704022426.6051159</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9497917237544824</v>
+        <v>5.983990441338503</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.51784453482500004</v>
+        <v>0.52088261805763436</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.2163817723061836</v>
+        <v>6.252144516740012</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7084941401521563</v>
+        <v>1.7185175102008612</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.46 HKD</v>
+        <v>17.56 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.3636229852552898E-2</v>
+        <v>2.3637144816192977E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.16 HKD</v>
+        <v>17.26 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.981064416844759E-2</v>
+        <v>2.9811811914266698E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>16.86 HKD</v>
+        <v>16.96 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.6016747100256985E-2</v>
+        <v>3.6018174802351255E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.57 HKD</v>
+        <v>16.67 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.2253478581955356E-2</v>
+        <v>4.2255173526660167E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.29 HKD</v>
+        <v>16.38 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,17 +6445,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.8519713635444148E-2</v>
+        <v>4.8521683217158891E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>16.914294180464442</v>
+        <v>17.012853707020131</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.59124560039999985</v>
+        <v>0.59471431199999991</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,15 +6566,15 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>1.0818916937601135</v>
+        <v>1.0882389211484453</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>7.7946056131172563</v>
+        <v>7.8400247497788644</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>8.8764973068773703</v>
+        <v>8.9282636709273095</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,15 +6587,15 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>1.2439830770470757</v>
+        <v>1.2512812599454139</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>9.769989418318815</v>
+        <v>9.8269191087480934</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>11.013972495365891</v>
+        <v>11.078200368693507</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,15 +6634,15 @@
       </c>
       <c r="C144" s="337">
         <f>Scenarios!C66</f>
-        <v>1.4264409837225129</v>
+        <v>1.4348096081716528</v>
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>12.123496144357683</v>
+        <v>12.194139709347091</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>13.549937128080195</v>
+        <v>13.628949317518744</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,15 +6655,15 @@
       </c>
       <c r="C145" s="337">
         <f>Scenarios!C67</f>
-        <v>1.5445553596599959</v>
+        <v>1.5536169359140437</v>
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>13.710774155557695</v>
+        <v>13.790666783359127</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>15.255329515217692</v>
+        <v>15.34428371927317</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,18 +6777,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6805,6 +6793,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.65693955599999987</v>
+        <v>0.66079367999999994</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.65693955599999987</v>
+        <v>0.66079367999999994</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10216,11 +10216,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.298707238416849</v>
+        <v>13.376727912112676</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7084941401521563</v>
+        <v>1.7185175102008612</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6704814989.3068295</v>
+        <v>6704022426.6051159</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10478,11 +10478,11 @@
       </c>
       <c r="C73" s="289">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-984126637.59788287</v>
+        <v>-984522918.94873989</v>
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-964851879.43658531</v>
+        <v>-965248160.78744221</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10494,11 +10494,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7737882690134956</v>
+        <v>8.7702567223115757</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9490614385516185</v>
+        <v>8.9453874132596383</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10511,7 +10511,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1929703758.8731706</v>
+        <v>1930496321.5748844</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10626,11 +10626,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>310008086.59793305</v>
+        <v>311826837.7993772</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.25125448627329861</v>
+        <v>0.25272854265612604</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10643,11 +10643,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7341096970.2289543</v>
+        <v>7383292750.1315403</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.9497917237544824</v>
+        <v>5.983990441338503</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10660,11 +10660,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>638937818.69301283</v>
+        <v>642686330.34684968</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.51784453482500004</v>
+        <v>0.52088261805763436</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10677,11 +10677,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>8290042875.5199003</v>
+        <v>8337805918.2777672</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.7188907448527804</v>
+        <v>6.7576016020522633</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11162,36 +11162,36 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-2578700.2762609757</v>
+        <v>-2573944.9000506923</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>42415315.083942771</v>
+        <v>42437845.883772507</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40883124.959752962</v>
+        <v>40907258.125402227</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>17668187.630883768</v>
+        <v>17684060.36479719</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>5040921.2181532532</v>
+        <v>5050995.6057627723</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
-        <v>-4717653.2764006034</v>
+        <v>-4710487.7786057256</v>
       </c>
       <c r="L10" s="270">
         <f t="shared" si="6"/>
-        <v>-6434883.2957109343</v>
+        <v>-6429541.7371483576</v>
       </c>
       <c r="M10" s="270">
         <f t="shared" si="6"/>
-        <v>7528772.9050722905</v>
+        <v>7532077.2016280871</v>
       </c>
       <c r="N10" s="270">
         <f t="shared" si="6"/>
@@ -11217,36 +11217,36 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>1558271597.1993115</v>
+        <v>1558276352.5755219</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1371968514.6239438</v>
+        <v>1371991045.4237735</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>1481867793.2797527</v>
+        <v>1481891926.4454019</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>1407195686.6308837</v>
+        <v>1407211559.3647971</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>1240495239.2181532</v>
+        <v>1240505313.6057627</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
-        <v>1157438037.7235994</v>
+        <v>1157445203.2213943</v>
       </c>
       <c r="L11" s="271">
         <f t="shared" si="7"/>
-        <v>999250931.28429115</v>
+        <v>999256272.84285367</v>
       </c>
       <c r="M11" s="271">
         <f t="shared" si="7"/>
-        <v>939476079.67507136</v>
+        <v>939479383.97162712</v>
       </c>
       <c r="N11" s="271">
         <f t="shared" si="7"/>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-389567899.29982787</v>
+        <v>-389569088.14388049</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11384,38 +11384,38 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>1109898219.8994837</v>
+        <v>1109901786.4316416</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207898587.6239438</v>
+        <v>1207921118.4237735</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>1497841736.2797527</v>
+        <v>1497865869.4454019</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>1418631163.6308837</v>
+        <v>1418647036.3647971</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>1235042427.2181532</v>
+        <v>1235052501.6057627</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
-        <v>1149267486.7235994</v>
+        <v>1149274652.2213943</v>
       </c>
       <c r="L14" s="271">
         <f t="shared" si="8"/>
-        <v>975078856.16429114</v>
+        <v>975084197.72285366</v>
       </c>
       <c r="M14" s="271">
         <f t="shared" si="8"/>
-        <v>950271926.04507136</v>
+        <v>950275230.34162712</v>
       </c>
       <c r="N14" s="271">
         <f t="shared" si="8"/>
@@ -11602,38 +11602,38 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>1109898219.8994837</v>
+        <v>1109901786.4316416</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207898587.6239438</v>
+        <v>1207921118.4237735</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>1497841736.2797527</v>
+        <v>1497865869.4454019</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>1418631163.6308837</v>
+        <v>1418647036.3647971</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>1235042427.2181532</v>
+        <v>1235052501.6057627</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
-        <v>1149267486.7235994</v>
+        <v>1149274652.2213943</v>
       </c>
       <c r="L19" s="275">
         <f t="shared" si="9"/>
-        <v>975078856.16429114</v>
+        <v>975084197.72285366</v>
       </c>
       <c r="M19" s="275">
         <f t="shared" si="9"/>
-        <v>950271926.04507136</v>
+        <v>950275230.34162712</v>
       </c>
       <c r="N19" s="275">
         <f t="shared" si="9"/>
@@ -12341,31 +12341,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.6725120057768201E-2</v>
+        <v>7.6723860079922351E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.3983845452058759E-2</v>
+        <v>-4.398312915864408E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.1264298268131328E-3</v>
+        <v>-8.1263381642216418E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3956734597681672E-3</v>
+        <v>4.3956377616395474E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.0591692459576472E-3</v>
+        <v>7.0591255441378765E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4190195238480035E-2</v>
+        <v>2.4190065928964534E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491347787943539E-2</v>
+        <v>-1.1491307371068444E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12479,36 +12479,36 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>11578222.553239023</v>
+        <v>11582977.929449307</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54857198.083942771</v>
+        <v>54879728.883772507</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>58758581.959752962</v>
+        <v>58782715.125402227</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>38646373.630883768</v>
+        <v>38662246.36479719</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>24528764.218153253</v>
+        <v>24538838.605762772</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
-        <v>17446301.723599397</v>
+        <v>17453467.221394274</v>
       </c>
       <c r="L46" s="278">
         <f t="shared" si="17"/>
-        <v>13005438.704289066</v>
+        <v>13010780.262851642</v>
       </c>
       <c r="M46" s="278">
         <f t="shared" si="17"/>
-        <v>8045184.9050722905</v>
+        <v>8048489.2016280871</v>
       </c>
       <c r="N46" s="278">
         <f t="shared" si="17"/>
@@ -12591,36 +12591,36 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-2578700.2762609757</v>
+        <v>-2573944.9000506923</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42415315.083942771</v>
+        <v>42437845.883772507</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40883124.959752962</v>
+        <v>40907258.125402227</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>17668187.630883768</v>
+        <v>17684060.36479719</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>5040921.2181532532</v>
+        <v>5050995.6057627723</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
-        <v>-4717653.2764006034</v>
+        <v>-4710487.7786057256</v>
       </c>
       <c r="L48" s="271">
         <f t="shared" si="18"/>
-        <v>-6434883.2957109343</v>
+        <v>-6429541.7371483576</v>
       </c>
       <c r="M48" s="271">
         <f t="shared" si="18"/>
-        <v>7528772.9050722905</v>
+        <v>7532077.2016280871</v>
       </c>
       <c r="N48" s="271">
         <f t="shared" si="18"/>
@@ -13556,38 +13556,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0916554086330714E-4</v>
+        <v>2.0877981909246424E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.4404240004520061E-3</v>
+        <v>3.4422515361977666E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4446777556171775E-3</v>
+        <v>3.4467111368463887E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.6164408672035837E-3</v>
+        <v>1.6178930442071295E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8190686536948076E-4</v>
+        <v>4.8286996642647349E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2371488213023528E-4</v>
+        <v>5.2291942777757633E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.2772565012081886E-4</v>
+        <v>7.2712156936302163E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.1964778658800296E-4</v>
+        <v>9.2005141000075347E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13613,38 +13613,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639573681386509</v>
+        <v>0.12639612253563595</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.1112841763932486</v>
+        <v>0.11128600392899436</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12485731042579097</v>
+        <v>0.12485934380702017</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12874261149721497</v>
+        <v>0.12874406367421853</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11859006446769867</v>
+        <v>0.11859102756875566</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12848920638821285</v>
+        <v>0.12849000184256551</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300601738766337</v>
+        <v>0.11300662146842116</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11475802340159147</v>
+        <v>0.1147584270250042</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1598934203466274E-2</v>
+        <v>3.1599030633908988E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13785,38 +13785,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.002692697776811E-2</v>
+        <v>9.0027216269096252E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.7976008966316031E-2</v>
+        <v>9.7977836502061794E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12620322236808418</v>
+        <v>0.12620525574931338</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12978882929526778</v>
+        <v>0.12979028147227131</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.1180687812687258</v>
+        <v>0.11806974436978279</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758217933403967</v>
+        <v>0.12758297478839234</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11027237976393273</v>
+        <v>0.11027298384469052</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607674775995612</v>
+        <v>0.11607715138336887</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14008,38 +14008,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.002692697776811E-2</v>
+        <v>9.0027216269096252E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.7976008966316031E-2</v>
+        <v>9.7977836502061794E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12620322236808418</v>
+        <v>0.12620525574931338</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12978882929526778</v>
+        <v>0.12979028147227131</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.1180687812687258</v>
+        <v>0.11806974436978279</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758217933403967</v>
+        <v>0.12758297478839234</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11027237976393273</v>
+        <v>0.11027298384469052</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607674775995612</v>
+        <v>0.11607715138336887</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14077,12 +14077,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.65693955599999987</v>
+        <v>0.66079367999999994</v>
       </c>
       <c r="E88" s="238"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.65693955599999987</v>
+        <v>0.66079367999999994</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14133,12 +14133,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>810558958.71459579</v>
+        <v>815314334.92487991</v>
       </c>
       <c r="E89" s="238"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>810558958.71459579</v>
+        <v>815314334.92487991</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.73030026013376526</v>
+        <v>0.73458241521182999</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.67104885047431473</v>
+        <v>0.6749731604898096</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14264,12 +14264,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6850538499999985E-2</v>
+        <v>5.6105123773584897E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.6850538499999985E-2</v>
+        <v>5.6105123773584897E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14401,38 +14401,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.13579253502507194</v>
+        <v>0.13577734911105743</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162674399295581E-2</v>
+        <v>-7.4162547929690459E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.306447948803017E-2</v>
+        <v>5.3069751014776179E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.13438217426597832</v>
+        <v>0.1343857571028626</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1759523004710557E-2</v>
+        <v>7.1761591955451509E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830568827791613</v>
+        <v>0.15830666734620324</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3625730236680056E-2</v>
+        <v>6.3627674956017843E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35102327697066049</v>
+        <v>0.35102802874844108</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -15012,31 +15012,31 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4674069910841121</v>
+        <v>1.4673796202130505</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5709458175763662</v>
+        <v>1.5709205069685108</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.4269960909492099</v>
+        <v>1.4269801248007132</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.6576997938536142</v>
+        <v>1.6576862719100194</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.5825778689564769</v>
+        <v>1.5825680018997135</v>
       </c>
       <c r="L113" s="254">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3992822334259603</v>
+        <v>1.399274568089969</v>
       </c>
       <c r="M113" s="254">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.0454378844007655</v>
+        <v>1.0454342492046766</v>
       </c>
       <c r="N113" s="254">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15120,36 +15120,36 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639573681386509</v>
+        <v>0.12639612253563595</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.1112841763932486</v>
+        <v>0.11128600392899436</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12485731042579097</v>
+        <v>0.12485934380702017</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12874261149721497</v>
+        <v>0.12874406367421853</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11859006446769867</v>
+        <v>0.11859102756875566</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12848920638821285</v>
+        <v>0.12849000184256551</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300601738766337</v>
+        <v>0.11300662146842116</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11475802340159147</v>
+        <v>0.1147584270250042</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15285,38 +15285,38 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.10095612908566674</v>
+        <v>0.10095643717340666</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.8886064991999802E-2</v>
+        <v>8.8887524700525647E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.1104704443864606</v>
+        <v>0.11047224346836643</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11113504810975192</v>
+        <v>0.11113630167886378</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11165886717978457</v>
+        <v>0.11165977399076815</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11541889937440886</v>
+        <v>0.11541961391276166</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.10956739263514978</v>
+        <v>0.10956797833452316</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176216966628974</v>
+        <v>0.11176256275277728</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15406,50 +15406,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.98491356636978489</v>
+        <v>0.99069502728301084</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0718781996582225</v>
+        <v>1.0781867909411356</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3291711076628319</v>
+        <v>1.3369906117255339</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2588803673021025</v>
+        <v>1.2662801173741027</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0959653955653603</v>
+        <v>1.1024041827232707</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0198494949962991</v>
+        <v>1.0258391299636598</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.86527609153523721</v>
+        <v>0.87035724933106184</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.84326264780107263</v>
+        <v>0.848212838972352</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.61657803230492669</v>
+        <v>0.62019536386987084</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.50774092438282348</v>
+        <v>0.51071973189193642</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.47867510225845622</v>
+        <v>0.48148338679995945</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15463,50 +15463,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.4703227535556239E-2</v>
+        <v>9.3461795026699143E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10306521150559832</v>
+        <v>0.10171573499444675</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.12780491419834922</v>
+        <v>0.12613118978542773</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12104618916366369</v>
+        <v>0.11946038843151913</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10538128803513079</v>
+        <v>0.10400039459653497</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.8062451441951831E-2</v>
+        <v>9.6777276411666016E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.3199624186080498E-2</v>
+        <v>8.2109174465194515E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.1082946903949293E-2</v>
+        <v>8.0020079148335102E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.9286349260089105E-2</v>
+        <v>5.8508996591497255E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.8821242729117642E-2</v>
+        <v>4.8181106782258155E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.6026452140236172E-2</v>
+        <v>4.5422961018864103E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15520,43 +15520,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12497415621997922</v>
+        <v>0.12261615327243244</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12689815358019263</v>
+        <v>0.1245038487956607</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10841964925913344</v>
+        <v>0.10637399549952714</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10156536049745345</v>
+        <v>9.9649032940897719E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6867217821296384E-2</v>
+        <v>9.5039534466177591E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7645723341705964E-2</v>
+        <v>8.5992030448466233E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2219477690461678E-2</v>
+        <v>7.0856846035924667E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.142177360560048E-2</v>
+        <v>7.0074192971532542E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9099175951202542E-2</v>
+        <v>4.8172776404953439E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7921007525405498E-2</v>
+        <v>4.701683757209596E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>1109898219.8994837</v>
+        <v>1109901786.4316416</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>6704814989.3068295</v>
+        <v>6704022426.6051159</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>11998899674.589012</v>
+        <v>11998938231.693422</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-2578700.2762609757</v>
+        <v>-2573944.9000506923</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16404,14 +16404,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>7005235077.3568296</v>
+        <v>7004442514.6551161</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>7005235077.3568296</v>
+        <v>7004442514.6551161</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>19004134751.945843</v>
+        <v>19003380746.348537</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.2163817723061836</v>
+        <v>6.252144516740012</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-2578700.2762609757</v>
+        <v>-2573944.9000506923</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0948992599999998</v>
+        <v>1.1013227999999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>20807613076.845783</v>
+        <v>20928856493.03466</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>16.915603035450467</v>
+        <v>17.014170240778682</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>1561004773.6626246</v>
+        <v>1561009529.038835</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16723,11 +16723,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>1111845129.0479093</v>
+        <v>1111848695.5800669</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>1.7541330488861639E-3</v>
+        <v>1.7541274121961603E-3</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>1017707211.9431663</v>
+        <v>1017710476.5034937</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>1563742736.14135</v>
+        <v>1563747491.5175605</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16772,11 +16772,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>1113795447.3934052</v>
+        <v>1113799013.9255629</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>1.7541277058668037E-3</v>
+        <v>1.7541220790644463E-3</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>933173821.83990502</v>
+        <v>933176809.9958111</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>1566485493.0161917</v>
+        <v>1566490248.3924022</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16821,11 +16821,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>1115749180.9057536</v>
+        <v>1115752747.4379113</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>1.754122372219058E-3</v>
+        <v>1.7541167552865833E-3</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>855661988.94092751</v>
+        <v>855664724.09507501</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>1566485493.0161917</v>
+        <v>1566490248.3924022</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>12062153307.089228</v>
+        <v>12062191864.193636</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18285,7 +18285,7 @@
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>9250399880.4424591</v>
+        <v>9250429449.676487</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18298,7 +18298,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>12056942903.166458</v>
+        <v>12056981460.270866</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18322,7 +18322,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>12056942903.166458</v>
+        <v>12056981460.270866</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18357,19 +18357,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>11758503513.484865</v>
+        <v>11758542070.589272</v>
       </c>
       <c r="C56" s="118">
-        <v>11878701594.036936</v>
+        <v>11878740151.141344</v>
       </c>
       <c r="D56" s="118">
-        <v>11998899674.589012</v>
+        <v>11998938231.693422</v>
       </c>
       <c r="E56" s="118">
-        <v>12119097755.141087</v>
+        <v>12119136312.245493</v>
       </c>
       <c r="F56" s="118">
-        <v>12239295835.693161</v>
+        <v>12239334392.797567</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18383,19 +18383,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>11542862105.812494</v>
+        <v>11542900662.916904</v>
       </c>
       <c r="C57" s="118">
-        <v>11769780678.937115</v>
+        <v>11769819236.041525</v>
       </c>
       <c r="D57" s="118">
-        <v>11998899674.589012</v>
+        <v>11998938231.693422</v>
       </c>
       <c r="E57" s="118">
-        <v>12230219092.768173</v>
+        <v>12230257649.872581</v>
       </c>
       <c r="F57" s="118">
-        <v>12463738933.474606</v>
+        <v>12463777490.579016</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18409,19 +18409,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>11349426335.085793</v>
+        <v>11349464892.190201</v>
       </c>
       <c r="C58" s="118">
-        <v>11671078888.594944</v>
+        <v>11671117445.699352</v>
       </c>
       <c r="D58" s="118">
-        <v>11998899674.589012</v>
+        <v>11998938231.69342</v>
       </c>
       <c r="E58" s="118">
-        <v>12332949116.569874</v>
+        <v>12332987673.674282</v>
       </c>
       <c r="F58" s="118">
-        <v>12673287638.039433</v>
+        <v>12673326195.143841</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18435,19 +18435,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>11175909579.651312</v>
+        <v>11175948136.75572</v>
       </c>
       <c r="C59" s="118">
-        <v>11581637449.29174</v>
+        <v>11581676006.396149</v>
       </c>
       <c r="D59" s="118">
-        <v>11998899674.589012</v>
+        <v>11998938231.69342</v>
       </c>
       <c r="E59" s="118">
-        <v>12427921495.5536</v>
+        <v>12427960052.658009</v>
       </c>
       <c r="F59" s="118">
-        <v>12868930364.498127</v>
+        <v>12868968921.602537</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18461,19 +18461,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>11020260682.327938</v>
+        <v>11020299239.432344</v>
       </c>
       <c r="C60" s="118">
-        <v>11500587540.907148</v>
+        <v>11500626098.011559</v>
       </c>
       <c r="D60" s="118">
-        <v>11998899674.589012</v>
+        <v>11998938231.69342</v>
       </c>
       <c r="E60" s="118">
-        <v>12515722047.291412</v>
+        <v>12515760604.395824</v>
       </c>
       <c r="F60" s="118">
-        <v>13051589935.196405</v>
+        <v>13051628492.300814</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18487,19 +18487,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>10880639703.493235</v>
+        <v>10880678260.597643</v>
       </c>
       <c r="C61" s="118">
-        <v>11427141857.336666</v>
+        <v>11427180414.441076</v>
       </c>
       <c r="D61" s="118">
-        <v>11998899674.58901</v>
+        <v>11998938231.69342</v>
       </c>
       <c r="E61" s="118">
-        <v>12596892351.415157</v>
+        <v>12596930908.519566</v>
       </c>
       <c r="F61" s="118">
-        <v>13222127932.553146</v>
+        <v>13222166489.657555</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18513,19 +18513,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>10755396170.991627</v>
+        <v>10755434728.096037</v>
       </c>
       <c r="C62" s="118">
-        <v>11360586958.723598</v>
+        <v>11360625515.828009</v>
       </c>
       <c r="D62" s="118">
-        <v>11998899674.589012</v>
+        <v>11998938231.69342</v>
       </c>
       <c r="E62" s="118">
-        <v>12671933090.238941</v>
+        <v>12671971647.343351</v>
       </c>
       <c r="F62" s="118">
-        <v>13381348763.037249</v>
+        <v>13381387320.141659</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18539,19 +18539,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>10643049569.75449</v>
+        <v>10643088126.858898</v>
       </c>
       <c r="C63" s="118">
-        <v>11300276341.216106</v>
+        <v>11300314898.320515</v>
       </c>
       <c r="D63" s="118">
-        <v>11998899674.58901</v>
+        <v>11998938231.69342</v>
       </c>
       <c r="E63" s="118">
-        <v>12741307137.114931</v>
+        <v>12741345694.219337</v>
       </c>
       <c r="F63" s="118">
-        <v>13530003451.45261</v>
+        <v>13530042008.557018</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18565,19 +18565,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>10542271840.498291</v>
+        <v>10542310397.602699</v>
       </c>
       <c r="C64" s="118">
-        <v>11245624156.930141</v>
+        <v>11245662714.03455</v>
       </c>
       <c r="D64" s="118">
-        <v>11998899674.589008</v>
+        <v>11998938231.693419</v>
       </c>
       <c r="E64" s="118">
-        <v>12805442411.572369</v>
+        <v>12805480968.676777</v>
       </c>
       <c r="F64" s="118">
-        <v>13668793183.428505</v>
+        <v>13668831740.532913</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18591,19 +18591,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>10451871680.616301</v>
+        <v>10451910237.720707</v>
       </c>
       <c r="C65" s="118">
-        <v>11196099523.114941</v>
+        <v>11196138080.219349</v>
       </c>
       <c r="D65" s="118">
-        <v>11998899674.589008</v>
+        <v>11998938231.693417</v>
       </c>
       <c r="E65" s="118">
-        <v>12864734518.851097</v>
+        <v>12864773075.955505</v>
       </c>
       <c r="F65" s="118">
-        <v>13798372612.82477</v>
+        <v>13798411169.929176</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18617,19 +18617,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>10121753976.51754</v>
+        <v>10121792533.621948</v>
       </c>
       <c r="C66" s="281">
-        <v>11010045548.683287</v>
+        <v>11010084105.787693</v>
       </c>
       <c r="D66" s="118">
-        <v>11998899674.589012</v>
+        <v>11998938231.693417</v>
       </c>
       <c r="E66" s="118">
-        <v>13100424209.812569</v>
+        <v>13100462766.916977</v>
       </c>
       <c r="F66" s="118">
-        <v>14328143228.622068</v>
+        <v>14328181785.726475</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18652,19 +18652,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>9930023140.3626118</v>
+        <v>9930061697.4670219</v>
       </c>
       <c r="C67" s="281">
-        <v>10896359362.761065</v>
+        <v>10896397919.865473</v>
       </c>
       <c r="D67" s="118">
-        <v>11998899674.58901</v>
+        <v>11998938231.693417</v>
       </c>
       <c r="E67" s="118">
-        <v>13259586517.615696</v>
+        <v>13259625074.720104</v>
       </c>
       <c r="F67" s="118">
-        <v>14703964620.534307</v>
+        <v>14704003177.638714</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18687,19 +18687,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>9818666757.2415466</v>
+        <v>9818705314.3459568</v>
       </c>
       <c r="C68" s="281">
-        <v>10826892699.073692</v>
+        <v>10826931256.178101</v>
       </c>
       <c r="D68" s="118">
-        <v>11998899674.589008</v>
+        <v>11998938231.693415</v>
       </c>
       <c r="E68" s="118">
-        <v>13367069539.558128</v>
+        <v>13367108096.662539</v>
       </c>
       <c r="F68" s="118">
-        <v>14970573817.811684</v>
+        <v>14970612374.916088</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18722,19 +18722,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>9753991484.8102226</v>
+        <v>9754030041.9146328</v>
       </c>
       <c r="C69" s="281">
-        <v>10784445876.491787</v>
+        <v>10784484433.596193</v>
       </c>
       <c r="D69" s="118">
-        <v>11998899674.58901</v>
+        <v>11998938231.693413</v>
       </c>
       <c r="E69" s="118">
-        <v>13439653307.444729</v>
+        <v>13439691864.549141</v>
       </c>
       <c r="F69" s="118">
-        <v>15159707447.782068</v>
+        <v>15159746004.886471</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18831,23 +18831,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18862,23 +18862,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>16.650770640581737</v>
+        <v>16.747784130838728</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>16.757433321956306</v>
+        <v>16.855072579373211</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>16.970758684705459</v>
+        <v>17.069649476442176</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>17.077421366080035</v>
+        <v>17.176937924976659</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>16.459412420449777</v>
+        <v>16.555303252918744</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>16.660777894440677</v>
+        <v>16.757850095117703</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>17.069366747120398</v>
+        <v>17.168836051288704</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>17.276590125809214</v>
+        <v>17.37727516526073</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18924,23 +18924,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>16.287759280194109</v>
+        <v>16.382643060368089</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>16.573190825113009</v>
+        <v>16.669749171169926</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>17.160528434112695</v>
+        <v>17.260532564419126</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>17.462541736723416</v>
+        <v>17.564317714541964</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18955,23 +18955,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>16.133782092596341</v>
+        <v>16.227762521512581</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>16.493821306912192</v>
+        <v>16.589914008965529</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>17.244806057785212</v>
+        <v>17.34530462690126</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>17.636153309384728</v>
+        <v>17.738947829202708</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18986,23 +18986,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>15.995660679465171</v>
+        <v>16.088830779564393</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>16.421898356780563</v>
+        <v>16.517569102254001</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>17.322719467313117</v>
+        <v>17.423675137754309</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>17.798243747933505</v>
+        <v>17.901989217718913</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -19017,23 +19017,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>15.871762295146127</v>
+        <v>15.964205509899198</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>16.356723326455334</v>
+        <v>16.452011703952468</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>16.864096003330882</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>17.394749255526563</v>
+        <v>17.49612750934385</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>17.949577612757075</v>
+        <v>18.054210925990336</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19049,23 +19049,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>15.760622325688319</v>
+        <v>15.852413505989002</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>16.297663115908897</v>
+        <v>16.392604999770764</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>17.461339723348601</v>
+        <v>17.563108649211529</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>18.090868726825764</v>
+        <v>18.196330964834143</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19080,23 +19080,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>15.66092697551106</v>
+        <v>15.752133264495191</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>16.244144023514419</v>
+        <v>16.338771922297184</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>16.864096003330882</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>17.522901620374007</v>
+        <v>17.62503171673222</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>18.222783542706832</v>
+        <v>18.329019696752379</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19112,23 +19112,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>15.571497736908119</v>
+        <v>15.662179363658634</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>16.195646173198142</v>
+        <v>16.289989545456137</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>16.864096003330882</v>
+        <v>16.962361027907694</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>17.579814678493609</v>
+        <v>17.68227867160261</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>18.345944286138124</v>
+        <v>18.452902997948353</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19144,23 +19144,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>15.491277458802045</v>
+        <v>15.581488450322407</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>16.151698464444717</v>
+        <v>16.245784004886215</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>16.864096003330882</v>
+        <v>16.962361027907694</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>17.632429954192279</v>
+        <v>17.735202629880952</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>18.460931890989308</v>
+        <v>18.568565210506613</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19176,23 +19176,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>15.198334016388777</v>
+        <v>15.286826371328747</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>15.986595862954511</v>
+        <v>16.079712781712239</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>16.864096003330886</v>
+        <v>16.962361027907694</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>17.841578838224617</v>
+        <v>17.945578545724906</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>18.931045507902834</v>
+        <v>19.04143688355655</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19208,23 +19208,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>15.028193819535849</v>
+        <v>15.115687998296496</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>15.8857117775347</v>
+        <v>15.978236830920215</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>16.864096003330882</v>
+        <v>16.962361027907694</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>17.982818019799499</v>
+        <v>18.08764634739806</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>19.264545986406048</v>
+        <v>19.376893938104647</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19240,23 +19240,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>14.929377179891414</v>
+        <v>15.016291622542436</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>15.824067693194847</v>
+        <v>15.916231093909666</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>16.864096003330882</v>
+        <v>16.96236102790769</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>18.078197474030095</v>
+        <v>18.183585372505913</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>19.50113255858852</v>
+        <v>19.614868513152221</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19272,23 +19272,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>14.87198493249053</v>
+        <v>14.958562667089643</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>15.786400769633156</v>
+        <v>15.878343186556117</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>16.864096003330882</v>
+        <v>16.96236102790769</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>18.142607648231674</v>
+        <v>18.248373427436348</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>19.668968018340372</v>
+        <v>19.783688627683304</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>17.462541736723416</v>
+        <v>17.564317714541964</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>17.160528434112695</v>
+        <v>17.260532564419126</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>16.573190825113009</v>
+        <v>16.669749171169926</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>16.287759280194109</v>
+        <v>16.382643060368089</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>1207898587.6239438</v>
+        <v>1207921118.4237735</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>1109898219.8994837</v>
+        <v>1109901786.4316416</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C14" s="252">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7257574792176764E-2</v>
+        <v>-7.7254131105641166E-2</v>
       </c>
       <c r="D14" s="465"/>
       <c r="E14" s="465"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>17.160528434112695</v>
+        <v>17.260532564419126</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>16.573190825113009</v>
+        <v>16.669749171169926</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>16.850656194932778</v>
+        <v>16.948842371025538</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19917,7 +19917,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>17.462541736723416</v>
+        <v>17.564317714541964</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19940,7 +19940,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>16.287759280194109</v>
+        <v>16.382643060368089</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.59124560039999985</v>
+        <v>0.59471431199999991</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22497970185102439</v>
+        <v>0.21934387142409759</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20005,7 +20005,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20016,7 +20016,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.6016747100256985E-2</v>
+        <v>3.6018174802351255E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>16.914294180464442</v>
+        <v>17.012853707020131</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>16.915603035450467</v>
+        <v>17.014170240778682</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.39723151750623564</v>
+        <v>0.39720564923589674</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.59124560039999985</v>
+        <v>0.59471431199999991</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20265,15 +20265,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.0818916937601135</v>
+        <v>1.0882389211484453</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>7.7946056131172563</v>
+        <v>7.8400247497788644</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>8.8764973068773703</v>
+        <v>8.9282636709273095</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.4752073475741313</v>
+        <v>0.47520481721163699</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20290,15 +20290,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2439830770470757</v>
+        <v>1.2512812599454139</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>9.769989418318815</v>
+        <v>9.8269191087480934</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>11.013972495365891</v>
+        <v>11.078200368693507</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34883641150768585</v>
+        <v>0.34883350204074037</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20336,15 +20336,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4264409837225129</v>
+        <v>1.4348096081716528</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>12.123496144357683</v>
+        <v>12.194139709347091</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>13.549937128080195</v>
+        <v>13.628949317518744</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19890614509176441</v>
+        <v>0.19890280888649881</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20361,15 +20361,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5445553596599959</v>
+        <v>1.5536169359140437</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>13.710774155557695</v>
+        <v>13.790666783359127</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>15.255329515217692</v>
+        <v>15.34428371927317</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>9.8080632129646239E-2</v>
+        <v>9.8077019674744359E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20488,7 +20488,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20506,14 +20506,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12831.946400000001</v>
+        <v>13078.714599999999</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.22497970185102439</v>
+        <v>0.21934387142409759</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20521,13 +20521,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0948992599999998</v>
+        <v>1.1013227999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>16.914294180464442</v>
+        <v>17.012853707020131</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20643,7 +20643,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>8.8764973068773703</v>
+        <v>8.9282636709273095</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>11.013972495365891</v>
+        <v>11.078200368693507</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>13.549937128080195</v>
+        <v>13.628949317518744</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>15.255329515217692</v>
+        <v>15.34428371927317</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20712,22 +20712,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>11578222.553239023</v>
+        <v>11582977.929449307</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-2578700.2762609757</v>
+        <v>-2573944.9000506923</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-389567899.29982787</v>
+        <v>-389569088.14388049</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20917,10 +20917,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20936,22 +20936,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>1207898587.6239438</v>
+        <v>1207921118.4237735</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>1109898219.8994837</v>
+        <v>1109901786.4316416</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.4703227535556239E-2</v>
+        <v>9.3461795026699143E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20995,14 +20995,14 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.6850538499999985E-2</v>
+        <v>5.6105123773584897E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>0.73030026013376526</v>
+        <v>0.73458241521182999</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21022,11 +21022,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095612908566674</v>
+        <v>0.10095643717340666</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>8.8886064991999802E-2</v>
+        <v>8.8887524700525647E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21036,11 +21036,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639573681386509</v>
+        <v>0.12639612253563595</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>0.1112841763932486</v>
+        <v>0.11128600392899436</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21086,22 +21086,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21109,13 +21109,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25125448627329861</v>
+        <v>-0.25272854265612604</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>6704814989.3068295</v>
+        <v>6704022426.6051159</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9497917237544824</v>
+        <v>5.983990441338503</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.51784453482500004</v>
+        <v>0.52088261805763436</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>6.2163817723061836</v>
+        <v>6.252144516740012</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21264,33 +21264,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21353,23 +21353,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.7084941401521563</v>
+        <v>1.7185175102008612</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>16.864096003330886</v>
+        <v>16.962361027907697</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21413,13 +21413,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21464,7 +21464,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.46 HKD</v>
+        <v>17.56 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.16 HKD</v>
+        <v>17.26 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>16.86 HKD</v>
+        <v>16.96 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.57 HKD</v>
+        <v>16.67 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.29 HKD</v>
+        <v>16.38 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>16.914294180464442</v>
+        <v>17.012853707020131</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21583,13 +21583,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21602,22 +21602,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C136" s="410">
         <f>Scenarios!C58</f>
-        <v>0.59124560039999985</v>
+        <v>0.59471431199999991</v>
       </c>
       <c r="D136" s="347" t="str">
         <f>Market_currency</f>
@@ -21678,15 +21678,15 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>1.0818916937601135</v>
+        <v>1.0882389211484453</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>7.7946056131172563</v>
+        <v>7.8400247497788644</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>8.8764973068773703</v>
+        <v>8.9282636709273095</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21699,15 +21699,15 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>1.2439830770470757</v>
+        <v>1.2512812599454139</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>9.769989418318815</v>
+        <v>9.8269191087480934</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>11.013972495365891</v>
+        <v>11.078200368693507</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21739,15 +21739,15 @@
       </c>
       <c r="C144" s="413">
         <f>Scenarios!C66</f>
-        <v>1.4264409837225129</v>
+        <v>1.4348096081716528</v>
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>12.123496144357683</v>
+        <v>12.194139709347091</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>13.549937128080195</v>
+        <v>13.628949317518744</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21760,15 +21760,15 @@
       </c>
       <c r="C145" s="413">
         <f>Scenarios!C67</f>
-        <v>1.5445553596599959</v>
+        <v>1.5536169359140437</v>
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>13.710774155557695</v>
+        <v>13.790666783359127</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>15.255329515217692</v>
+        <v>15.34428371927317</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21786,13 +21786,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21800,13 +21800,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21843,22 +21843,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21882,15 +21882,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21905,12 +21902,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B363DE7-7AFE-4E37-8250-08F66E05AB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E420E1-8388-44A0-9E70-C7D91EC23913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4972,30 +4972,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5005,6 +5005,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5014,16 +5023,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5393,7 +5393,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.6</v>
+        <v>10.210000000000001</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>13078.714599999999</v>
+        <v>12597.516610000002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.21934387142409759</v>
+        <v>0.23583181729627789</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.1013227999999999</v>
+        <v>1.1024826515674591</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>17.012853707020131</v>
+        <v>17.030649042042409</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>8.9282636709273095</v>
+        <v>8.9376103585030844</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>11.078200368693507</v>
+        <v>11.089797041998329</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>13.628949317518744</v>
+        <v>13.643215370062471</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>15.34428371927317</v>
+        <v>15.360344850049612</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>11582977.929449307</v>
+        <v>11583836.572900016</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-2573944.9000506923</v>
+        <v>-2573086.2565999832</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-389569088.14388049</v>
+        <v>-389569302.80474317</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>1207921118.4237735</v>
+        <v>1207925186.645268</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>1109901786.4316416</v>
+        <v>1109902430.4142294</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.3461795026699143E-2</v>
+        <v>9.7134079068640064E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5894,14 +5894,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6105123773584897E-2</v>
+        <v>5.8309562374772562E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.73458241521182999</v>
+        <v>0.73535560965568947</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5921,11 +5921,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095643717340666</v>
+        <v>0.10095649280255321</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.8887524700525647E-2</v>
+        <v>8.888778826940226E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5935,11 +5935,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639612253563595</v>
+        <v>0.12639619218259082</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128600392899436</v>
+        <v>0.11128633391373786</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25272854265612604</v>
+        <v>-0.25299470222018966</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>6704022426.6051159</v>
+        <v>6703879319.3633308</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.983990441338503</v>
+        <v>5.9901645737173084</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52088261805763436</v>
+        <v>0.52143118249397991</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.252144516740012</v>
+        <v>6.2586010539910992</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7185175102008612</v>
+        <v>1.7203273567126307</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.56 HKD</v>
+        <v>17.58 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.3637144816192977E-2</v>
+        <v>2.3637310032024433E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.26 HKD</v>
+        <v>17.28 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.9811811914266698E-2</v>
+        <v>2.9812022775325912E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>16.96 HKD</v>
+        <v>16.98 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.6018174802351255E-2</v>
+        <v>3.6018432604125329E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.67 HKD</v>
+        <v>16.69 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.2255173526660167E-2</v>
+        <v>4.2255479584906545E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.38 HKD</v>
+        <v>16.4 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,17 +6445,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.8521683217158891E-2</v>
+        <v>4.8522038867152312E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>17.012853707020131</v>
+        <v>17.030649042042409</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.59471431199999991</v>
+        <v>0.59534063184642794</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,15 +6566,15 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>1.0882389211484453</v>
+        <v>1.0893849935065805</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>7.8400247497788644</v>
+        <v>7.8482253649965035</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>8.9282636709273095</v>
+        <v>8.9376103585030844</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,15 +6587,15 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>1.2512812599454139</v>
+        <v>1.2525990393745514</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>9.8269191087480934</v>
+        <v>9.8371980026237775</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>11.078200368693507</v>
+        <v>11.089797041998329</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,15 +6634,15 @@
       </c>
       <c r="C144" s="337">
         <f>Scenarios!C66</f>
-        <v>1.4348096081716528</v>
+        <v>1.4363206693909827</v>
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>12.194139709347091</v>
+        <v>12.206894700671489</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>13.628949317518744</v>
+        <v>13.643215370062471</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,15 +6655,15 @@
       </c>
       <c r="C145" s="337">
         <f>Scenarios!C67</f>
-        <v>1.5536169359140437</v>
+        <v>1.555253118365139</v>
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>13.790666783359127</v>
+        <v>13.805091731684474</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>15.34428371927317</v>
+        <v>15.360344850049612</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,6 +6777,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6793,18 +6805,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.66079367999999994</v>
+        <v>0.66148959094047544</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.66079367999999994</v>
+        <v>0.66148959094047544</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10216,11 +10216,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.376727912112676</v>
+        <v>13.390815533685876</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7185175102008612</v>
+        <v>1.7203273567126307</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6704022426.6051159</v>
+        <v>6703879319.3633308</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10478,11 +10478,11 @@
       </c>
       <c r="C73" s="289">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-984522918.94873989</v>
+        <v>-984594472.56963217</v>
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-965248160.78744221</v>
+        <v>-965319714.40833461</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10494,11 +10494,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7702567223115757</v>
+        <v>8.7696193597809913</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9453874132596383</v>
+        <v>8.9447243429315897</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10511,7 +10511,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1930496321.5748844</v>
+        <v>1930639428.8166692</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10626,11 +10626,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>311826837.7993772</v>
+        <v>312155236.38206106</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.25272854265612604</v>
+        <v>0.25299470222018966</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10643,11 +10643,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7383292750.1315403</v>
+        <v>7390910647.7999372</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.983990441338503</v>
+        <v>5.9901645737173084</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10660,11 +10660,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>642686330.34684968</v>
+        <v>643363171.63955462</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.52088261805763436</v>
+        <v>0.52143118249397991</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10677,11 +10677,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>8337805918.2777672</v>
+        <v>8346429055.8215532</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.7576016020522633</v>
+        <v>6.7645904584314778</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11162,36 +11162,36 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-2573944.9000506923</v>
+        <v>-2573086.2565999832</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>42437845.883772507</v>
+        <v>42441914.105266996</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40907258.125402227</v>
+        <v>40911615.674355939</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>17684060.36479719</v>
+        <v>17686926.388097338</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>5050995.6057627723</v>
+        <v>5052814.6641418189</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
-        <v>-4710487.7786057256</v>
+        <v>-4709193.9571538419</v>
       </c>
       <c r="L10" s="270">
         <f t="shared" si="6"/>
-        <v>-6429541.7371483576</v>
+        <v>-6428577.2510438897</v>
       </c>
       <c r="M10" s="270">
         <f t="shared" si="6"/>
-        <v>7532077.2016280871</v>
+        <v>7532673.8342542714</v>
       </c>
       <c r="N10" s="270">
         <f t="shared" si="6"/>
@@ -11217,36 +11217,36 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>1558276352.5755219</v>
+        <v>1558277211.2189727</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1371991045.4237735</v>
+        <v>1371995113.645268</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>1481891926.4454019</v>
+        <v>1481896283.9943557</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>1407211559.3647971</v>
+        <v>1407214425.3880973</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>1240505313.6057627</v>
+        <v>1240507132.6641419</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
-        <v>1157445203.2213943</v>
+        <v>1157446497.0428462</v>
       </c>
       <c r="L11" s="271">
         <f t="shared" si="7"/>
-        <v>999256272.84285367</v>
+        <v>999257237.32895815</v>
       </c>
       <c r="M11" s="271">
         <f t="shared" si="7"/>
-        <v>939479383.97162712</v>
+        <v>939479980.60425329</v>
       </c>
       <c r="N11" s="271">
         <f t="shared" si="7"/>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-389569088.14388049</v>
+        <v>-389569302.80474317</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11384,38 +11384,38 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>1109901786.4316416</v>
+        <v>1109902430.4142294</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207921118.4237735</v>
+        <v>1207925186.645268</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>1497865869.4454019</v>
+        <v>1497870226.9943557</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>1418647036.3647971</v>
+        <v>1418649902.3880973</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>1235052501.6057627</v>
+        <v>1235054320.6641419</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
-        <v>1149274652.2213943</v>
+        <v>1149275946.0428462</v>
       </c>
       <c r="L14" s="271">
         <f t="shared" si="8"/>
-        <v>975084197.72285366</v>
+        <v>975085162.20895815</v>
       </c>
       <c r="M14" s="271">
         <f t="shared" si="8"/>
-        <v>950275230.34162712</v>
+        <v>950275826.9742533</v>
       </c>
       <c r="N14" s="271">
         <f t="shared" si="8"/>
@@ -11602,38 +11602,38 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>1109901786.4316416</v>
+        <v>1109902430.4142294</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207921118.4237735</v>
+        <v>1207925186.645268</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>1497865869.4454019</v>
+        <v>1497870226.9943557</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>1418647036.3647971</v>
+        <v>1418649902.3880973</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>1235052501.6057627</v>
+        <v>1235054320.6641419</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
-        <v>1149274652.2213943</v>
+        <v>1149275946.0428462</v>
       </c>
       <c r="L19" s="275">
         <f t="shared" si="9"/>
-        <v>975084197.72285366</v>
+        <v>975085162.20895815</v>
       </c>
       <c r="M19" s="275">
         <f t="shared" si="9"/>
-        <v>950275230.34162712</v>
+        <v>950275826.9742533</v>
       </c>
       <c r="N19" s="275">
         <f t="shared" si="9"/>
@@ -12341,31 +12341,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.6723860079922351E-2</v>
+        <v>7.6723632579362322E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.398312915864408E-2</v>
+        <v>-4.3982999825275391E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.1263381642216418E-3</v>
+        <v>-8.12632161359929E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3956377616395474E-3</v>
+        <v>4.3956313159517384E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.0591255441378765E-3</v>
+        <v>7.0591176532780534E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4190065928964534E-2</v>
+        <v>2.4190042580639812E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491307371068444E-2</v>
+        <v>-1.149130007331965E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12479,36 +12479,36 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>11582977.929449307</v>
+        <v>11583836.572900016</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54879728.883772507</v>
+        <v>54883797.105266996</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>58782715.125402227</v>
+        <v>58787072.674355939</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>38662246.36479719</v>
+        <v>38665112.388097338</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>24538838.605762772</v>
+        <v>24540657.664141819</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
-        <v>17453467.221394274</v>
+        <v>17454761.042846158</v>
       </c>
       <c r="L46" s="278">
         <f t="shared" si="17"/>
-        <v>13010780.262851642</v>
+        <v>13011744.74895611</v>
       </c>
       <c r="M46" s="278">
         <f t="shared" si="17"/>
-        <v>8048489.2016280871</v>
+        <v>8049085.8342542714</v>
       </c>
       <c r="N46" s="278">
         <f t="shared" si="17"/>
@@ -12591,36 +12591,36 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-2573944.9000506923</v>
+        <v>-2573086.2565999832</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42437845.883772507</v>
+        <v>42441914.105266996</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40907258.125402227</v>
+        <v>40911615.674355939</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>17684060.36479719</v>
+        <v>17686926.388097338</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>5050995.6057627723</v>
+        <v>5052814.6641418189</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
-        <v>-4710487.7786057256</v>
+        <v>-4709193.9571538419</v>
       </c>
       <c r="L48" s="271">
         <f t="shared" si="18"/>
-        <v>-6429541.7371483576</v>
+        <v>-6428577.2510438897</v>
       </c>
       <c r="M48" s="271">
         <f t="shared" si="18"/>
-        <v>7532077.2016280871</v>
+        <v>7532673.8342542714</v>
       </c>
       <c r="N48" s="271">
         <f t="shared" si="18"/>
@@ -13556,38 +13556,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0877981909246424E-4</v>
+        <v>2.0871017213758947E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.4422515361977666E-3</v>
+        <v>3.442581520941275E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4467111368463887E-3</v>
+        <v>3.4470782896010919E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.6178930442071295E-3</v>
+        <v>1.618155253171937E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8286996642647349E-4</v>
+        <v>4.8304386652993342E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2291942777757633E-4</v>
+        <v>5.2277579841156067E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.2712156936302163E-4</v>
+        <v>7.2701249492528096E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.2005141000075347E-4</v>
+        <v>9.2012428932398374E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13613,38 +13613,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639612253563595</v>
+        <v>0.12639619218259082</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.11128600392899436</v>
+        <v>0.11128633391373786</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12485934380702017</v>
+        <v>0.12485971095977487</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12874406367421853</v>
+        <v>0.12874432588318332</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11859102756875566</v>
+        <v>0.11859120146885913</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12849000184256551</v>
+        <v>0.12849014547193152</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300662146842116</v>
+        <v>0.11300673054285891</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.1147584270250042</v>
+        <v>0.11475849990432743</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1599030633908988E-2</v>
+        <v>3.1599048045647705E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13785,38 +13785,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.0027216269096252E-2</v>
+        <v>9.0027268504312391E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.7977836502061794E-2</v>
+        <v>9.7978166486805296E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12620525574931338</v>
+        <v>0.12620562290206808</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12979028147227131</v>
+        <v>0.12979054368123613</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11806974436978279</v>
+        <v>0.11806991826988626</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758297478839234</v>
+        <v>0.12758311841775835</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11027298384469052</v>
+        <v>0.11027309291912826</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607715138336887</v>
+        <v>0.1160772242626921</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14008,38 +14008,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.0027216269096252E-2</v>
+        <v>9.0027268504312391E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.7977836502061794E-2</v>
+        <v>9.7978166486805296E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12620525574931338</v>
+        <v>0.12620562290206808</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12979028147227131</v>
+        <v>0.12979054368123613</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11806974436978279</v>
+        <v>0.11806991826988626</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758297478839234</v>
+        <v>0.12758311841775835</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11027298384469052</v>
+        <v>0.11027309291912826</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607715138336887</v>
+        <v>0.1160772242626921</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14077,12 +14077,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.66079367999999994</v>
+        <v>0.66148959094047544</v>
       </c>
       <c r="E88" s="238"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.66079367999999994</v>
+        <v>0.66148959094047544</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14133,12 +14133,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>815314334.92487991</v>
+        <v>816172978.37558711</v>
       </c>
       <c r="E89" s="238"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>815314334.92487991</v>
+        <v>816172978.37558711</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.73458241521182999</v>
+        <v>0.73535560965568947</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.6749731604898096</v>
+        <v>0.67568172880169697</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14264,12 +14264,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6105123773584897E-2</v>
+        <v>5.8309562374772562E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.6105123773584897E-2</v>
+        <v>5.8309562374772562E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14401,38 +14401,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.13577734911105743</v>
+        <v>0.13577460715495548</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162547929690459E-2</v>
+        <v>-7.4162525094439324E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.3069751014776179E-2</v>
+        <v>5.3070702843073692E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.1343857571028626</v>
+        <v>0.13438640402327318</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1761591955451509E-2</v>
+        <v>7.1761965528002181E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830666734620324</v>
+        <v>0.15830684412827689</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3627674956017843E-2</v>
+        <v>6.3628026098286217E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35102802874844108</v>
+        <v>0.35102888674214983</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -15012,31 +15012,31 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4673796202130505</v>
+        <v>1.4673746781641741</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5709205069685108</v>
+        <v>1.5709159369043701</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.4269801248007132</v>
+        <v>1.4269772419483056</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.6576862719100194</v>
+        <v>1.6576838303752199</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.5825680018997135</v>
+        <v>1.5825662202906603</v>
       </c>
       <c r="L113" s="254">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.399274568089969</v>
+        <v>1.3992731840253461</v>
       </c>
       <c r="M113" s="254">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.0454342492046766</v>
+        <v>1.0454335928266398</v>
       </c>
       <c r="N113" s="254">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15120,36 +15120,36 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639612253563595</v>
+        <v>0.12639619218259082</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.11128600392899436</v>
+        <v>0.11128633391373786</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12485934380702017</v>
+        <v>0.12485971095977487</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12874406367421853</v>
+        <v>0.12874432588318332</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11859102756875566</v>
+        <v>0.11859120146885913</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12849000184256551</v>
+        <v>0.12849014547193152</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300662146842116</v>
+        <v>0.11300673054285891</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.1147584270250042</v>
+        <v>0.11475849990432743</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15285,38 +15285,38 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.10095643717340666</v>
+        <v>0.10095649280255321</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.8887524700525647E-2</v>
+        <v>8.888778826940226E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11047224346836643</v>
+        <v>0.11047256831540847</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11113630167886378</v>
+        <v>0.11113652802665631</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11165977399076815</v>
+        <v>0.11165993772698538</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11541961391276166</v>
+        <v>0.11541974293171826</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.10956797833452316</v>
+        <v>0.10956808408996896</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176256275277728</v>
+        <v>0.11176263372952511</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15406,50 +15406,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.99069502728301084</v>
+        <v>0.99173894729081535</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0781867909411356</v>
+        <v>1.0793259120646768</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3369906117255339</v>
+        <v>1.3384025490810316</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2662801173741027</v>
+        <v>1.2676162536588964</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1024041827232707</v>
+        <v>1.1035667985385882</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0258391299636598</v>
+        <v>1.02692064242963</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.87035724933106184</v>
+        <v>0.87127472270431772</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.848212838972352</v>
+        <v>0.84910666240061294</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.62019536386987084</v>
+        <v>0.62084851893477588</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.51071973189193642</v>
+        <v>0.51125759334506093</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.48148338679995945</v>
+        <v>0.48199045816984798</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15463,50 +15463,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.3461795026699143E-2</v>
+        <v>9.7134079068640064E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10171573499444675</v>
+        <v>0.10571262605922396</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.12613118978542773</v>
+        <v>0.13108741910685912</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.11946038843151913</v>
+        <v>0.12415438331624841</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10400039459653497</v>
+        <v>0.10808685588037102</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.6777276411666016E-2</v>
+        <v>0.10057988662386189</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.2109174465194515E-2</v>
+        <v>8.5335428276622688E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.0020079148335102E-2</v>
+        <v>8.3164217669012039E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.8508996591497255E-2</v>
+        <v>6.0807886281564721E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.8181106782258155E-2</v>
+        <v>5.0074201111171487E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.5422961018864103E-2</v>
+        <v>4.7207684443667769E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15520,43 +15520,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12261615327243244</v>
+        <v>0.12729982612025306</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1245038487956607</v>
+        <v>0.12925962754495623</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10637399549952714</v>
+        <v>0.11043725291821622</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9649032940897719E-2</v>
+        <v>0.10345541128046187</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5039534466177591E-2</v>
+        <v>9.8669839896325398E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5992030448466233E-2</v>
+        <v>8.9276740720248965E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0856846035924667E-2</v>
+        <v>7.3563424875690619E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0074192971532542E-2</v>
+        <v>7.2750876150660615E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8172776404953439E-2</v>
+        <v>5.0012872663320898E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.701683757209596E-2</v>
+        <v>4.8812779457807751E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>1109901786.4316416</v>
+        <v>1109902430.4142294</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>6704022426.6051159</v>
+        <v>6703879319.3633308</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>11998938231.693422</v>
+        <v>11998945193.667345</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-2573944.9000506923</v>
+        <v>-2573086.2565999832</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16404,14 +16404,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>7004442514.6551161</v>
+        <v>7004299407.413331</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>7004442514.6551161</v>
+        <v>7004299407.413331</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>19003380746.348537</v>
+        <v>19003244601.080677</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.252144516740012</v>
+        <v>6.2586010539910992</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-2573944.9000506923</v>
+        <v>-2573086.2565999832</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1013227999999999</v>
+        <v>1.1024826515674591</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>20928856493.03466</v>
+        <v>20950747496.184425</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>17.014170240778682</v>
+        <v>17.031966962300672</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>1561009529.038835</v>
+        <v>1561010387.6822858</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16723,11 +16723,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>1111848695.5800669</v>
+        <v>1111849339.5626552</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>1.7541274121961603E-3</v>
+        <v>1.7541263944247376E-3</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>1017710476.5034937</v>
+        <v>1017711065.9612404</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>1563747491.5175605</v>
+        <v>1563748350.1610112</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16772,11 +16772,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>1113799013.9255629</v>
+        <v>1113799657.9081511</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>1.7541220790644463E-3</v>
+        <v>1.7541210630778181E-3</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>933176809.9958111</v>
+        <v>933177349.54523599</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>1566490248.3924022</v>
+        <v>1566491107.0358529</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16821,11 +16821,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>1115752747.4379113</v>
+        <v>1115753391.4204996</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>1.7541167552865833E-3</v>
+        <v>1.7541157410820851E-3</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>855664724.09507501</v>
+        <v>855665217.96182549</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>1566490248.3924022</v>
+        <v>1566491107.0358529</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>12062191864.193636</v>
+        <v>12062198826.167562</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18285,7 +18285,7 @@
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>9250429449.676487</v>
+        <v>9250434788.7764912</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18298,7 +18298,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>12056981460.270866</v>
+        <v>12056988422.244793</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18322,7 +18322,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>12056981460.270866</v>
+        <v>12056988422.244793</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18357,19 +18357,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>11758542070.589272</v>
+        <v>11758549032.563198</v>
       </c>
       <c r="C56" s="118">
-        <v>11878740151.141344</v>
+        <v>11878747113.115269</v>
       </c>
       <c r="D56" s="118">
-        <v>11998938231.693422</v>
+        <v>11998945193.667345</v>
       </c>
       <c r="E56" s="118">
-        <v>12119136312.245493</v>
+        <v>12119143274.219418</v>
       </c>
       <c r="F56" s="118">
-        <v>12239334392.797567</v>
+        <v>12239341354.771496</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18383,19 +18383,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>11542900662.916904</v>
+        <v>11542907624.890829</v>
       </c>
       <c r="C57" s="118">
-        <v>11769819236.041525</v>
+        <v>11769826198.015453</v>
       </c>
       <c r="D57" s="118">
-        <v>11998938231.693422</v>
+        <v>11998945193.667343</v>
       </c>
       <c r="E57" s="118">
-        <v>12230257649.872581</v>
+        <v>12230264611.846506</v>
       </c>
       <c r="F57" s="118">
-        <v>12463777490.579016</v>
+        <v>12463784452.55294</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18409,19 +18409,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>11349464892.190201</v>
+        <v>11349471854.164124</v>
       </c>
       <c r="C58" s="118">
-        <v>11671117445.699352</v>
+        <v>11671124407.673277</v>
       </c>
       <c r="D58" s="118">
-        <v>11998938231.69342</v>
+        <v>11998945193.667343</v>
       </c>
       <c r="E58" s="118">
-        <v>12332987673.674282</v>
+        <v>12332994635.648207</v>
       </c>
       <c r="F58" s="118">
-        <v>12673326195.143841</v>
+        <v>12673333157.117767</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18435,19 +18435,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>11175948136.75572</v>
+        <v>11175955098.729645</v>
       </c>
       <c r="C59" s="118">
-        <v>11581676006.396149</v>
+        <v>11581682968.370075</v>
       </c>
       <c r="D59" s="118">
-        <v>11998938231.69342</v>
+        <v>11998945193.667343</v>
       </c>
       <c r="E59" s="118">
-        <v>12427960052.658009</v>
+        <v>12427967014.631935</v>
       </c>
       <c r="F59" s="118">
-        <v>12868968921.602537</v>
+        <v>12868975883.57646</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18461,19 +18461,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>11020299239.432344</v>
+        <v>11020306201.406269</v>
       </c>
       <c r="C60" s="118">
-        <v>11500626098.011559</v>
+        <v>11500633059.985481</v>
       </c>
       <c r="D60" s="118">
-        <v>11998938231.69342</v>
+        <v>11998945193.667343</v>
       </c>
       <c r="E60" s="118">
-        <v>12515760604.395824</v>
+        <v>12515767566.369747</v>
       </c>
       <c r="F60" s="118">
-        <v>13051628492.300814</v>
+        <v>13051635454.274738</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18487,19 +18487,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>10880678260.597643</v>
+        <v>10880685222.571568</v>
       </c>
       <c r="C61" s="118">
-        <v>11427180414.441076</v>
+        <v>11427187376.415001</v>
       </c>
       <c r="D61" s="118">
-        <v>11998938231.69342</v>
+        <v>11998945193.667343</v>
       </c>
       <c r="E61" s="118">
-        <v>12596930908.519566</v>
+        <v>12596937870.493492</v>
       </c>
       <c r="F61" s="118">
-        <v>13222166489.657555</v>
+        <v>13222173451.631481</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18513,19 +18513,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>10755434728.096037</v>
+        <v>10755441690.069962</v>
       </c>
       <c r="C62" s="118">
-        <v>11360625515.828009</v>
+        <v>11360632477.801933</v>
       </c>
       <c r="D62" s="118">
-        <v>11998938231.69342</v>
+        <v>11998945193.667343</v>
       </c>
       <c r="E62" s="118">
-        <v>12671971647.343351</v>
+        <v>12671978609.317276</v>
       </c>
       <c r="F62" s="118">
-        <v>13381387320.141659</v>
+        <v>13381394282.115583</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18539,19 +18539,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>10643088126.858898</v>
+        <v>10643095088.832821</v>
       </c>
       <c r="C63" s="118">
-        <v>11300314898.320515</v>
+        <v>11300321860.294441</v>
       </c>
       <c r="D63" s="118">
-        <v>11998938231.69342</v>
+        <v>11998945193.667341</v>
       </c>
       <c r="E63" s="118">
-        <v>12741345694.219337</v>
+        <v>12741352656.193264</v>
       </c>
       <c r="F63" s="118">
-        <v>13530042008.557018</v>
+        <v>13530048970.530945</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18565,19 +18565,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>10542310397.602699</v>
+        <v>10542317359.576622</v>
       </c>
       <c r="C64" s="118">
-        <v>11245662714.03455</v>
+        <v>11245669676.008476</v>
       </c>
       <c r="D64" s="118">
-        <v>11998938231.693419</v>
+        <v>11998945193.667339</v>
       </c>
       <c r="E64" s="118">
-        <v>12805480968.676777</v>
+        <v>12805487930.650703</v>
       </c>
       <c r="F64" s="118">
-        <v>13668831740.532913</v>
+        <v>13668838702.506838</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18591,19 +18591,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>10451910237.720707</v>
+        <v>10451917199.694632</v>
       </c>
       <c r="C65" s="118">
-        <v>11196138080.219349</v>
+        <v>11196145042.193275</v>
       </c>
       <c r="D65" s="118">
-        <v>11998938231.693417</v>
+        <v>11998945193.667339</v>
       </c>
       <c r="E65" s="118">
-        <v>12864773075.955505</v>
+        <v>12864780037.929432</v>
       </c>
       <c r="F65" s="118">
-        <v>13798411169.929176</v>
+        <v>13798418131.903101</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18617,19 +18617,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>10121792533.621948</v>
+        <v>10121799495.595875</v>
       </c>
       <c r="C66" s="281">
-        <v>11010084105.787693</v>
+        <v>11010091067.76162</v>
       </c>
       <c r="D66" s="118">
-        <v>11998938231.693417</v>
+        <v>11998945193.667341</v>
       </c>
       <c r="E66" s="118">
-        <v>13100462766.916977</v>
+        <v>13100469728.890903</v>
       </c>
       <c r="F66" s="118">
-        <v>14328181785.726475</v>
+        <v>14328188747.700397</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18652,19 +18652,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>9930061697.4670219</v>
+        <v>9930068659.4409447</v>
       </c>
       <c r="C67" s="281">
-        <v>10896397919.865473</v>
+        <v>10896404881.839397</v>
       </c>
       <c r="D67" s="118">
-        <v>11998938231.693417</v>
+        <v>11998945193.667339</v>
       </c>
       <c r="E67" s="118">
-        <v>13259625074.720104</v>
+        <v>13259632036.694031</v>
       </c>
       <c r="F67" s="118">
-        <v>14704003177.638714</v>
+        <v>14704010139.61264</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18687,19 +18687,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>9818705314.3459568</v>
+        <v>9818712276.3198814</v>
       </c>
       <c r="C68" s="281">
-        <v>10826931256.178101</v>
+        <v>10826938218.152027</v>
       </c>
       <c r="D68" s="118">
-        <v>11998938231.693415</v>
+        <v>11998945193.667339</v>
       </c>
       <c r="E68" s="118">
-        <v>13367108096.662539</v>
+        <v>13367115058.636463</v>
       </c>
       <c r="F68" s="118">
-        <v>14970612374.916088</v>
+        <v>14970619336.890015</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18722,19 +18722,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>9754030041.9146328</v>
+        <v>9754037003.8885574</v>
       </c>
       <c r="C69" s="281">
-        <v>10784484433.596193</v>
+        <v>10784491395.570122</v>
       </c>
       <c r="D69" s="118">
-        <v>11998938231.693413</v>
+        <v>11998945193.667339</v>
       </c>
       <c r="E69" s="118">
-        <v>13439691864.549141</v>
+        <v>13439698826.523062</v>
       </c>
       <c r="F69" s="118">
-        <v>15159746004.886471</v>
+        <v>15159752966.860397</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18831,23 +18831,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18862,23 +18862,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>16.747784130838728</v>
+        <v>16.765300309410762</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>16.855072579373211</v>
+        <v>16.872701748137768</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>17.069649476442176</v>
+        <v>17.087504625591784</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>17.176937924976659</v>
+        <v>17.194906064318793</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>16.555303252918744</v>
+        <v>16.572616721397097</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>16.757850095117703</v>
+        <v>16.775376874600255</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>17.168836051288704</v>
+        <v>17.186795658190665</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>17.37727516526073</v>
+        <v>17.39545428857792</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18924,23 +18924,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>16.382643060368089</v>
+        <v>16.399774692789865</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>16.669749171169926</v>
+        <v>16.687183167687536</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>17.260532564419126</v>
+        <v>17.278588740959425</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>17.564317714541964</v>
+        <v>17.582693820609322</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18955,23 +18955,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>16.227762521512581</v>
+        <v>16.244731042414504</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>16.589914008965529</v>
+        <v>16.607263927556104</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>17.34530462690126</v>
+        <v>17.363450080635808</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>17.738947829202708</v>
+        <v>17.757507845938409</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18986,23 +18986,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>16.088830779564393</v>
+        <v>16.105652985327225</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>16.517569102254001</v>
+        <v>16.534842831235633</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>17.423675137754309</v>
+        <v>17.441903126927013</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>17.901989217718913</v>
+        <v>17.920720940524834</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -19017,23 +19017,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>15.964205509899198</v>
+        <v>15.980896467299271</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>16.452011703952468</v>
+        <v>16.469216391549345</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>17.49612750934385</v>
+        <v>17.514431801301495</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>18.054210925990336</v>
+        <v>18.073102960184471</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19049,23 +19049,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>15.852413505989002</v>
+        <v>15.86898673030395</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>16.392604999770764</v>
+        <v>16.409747123549874</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>17.563108649211529</v>
+        <v>17.581483481958909</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>18.196330964834143</v>
+        <v>18.215372671903314</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19080,23 +19080,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>15.752133264495191</v>
+        <v>15.768600879269242</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>16.338771922297184</v>
+        <v>16.355857352090396</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>17.62503171673222</v>
+        <v>17.643471763390476</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>18.329019696752379</v>
+        <v>18.348201144171703</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19112,23 +19112,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>15.662179363658634</v>
+        <v>15.67855224401614</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>16.289989545456137</v>
+        <v>16.307023600378837</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>16.962361027907694</v>
+        <v>16.98010318686477</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>17.68227867160261</v>
+        <v>17.700779007551468</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>18.452902997948353</v>
+        <v>18.472214912330742</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19144,23 +19144,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>15.581488450322407</v>
+        <v>15.597776351523658</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>16.245784004886215</v>
+        <v>16.262771505006345</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>16.962361027907694</v>
+        <v>16.98010318686477</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>17.735202629880952</v>
+        <v>17.753758702382225</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>18.568565210506613</v>
+        <v>18.587998933861389</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19176,23 +19176,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>15.286826371328747</v>
+        <v>15.30280395091113</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>16.079712781712239</v>
+        <v>16.096525384909771</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>16.962361027907694</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>17.945578545724906</v>
+        <v>17.964356174372799</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>19.04143688355655</v>
+        <v>19.061368608906005</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19208,23 +19208,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>15.115687998296496</v>
+        <v>15.131485344517491</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>15.978236830920215</v>
+        <v>15.994942565322706</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>16.962361027907694</v>
+        <v>16.98010318686477</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>18.08764634739806</v>
+        <v>18.106573593907719</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>19.376893938104647</v>
+        <v>19.397178948059256</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19240,23 +19240,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>15.016291622542436</v>
+        <v>15.031984290060498</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>15.916231093909666</v>
+        <v>15.932871527338399</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>16.96236102790769</v>
+        <v>16.98010318686477</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>18.183585372505913</v>
+        <v>18.202613656630206</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>19.614868513152221</v>
+        <v>19.635404144617507</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19272,23 +19272,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>14.958562667089643</v>
+        <v>14.974194537701051</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>15.878343186556117</v>
+        <v>15.894943718560192</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>16.96236102790769</v>
+        <v>16.98010318686477</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>18.248373427436348</v>
+        <v>18.267469942715994</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>19.783688627683304</v>
+        <v>19.804402051049799</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>17.564317714541964</v>
+        <v>17.582693820609322</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>17.260532564419126</v>
+        <v>17.278588740959425</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>16.669749171169926</v>
+        <v>16.687183167687536</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>16.382643060368089</v>
+        <v>16.399774692789865</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>1207921118.4237735</v>
+        <v>1207925186.645268</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>1109901786.4316416</v>
+        <v>1109902430.4142294</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C14" s="252">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7254131105641166E-2</v>
+        <v>-7.7253509313970459E-2</v>
       </c>
       <c r="D14" s="465"/>
       <c r="E14" s="465"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>17.260532564419126</v>
+        <v>17.278588740959425</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>16.669749171169926</v>
+        <v>16.687183167687536</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>16.948842371025538</v>
+        <v>16.966570292889397</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19917,7 +19917,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>17.564317714541964</v>
+        <v>17.582693820609322</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19940,7 +19940,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>16.382643060368089</v>
+        <v>16.399774692789865</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.59471431199999991</v>
+        <v>0.59534063184642794</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.6</v>
+        <v>10.210000000000001</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.21934387142409759</v>
+        <v>0.23583181729627789</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20005,7 +20005,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20016,7 +20016,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.6018174802351255E-2</v>
+        <v>3.6018432604125329E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>17.012853707020131</v>
+        <v>17.030649042042409</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>17.014170240778682</v>
+        <v>17.031966962300672</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.39720564923589674</v>
+        <v>0.39720097817365574</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.59471431199999991</v>
+        <v>0.59534063184642794</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20265,15 +20265,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.0882389211484453</v>
+        <v>1.0893849935065805</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>7.8400247497788644</v>
+        <v>7.8482253649965035</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>8.9282636709273095</v>
+        <v>8.9376103585030844</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.47520481721163699</v>
+        <v>0.47520436030127733</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20290,15 +20290,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2512812599454139</v>
+        <v>1.2525990393745514</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>9.8269191087480934</v>
+        <v>9.8371980026237775</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>11.078200368693507</v>
+        <v>11.089797041998329</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34883350204074037</v>
+        <v>0.34883297667506985</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20336,15 +20336,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4348096081716528</v>
+        <v>1.4363206693909827</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>12.194139709347091</v>
+        <v>12.206894700671489</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>13.628949317518744</v>
+        <v>13.643215370062471</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19890280888649881</v>
+        <v>0.19890220646421697</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20361,15 +20361,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5536169359140437</v>
+        <v>1.555253118365139</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>13.790666783359127</v>
+        <v>13.805091731684474</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>15.34428371927317</v>
+        <v>15.360344850049612</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>9.8077019674744359E-2</v>
+        <v>9.8076367369759665E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20488,7 +20488,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>10.6</v>
+        <v>10.210000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20506,14 +20506,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>13078.714599999999</v>
+        <v>12597.516610000002</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.21934387142409759</v>
+        <v>0.23583181729627789</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20521,13 +20521,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.1013227999999999</v>
+        <v>1.1024826515674591</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>17.012853707020131</v>
+        <v>17.030649042042409</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20643,7 +20643,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>8.9282636709273095</v>
+        <v>8.9376103585030844</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>11.078200368693507</v>
+        <v>11.089797041998329</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>13.628949317518744</v>
+        <v>13.643215370062471</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>15.34428371927317</v>
+        <v>15.360344850049612</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20712,22 +20712,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>11582977.929449307</v>
+        <v>11583836.572900016</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-2573944.9000506923</v>
+        <v>-2573086.2565999832</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-389569088.14388049</v>
+        <v>-389569302.80474317</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20917,10 +20917,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20936,22 +20936,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>1207921118.4237735</v>
+        <v>1207925186.645268</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>1109901786.4316416</v>
+        <v>1109902430.4142294</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.3461795026699143E-2</v>
+        <v>9.7134079068640064E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20995,14 +20995,14 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.6105123773584897E-2</v>
+        <v>5.8309562374772562E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>0.73458241521182999</v>
+        <v>0.73535560965568947</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21022,11 +21022,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095643717340666</v>
+        <v>0.10095649280255321</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>8.8887524700525647E-2</v>
+        <v>8.888778826940226E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21036,11 +21036,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639612253563595</v>
+        <v>0.12639619218259082</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128600392899436</v>
+        <v>0.11128633391373786</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21086,22 +21086,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21109,13 +21109,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25272854265612604</v>
+        <v>-0.25299470222018966</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>6704022426.6051159</v>
+        <v>6703879319.3633308</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.983990441338503</v>
+        <v>5.9901645737173084</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52088261805763436</v>
+        <v>0.52143118249397991</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>6.252144516740012</v>
+        <v>6.2586010539910992</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21264,33 +21264,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21353,23 +21353,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.7185175102008612</v>
+        <v>1.7203273567126307</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>16.962361027907697</v>
+        <v>16.980103186864778</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21413,13 +21413,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21464,7 +21464,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.56 HKD</v>
+        <v>17.58 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.26 HKD</v>
+        <v>17.28 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>16.96 HKD</v>
+        <v>16.98 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.67 HKD</v>
+        <v>16.69 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.38 HKD</v>
+        <v>16.4 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>17.012853707020131</v>
+        <v>17.030649042042409</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21583,13 +21583,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21602,22 +21602,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C136" s="410">
         <f>Scenarios!C58</f>
-        <v>0.59471431199999991</v>
+        <v>0.59534063184642794</v>
       </c>
       <c r="D136" s="347" t="str">
         <f>Market_currency</f>
@@ -21678,15 +21678,15 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>1.0882389211484453</v>
+        <v>1.0893849935065805</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>7.8400247497788644</v>
+        <v>7.8482253649965035</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>8.9282636709273095</v>
+        <v>8.9376103585030844</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21699,15 +21699,15 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>1.2512812599454139</v>
+        <v>1.2525990393745514</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>9.8269191087480934</v>
+        <v>9.8371980026237775</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>11.078200368693507</v>
+        <v>11.089797041998329</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21739,15 +21739,15 @@
       </c>
       <c r="C144" s="413">
         <f>Scenarios!C66</f>
-        <v>1.4348096081716528</v>
+        <v>1.4363206693909827</v>
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>12.194139709347091</v>
+        <v>12.206894700671489</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>13.628949317518744</v>
+        <v>13.643215370062471</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21760,15 +21760,15 @@
       </c>
       <c r="C145" s="413">
         <f>Scenarios!C67</f>
-        <v>1.5536169359140437</v>
+        <v>1.555253118365139</v>
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>13.790666783359127</v>
+        <v>13.805091731684474</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>15.34428371927317</v>
+        <v>15.360344850049612</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21786,13 +21786,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21800,13 +21800,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21843,22 +21843,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21882,12 +21882,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21902,15 +21905,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E420E1-8388-44A0-9E70-C7D91EC23913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C6FEFB-B7C2-4447-B497-7DC96FEC5689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3252,16 +3252,16 @@
     <t>Historical Average or D&amp;A</t>
   </si>
   <si>
+    <t>新华文轩</t>
+  </si>
+  <si>
     <t>0811.HK</t>
   </si>
   <si>
-    <t>新华文轩</t>
+    <t>CNS_04</t>
   </si>
   <si>
     <t>CNY</t>
-  </si>
-  <si>
-    <t>CNS_04</t>
   </si>
 </sst>
 </file>
@@ -5345,7 +5345,7 @@
         <v>536</v>
       </c>
       <c r="C4" s="425" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E4" s="435" t="s">
         <v>540</v>
@@ -5359,7 +5359,7 @@
         <v>349</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E5" s="438" t="s">
         <v>542</v>
@@ -5373,7 +5373,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
@@ -5393,7 +5393,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.210000000000001</v>
+        <v>10.43</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12597.516610000002</v>
+        <v>12868.96163</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.23583181729627789</v>
+        <v>0.22759647505526587</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.1024826515674591</v>
+        <v>1.10486085128784</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5482,7 +5482,7 @@
         <v>274</v>
       </c>
       <c r="E17" s="224" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>17.030649042042409</v>
+        <v>17.067136411217234</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,13 +5542,13 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>8.9376103585030844</v>
+        <v>8.9567747606976056</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5557,13 +5557,13 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>11.089797041998329</v>
+        <v>11.11357479916931</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E23" s="448">
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>13.643215370062471</v>
+        <v>13.672466403255225</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>15.360344850049612</v>
+        <v>15.393276498541292</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>11583836.572900016</v>
+        <v>11585597.165092731</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-2573086.2565999832</v>
+        <v>-2571325.6644072682</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-389569302.80474317</v>
+        <v>-389569742.95279133</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>1207925186.645268</v>
+        <v>1207933528.2671547</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>1109902430.4142294</v>
+        <v>1109903750.8583741</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.7134079068640064E-2</v>
+        <v>9.5290454527600446E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5894,14 +5894,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.8309562374772562E-2</v>
+        <v>5.7202766989015684E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.73535560965568947</v>
+        <v>0.73694099144699055</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5921,11 +5921,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095649280255321</v>
+        <v>0.10095660686647698</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.888778826940226E-2</v>
+        <v>8.8888328700131733E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5935,11 +5935,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639619218259082</v>
+        <v>0.12639633498911301</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128633391373786</v>
+        <v>0.11128701052585509</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25299470222018966</v>
+        <v>-0.25354044498468808</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>6703879319.3633308</v>
+        <v>6703585887.331212</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9901645737173084</v>
+        <v>6.0028233866097116</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52143118249397991</v>
+        <v>0.52255597796413267</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.2586010539910992</v>
+        <v>6.2718389195891557</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7203273567126307</v>
+        <v>1.7240383285205596</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.58 HKD</v>
+        <v>17.62 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.3637310032024433E-2</v>
+        <v>2.3637648803494685E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.28 HKD</v>
+        <v>17.32 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.9812022775325912E-2</v>
+        <v>2.9812455141453607E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>16.98 HKD</v>
+        <v>17.02 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.6018432604125329E-2</v>
+        <v>3.601896122133004E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.69 HKD</v>
+        <v>16.72 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.2255479584906545E-2</v>
+        <v>4.2256107151175795E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.4 HKD</v>
+        <v>16.43 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.8522038867152312E-2</v>
+        <v>4.8522768120495594E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>17.030649042042409</v>
+        <v>17.067136411217234</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.59534063184642794</v>
+        <v>0.59662485969543355</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,19 +6566,19 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>1.0893849935065805</v>
+        <v>1.0917349398601683</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>7.8482253649965035</v>
+        <v>7.8650398208374366</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>8.9376103585030844</v>
+        <v>8.9567747606976056</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6587,19 +6587,19 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>1.2525990393745514</v>
+        <v>1.2553010598380527</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>9.8371980026237775</v>
+        <v>9.8582737393312581</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>11.089797041998329</v>
+        <v>11.11357479916931</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6634,15 +6634,15 @@
       </c>
       <c r="C144" s="337">
         <f>Scenarios!C66</f>
-        <v>1.4363206693909827</v>
+        <v>1.4394190015139108</v>
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>12.206894700671489</v>
+        <v>12.233047401741313</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>13.643215370062471</v>
+        <v>13.672466403255225</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,15 +6655,15 @@
       </c>
       <c r="C145" s="337">
         <f>Scenarios!C67</f>
-        <v>1.555253118365139</v>
+        <v>1.5586080033839271</v>
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>13.805091731684474</v>
+        <v>13.834668495157365</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>15.360344850049612</v>
+        <v>15.393276498541292</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -7013,7 +7013,7 @@
         <v>2126015036.6900001</v>
       </c>
       <c r="J6" s="291">
-        <v>1963522925.3899999</v>
+        <v>1963522925.3900001</v>
       </c>
       <c r="K6" s="291">
         <v>1800975493.3800001</v>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.66148959094047544</v>
+        <v>0.66291651077270397</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="J39" s="274">
         <f t="shared" si="13"/>
-        <v>-1963522925.3899999</v>
+        <v>-1963522925.3900001</v>
       </c>
       <c r="K39" s="274">
         <f t="shared" si="13"/>
@@ -7980,7 +7980,7 @@
       </c>
       <c r="J41" s="286">
         <f t="shared" si="15"/>
-        <v>-1071006550.5599998</v>
+        <v>-1071006550.5600001</v>
       </c>
       <c r="K41" s="286">
         <f t="shared" si="15"/>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="J43" s="275">
         <f t="shared" si="17"/>
-        <v>695381120.13999987</v>
+        <v>695381120.13999963</v>
       </c>
       <c r="K43" s="275">
         <f t="shared" si="17"/>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="J44" s="294">
         <f t="shared" si="18"/>
-        <v>221659135.77000022</v>
+        <v>221659135.77000046</v>
       </c>
       <c r="K44" s="294">
         <f t="shared" si="18"/>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="J58" s="289">
         <f t="shared" si="28"/>
-        <v>221659135.77000022</v>
+        <v>221659135.77000046</v>
       </c>
       <c r="K58" s="289">
         <f t="shared" si="28"/>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.66148959094047544</v>
+        <v>0.66291651077270397</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -9028,11 +9028,11 @@
       </c>
       <c r="I70" s="98">
         <f t="shared" si="36"/>
-        <v>0.34019644735590715</v>
+        <v>0.34019644735590782</v>
       </c>
       <c r="J70" s="98">
         <f t="shared" si="36"/>
-        <v>0.20339202979420512</v>
+        <v>0.2033920297942049</v>
       </c>
       <c r="K70" s="98">
         <f t="shared" si="36"/>
@@ -9077,11 +9077,11 @@
       </c>
       <c r="I71" s="98">
         <f t="shared" si="37"/>
-        <v>-1.2323779762159051</v>
+        <v>-1.2323779762159046</v>
       </c>
       <c r="J71" s="98">
         <f t="shared" si="37"/>
-        <v>2.8306121712027603</v>
+        <v>2.8306121712027643</v>
       </c>
       <c r="K71" s="98">
         <f t="shared" si="37"/>
@@ -10216,11 +10216,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.390815533685876</v>
+        <v>13.419701279609049</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7203273567126307</v>
+        <v>1.7240383285205596</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6703879319.3633308</v>
+        <v>6703585887.331212</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10478,11 +10478,11 @@
       </c>
       <c r="C73" s="289">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-984594472.56963217</v>
+        <v>-984741188.58569193</v>
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-965319714.40833461</v>
+        <v>-965466430.42439425</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10494,11 +10494,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7696193597809913</v>
+        <v>8.7683127793010218</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9447243429315897</v>
+        <v>8.9433650679956713</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10511,7 +10511,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1930639428.8166692</v>
+        <v>1930932860.8487885</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10625,12 +10625,12 @@
         <v>239</v>
       </c>
       <c r="C86" s="73">
-        <f>-DCF!F4*Exchange_Rate</f>
-        <v>312155236.38206106</v>
+        <f>DCF!F4*Exchange_Rate</f>
+        <v>-312828596.18035251</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.25299470222018966</v>
+        <v>-0.25354044498468808</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10643,11 +10643,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7390910647.7999372</v>
+        <v>7406529610.1579132</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.9901645737173084</v>
+        <v>6.0028233866097116</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10660,11 +10660,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>643363171.63955462</v>
+        <v>644750990.40724337</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.52143118249397991</v>
+        <v>0.52255597796413267</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10677,11 +10677,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>8346429055.8215532</v>
+        <v>7738452004.3848047</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.7645904584314778</v>
+        <v>6.2718389195891557</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="N7" s="270">
         <f t="shared" si="3"/>
-        <v>-1071006550.5599998</v>
+        <v>-1071006550.5600001</v>
       </c>
       <c r="O7" s="270">
         <f t="shared" si="3"/>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="N8" s="271">
         <f t="shared" si="4"/>
-        <v>695381120.13999999</v>
+        <v>695381120.13999975</v>
       </c>
       <c r="O8" s="271">
         <f t="shared" si="4"/>
@@ -11162,36 +11162,36 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-2573086.2565999832</v>
+        <v>-2571325.6644072682</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>42441914.105266996</v>
+        <v>42450255.727153838</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40911615.674355939</v>
+        <v>40920550.543259837</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>17686926.388097338</v>
+        <v>17692802.981277198</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>5052814.6641418189</v>
+        <v>5056544.5242806152</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
-        <v>-4709193.9571538419</v>
+        <v>-4706541.0609545261</v>
       </c>
       <c r="L10" s="270">
         <f t="shared" si="6"/>
-        <v>-6428577.2510438897</v>
+        <v>-6426599.635417629</v>
       </c>
       <c r="M10" s="270">
         <f t="shared" si="6"/>
-        <v>7532673.8342542714</v>
+        <v>7533897.1904013557</v>
       </c>
       <c r="N10" s="270">
         <f t="shared" si="6"/>
@@ -11217,40 +11217,40 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>1558277211.2189727</v>
+        <v>1558278971.8111653</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1371995113.645268</v>
+        <v>1372003455.2671547</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>1481896283.9943557</v>
+        <v>1481905218.8632596</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>1407214425.3880973</v>
+        <v>1407220301.9812772</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>1240507132.6641419</v>
+        <v>1240510862.5242805</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
-        <v>1157446497.0428462</v>
+        <v>1157449149.9390454</v>
       </c>
       <c r="L11" s="271">
         <f t="shared" si="7"/>
-        <v>999257237.32895815</v>
+        <v>999259214.94458449</v>
       </c>
       <c r="M11" s="271">
         <f t="shared" si="7"/>
-        <v>939479980.60425329</v>
+        <v>939481203.96040034</v>
       </c>
       <c r="N11" s="271">
         <f t="shared" si="7"/>
-        <v>695381120.13999999</v>
+        <v>695381120.13999975</v>
       </c>
       <c r="O11" s="271">
         <f t="shared" si="7"/>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-389569302.80474317</v>
+        <v>-389569742.95279133</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11384,42 +11384,42 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>1109902430.4142294</v>
+        <v>1109903750.8583741</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207925186.645268</v>
+        <v>1207933528.2671547</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>1497870226.9943557</v>
+        <v>1497879161.8632596</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>1418649902.3880973</v>
+        <v>1418655778.9812772</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>1235054320.6641419</v>
+        <v>1235058050.5242805</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
-        <v>1149275946.0428462</v>
+        <v>1149278598.9390454</v>
       </c>
       <c r="L14" s="271">
         <f t="shared" si="8"/>
-        <v>975085162.20895815</v>
+        <v>975087139.82458448</v>
       </c>
       <c r="M14" s="271">
         <f t="shared" si="8"/>
-        <v>950275826.9742533</v>
+        <v>950277050.33040035</v>
       </c>
       <c r="N14" s="271">
         <f t="shared" si="8"/>
-        <v>694821234.92999995</v>
+        <v>694821234.92999971</v>
       </c>
       <c r="O14" s="271">
         <f t="shared" si="8"/>
@@ -11602,42 +11602,42 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>1109902430.4142294</v>
+        <v>1109903750.8583741</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207925186.645268</v>
+        <v>1207933528.2671547</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>1497870226.9943557</v>
+        <v>1497879161.8632596</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>1418649902.3880973</v>
+        <v>1418655778.9812772</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>1235054320.6641419</v>
+        <v>1235058050.5242805</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
-        <v>1149275946.0428462</v>
+        <v>1149278598.9390454</v>
       </c>
       <c r="L19" s="275">
         <f t="shared" si="9"/>
-        <v>975085162.20895815</v>
+        <v>975087139.82458448</v>
       </c>
       <c r="M19" s="275">
         <f t="shared" si="9"/>
-        <v>950275826.9742533</v>
+        <v>950277050.33040035</v>
       </c>
       <c r="N19" s="275">
         <f t="shared" si="9"/>
-        <v>694821234.92999995</v>
+        <v>694821234.92999971</v>
       </c>
       <c r="O19" s="275">
         <f t="shared" si="9"/>
@@ -12234,7 +12234,7 @@
       </c>
       <c r="N35" s="271">
         <f>IF(N4="","",Data!J41)</f>
-        <v>-1071006550.5599998</v>
+        <v>-1071006550.5600001</v>
       </c>
       <c r="O35" s="271">
         <f>IF(O4="","",Data!K41)</f>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="N38" s="29">
         <f t="shared" si="15"/>
-        <v>0.14579684385567238</v>
+        <v>0.1457968438556724</v>
       </c>
       <c r="O38" s="29">
         <f t="shared" si="15"/>
@@ -12341,35 +12341,35 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.6723632579362322E-2</v>
+        <v>7.672316610857445E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.3982999825275391E-2</v>
+        <v>-4.3982734638047201E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.12632161359929E-3</v>
+        <v>-8.1262876778423181E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3956313159517384E-3</v>
+        <v>4.3956180995499122E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.0591176532780534E-3</v>
+        <v>7.0591014736416579E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4190042580639812E-2</v>
+        <v>2.4189994706569209E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.149130007331965E-2</v>
+        <v>-1.1491285109792415E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
-        <v>8.051487073552977E-4</v>
+        <v>8.0514870735529803E-4</v>
       </c>
       <c r="O41" s="6">
         <f t="shared" si="16"/>
@@ -12479,36 +12479,36 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>11583836.572900016</v>
+        <v>11585597.165092731</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54883797.105266996</v>
+        <v>54892138.727153838</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>58787072.674355939</v>
+        <v>58796007.543259837</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>38665112.388097338</v>
+        <v>38670988.981277198</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>24540657.664141819</v>
+        <v>24544387.524280615</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
-        <v>17454761.042846158</v>
+        <v>17457413.939045474</v>
       </c>
       <c r="L46" s="278">
         <f t="shared" si="17"/>
-        <v>13011744.74895611</v>
+        <v>13013722.364582371</v>
       </c>
       <c r="M46" s="278">
         <f t="shared" si="17"/>
-        <v>8049085.8342542714</v>
+        <v>8050309.1904013557</v>
       </c>
       <c r="N46" s="278">
         <f t="shared" si="17"/>
@@ -12591,36 +12591,36 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-2573086.2565999832</v>
+        <v>-2571325.6644072682</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42441914.105266996</v>
+        <v>42450255.727153838</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40911615.674355939</v>
+        <v>40920550.543259837</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>17686926.388097338</v>
+        <v>17692802.981277198</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>5052814.6641418189</v>
+        <v>5056544.5242806152</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
-        <v>-4709193.9571538419</v>
+        <v>-4706541.0609545261</v>
       </c>
       <c r="L48" s="271">
         <f t="shared" si="18"/>
-        <v>-6428577.2510438897</v>
+        <v>-6426599.635417629</v>
       </c>
       <c r="M48" s="271">
         <f t="shared" si="18"/>
-        <v>7532673.8342542714</v>
+        <v>7533897.1904013557</v>
       </c>
       <c r="N48" s="271">
         <f t="shared" si="18"/>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="N60" s="270">
         <f>Data!J58</f>
-        <v>221659135.77000022</v>
+        <v>221659135.77000046</v>
       </c>
       <c r="O60" s="270">
         <f>Data!K58</f>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="N61" s="271">
         <f t="shared" si="21"/>
-        <v>221659135.77000022</v>
+        <v>221659135.77000046</v>
       </c>
       <c r="O61" s="271">
         <f t="shared" si="21"/>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="N73" s="6">
         <f t="shared" si="25"/>
-        <v>0.14579684385567238</v>
+        <v>0.1457968438556724</v>
       </c>
       <c r="O73" s="6">
         <f t="shared" si="25"/>
@@ -13477,7 +13477,7 @@
       </c>
       <c r="N74" s="62">
         <f t="shared" si="26"/>
-        <v>9.4662700746529549E-2</v>
+        <v>9.4662700746529521E-2</v>
       </c>
       <c r="O74" s="62">
         <f t="shared" si="26"/>
@@ -13556,38 +13556,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0871017213758947E-4</v>
+        <v>2.0856736561539725E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.442581520941275E-3</v>
+        <v>3.4432581330585111E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4470782896010919E-3</v>
+        <v>3.4478311122924325E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.618155253171937E-3</v>
+        <v>1.618692895491246E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8304386652993342E-4</v>
+        <v>4.8340043730935386E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2277579841156067E-4</v>
+        <v>5.2248129579788227E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.2701249492528096E-4</v>
+        <v>7.2678884493021913E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.2012428932398374E-4</v>
+        <v>9.2027372360591259E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13613,42 +13613,42 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639619218259082</v>
+        <v>0.12639633498911301</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.11128633391373786</v>
+        <v>0.11128701052585509</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12485971095977487</v>
+        <v>0.12486046378246622</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12874432588318332</v>
+        <v>0.12874486352550266</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11859120146885913</v>
+        <v>0.11859155803963853</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12849014547193152</v>
+        <v>0.12849043997454521</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300673054285891</v>
+        <v>0.11300695419285398</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11475849990432743</v>
+        <v>0.11475864933860937</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
-        <v>9.4662700746529549E-2</v>
+        <v>9.4662700746529521E-2</v>
       </c>
       <c r="O77" s="62">
         <f t="shared" si="29"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1599048045647705E-2</v>
+        <v>3.1599083747278253E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13785,42 +13785,42 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.0027268504312391E-2</v>
+        <v>9.0027375609204055E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.7978166486805296E-2</v>
+        <v>9.7978843098922533E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12620562290206808</v>
+        <v>0.12620637572475943</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12979054368123613</v>
+        <v>0.12979108132355544</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11806991826988626</v>
+        <v>0.11807027484066568</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758311841775835</v>
+        <v>0.12758341292037201</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11027309291912826</v>
+        <v>0.11027331656912333</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.1160772242626921</v>
+        <v>0.11607737369697402</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
-        <v>9.4586483195388718E-2</v>
+        <v>9.458648319538869E-2</v>
       </c>
       <c r="O80" s="62">
         <f t="shared" si="32"/>
@@ -14008,42 +14008,42 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.0027268504312391E-2</v>
+        <v>9.0027375609204055E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.7978166486805296E-2</v>
+        <v>9.7978843098922533E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12620562290206808</v>
+        <v>0.12620637572475943</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12979054368123613</v>
+        <v>0.12979108132355544</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11806991826988626</v>
+        <v>0.11807027484066568</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758311841775835</v>
+        <v>0.12758341292037201</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11027309291912826</v>
+        <v>0.11027331656912333</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.1160772242626921</v>
+        <v>0.11607737369697402</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
-        <v>9.4586483195388718E-2</v>
+        <v>9.458648319538869E-2</v>
       </c>
       <c r="O85" s="62">
         <f t="shared" si="35"/>
@@ -14077,12 +14077,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.66148959094047544</v>
+        <v>0.66291651077270397</v>
       </c>
       <c r="E88" s="238"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.66148959094047544</v>
+        <v>0.66291651077270397</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14133,12 +14133,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>816172978.37558711</v>
+        <v>817933570.56830382</v>
       </c>
       <c r="E89" s="238"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>816172978.37558711</v>
+        <v>817933570.56830382</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.73535560965568947</v>
+        <v>0.73694099144699055</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.67568172880169697</v>
+        <v>0.67713458681925431</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14264,12 +14264,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8309562374772562E-2</v>
+        <v>5.7202766989015684E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.8309562374772562E-2</v>
+        <v>5.7202766989015684E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14401,42 +14401,42 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.13577460715495548</v>
+        <v>0.13576898500429757</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162525094439324E-2</v>
+        <v>-7.4162478272671417E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.3070702843073692E-2</v>
+        <v>5.3072654492569926E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.13438640402327318</v>
+        <v>0.13438773048529717</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1761965528002181E-2</v>
+        <v>7.1762731511452849E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830684412827689</v>
+        <v>0.15830720660728015</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3628026098286217E-2</v>
+        <v>6.3628746091128674E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35102888674214983</v>
+        <v>0.35103064600208933</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
-        <v>0.20339202979420601</v>
+        <v>0.20339202979420556</v>
       </c>
       <c r="O96" s="6">
         <f t="shared" si="40"/>
@@ -15012,35 +15012,35 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4673746781641741</v>
+        <v>1.4673645449205435</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5709159369043701</v>
+        <v>1.5709065663701425</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.4269772419483056</v>
+        <v>1.4269713308845704</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.6576838303752199</v>
+        <v>1.6576788241904186</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.5825662202906603</v>
+        <v>1.5825625672304584</v>
       </c>
       <c r="L113" s="254">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3992731840253461</v>
+        <v>1.3992703460999942</v>
       </c>
       <c r="M113" s="254">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.0454335928266398</v>
+        <v>1.0454322469690169</v>
       </c>
       <c r="N113" s="254">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>0.49742560109697831</v>
+        <v>0.49742560109697848</v>
       </c>
       <c r="O113" s="254">
         <f>IF(O$4="","",Data!K$22/O19)</f>
@@ -15120,40 +15120,40 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639619218259082</v>
+        <v>0.12639633498911301</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.11128633391373786</v>
+        <v>0.11128701052585509</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12485971095977487</v>
+        <v>0.12486046378246622</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12874432588318332</v>
+        <v>0.12874486352550266</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11859120146885913</v>
+        <v>0.11859155803963853</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12849014547193152</v>
+        <v>0.12849043997454521</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300673054285891</v>
+        <v>0.11300695419285398</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11475849990432743</v>
+        <v>0.11475864933860937</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
-        <v>9.4662700746529549E-2</v>
+        <v>9.4662700746529521E-2</v>
       </c>
       <c r="O116" s="22">
         <f t="shared" si="44"/>
@@ -15285,42 +15285,42 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.10095649280255321</v>
+        <v>0.10095660686647698</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.888778826940226E-2</v>
+        <v>8.8888328700131733E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11047256831540847</v>
+        <v>0.11047323439300516</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11113652802665631</v>
+        <v>0.11113699213798922</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11165993772698538</v>
+        <v>0.11166027345738132</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11541974293171826</v>
+        <v>0.11542000747664377</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.10956808408996896</v>
+        <v>0.10956830093458829</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176263372952511</v>
+        <v>0.1117627792627007</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
-        <v>8.7394326529514052E-2</v>
+        <v>8.7394326529514024E-2</v>
       </c>
       <c r="O119" s="99">
         <f t="shared" si="47"/>
@@ -15406,50 +15406,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.99173894729081535</v>
+        <v>0.9938794407228726</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0793259120646768</v>
+        <v>1.0816616292864094</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3384025490810316</v>
+        <v>1.3412976598302027</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2676162536588964</v>
+        <v>1.2703559305045526</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1035667985385882</v>
+        <v>1.1059506768636775</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.02692064242963</v>
+        <v>1.0291382205573407</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.87127472270431772</v>
+        <v>0.87315594747330938</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.84910666240061294</v>
+        <v>0.85093939234256577</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.62084851893477588</v>
+        <v>0.62218777064275521</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.51125759334506093</v>
+        <v>0.51236044304868855</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.48199045816984798</v>
+        <v>0.48303017482318134</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15463,50 +15463,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.7134079068640064E-2</v>
+        <v>9.5290454527600446E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10571262605922396</v>
+        <v>0.10370677174366341</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.13108741910685912</v>
+        <v>0.1285999673854461</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12415438331624841</v>
+        <v>0.12179826754597821</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10808685588037102</v>
+        <v>0.10603553948836794</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.10057988662386189</v>
+        <v>9.8670970331480423E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.5335428276622688E-2</v>
+        <v>8.3715814714603015E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.3164217669012039E-2</v>
+        <v>8.1585751902451181E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>6.0807886281564721E-2</v>
+        <v>5.9653669285019674E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>5.0074201111171487E-2</v>
+        <v>4.9123724165741955E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.7207684443667769E-2</v>
+        <v>4.6311617912097924E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15520,43 +15520,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12729982612025306</v>
+        <v>0.12461469076584697</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12925962754495623</v>
+        <v>0.12653315409721988</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11043725291821622</v>
+        <v>0.10810779983652807</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10345541128046187</v>
+        <v>0.10127322619113287</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8669839896325398E-2</v>
+        <v>9.6588596868790261E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9276740720248965E-2</v>
+        <v>8.7393626342640654E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3563424875690619E-2</v>
+        <v>7.2011751484257092E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2750876150660615E-2</v>
+        <v>7.1216341850263182E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0012872663320898E-2</v>
+        <v>4.8957951092282494E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8812779457807751E-2</v>
+        <v>4.7783171453903851E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>1109902430.4142294</v>
+        <v>1109903750.8583741</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>6703879319.3633308</v>
+        <v>6703585887.331212</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>11998945193.667345</v>
+        <v>11998959468.73918</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-2573086.2565999832</v>
+        <v>-2571325.6644072682</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16404,14 +16404,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>7004299407.413331</v>
+        <v>7004005975.3812122</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>7004299407.413331</v>
+        <v>7004005975.3812122</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>19003244601.080677</v>
+        <v>19002965444.120392</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.2586010539910992</v>
+        <v>6.2718389195891557</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-2573086.2565999832</v>
+        <v>-2571325.6644072682</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1024826515674591</v>
+        <v>1.10486085128784</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>20950747496.184425</v>
+        <v>20995632577.584263</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16591,14 +16591,14 @@
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
-        <v>1.7510817454651968E-3</v>
+        <v>1.7510817454652E-3</v>
       </c>
       <c r="E16" s="312" t="s">
         <v>401</v>
       </c>
       <c r="F16" s="315">
         <f>Scenarios!C41</f>
-        <v>1.7510817454651968E-3</v>
+        <v>1.7510817454652E-3</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>17.031966962300672</v>
+        <v>17.068457174402401</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16703,7 +16703,7 @@
       </c>
       <c r="D21" s="303">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
-        <v>1.7510817454651968E-3</v>
+        <v>1.7510817454652E-3</v>
       </c>
       <c r="E21" s="303">
         <f>$C$17</f>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>1561010387.6822858</v>
+        <v>1561012148.2744784</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16723,11 +16723,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>1111849339.5626552</v>
+        <v>1111850660.0067995</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>1.7541263944247376E-3</v>
+        <v>1.7541243075533952E-3</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>1017711065.9612404</v>
+        <v>1017712274.6057661</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16752,7 +16752,7 @@
       </c>
       <c r="D22" s="303">
         <f t="shared" si="1"/>
-        <v>1.7510817454651968E-3</v>
+        <v>1.7510817454652E-3</v>
       </c>
       <c r="E22" s="303">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>1563748350.1610112</v>
+        <v>1563750110.7532039</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16772,11 +16772,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>1113799657.9081511</v>
+        <v>1113800978.3522954</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>1.7541210630778181E-3</v>
+        <v>1.7541189798673251E-3</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>933177349.54523599</v>
+        <v>933178455.85601461</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="D23" s="303">
         <f t="shared" si="1"/>
-        <v>1.7510817454651968E-3</v>
+        <v>1.7510817454652E-3</v>
       </c>
       <c r="E23" s="303">
         <f t="shared" si="6"/>
@@ -16813,7 +16813,7 @@
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>1566491107.0358529</v>
+        <v>1566492867.6280456</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16821,11 +16821,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>1115753391.4204996</v>
+        <v>1115754711.8646438</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>1.7541157410820851E-3</v>
+        <v>1.7541136615255581E-3</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>855665217.96182549</v>
+        <v>855666230.60327041</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>1566491107.0358529</v>
+        <v>1566492867.6280456</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>12062198826.167562</v>
+        <v>12062213101.239393</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18285,7 +18285,7 @@
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>9250434788.7764912</v>
+        <v>9250445736.2515736</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18298,7 +18298,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>12056988422.244793</v>
+        <v>12057002697.316624</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18322,7 +18322,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>12056988422.244793</v>
+        <v>12057002697.316624</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18357,19 +18357,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>11758549032.563198</v>
+        <v>11758563307.635027</v>
       </c>
       <c r="C56" s="118">
-        <v>11878747113.115269</v>
+        <v>11878761388.187101</v>
       </c>
       <c r="D56" s="118">
-        <v>11998945193.667345</v>
+        <v>11998959468.739178</v>
       </c>
       <c r="E56" s="118">
-        <v>12119143274.219418</v>
+        <v>12119157549.29125</v>
       </c>
       <c r="F56" s="118">
-        <v>12239341354.771496</v>
+        <v>12239355629.843325</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18383,19 +18383,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>11542907624.890829</v>
+        <v>11542921899.962662</v>
       </c>
       <c r="C57" s="118">
-        <v>11769826198.015453</v>
+        <v>11769840473.087282</v>
       </c>
       <c r="D57" s="118">
-        <v>11998945193.667343</v>
+        <v>11998959468.739178</v>
       </c>
       <c r="E57" s="118">
-        <v>12230264611.846506</v>
+        <v>12230278886.918341</v>
       </c>
       <c r="F57" s="118">
-        <v>12463784452.55294</v>
+        <v>12463798727.624771</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18409,19 +18409,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>11349471854.164124</v>
+        <v>11349486129.235958</v>
       </c>
       <c r="C58" s="118">
-        <v>11671124407.673277</v>
+        <v>11671138682.74511</v>
       </c>
       <c r="D58" s="118">
-        <v>11998945193.667343</v>
+        <v>11998959468.739178</v>
       </c>
       <c r="E58" s="118">
-        <v>12332994635.648207</v>
+        <v>12333008910.720041</v>
       </c>
       <c r="F58" s="118">
-        <v>12673333157.117767</v>
+        <v>12673347432.189598</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18435,19 +18435,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>11175955098.729645</v>
+        <v>11175969373.801476</v>
       </c>
       <c r="C59" s="118">
-        <v>11581682968.370075</v>
+        <v>11581697243.441908</v>
       </c>
       <c r="D59" s="118">
-        <v>11998945193.667343</v>
+        <v>11998959468.739178</v>
       </c>
       <c r="E59" s="118">
-        <v>12427967014.631935</v>
+        <v>12427981289.703766</v>
       </c>
       <c r="F59" s="118">
-        <v>12868975883.57646</v>
+        <v>12868990158.648296</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18461,19 +18461,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>11020306201.406269</v>
+        <v>11020320476.478102</v>
       </c>
       <c r="C60" s="118">
-        <v>11500633059.985481</v>
+        <v>11500647335.057314</v>
       </c>
       <c r="D60" s="118">
-        <v>11998945193.667343</v>
+        <v>11998959468.739178</v>
       </c>
       <c r="E60" s="118">
-        <v>12515767566.369747</v>
+        <v>12515781841.441582</v>
       </c>
       <c r="F60" s="118">
-        <v>13051635454.274738</v>
+        <v>13051649729.346573</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18487,19 +18487,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>10880685222.571568</v>
+        <v>10880699497.643398</v>
       </c>
       <c r="C61" s="118">
-        <v>11427187376.415001</v>
+        <v>11427201651.486832</v>
       </c>
       <c r="D61" s="118">
-        <v>11998945193.667343</v>
+        <v>11998959468.739178</v>
       </c>
       <c r="E61" s="118">
-        <v>12596937870.493492</v>
+        <v>12596952145.565323</v>
       </c>
       <c r="F61" s="118">
-        <v>13222173451.631481</v>
+        <v>13222187726.703312</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18513,19 +18513,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>10755441690.069962</v>
+        <v>10755455965.141792</v>
       </c>
       <c r="C62" s="118">
-        <v>11360632477.801933</v>
+        <v>11360646752.873764</v>
       </c>
       <c r="D62" s="118">
-        <v>11998945193.667343</v>
+        <v>11998959468.739178</v>
       </c>
       <c r="E62" s="118">
-        <v>12671978609.317276</v>
+        <v>12671992884.389109</v>
       </c>
       <c r="F62" s="118">
-        <v>13381394282.115583</v>
+        <v>13381408557.187416</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18539,19 +18539,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>10643095088.832821</v>
+        <v>10643109363.904652</v>
       </c>
       <c r="C63" s="118">
-        <v>11300321860.294441</v>
+        <v>11300336135.366272</v>
       </c>
       <c r="D63" s="118">
-        <v>11998945193.667341</v>
+        <v>11998959468.739178</v>
       </c>
       <c r="E63" s="118">
-        <v>12741352656.193264</v>
+        <v>12741366931.265097</v>
       </c>
       <c r="F63" s="118">
-        <v>13530048970.530945</v>
+        <v>13530063245.602776</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18565,19 +18565,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>10542317359.576622</v>
+        <v>10542331634.648455</v>
       </c>
       <c r="C64" s="118">
-        <v>11245669676.008476</v>
+        <v>11245683951.080307</v>
       </c>
       <c r="D64" s="118">
-        <v>11998945193.667339</v>
+        <v>11998959468.739176</v>
       </c>
       <c r="E64" s="118">
-        <v>12805487930.650703</v>
+        <v>12805502205.722534</v>
       </c>
       <c r="F64" s="118">
-        <v>13668838702.506838</v>
+        <v>13668852977.578671</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18591,19 +18591,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>10451917199.694632</v>
+        <v>10451931474.766464</v>
       </c>
       <c r="C65" s="118">
-        <v>11196145042.193275</v>
+        <v>11196159317.265106</v>
       </c>
       <c r="D65" s="118">
-        <v>11998945193.667339</v>
+        <v>11998959468.739176</v>
       </c>
       <c r="E65" s="118">
-        <v>12864780037.929432</v>
+        <v>12864794313.001265</v>
       </c>
       <c r="F65" s="118">
-        <v>13798418131.903101</v>
+        <v>13798432406.974934</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18617,19 +18617,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>10121799495.595875</v>
+        <v>10121813770.667706</v>
       </c>
       <c r="C66" s="281">
-        <v>11010091067.76162</v>
+        <v>11010105342.83345</v>
       </c>
       <c r="D66" s="118">
-        <v>11998945193.667341</v>
+        <v>11998959468.739176</v>
       </c>
       <c r="E66" s="118">
-        <v>13100469728.890903</v>
+        <v>13100484003.962734</v>
       </c>
       <c r="F66" s="118">
-        <v>14328188747.700397</v>
+        <v>14328203022.772232</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18652,19 +18652,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>9930068659.4409447</v>
+        <v>9930082934.5127792</v>
       </c>
       <c r="C67" s="281">
-        <v>10896404881.839397</v>
+        <v>10896419156.911228</v>
       </c>
       <c r="D67" s="118">
-        <v>11998945193.667339</v>
+        <v>11998959468.739174</v>
       </c>
       <c r="E67" s="118">
-        <v>13259632036.694031</v>
+        <v>13259646311.765862</v>
       </c>
       <c r="F67" s="118">
-        <v>14704010139.61264</v>
+        <v>14704024414.684475</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18687,19 +18687,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>9818712276.3198814</v>
+        <v>9818726551.3917141</v>
       </c>
       <c r="C68" s="281">
-        <v>10826938218.152027</v>
+        <v>10826952493.223856</v>
       </c>
       <c r="D68" s="118">
-        <v>11998945193.667339</v>
+        <v>11998959468.739174</v>
       </c>
       <c r="E68" s="118">
-        <v>13367115058.636463</v>
+        <v>13367129333.708296</v>
       </c>
       <c r="F68" s="118">
-        <v>14970619336.890015</v>
+        <v>14970633611.961849</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18722,19 +18722,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>9754037003.8885574</v>
+        <v>9754051278.9603882</v>
       </c>
       <c r="C69" s="281">
-        <v>10784491395.570122</v>
+        <v>10784505670.641951</v>
       </c>
       <c r="D69" s="118">
-        <v>11998945193.667339</v>
+        <v>11998959468.739172</v>
       </c>
       <c r="E69" s="118">
-        <v>13439698826.523062</v>
+        <v>13439713101.594896</v>
       </c>
       <c r="F69" s="118">
-        <v>15159752966.860397</v>
+        <v>15159767241.932234</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18831,23 +18831,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18862,23 +18862,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>16.765300309410762</v>
+        <v>16.801215286556694</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>16.872701748137768</v>
+        <v>16.908848404277641</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>17.087504625591784</v>
+        <v>17.124114639719533</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>17.194906064318793</v>
+        <v>17.231747757440477</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>16.572616721397097</v>
+        <v>16.60811605476443</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>16.775376874600255</v>
+        <v>16.811313588219303</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>17.186795658190665</v>
+        <v>17.223619856102285</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>17.39545428857792</v>
+        <v>17.432728590530385</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18924,23 +18924,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>16.399774692789865</v>
+        <v>16.434901183225374</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>16.687183167687536</v>
+        <v>16.722929635910141</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>17.278588740959425</v>
+        <v>17.315610948593427</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>17.582693820609322</v>
+        <v>17.620372022797394</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18955,23 +18955,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>16.244731042414504</v>
+        <v>16.279523083355091</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>16.607263927556104</v>
+        <v>16.642837999492691</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>17.363450080635808</v>
+        <v>17.400655345312931</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>17.757507845938409</v>
+        <v>17.79556314491397</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18986,23 +18986,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>16.105652985327225</v>
+        <v>16.140145016652237</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>16.534842831235633</v>
+        <v>16.570260681366122</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>17.441903126927013</v>
+        <v>17.479277625117689</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>17.920720940524834</v>
+        <v>17.959128311558263</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -19017,23 +19017,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>15.980896467299271</v>
+        <v>16.015119382447384</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>16.469216391549345</v>
+        <v>16.504492676839522</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>17.514431801301495</v>
+        <v>17.551962753358243</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>18.073102960184471</v>
+        <v>18.111839039226172</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19049,23 +19049,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>15.86898673030395</v>
+        <v>15.902968241467287</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>16.409747123549874</v>
+        <v>16.444895125826864</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>17.581483481958909</v>
+        <v>17.619159073287729</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>18.215372671903314</v>
+        <v>18.254415645378355</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19080,23 +19080,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>15.768600879269242</v>
+        <v>15.802365844981711</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>16.355857352090396</v>
+        <v>16.390889107060246</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>17.643471763390476</v>
+        <v>17.681281071574936</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>18.348201144171703</v>
+        <v>18.387530646087949</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19112,23 +19112,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>15.67855224401614</v>
+        <v>15.71212296300838</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>16.307023600378837</v>
+        <v>16.341950014539467</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>16.98010318686477</v>
+        <v>17.016481521998585</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>17.700779007551468</v>
+        <v>17.738711934980042</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>18.472214912330742</v>
+        <v>18.511811928214982</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19144,23 +19144,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>15.597776351523658</v>
+        <v>15.631172826318339</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>16.262771505006345</v>
+        <v>16.297602461591573</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>16.98010318686477</v>
+        <v>17.016481521998585</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>17.753758702382225</v>
+        <v>17.791805913963262</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>18.587998933861389</v>
+        <v>18.627845711070428</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19176,23 +19176,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>15.30280395091113</v>
+        <v>15.335564131538591</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>16.096525384909771</v>
+        <v>16.13099772680318</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>16.980103186864778</v>
+        <v>17.016481521998585</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>17.964356174372799</v>
+        <v>18.002857672330393</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>19.061368608906005</v>
+        <v>19.102236506608168</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19208,23 +19208,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>15.131485344517491</v>
+        <v>15.163875968434704</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>15.994942565322706</v>
+        <v>16.029195779747045</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>16.98010318686477</v>
+        <v>17.016481521998582</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>18.106573593907719</v>
+        <v>18.145381873497556</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>19.397178948059256</v>
+        <v>19.438771232719841</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19240,23 +19240,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>15.031984290060498</v>
+        <v>15.064160277149139</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>15.932871527338399</v>
+        <v>15.966990846390349</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>16.98010318686477</v>
+        <v>17.016481521998582</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>18.202613656630206</v>
+        <v>18.241629107235379</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>19.635404144617507</v>
+        <v>19.677510312281182</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19272,23 +19272,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>14.974194537701051</v>
+        <v>15.006245864712083</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>15.894943718560192</v>
+        <v>15.928981222352641</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>16.98010318686477</v>
+        <v>17.016481521998582</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>18.267469942715994</v>
+        <v>18.306625296839123</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>19.804402051049799</v>
+        <v>19.846872769369444</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>17.582693820609322</v>
+        <v>17.620372022797394</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>17.278588740959425</v>
+        <v>17.315610948593427</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>16.687183167687536</v>
+        <v>16.722929635910141</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>16.399774692789865</v>
+        <v>16.434901183225374</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>1207925186.645268</v>
+        <v>1207933528.2671547</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>1109902430.4142294</v>
+        <v>1109903750.8583741</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C14" s="252">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7253509313970459E-2</v>
+        <v>-7.7252234380016493E-2</v>
       </c>
       <c r="D14" s="465"/>
       <c r="E14" s="465"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>17.278588740959425</v>
+        <v>17.315610948593427</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>16.687183167687536</v>
+        <v>16.722929635910141</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>16.966570292889397</v>
+        <v>17.002919435795445</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19917,7 +19917,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>17.582693820609322</v>
+        <v>17.620372022797394</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19940,7 +19940,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>16.399774692789865</v>
+        <v>16.434901183225374</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.59534063184642794</v>
+        <v>0.59662485969543355</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.210000000000001</v>
+        <v>10.43</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.23583181729627789</v>
+        <v>0.22759647505526587</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20005,7 +20005,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20016,7 +20016,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.6018432604125329E-2</v>
+        <v>3.601896122133004E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>17.030649042042409</v>
+        <v>17.067136411217234</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20075,7 +20075,7 @@
       </c>
       <c r="C41" s="138">
         <f>DCF!C16</f>
-        <v>1.7510817454651968E-3</v>
+        <v>1.7510817454652E-3</v>
       </c>
       <c r="E41" s="97"/>
     </row>
@@ -20115,7 +20115,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="138">
-        <v>1.7510817454651968E-3</v>
+        <v>1.7510817454652E-3</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="221" t="s">
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>17.031966962300672</v>
+        <v>17.068457174402401</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.39720097817365574</v>
+        <v>0.36748044712802796</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.59534063184642794</v>
+        <v>0.59662485969543355</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20265,23 +20265,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.0893849935065805</v>
+        <v>1.0917349398601683</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>7.8482253649965035</v>
+        <v>7.8650398208374366</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>8.9376103585030844</v>
+        <v>8.9567747606976056</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.47520436030127733</v>
+        <v>0.47520342341607824</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20290,23 +20290,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2525990393745514</v>
+        <v>1.2553010598380527</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>9.8371980026237775</v>
+        <v>9.8582737393312581</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>11.089797041998329</v>
+        <v>11.11357479916931</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34883297667506985</v>
+        <v>0.34883189942367809</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20336,15 +20336,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4363206693909827</v>
+        <v>1.4394190015139108</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>12.206894700671489</v>
+        <v>12.233047401741313</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>13.643215370062471</v>
+        <v>13.672466403255225</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19890220646421697</v>
+        <v>0.19890097120984462</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20361,15 +20361,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.555253118365139</v>
+        <v>1.5586080033839271</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>13.805091731684474</v>
+        <v>13.834668495157365</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>15.360344850049612</v>
+        <v>15.393276498541292</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>9.8076367369759665E-2</v>
+        <v>9.8075029831941274E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20488,7 +20488,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>10.210000000000001</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20506,14 +20506,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12597.516610000002</v>
+        <v>12868.96163</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.23583181729627789</v>
+        <v>0.22759647505526587</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.1024826515674591</v>
+        <v>1.10486085128784</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>17.030649042042409</v>
+        <v>17.067136411217234</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20643,14 +20643,14 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>8.9376103585030844</v>
+        <v>8.9567747606976056</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
       </c>
       <c r="E22" s="370">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20659,14 +20659,14 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>11.089797041998329</v>
+        <v>11.11357479916931</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
       </c>
       <c r="E23" s="372">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>13.643215370062471</v>
+        <v>13.672466403255225</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>15.360344850049612</v>
+        <v>15.393276498541292</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>11583836.572900016</v>
+        <v>11585597.165092731</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-2573086.2565999832</v>
+        <v>-2571325.6644072682</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-389569302.80474317</v>
+        <v>-389569742.95279133</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20959,7 +20959,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>1207925186.645268</v>
+        <v>1207933528.2671547</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>1109902430.4142294</v>
+        <v>1109903750.8583741</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.7134079068640064E-2</v>
+        <v>9.5290454527600446E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20995,14 +20995,14 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.8309562374772562E-2</v>
+        <v>5.7202766989015684E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>0.73535560965568947</v>
+        <v>0.73694099144699055</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21022,11 +21022,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095649280255321</v>
+        <v>0.10095660686647698</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>8.888778826940226E-2</v>
+        <v>8.8888328700131733E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21036,11 +21036,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639619218259082</v>
+        <v>0.12639633498911301</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128633391373786</v>
+        <v>0.11128701052585509</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25299470222018966</v>
+        <v>-0.25354044498468808</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>6703879319.3633308</v>
+        <v>6703585887.331212</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9901645737173084</v>
+        <v>6.0028233866097116</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52143118249397991</v>
+        <v>0.52255597796413267</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>6.2586010539910992</v>
+        <v>6.2718389195891557</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.7203273567126307</v>
+        <v>1.7240383285205596</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>16.980103186864778</v>
+        <v>17.016481521998589</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21464,7 +21464,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.58 HKD</v>
+        <v>17.62 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.28 HKD</v>
+        <v>17.32 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>16.98 HKD</v>
+        <v>17.02 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.69 HKD</v>
+        <v>16.72 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.4 HKD</v>
+        <v>16.43 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>17.030649042042409</v>
+        <v>17.067136411217234</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C136" s="410">
         <f>Scenarios!C58</f>
-        <v>0.59534063184642794</v>
+        <v>0.59662485969543355</v>
       </c>
       <c r="D136" s="347" t="str">
         <f>Market_currency</f>
@@ -21678,19 +21678,19 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>1.0893849935065805</v>
+        <v>1.0917349398601683</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>7.8482253649965035</v>
+        <v>7.8650398208374366</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>8.9376103585030844</v>
+        <v>8.9567747606976056</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21699,19 +21699,19 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>1.2525990393745514</v>
+        <v>1.2553010598380527</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>9.8371980026237775</v>
+        <v>9.8582737393312581</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>11.089797041998329</v>
+        <v>11.11357479916931</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21739,15 +21739,15 @@
       </c>
       <c r="C144" s="413">
         <f>Scenarios!C66</f>
-        <v>1.4363206693909827</v>
+        <v>1.4394190015139108</v>
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>12.206894700671489</v>
+        <v>12.233047401741313</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>13.643215370062471</v>
+        <v>13.672466403255225</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21760,15 +21760,15 @@
       </c>
       <c r="C145" s="413">
         <f>Scenarios!C67</f>
-        <v>1.555253118365139</v>
+        <v>1.5586080033839271</v>
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>13.805091731684474</v>
+        <v>13.834668495157365</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>15.360344850049612</v>
+        <v>15.393276498541292</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C6FEFB-B7C2-4447-B497-7DC96FEC5689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAC41BD-B769-4745-BAFA-FAFA61B8AA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4972,30 +4972,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5005,25 +5005,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5393,7 +5393,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.43</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12868.96163</v>
+        <v>12585.1782</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.22759647505526587</v>
+        <v>0.24164439429930151</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.10486085128784</v>
+        <v>1.1164044342041017</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>17.067136411217234</v>
+        <v>17.244227766406713</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,13 +5542,13 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>8.9567747606976056</v>
+        <v>9.0497901235721319</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5557,13 +5557,13 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>11.11357479916931</v>
+        <v>11.228981216429396</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E23" s="448">
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>13.672466403255225</v>
+        <v>13.814437518083643</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>15.393276498541292</v>
+        <v>15.553111578033977</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>11585597.165092731</v>
+        <v>11594142.932626123</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-2571325.6644072682</v>
+        <v>-2562779.8968738765</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-389569742.95279133</v>
+        <v>-389571879.39467466</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>1207933528.2671547</v>
+        <v>1207974017.8034546</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>1109903750.8583741</v>
+        <v>1109910160.1840239</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.5290454527600446E-2</v>
+        <v>9.8457773478140262E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5894,14 +5894,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.7202766989015684E-2</v>
+        <v>5.9103764163746568E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.73694099144699055</v>
+        <v>0.74463624872544909</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5921,11 +5921,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095660686647698</v>
+        <v>0.10095716052324116</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.8888328700131733E-2</v>
+        <v>8.8890951905778726E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5935,11 +5935,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639633498911301</v>
+        <v>0.12639702816005058</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128701052585509</v>
+        <v>0.11129029474459018</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25354044498468808</v>
+        <v>-0.25618943480625261</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>6703585887.331212</v>
+        <v>6702161592.7423134</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0028233866097116</v>
+        <v>6.0642521369365614</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52255597796413267</v>
+        <v>0.52801564128099832</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.2718389195891557</v>
+        <v>6.336078343411307</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7240383285205596</v>
+        <v>1.7420510758931296</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>17.016481521998589</v>
+        <v>17.193043635054881</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.62 HKD</v>
+        <v>17.8 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.3637648803494685E-2</v>
+        <v>2.3639293309878604E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.32 HKD</v>
+        <v>17.5 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.9812455141453607E-2</v>
+        <v>2.9814553988717414E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>17.02 HKD</v>
+        <v>17.19 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.601896122133004E-2</v>
+        <v>3.6021527305578151E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.72 HKD</v>
+        <v>16.9 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.2256107151175795E-2</v>
+        <v>4.2259153570360516E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.43 HKD</v>
+        <v>16.61 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,17 +6445,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.8522768120495594E-2</v>
+        <v>4.8526308166916762E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>17.067136411217234</v>
+        <v>17.244227766406713</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.59662485969543355</v>
+        <v>0.60285839447021494</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,19 +6566,19 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>1.0917349398601683</v>
+        <v>1.103141383292539</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>7.8650398208374366</v>
+        <v>7.9466487402795929</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>8.9567747606976056</v>
+        <v>9.0497901235721319</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6587,19 +6587,19 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>1.2553010598380527</v>
+        <v>1.2684164416096313</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>9.8582737393312581</v>
+        <v>9.9605647748197654</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>11.11357479916931</v>
+        <v>11.228981216429396</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6634,15 +6634,15 @@
       </c>
       <c r="C144" s="337">
         <f>Scenarios!C66</f>
-        <v>1.4394190015139108</v>
+        <v>1.4544580469971957</v>
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>12.233047401741313</v>
+        <v>12.359979471086447</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>13.672466403255225</v>
+        <v>13.814437518083643</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,15 +6655,15 @@
       </c>
       <c r="C145" s="337">
         <f>Scenarios!C67</f>
-        <v>1.5586080033839271</v>
+        <v>1.5748923352072874</v>
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>13.834668495157365</v>
+        <v>13.97821924282669</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>15.393276498541292</v>
+        <v>15.553111578033977</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,18 +6777,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6805,6 +6793,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.66291651077270397</v>
+        <v>0.669842660522461</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.66291651077270397</v>
+        <v>0.669842660522461</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10216,11 +10216,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.419701279609049</v>
+        <v>13.559910279006633</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7240383285205596</v>
+        <v>1.7420510758931296</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6703585887.331212</v>
+        <v>6702161592.7423134</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10478,11 +10478,11 @@
       </c>
       <c r="C73" s="289">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-984741188.58569193</v>
+        <v>-985453335.88014114</v>
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-965466430.42439425</v>
+        <v>-966178577.71884346</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10494,11 +10494,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7683127793010218</v>
+        <v>8.7619762740649954</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9433650679956713</v>
+        <v>8.9367731259020236</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10511,7 +10511,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1930932860.8487885</v>
+        <v>1932357155.4376869</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10626,11 +10626,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-312828596.18035251</v>
+        <v>-316097028.43078154</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.25354044498468808</v>
+        <v>-0.25618943480625261</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10643,11 +10643,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7406529610.1579132</v>
+        <v>7482322920.8899441</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>6.0028233866097116</v>
+        <v>6.0642521369365614</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10660,11 +10660,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>644750990.40724337</v>
+        <v>651487346.85378826</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.52255597796413267</v>
+        <v>0.52801564128099832</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10677,11 +10677,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>7738452004.3848047</v>
+        <v>7817713239.3129511</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.2718389195891557</v>
+        <v>6.336078343411307</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11162,36 +11162,36 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-2571325.6644072682</v>
+        <v>-2562779.8968738765</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>42450255.727153838</v>
+        <v>42490745.263453811</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40920550.543259837</v>
+        <v>40963919.651057757</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>17692802.981277198</v>
+        <v>17721327.474008225</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>5056544.5242806152</v>
+        <v>5074648.9540344775</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
-        <v>-4706541.0609545261</v>
+        <v>-4693664.1242605112</v>
       </c>
       <c r="L10" s="270">
         <f t="shared" si="6"/>
-        <v>-6426599.635417629</v>
+        <v>-6417000.4542544093</v>
       </c>
       <c r="M10" s="270">
         <f t="shared" si="6"/>
-        <v>7533897.1904013557</v>
+        <v>7539835.259016444</v>
       </c>
       <c r="N10" s="270">
         <f t="shared" si="6"/>
@@ -11217,36 +11217,36 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>1558278971.8111653</v>
+        <v>1558287517.5786986</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1372003455.2671547</v>
+        <v>1372043944.8034546</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>1481905218.8632596</v>
+        <v>1481948587.9710574</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>1407220301.9812772</v>
+        <v>1407248826.4740083</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>1240510862.5242805</v>
+        <v>1240528966.9540346</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
-        <v>1157449149.9390454</v>
+        <v>1157462026.8757396</v>
       </c>
       <c r="L11" s="271">
         <f t="shared" si="7"/>
-        <v>999259214.94458449</v>
+        <v>999268814.12574768</v>
       </c>
       <c r="M11" s="271">
         <f t="shared" si="7"/>
-        <v>939481203.96040034</v>
+        <v>939487142.02901542</v>
       </c>
       <c r="N11" s="271">
         <f t="shared" si="7"/>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-389569742.95279133</v>
+        <v>-389571879.39467466</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11384,38 +11384,38 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>1109903750.8583741</v>
+        <v>1109910160.1840239</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207933528.2671547</v>
+        <v>1207974017.8034546</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>1497879161.8632596</v>
+        <v>1497922530.9710574</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>1418655778.9812772</v>
+        <v>1418684303.4740083</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>1235058050.5242805</v>
+        <v>1235076154.9540346</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
-        <v>1149278598.9390454</v>
+        <v>1149291475.8757396</v>
       </c>
       <c r="L14" s="271">
         <f t="shared" si="8"/>
-        <v>975087139.82458448</v>
+        <v>975096739.00574768</v>
       </c>
       <c r="M14" s="271">
         <f t="shared" si="8"/>
-        <v>950277050.33040035</v>
+        <v>950282988.39901543</v>
       </c>
       <c r="N14" s="271">
         <f t="shared" si="8"/>
@@ -11602,38 +11602,38 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>1109903750.8583741</v>
+        <v>1109910160.1840239</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207933528.2671547</v>
+        <v>1207974017.8034546</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>1497879161.8632596</v>
+        <v>1497922530.9710574</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>1418655778.9812772</v>
+        <v>1418684303.4740083</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>1235058050.5242805</v>
+        <v>1235076154.9540346</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
-        <v>1149278598.9390454</v>
+        <v>1149291475.8757396</v>
       </c>
       <c r="L19" s="275">
         <f t="shared" si="9"/>
-        <v>975087139.82458448</v>
+        <v>975096739.00574768</v>
       </c>
       <c r="M19" s="275">
         <f t="shared" si="9"/>
-        <v>950277050.33040035</v>
+        <v>950282988.39901543</v>
       </c>
       <c r="N19" s="275">
         <f t="shared" si="9"/>
@@ -12341,31 +12341,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.672316610857445E-2</v>
+        <v>7.6720901978893349E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.3982734638047201E-2</v>
+        <v>-4.3981447486809128E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.1262876778423181E-3</v>
+        <v>-8.1261229605375778E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3956180995499122E-3</v>
+        <v>4.3955539493678291E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.0591014736416579E-3</v>
+        <v>7.0590229400909381E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4189994706569209E-2</v>
+        <v>2.4189762332519061E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491285109792415E-2</v>
+        <v>-1.1491212478633984E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12479,36 +12479,36 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>11585597.165092731</v>
+        <v>11594142.932626123</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54892138.727153838</v>
+        <v>54932628.263453811</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>58796007.543259837</v>
+        <v>58839376.651057757</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>38670988.981277198</v>
+        <v>38699513.474008225</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>24544387.524280615</v>
+        <v>24562491.954034477</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
-        <v>17457413.939045474</v>
+        <v>17470290.875739489</v>
       </c>
       <c r="L46" s="278">
         <f t="shared" si="17"/>
-        <v>13013722.364582371</v>
+        <v>13023321.545745591</v>
       </c>
       <c r="M46" s="278">
         <f t="shared" si="17"/>
-        <v>8050309.1904013557</v>
+        <v>8056247.259016444</v>
       </c>
       <c r="N46" s="278">
         <f t="shared" si="17"/>
@@ -12591,36 +12591,36 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-2571325.6644072682</v>
+        <v>-2562779.8968738765</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42450255.727153838</v>
+        <v>42490745.263453811</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40920550.543259837</v>
+        <v>40963919.651057757</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>17692802.981277198</v>
+        <v>17721327.474008225</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>5056544.5242806152</v>
+        <v>5074648.9540344775</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
-        <v>-4706541.0609545261</v>
+        <v>-4693664.1242605112</v>
       </c>
       <c r="L48" s="271">
         <f t="shared" si="18"/>
-        <v>-6426599.635417629</v>
+        <v>-6417000.4542544093</v>
       </c>
       <c r="M48" s="271">
         <f t="shared" si="18"/>
-        <v>7533897.1904013557</v>
+        <v>7539835.259016444</v>
       </c>
       <c r="N48" s="271">
         <f t="shared" si="18"/>
@@ -13556,38 +13556,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0856736561539725E-4</v>
+        <v>2.0787419467782487E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.4432581330585111E-3</v>
+        <v>3.446542351793605E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4478311122924325E-3</v>
+        <v>3.4514852507923524E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.618692895491246E-3</v>
+        <v>1.6213025664280707E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8340043730935386E-4</v>
+        <v>4.8513120210697989E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2248129579788227E-4</v>
+        <v>5.2105180469546502E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.2678884493021913E-4</v>
+        <v>7.2570326652395835E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.2027372360591259E-4</v>
+        <v>9.2099906513597716E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13613,38 +13613,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639633498911301</v>
+        <v>0.12639702816005058</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.11128701052585509</v>
+        <v>0.11129029474459018</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12486046378246622</v>
+        <v>0.12486411792096613</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12874486352550266</v>
+        <v>0.12874747319643948</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11859155803963853</v>
+        <v>0.11859328880443618</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12849043997454521</v>
+        <v>0.12849186946564761</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300695419285398</v>
+        <v>0.11300803977126024</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11475864933860937</v>
+        <v>0.11475937468013943</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1599083747278253E-2</v>
+        <v>3.1599257040012645E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13785,38 +13785,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.0027375609204055E-2</v>
+        <v>9.0027895487407208E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.7978843098922533E-2</v>
+        <v>9.7982127317657625E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12620637572475943</v>
+        <v>0.12621002986325933</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12979108132355544</v>
+        <v>0.12979369099449226</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11807027484066568</v>
+        <v>0.11807200560546331</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758341292037201</v>
+        <v>0.12758484241147444</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11027331656912333</v>
+        <v>0.11027440214752959</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607737369697402</v>
+        <v>0.11607809903850408</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14008,38 +14008,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.0027375609204055E-2</v>
+        <v>9.0027895487407208E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.7978843098922533E-2</v>
+        <v>9.7982127317657625E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12620637572475943</v>
+        <v>0.12621002986325933</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12979108132355544</v>
+        <v>0.12979369099449226</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11807027484066568</v>
+        <v>0.11807200560546331</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758341292037201</v>
+        <v>0.12758484241147444</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11027331656912333</v>
+        <v>0.11027440214752959</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607737369697402</v>
+        <v>0.11607809903850408</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14077,12 +14077,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.66291651077270397</v>
+        <v>0.669842660522461</v>
       </c>
       <c r="E88" s="238"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.66291651077270397</v>
+        <v>0.669842660522461</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14133,12 +14133,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>817933570.56830382</v>
+        <v>826479338.10169375</v>
       </c>
       <c r="E89" s="238"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>817933570.56830382</v>
+        <v>826479338.10169375</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.73694099144699055</v>
+        <v>0.74463624872544909</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.67713458681925431</v>
+        <v>0.68418635328311128</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14264,12 +14264,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.7202766989015684E-2</v>
+        <v>5.9103764163746568E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.7202766989015684E-2</v>
+        <v>5.9103764163746568E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14401,38 +14401,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.13576898500429757</v>
+        <v>0.1357416965255609</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162478272671417E-2</v>
+        <v>-7.4162251011739677E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.3072654492569926E-2</v>
+        <v>5.3082127404729285E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.13438773048529717</v>
+        <v>0.13439416890790845</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1762731511452849E-2</v>
+        <v>7.1766449481294847E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830720660728015</v>
+        <v>0.15830896602972033</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3628746091128674E-2</v>
+        <v>6.3632240849642141E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35103064600208933</v>
+        <v>0.35103918530297507</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -15012,31 +15012,31 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4673645449205435</v>
+        <v>1.4673153609901517</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5709065663701425</v>
+        <v>1.5708610841674193</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.4269713308845704</v>
+        <v>1.4269426397703771</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.6576788241904186</v>
+        <v>1.6576545250168762</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.5825625672304584</v>
+        <v>1.582544835820785</v>
       </c>
       <c r="L113" s="254">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3992703460999942</v>
+        <v>1.3992565712107847</v>
       </c>
       <c r="M113" s="254">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.0454322469690169</v>
+        <v>1.0454257143376948</v>
       </c>
       <c r="N113" s="254">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15120,36 +15120,36 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639633498911301</v>
+        <v>0.12639702816005058</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.11128701052585509</v>
+        <v>0.11129029474459018</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12486046378246622</v>
+        <v>0.12486411792096613</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12874486352550266</v>
+        <v>0.12874747319643948</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11859155803963853</v>
+        <v>0.11859328880443618</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12849043997454521</v>
+        <v>0.12849186946564761</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300695419285398</v>
+        <v>0.11300803977126024</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11475864933860937</v>
+        <v>0.11475937468013943</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15285,38 +15285,38 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.10095660686647698</v>
+        <v>0.10095716052324116</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.8888328700131733E-2</v>
+        <v>8.8890951905778726E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11047323439300516</v>
+        <v>0.11047646747805687</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11113699213798922</v>
+        <v>0.11113924489565619</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11166027345738132</v>
+        <v>0.1116619030646973</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11542000747664377</v>
+        <v>0.11542129155562866</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.10956830093458829</v>
+        <v>0.10956935348026882</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.1117627792627007</v>
+        <v>0.11176348566858628</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15406,50 +15406,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.9938794407228726</v>
+        <v>1.0042692894770306</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0816616292864094</v>
+        <v>1.0929994625556465</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3412976598302027</v>
+        <v>1.3553507750758156</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2703559305045526</v>
+        <v>1.2836544150616978</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1059506768636775</v>
+        <v>1.1175220275306432</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0291382205573407</v>
+        <v>1.0399023049652687</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.87315594747330938</v>
+        <v>0.88228736377213635</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.85093939234256577</v>
+        <v>0.85983537748979466</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.62218777064275521</v>
+        <v>0.62868838663573468</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.51236044304868855</v>
+        <v>0.51771358344682217</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.48303017482318134</v>
+        <v>0.48807687266538335</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15463,50 +15463,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.5290454527600446E-2</v>
+        <v>9.8457773478140262E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10370677174366341</v>
+        <v>0.10715681005447515</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.1285999673854461</v>
+        <v>0.13287752696821722</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12179826754597821</v>
+        <v>0.12584847206487235</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10603553948836794</v>
+        <v>0.10956098309123954</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.8670970331480423E-2</v>
+        <v>0.101951206369144</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.3715814714603015E-2</v>
+        <v>8.6498761154131021E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.1585751902451181E-2</v>
+        <v>8.4297586028411253E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.9653669285019674E-2</v>
+        <v>6.1636116336836737E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.9123724165741955E-2</v>
+        <v>5.0756233671257076E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.6311617912097924E-2</v>
+        <v>4.7850673790723865E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15520,43 +15520,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12461469076584697</v>
+        <v>0.12742462987135136</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12653315409721988</v>
+        <v>0.12938635267000034</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10810779983652807</v>
+        <v>0.11054552473480272</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10127322619113287</v>
+        <v>0.10355683815426626</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6588596868790261E-2</v>
+        <v>9.8766575033478674E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7393626342640654E-2</v>
+        <v>8.9364266936641387E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2011751484257092E-2</v>
+        <v>7.3635545880470721E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1216341850263182E-2</v>
+        <v>7.2822200539043619E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8957951092282494E-2</v>
+        <v>5.0061904891422197E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7783171453903851E-2</v>
+        <v>4.8860635123942862E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>1109903750.8583741</v>
+        <v>1109910160.1840239</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>6703585887.331212</v>
+        <v>6702161592.7423134</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>11998959468.73918</v>
+        <v>11999028758.746204</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-2571325.6644072682</v>
+        <v>-2562779.8968738765</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16404,14 +16404,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>7004005975.3812122</v>
+        <v>7002581680.7923136</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>7004005975.3812122</v>
+        <v>7002581680.7923136</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>19002965444.120392</v>
+        <v>19001610439.538517</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.2718389195891557</v>
+        <v>6.336078343411307</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-2571325.6644072682</v>
+        <v>-2562779.8968738765</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.10486085128784</v>
+        <v>1.1164044342041017</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>20995632577.584263</v>
+        <v>21213482151.719749</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>17.016481521998589</v>
+        <v>17.193043635054881</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>17.068457174402401</v>
+        <v>17.245562328921746</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>1561012148.2744784</v>
+        <v>1561020694.0420117</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16723,11 +16723,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>1111850660.0067995</v>
+        <v>1111857069.3324497</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>1.7541243075533952E-3</v>
+        <v>1.7541141781267644E-3</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>1017712274.6057661</v>
+        <v>1017718141.2654001</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>1563750110.7532039</v>
+        <v>1563758656.5207372</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16772,11 +16772,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>1113800978.3522954</v>
+        <v>1113807387.6779456</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>1.7541189798673251E-3</v>
+        <v>1.7541088682080375E-3</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>933178455.85601461</v>
+        <v>933183825.79618311</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>1566492867.6280456</v>
+        <v>1566501413.3955789</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16821,11 +16821,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>1115754711.8646438</v>
+        <v>1115761121.190294</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>1.7541136615255581E-3</v>
+        <v>1.7541035676029715E-3</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>855666230.60327041</v>
+        <v>855671145.88031256</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>1566492867.6280456</v>
+        <v>1566501413.3955789</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>12062213101.239393</v>
+        <v>12062282391.246422</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18285,7 +18285,7 @@
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>9250445736.2515736</v>
+        <v>9250498874.3817577</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18298,7 +18298,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>12057002697.316624</v>
+        <v>12057071987.323654</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18322,7 +18322,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>12057002697.316624</v>
+        <v>12057071987.323654</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18357,19 +18357,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>11758563307.635027</v>
+        <v>11758632597.642057</v>
       </c>
       <c r="C56" s="118">
-        <v>11878761388.187101</v>
+        <v>11878830678.194126</v>
       </c>
       <c r="D56" s="118">
-        <v>11998959468.739178</v>
+        <v>11999028758.746202</v>
       </c>
       <c r="E56" s="118">
-        <v>12119157549.29125</v>
+        <v>12119226839.298275</v>
       </c>
       <c r="F56" s="118">
-        <v>12239355629.843325</v>
+        <v>12239424919.850353</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18383,19 +18383,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>11542921899.962662</v>
+        <v>11542991189.969688</v>
       </c>
       <c r="C57" s="118">
-        <v>11769840473.087282</v>
+        <v>11769909763.094311</v>
       </c>
       <c r="D57" s="118">
-        <v>11998959468.739178</v>
+        <v>11999028758.746202</v>
       </c>
       <c r="E57" s="118">
-        <v>12230278886.918341</v>
+        <v>12230348176.925367</v>
       </c>
       <c r="F57" s="118">
-        <v>12463798727.624771</v>
+        <v>12463868017.6318</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18409,19 +18409,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>11349486129.235958</v>
+        <v>11349555419.242985</v>
       </c>
       <c r="C58" s="118">
-        <v>11671138682.74511</v>
+        <v>11671207972.752136</v>
       </c>
       <c r="D58" s="118">
-        <v>11998959468.739178</v>
+        <v>11999028758.746202</v>
       </c>
       <c r="E58" s="118">
-        <v>12333008910.720041</v>
+        <v>12333078200.727066</v>
       </c>
       <c r="F58" s="118">
-        <v>12673347432.189598</v>
+        <v>12673416722.196625</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18435,19 +18435,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>11175969373.801476</v>
+        <v>11176038663.808506</v>
       </c>
       <c r="C59" s="118">
-        <v>11581697243.441908</v>
+        <v>11581766533.448933</v>
       </c>
       <c r="D59" s="118">
-        <v>11998959468.739178</v>
+        <v>11999028758.746204</v>
       </c>
       <c r="E59" s="118">
-        <v>12427981289.703766</v>
+        <v>12428050579.710793</v>
       </c>
       <c r="F59" s="118">
-        <v>12868990158.648296</v>
+        <v>12869059448.655319</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18461,19 +18461,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>11020320476.478102</v>
+        <v>11020389766.48513</v>
       </c>
       <c r="C60" s="118">
-        <v>11500647335.057314</v>
+        <v>11500716625.064341</v>
       </c>
       <c r="D60" s="118">
-        <v>11998959468.739178</v>
+        <v>11999028758.746204</v>
       </c>
       <c r="E60" s="118">
-        <v>12515781841.441582</v>
+        <v>12515851131.448608</v>
       </c>
       <c r="F60" s="118">
-        <v>13051649729.346573</v>
+        <v>13051719019.3536</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18487,19 +18487,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>10880699497.643398</v>
+        <v>10880768787.650427</v>
       </c>
       <c r="C61" s="118">
-        <v>11427201651.486832</v>
+        <v>11427270941.493858</v>
       </c>
       <c r="D61" s="118">
-        <v>11998959468.739178</v>
+        <v>11999028758.746202</v>
       </c>
       <c r="E61" s="118">
-        <v>12596952145.565323</v>
+        <v>12597021435.572351</v>
       </c>
       <c r="F61" s="118">
-        <v>13222187726.703312</v>
+        <v>13222257016.71034</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18513,19 +18513,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>10755455965.141792</v>
+        <v>10755525255.148823</v>
       </c>
       <c r="C62" s="118">
-        <v>11360646752.873764</v>
+        <v>11360716042.880791</v>
       </c>
       <c r="D62" s="118">
-        <v>11998959468.739178</v>
+        <v>11999028758.746202</v>
       </c>
       <c r="E62" s="118">
-        <v>12671992884.389109</v>
+        <v>12672062174.396137</v>
       </c>
       <c r="F62" s="118">
-        <v>13381408557.187416</v>
+        <v>13381477847.194443</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18539,19 +18539,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>10643109363.904652</v>
+        <v>10643178653.911682</v>
       </c>
       <c r="C63" s="118">
-        <v>11300336135.366272</v>
+        <v>11300405425.373299</v>
       </c>
       <c r="D63" s="118">
-        <v>11998959468.739178</v>
+        <v>11999028758.746201</v>
       </c>
       <c r="E63" s="118">
-        <v>12741366931.265097</v>
+        <v>12741436221.272125</v>
       </c>
       <c r="F63" s="118">
-        <v>13530063245.602776</v>
+        <v>13530132535.609802</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18565,19 +18565,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>10542331634.648455</v>
+        <v>10542400924.655483</v>
       </c>
       <c r="C64" s="118">
-        <v>11245683951.080307</v>
+        <v>11245753241.087334</v>
       </c>
       <c r="D64" s="118">
-        <v>11998959468.739176</v>
+        <v>11999028758.746201</v>
       </c>
       <c r="E64" s="118">
-        <v>12805502205.722534</v>
+        <v>12805571495.729563</v>
       </c>
       <c r="F64" s="118">
-        <v>13668852977.578671</v>
+        <v>13668922267.585697</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18591,19 +18591,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>10451931474.766464</v>
+        <v>10452000764.773493</v>
       </c>
       <c r="C65" s="118">
-        <v>11196159317.265106</v>
+        <v>11196228607.272131</v>
       </c>
       <c r="D65" s="118">
-        <v>11998959468.739176</v>
+        <v>11999028758.746201</v>
       </c>
       <c r="E65" s="118">
-        <v>12864794313.001265</v>
+        <v>12864863603.008293</v>
       </c>
       <c r="F65" s="118">
-        <v>13798432406.974934</v>
+        <v>13798501696.98196</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18617,19 +18617,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>10121813770.667706</v>
+        <v>10121883060.674732</v>
       </c>
       <c r="C66" s="281">
-        <v>11010105342.83345</v>
+        <v>11010174632.840477</v>
       </c>
       <c r="D66" s="118">
-        <v>11998959468.739176</v>
+        <v>11999028758.746201</v>
       </c>
       <c r="E66" s="118">
-        <v>13100484003.962734</v>
+        <v>13100553293.969763</v>
       </c>
       <c r="F66" s="118">
-        <v>14328203022.772232</v>
+        <v>14328272312.779261</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18652,19 +18652,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>9930082934.5127792</v>
+        <v>9930152224.5198059</v>
       </c>
       <c r="C67" s="281">
-        <v>10896419156.911228</v>
+        <v>10896488446.918255</v>
       </c>
       <c r="D67" s="118">
-        <v>11998959468.739174</v>
+        <v>11999028758.746199</v>
       </c>
       <c r="E67" s="118">
-        <v>13259646311.765862</v>
+        <v>13259715601.77289</v>
       </c>
       <c r="F67" s="118">
-        <v>14704024414.684475</v>
+        <v>14704093704.691502</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18687,19 +18687,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>9818726551.3917141</v>
+        <v>9818795841.3987427</v>
       </c>
       <c r="C68" s="281">
-        <v>10826952493.223856</v>
+        <v>10827021783.230883</v>
       </c>
       <c r="D68" s="118">
-        <v>11998959468.739174</v>
+        <v>11999028758.746197</v>
       </c>
       <c r="E68" s="118">
-        <v>13367129333.708296</v>
+        <v>13367198623.715324</v>
       </c>
       <c r="F68" s="118">
-        <v>14970633611.961849</v>
+        <v>14970702901.968874</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18722,19 +18722,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>9754051278.9603882</v>
+        <v>9754120568.9674206</v>
       </c>
       <c r="C69" s="281">
-        <v>10784505670.641951</v>
+        <v>10784574960.648979</v>
       </c>
       <c r="D69" s="118">
-        <v>11998959468.739172</v>
+        <v>11999028758.746197</v>
       </c>
       <c r="E69" s="118">
-        <v>13439713101.594896</v>
+        <v>13439782391.601925</v>
       </c>
       <c r="F69" s="118">
-        <v>15159767241.932234</v>
+        <v>15159836531.93926</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18831,23 +18831,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>17.016481521998589</v>
+        <v>17.193043635054881</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>17.016481521998589</v>
+        <v>17.193043635054881</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>17.016481521998589</v>
+        <v>17.193043635054881</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>17.016481521998589</v>
+        <v>17.193043635054881</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>17.016481521998589</v>
+        <v>17.193043635054881</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18862,23 +18862,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>16.801215286556694</v>
+        <v>16.975528298619871</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>16.908848404277641</v>
+        <v>17.084285966837371</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>17.016481521998589</v>
+        <v>17.193043635054885</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>17.124114639719533</v>
+        <v>17.301801303272388</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>17.231747757440477</v>
+        <v>17.410558971489898</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>16.60811605476443</v>
+        <v>16.780411566623243</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>16.811313588219303</v>
+        <v>16.985732107308468</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>17.016481521998589</v>
+        <v>17.193043635054885</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>17.223619856102285</v>
+        <v>17.402346149862488</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>17.432728590530385</v>
+        <v>17.613639651731287</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18924,23 +18924,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>16.434901183225374</v>
+        <v>16.605386946617116</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>16.722929635910141</v>
+        <v>16.896424719726205</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>17.016481521998589</v>
+        <v>17.193043635054885</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>17.315610948593427</v>
+        <v>17.495298365016716</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>17.620372022797394</v>
+        <v>17.803243582025296</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18955,23 +18955,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>16.279523083355091</v>
+        <v>16.448385456817572</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>16.642837999492691</v>
+        <v>16.815496286127633</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>17.016481521998589</v>
+        <v>17.193043635054885</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>17.400655345312931</v>
+        <v>17.581231305342371</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>17.79556314491397</v>
+        <v>17.980265100469136</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18986,23 +18986,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>16.140145016652237</v>
+        <v>16.3075511684848</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>16.570260681366122</v>
+        <v>16.742160680395298</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>17.016481521998589</v>
+        <v>17.193043635054885</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>17.479277625117689</v>
+        <v>17.660675030494691</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>17.959128311558263</v>
+        <v>18.145539195492223</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -19017,23 +19017,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>16.015119382447384</v>
+        <v>16.181219266822449</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>16.504492676839522</v>
+        <v>16.675705531951341</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>17.016481521998589</v>
+        <v>17.193043635054885</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>17.551962753358243</v>
+        <v>17.73411957274077</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>18.111839039226172</v>
+        <v>18.299845444392489</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19049,23 +19049,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>15.902968241467287</v>
+        <v>16.067896371052104</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>16.444895125826864</v>
+        <v>16.615485305901441</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>17.016481521998589</v>
+        <v>17.193043635054885</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>17.619159073287729</v>
+        <v>17.802017959622731</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>18.254415645378355</v>
+        <v>18.443911690505324</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19080,23 +19080,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>15.802365844981711</v>
+        <v>15.966242881024698</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>16.390889107060246</v>
+        <v>16.560915032410001</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>17.016481521998589</v>
+        <v>17.193043635054877</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>17.681281071574936</v>
+        <v>17.864789008364856</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>18.387530646087949</v>
+        <v>18.578417476349802</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19112,23 +19112,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>15.71212296300838</v>
+        <v>15.875057141686613</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>16.341950014539467</v>
+        <v>16.511464624394876</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>17.016481521998585</v>
+        <v>17.193043635054877</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>17.738711934980042</v>
+        <v>17.922819909261474</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>18.511811928214982</v>
+        <v>18.70399724894602</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19144,23 +19144,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>15.631172826318339</v>
+        <v>15.793261238207144</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>16.297602461591573</v>
+        <v>16.466653728344554</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>17.016481521998585</v>
+        <v>17.193043635054877</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>17.791805913963262</v>
+        <v>17.97646861398054</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>18.627845711070428</v>
+        <v>18.821243352422581</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19176,23 +19176,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>15.335564131538591</v>
+        <v>15.494564024656016</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>16.13099772680318</v>
+        <v>16.298308307778374</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>17.016481521998585</v>
+        <v>17.193043635054877</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>18.002857672330393</v>
+        <v>18.189725440496748</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>19.102236506608168</v>
+        <v>19.300590581593234</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19208,23 +19208,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>15.163875968434704</v>
+        <v>15.321082064130294</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>16.029195779747045</v>
+        <v>16.195442734279585</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>17.016481521998582</v>
+        <v>17.193043635054877</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>18.145381873497556</v>
+        <v>18.333738734097437</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>19.438771232719841</v>
+        <v>19.640641421530944</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19240,23 +19240,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>15.064160277149139</v>
+        <v>15.220324543596217</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>15.966990846390349</v>
+        <v>16.132587883962611</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>17.016481521998582</v>
+        <v>17.193043635054874</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>18.241629107235379</v>
+        <v>18.430991558649534</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>19.677510312281182</v>
+        <v>19.881874846291552</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19272,23 +19272,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>15.006245864712083</v>
+        <v>15.161805041548801</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>15.928981222352641</v>
+        <v>16.094181135485037</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>17.016481521998582</v>
+        <v>17.193043635054874</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>18.306625296839123</v>
+        <v>18.496666828250596</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>19.846872769369444</v>
+        <v>20.053006801832062</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>17.620372022797394</v>
+        <v>17.803243582025296</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>17.315610948593427</v>
+        <v>17.495298365016716</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>17.016481521998589</v>
+        <v>17.193043635054885</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>16.722929635910141</v>
+        <v>16.896424719726205</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>16.434901183225374</v>
+        <v>16.605386946617116</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>1207933528.2671547</v>
+        <v>1207974017.8034546</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>1109903750.8583741</v>
+        <v>1109910160.1840239</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C14" s="252">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7252234380016493E-2</v>
+        <v>-7.7246046132118273E-2</v>
       </c>
       <c r="D14" s="465"/>
       <c r="E14" s="465"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>17.315610948593427</v>
+        <v>17.495298365016716</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>17.016481521998589</v>
+        <v>17.193043635054885</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>16.722929635910141</v>
+        <v>16.896424719726205</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>17.002919435795445</v>
+        <v>17.17933985221508</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19917,7 +19917,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>17.620372022797394</v>
+        <v>17.803243582025296</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19940,7 +19940,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>16.434901183225374</v>
+        <v>16.605386946617116</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.59662485969543355</v>
+        <v>0.60285839447021494</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.43</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22759647505526587</v>
+        <v>0.24164439429930151</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20005,7 +20005,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>17.016481521998589</v>
+        <v>17.193043635054881</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20016,7 +20016,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.601896122133004E-2</v>
+        <v>3.6021527305578262E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>17.067136411217234</v>
+        <v>17.244227766406713</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>17.068457174402401</v>
+        <v>17.245562328921746</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.36748044712802796</v>
+        <v>0.36743184033758536</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.59662485969543355</v>
+        <v>0.60285839447021494</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20265,23 +20265,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.0917349398601683</v>
+        <v>1.103141383292539</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>7.8650398208374366</v>
+        <v>7.9466487402795929</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>8.9567747606976056</v>
+        <v>9.0497901235721319</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.47520342341607824</v>
+        <v>0.47519887546359563</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20290,23 +20290,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2553010598380527</v>
+        <v>1.2684164416096313</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>9.8582737393312581</v>
+        <v>9.9605647748197654</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>11.11357479916931</v>
+        <v>11.228981216429396</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34883189942367809</v>
+        <v>0.34882667008699286</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20336,15 +20336,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4394190015139108</v>
+        <v>1.4544580469971957</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>12.233047401741313</v>
+        <v>12.359979471086447</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>13.672466403255225</v>
+        <v>13.814437518083643</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19890097120984462</v>
+        <v>0.19889497487412022</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20361,15 +20361,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5586080033839271</v>
+        <v>1.5748923352072874</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>13.834668495157365</v>
+        <v>13.97821924282669</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>15.393276498541292</v>
+        <v>15.553111578033977</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>9.8075029831941274E-2</v>
+        <v>9.8068536978337728E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20488,7 +20488,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>10.43</v>
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20506,14 +20506,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12868.96163</v>
+        <v>12585.1782</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.22759647505526587</v>
+        <v>0.24164439429930151</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20521,13 +20521,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.10486085128784</v>
+        <v>1.1164044342041017</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>17.067136411217234</v>
+        <v>17.244227766406713</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20643,14 +20643,14 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>8.9567747606976056</v>
+        <v>9.0497901235721319</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
       </c>
       <c r="E22" s="370">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20659,14 +20659,14 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>11.11357479916931</v>
+        <v>11.228981216429396</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
       </c>
       <c r="E23" s="372">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>13.672466403255225</v>
+        <v>13.814437518083643</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>15.393276498541292</v>
+        <v>15.553111578033977</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20712,22 +20712,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>11585597.165092731</v>
+        <v>11594142.932626123</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-2571325.6644072682</v>
+        <v>-2562779.8968738765</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-389569742.95279133</v>
+        <v>-389571879.39467466</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20917,10 +20917,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20936,22 +20936,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>1207933528.2671547</v>
+        <v>1207974017.8034546</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>1109903750.8583741</v>
+        <v>1109910160.1840239</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.5290454527600446E-2</v>
+        <v>9.8457773478140262E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20995,14 +20995,14 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.7202766989015684E-2</v>
+        <v>5.9103764163746568E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>0.73694099144699055</v>
+        <v>0.74463624872544909</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21022,11 +21022,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095660686647698</v>
+        <v>0.10095716052324116</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>8.8888328700131733E-2</v>
+        <v>8.8890951905778726E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21036,11 +21036,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639633498911301</v>
+        <v>0.12639702816005058</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128701052585509</v>
+        <v>0.11129029474459018</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21086,22 +21086,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21109,13 +21109,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25354044498468808</v>
+        <v>-0.25618943480625261</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>6703585887.331212</v>
+        <v>6702161592.7423134</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0028233866097116</v>
+        <v>6.0642521369365614</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52255597796413267</v>
+        <v>0.52801564128099832</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>6.2718389195891557</v>
+        <v>6.336078343411307</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21264,33 +21264,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21353,23 +21353,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.7240383285205596</v>
+        <v>1.7420510758931296</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>17.016481521998589</v>
+        <v>17.193043635054881</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21413,13 +21413,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21464,7 +21464,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.62 HKD</v>
+        <v>17.8 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.32 HKD</v>
+        <v>17.5 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>17.02 HKD</v>
+        <v>17.19 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.72 HKD</v>
+        <v>16.9 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.43 HKD</v>
+        <v>16.61 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>17.067136411217234</v>
+        <v>17.244227766406713</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21583,13 +21583,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21602,22 +21602,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C136" s="410">
         <f>Scenarios!C58</f>
-        <v>0.59662485969543355</v>
+        <v>0.60285839447021494</v>
       </c>
       <c r="D136" s="347" t="str">
         <f>Market_currency</f>
@@ -21678,19 +21678,19 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>1.0917349398601683</v>
+        <v>1.103141383292539</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>7.8650398208374366</v>
+        <v>7.9466487402795929</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>8.9567747606976056</v>
+        <v>9.0497901235721319</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21699,19 +21699,19 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>1.2553010598380527</v>
+        <v>1.2684164416096313</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>9.8582737393312581</v>
+        <v>9.9605647748197654</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>11.11357479916931</v>
+        <v>11.228981216429396</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21739,15 +21739,15 @@
       </c>
       <c r="C144" s="413">
         <f>Scenarios!C66</f>
-        <v>1.4394190015139108</v>
+        <v>1.4544580469971957</v>
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>12.233047401741313</v>
+        <v>12.359979471086447</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>13.672466403255225</v>
+        <v>13.814437518083643</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21760,15 +21760,15 @@
       </c>
       <c r="C145" s="413">
         <f>Scenarios!C67</f>
-        <v>1.5586080033839271</v>
+        <v>1.5748923352072874</v>
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>13.834668495157365</v>
+        <v>13.97821924282669</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>15.393276498541292</v>
+        <v>15.553111578033977</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21786,13 +21786,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21800,13 +21800,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21843,22 +21843,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21882,15 +21882,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21905,12 +21902,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAC41BD-B769-4745-BAFA-FAFA61B8AA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEB0904-D2F4-4AC3-8AE6-8D44E4B1BC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4972,30 +4972,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5005,6 +5005,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5014,16 +5023,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5393,7 +5393,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.199999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12585.1782</v>
+        <v>12770.254349999999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.24164439429930151</v>
+        <v>0.23484614211405236</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.1164044342041017</v>
+        <v>1.1151225151062012</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>17.244227766406713</v>
+        <v>17.224562958216211</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>9.0497901235721319</v>
+        <v>9.0394613102739001</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>11.228981216429396</v>
+        <v>11.216166014521832</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>13.814437518083643</v>
+        <v>13.798672470944149</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>15.553111578033977</v>
+        <v>15.535362848536284</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>11594142.932626123</v>
+        <v>11593193.922021119</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-2562779.8968738765</v>
+        <v>-2563728.9074788801</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-389571879.39467466</v>
+        <v>-389571642.14202344</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>1207974017.8034546</v>
+        <v>1207969521.4256642</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>1109910160.1840239</v>
+        <v>1109909448.4260702</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.8457773478140262E-2</v>
+        <v>9.691937073038924E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5894,14 +5894,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.9103764163746568E-2</v>
+        <v>5.8180305135975718E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.74463624872544909</v>
+        <v>0.74378169198158484</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5921,11 +5921,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095716052324116</v>
+        <v>0.10095709903945535</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.8890951905778726E-2</v>
+        <v>8.8890660597833779E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5935,11 +5935,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639702816005058</v>
+        <v>0.12639695118316485</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>0.11129029474459018</v>
+        <v>0.11128993003090044</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25618943480625261</v>
+        <v>-0.2558952635193098</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>6702161592.7423134</v>
+        <v>6702319761.1764803</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0642521369365614</v>
+        <v>6.0574317672448155</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52801564128099832</v>
+        <v>0.5274093436761067</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.336078343411307</v>
+        <v>6.328945847401612</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7420510758931296</v>
+        <v>1.740050753720191</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>17.193043635054881</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.8 HKD</v>
+        <v>17.78 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.3639293309878604E-2</v>
+        <v>2.3639110675551758E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.5 HKD</v>
+        <v>17.48 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.9814553988717414E-2</v>
+        <v>2.9814320896376947E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>17.19 HKD</v>
+        <v>17.17 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.6021527305578151E-2</v>
+        <v>3.6021242322938081E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.9 HKD</v>
+        <v>16.88 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.2259153570360516E-2</v>
+        <v>4.2258815242712591E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.61 HKD</v>
+        <v>16.59 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,17 +6445,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.8526308166916762E-2</v>
+        <v>4.8525915017963731E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>17.244227766406713</v>
+        <v>17.224562958216211</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.60285839447021494</v>
+        <v>0.60216615815734864</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,15 +6566,15 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>1.103141383292539</v>
+        <v>1.1018746935843999</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>7.9466487402795929</v>
+        <v>7.9375866166894999</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>9.0497901235721319</v>
+        <v>9.0394613102739001</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,15 +6587,15 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>1.2684164416096313</v>
+        <v>1.2669599736749177</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>9.9605647748197654</v>
+        <v>9.9492060408469136</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>11.228981216429396</v>
+        <v>11.216166014521832</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,15 +6634,15 @@
       </c>
       <c r="C144" s="337">
         <f>Scenarios!C66</f>
-        <v>1.4544580469971957</v>
+        <v>1.4527879555048862</v>
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>12.359979471086447</v>
+        <v>12.345884515439263</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>13.814437518083643</v>
+        <v>13.798672470944149</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,15 +6655,15 @@
       </c>
       <c r="C145" s="337">
         <f>Scenarios!C67</f>
-        <v>1.5748923352072874</v>
+        <v>1.5730839542122059</v>
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>13.97821924282669</v>
+        <v>13.962278894324077</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>15.553111578033977</v>
+        <v>15.535362848536284</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,6 +6777,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6793,18 +6805,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.669842660522461</v>
+        <v>0.66907350906372065</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.669842660522461</v>
+        <v>0.66907350906372065</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10216,11 +10216,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.559910279006633</v>
+        <v>13.544340018427304</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7420510758931296</v>
+        <v>1.740050753720191</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6702161592.7423134</v>
+        <v>6702319761.1764803</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10478,11 +10478,11 @@
       </c>
       <c r="C73" s="289">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-985453335.88014114</v>
+        <v>-985374251.66305745</v>
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-966178577.71884346</v>
+        <v>-966099493.50175989</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10494,11 +10494,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7619762740649954</v>
+        <v>8.762679493204903</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9367731259020236</v>
+        <v>8.9375046837909053</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10511,7 +10511,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1932357155.4376869</v>
+        <v>1932198987.0035198</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10626,11 +10626,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-316097028.43078154</v>
+        <v>-315734067.83592874</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.25618943480625261</v>
+        <v>-0.2558952635193098</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10643,11 +10643,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7482322920.8899441</v>
+        <v>7473907669.1291103</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>6.0642521369365614</v>
+        <v>6.0574317672448155</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10660,11 +10660,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>651487346.85378826</v>
+        <v>650739272.01067114</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.52801564128099832</v>
+        <v>0.5274093436761067</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10677,11 +10677,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>7817713239.3129511</v>
+        <v>7808912873.3038521</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.336078343411307</v>
+        <v>6.328945847401612</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11162,36 +11162,36 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-2562779.8968738765</v>
+        <v>-2563728.9074788801</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>42490745.263453811</v>
+        <v>42486248.885663263</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40963919.651057757</v>
+        <v>40959103.495800912</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>17721327.474008225</v>
+        <v>17718159.818674952</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>5074648.9540344775</v>
+        <v>5072638.4504996203</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
-        <v>-4693664.1242605112</v>
+        <v>-4695094.1127822921</v>
       </c>
       <c r="L10" s="270">
         <f t="shared" si="6"/>
-        <v>-6417000.4542544093</v>
+        <v>-6418066.4468276501</v>
       </c>
       <c r="M10" s="270">
         <f t="shared" si="6"/>
-        <v>7539835.259016444</v>
+        <v>7539175.8343284996</v>
       </c>
       <c r="N10" s="270">
         <f t="shared" si="6"/>
@@ -11217,36 +11217,36 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>1558287517.5786986</v>
+        <v>1558286568.5680938</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1372043944.8034546</v>
+        <v>1372039448.4256642</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>1481948587.9710574</v>
+        <v>1481943771.8158007</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>1407248826.4740083</v>
+        <v>1407245658.818675</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>1240528966.9540346</v>
+        <v>1240526956.4504995</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
-        <v>1157462026.8757396</v>
+        <v>1157460596.8872178</v>
       </c>
       <c r="L11" s="271">
         <f t="shared" si="7"/>
-        <v>999268814.12574768</v>
+        <v>999267748.13317442</v>
       </c>
       <c r="M11" s="271">
         <f t="shared" si="7"/>
-        <v>939487142.02901542</v>
+        <v>939486482.60432756</v>
       </c>
       <c r="N11" s="271">
         <f t="shared" si="7"/>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-389571879.39467466</v>
+        <v>-389571642.14202344</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11384,38 +11384,38 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>1109910160.1840239</v>
+        <v>1109909448.4260702</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207974017.8034546</v>
+        <v>1207969521.4256642</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>1497922530.9710574</v>
+        <v>1497917714.8158007</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>1418684303.4740083</v>
+        <v>1418681135.818675</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>1235076154.9540346</v>
+        <v>1235074144.4504995</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
-        <v>1149291475.8757396</v>
+        <v>1149290045.8872178</v>
       </c>
       <c r="L14" s="271">
         <f t="shared" si="8"/>
-        <v>975096739.00574768</v>
+        <v>975095673.01317441</v>
       </c>
       <c r="M14" s="271">
         <f t="shared" si="8"/>
-        <v>950282988.39901543</v>
+        <v>950282328.97432756</v>
       </c>
       <c r="N14" s="271">
         <f t="shared" si="8"/>
@@ -11602,38 +11602,38 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>1109910160.1840239</v>
+        <v>1109909448.4260702</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207974017.8034546</v>
+        <v>1207969521.4256642</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>1497922530.9710574</v>
+        <v>1497917714.8158007</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>1418684303.4740083</v>
+        <v>1418681135.818675</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>1235076154.9540346</v>
+        <v>1235074144.4504995</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
-        <v>1149291475.8757396</v>
+        <v>1149290045.8872178</v>
       </c>
       <c r="L19" s="275">
         <f t="shared" si="9"/>
-        <v>975096739.00574768</v>
+        <v>975095673.01317441</v>
       </c>
       <c r="M19" s="275">
         <f t="shared" si="9"/>
-        <v>950282988.39901543</v>
+        <v>950282328.97432756</v>
       </c>
       <c r="N19" s="275">
         <f t="shared" si="9"/>
@@ -12341,31 +12341,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.6720901978893349E-2</v>
+        <v>7.6721153404725254E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.3981447486809128E-2</v>
+        <v>-4.398159042170554E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.1261229605375778E-3</v>
+        <v>-8.1261412521248157E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3955539493678291E-3</v>
+        <v>4.3955610731765526E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.0590229400909381E-3</v>
+        <v>7.059031661184172E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4189762332519061E-2</v>
+        <v>2.4189788137521817E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491212478633984E-2</v>
+        <v>-1.1491220544305328E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12479,36 +12479,36 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>11594142.932626123</v>
+        <v>11593193.922021119</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54932628.263453811</v>
+        <v>54928131.885663263</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>58839376.651057757</v>
+        <v>58834560.495800912</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>38699513.474008225</v>
+        <v>38696345.818674952</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>24562491.954034477</v>
+        <v>24560481.45049962</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
-        <v>17470290.875739489</v>
+        <v>17468860.887217708</v>
       </c>
       <c r="L46" s="278">
         <f t="shared" si="17"/>
-        <v>13023321.545745591</v>
+        <v>13022255.55317235</v>
       </c>
       <c r="M46" s="278">
         <f t="shared" si="17"/>
-        <v>8056247.259016444</v>
+        <v>8055587.8343284996</v>
       </c>
       <c r="N46" s="278">
         <f t="shared" si="17"/>
@@ -12591,36 +12591,36 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-2562779.8968738765</v>
+        <v>-2563728.9074788801</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42490745.263453811</v>
+        <v>42486248.885663263</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40963919.651057757</v>
+        <v>40959103.495800912</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>17721327.474008225</v>
+        <v>17718159.818674952</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>5074648.9540344775</v>
+        <v>5072638.4504996203</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
-        <v>-4693664.1242605112</v>
+        <v>-4695094.1127822921</v>
       </c>
       <c r="L48" s="271">
         <f t="shared" si="18"/>
-        <v>-6417000.4542544093</v>
+        <v>-6418066.4468276501</v>
       </c>
       <c r="M48" s="271">
         <f t="shared" si="18"/>
-        <v>7539835.259016444</v>
+        <v>7539175.8343284996</v>
       </c>
       <c r="N48" s="271">
         <f t="shared" si="18"/>
@@ -13556,38 +13556,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0787419467782487E-4</v>
+        <v>2.0795117156354825E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.446542351793605E-3</v>
+        <v>3.4461776381038661E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4514852507923524E-3</v>
+        <v>3.4510794573776567E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.6213025664280707E-3</v>
+        <v>1.6210127615176356E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8513120210697989E-4</v>
+        <v>4.8493900004422833E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2105180469546502E-4</v>
+        <v>5.2121055020435563E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.2570326652395835E-4</v>
+        <v>7.25823820402364E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.2099906513597716E-4</v>
+        <v>9.2091851569421081E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13613,38 +13613,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639702816005058</v>
+        <v>0.12639695118316485</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.11129029474459018</v>
+        <v>0.11128993003090044</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12486411792096613</v>
+        <v>0.12486371212755144</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12874747319643948</v>
+        <v>0.12874718339152905</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11859328880443618</v>
+        <v>0.11859309660237341</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12849186946564761</v>
+        <v>0.12849171072013874</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300803977126024</v>
+        <v>0.11300791921738183</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11475937468013943</v>
+        <v>0.11475929413069767</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1599257040012645E-2</v>
+        <v>3.1599237795791213E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13785,38 +13785,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.0027895487407208E-2</v>
+        <v>9.002783775474292E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.7982127317657625E-2</v>
+        <v>9.798176260396789E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12621002986325933</v>
+        <v>0.12620962406984465</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12979369099449226</v>
+        <v>0.12979340118958183</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11807200560546331</v>
+        <v>0.11807181340340055</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758484241147444</v>
+        <v>0.12758468366596556</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11027440214752959</v>
+        <v>0.11027428159365119</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607809903850408</v>
+        <v>0.11607801848906232</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14008,38 +14008,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.0027895487407208E-2</v>
+        <v>9.002783775474292E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.7982127317657625E-2</v>
+        <v>9.798176260396789E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12621002986325933</v>
+        <v>0.12620962406984465</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12979369099449226</v>
+        <v>0.12979340118958183</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11807200560546331</v>
+        <v>0.11807181340340055</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758484241147444</v>
+        <v>0.12758468366596556</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11027440214752959</v>
+        <v>0.11027428159365119</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607809903850408</v>
+        <v>0.11607801848906232</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14077,12 +14077,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.669842660522461</v>
+        <v>0.66907350906372065</v>
       </c>
       <c r="E88" s="238"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.669842660522461</v>
+        <v>0.66907350906372065</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14133,12 +14133,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>826479338.10169375</v>
+        <v>825530327.49669015</v>
       </c>
       <c r="E89" s="238"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>826479338.10169375</v>
+        <v>825530327.49669015</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.74463624872544909</v>
+        <v>0.74378169198158484</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.68418635328311128</v>
+        <v>0.68340327537600998</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14264,12 +14264,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.9103764163746568E-2</v>
+        <v>5.8180305135975718E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.9103764163746568E-2</v>
+        <v>5.8180305135975718E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14401,38 +14401,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.1357416965255609</v>
+        <v>0.13574472684159145</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162251011739677E-2</v>
+        <v>-7.4162276248492587E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.3082127404729285E-2</v>
+        <v>5.3081075453330406E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.13439416890790845</v>
+        <v>0.1343934539280025</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1766449481294847E-2</v>
+        <v>7.1766036603469585E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830896602972033</v>
+        <v>0.15830877064688442</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3632240849642141E-2</v>
+        <v>6.3631852757613627E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35103918530297507</v>
+        <v>0.35103823701049364</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -15012,31 +15012,31 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4673153609901517</v>
+        <v>1.4673208227208359</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5708610841674193</v>
+        <v>1.5708661348526427</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.4269426397703771</v>
+        <v>1.4269458258721366</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.6576545250168762</v>
+        <v>1.6576572234138085</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.582544835820785</v>
+        <v>1.5825468048806917</v>
       </c>
       <c r="L113" s="254">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3992565712107847</v>
+        <v>1.3992581009038745</v>
       </c>
       <c r="M113" s="254">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.0454257143376948</v>
+        <v>1.0454264397847586</v>
       </c>
       <c r="N113" s="254">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15120,36 +15120,36 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639702816005058</v>
+        <v>0.12639695118316485</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.11129029474459018</v>
+        <v>0.11128993003090044</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12486411792096613</v>
+        <v>0.12486371212755144</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12874747319643948</v>
+        <v>0.12874718339152905</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11859328880443618</v>
+        <v>0.11859309660237341</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12849186946564761</v>
+        <v>0.12849171072013874</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300803977126024</v>
+        <v>0.11300791921738183</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11475937468013943</v>
+        <v>0.11475929413069767</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15285,38 +15285,38 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.10095716052324116</v>
+        <v>0.10095709903945535</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.8890951905778726E-2</v>
+        <v>8.8890660597833779E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11047646747805687</v>
+        <v>0.11047610844278136</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11113924489565619</v>
+        <v>0.11113899472609469</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.1116619030646973</v>
+        <v>0.11166172209620981</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11542129155562866</v>
+        <v>0.11542114895818852</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.10956935348026882</v>
+        <v>0.10956923659468666</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176348566858628</v>
+        <v>0.11176340722195477</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15406,50 +15406,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0042692894770306</v>
+        <v>1.0031154870595287</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0929994625556465</v>
+        <v>1.0917403546355007</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3553507750758156</v>
+        <v>1.35379013144119</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2836544150616978</v>
+        <v>1.2821775871508916</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1175220275306432</v>
+        <v>1.1162370080928425</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0399023049652687</v>
+        <v>1.0387069375683542</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.88228736377213635</v>
+        <v>0.88127330779219126</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.85983537748979466</v>
+        <v>0.85884746960656244</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.62868838663573468</v>
+        <v>0.62796649085606493</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.51771358344682217</v>
+        <v>0.51711911525095178</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.48807687266538335</v>
+        <v>0.48751643502724429</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15463,50 +15463,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.8457773478140262E-2</v>
+        <v>9.691937073038924E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10715681005447515</v>
+        <v>0.10548215986816432</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.13287752696821722</v>
+        <v>0.13080097888320677</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12584847206487235</v>
+        <v>0.12388189247834702</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10956098309123954</v>
+        <v>0.10784898628916353</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.101951206369144</v>
+        <v>0.10035815821916466</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.6498761154131021E-2</v>
+        <v>8.514717949683008E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.4297586028411253E-2</v>
+        <v>8.2980431846044686E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>6.1636116336836737E-2</v>
+        <v>6.0673090903967629E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>5.0756233671257076E-2</v>
+        <v>4.996319954115476E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.7850673790723865E-2</v>
+        <v>4.7103037200699936E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15520,43 +15520,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12742462987135136</v>
+        <v>0.1255778961050999</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12938635267000034</v>
+        <v>0.12751118813855106</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11054552473480272</v>
+        <v>0.10894341568067514</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10355683815426626</v>
+        <v>0.10205601441290009</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8766575033478674E-2</v>
+        <v>9.7335175395312307E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9364266936641387E-2</v>
+        <v>8.8069132633211797E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3635545880470721E-2</v>
+        <v>7.256836405611608E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2822200539043619E-2</v>
+        <v>7.1766806328332849E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0061904891422197E-2</v>
+        <v>4.9336370037923329E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8860635123942862E-2</v>
+        <v>4.8152509977219052E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>1109910160.1840239</v>
+        <v>1109909448.4260702</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>6702161592.7423134</v>
+        <v>6702319761.1764803</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>11999028758.746204</v>
+        <v>11999021064.065624</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-2562779.8968738765</v>
+        <v>-2563728.9074788801</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16404,14 +16404,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>7002581680.7923136</v>
+        <v>7002739849.2264805</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>7002581680.7923136</v>
+        <v>7002739849.2264805</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>19001610439.538517</v>
+        <v>19001760913.292107</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.336078343411307</v>
+        <v>6.328945847401612</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-2562779.8968738765</v>
+        <v>-2563728.9074788801</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1164044342041017</v>
+        <v>1.1151225151062012</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>21213482151.719749</v>
+        <v>21189291421.077</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>17.193043635054881</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>17.245562328921746</v>
+        <v>17.225895988310622</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>1561020694.0420117</v>
+        <v>1561019745.0314069</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16723,11 +16723,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>1111857069.3324497</v>
+        <v>1111856357.574496</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>1.7541141781267644E-3</v>
+        <v>1.7541153029976275E-3</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>1017718141.2654001</v>
+        <v>1017717489.7707057</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>1563758656.5207372</v>
+        <v>1563757707.5101323</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16772,11 +16772,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>1113807387.6779456</v>
+        <v>1113806675.919992</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>1.7541088682080375E-3</v>
+        <v>1.7541099911058122E-3</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>933183825.79618311</v>
+        <v>933183229.4623667</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>1566501413.3955789</v>
+        <v>1566500464.384974</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16821,11 +16821,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>1115761121.190294</v>
+        <v>1115760409.4323404</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>1.7541035676029715E-3</v>
+        <v>1.7541046885309886E-3</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>855671145.88031256</v>
+        <v>855670600.03700233</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>1566501413.3955789</v>
+        <v>1566500464.384974</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>12062282391.246422</v>
+        <v>12062274696.565842</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18285,7 +18285,7 @@
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>9250498874.3817577</v>
+        <v>9250492973.3729973</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18298,7 +18298,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>12057071987.323654</v>
+        <v>12057064292.643072</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18322,7 +18322,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>12057071987.323654</v>
+        <v>12057064292.643072</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18357,19 +18357,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>11758632597.642057</v>
+        <v>11758624902.961479</v>
       </c>
       <c r="C56" s="118">
-        <v>11878830678.194126</v>
+        <v>11878822983.513548</v>
       </c>
       <c r="D56" s="118">
-        <v>11999028758.746202</v>
+        <v>11999021064.065624</v>
       </c>
       <c r="E56" s="118">
-        <v>12119226839.298275</v>
+        <v>12119219144.617697</v>
       </c>
       <c r="F56" s="118">
-        <v>12239424919.850353</v>
+        <v>12239417225.169775</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18383,19 +18383,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>11542991189.969688</v>
+        <v>11542983495.289108</v>
       </c>
       <c r="C57" s="118">
-        <v>11769909763.094311</v>
+        <v>11769902068.413733</v>
       </c>
       <c r="D57" s="118">
-        <v>11999028758.746202</v>
+        <v>11999021064.065624</v>
       </c>
       <c r="E57" s="118">
-        <v>12230348176.925367</v>
+        <v>12230340482.244785</v>
       </c>
       <c r="F57" s="118">
-        <v>12463868017.6318</v>
+        <v>12463860322.951221</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18409,19 +18409,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>11349555419.242985</v>
+        <v>11349547724.562405</v>
       </c>
       <c r="C58" s="118">
-        <v>11671207972.752136</v>
+        <v>11671200278.071556</v>
       </c>
       <c r="D58" s="118">
-        <v>11999028758.746202</v>
+        <v>11999021064.065622</v>
       </c>
       <c r="E58" s="118">
-        <v>12333078200.727066</v>
+        <v>12333070506.046488</v>
       </c>
       <c r="F58" s="118">
-        <v>12673416722.196625</v>
+        <v>12673409027.516045</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18435,19 +18435,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>11176038663.808506</v>
+        <v>11176030969.127926</v>
       </c>
       <c r="C59" s="118">
-        <v>11581766533.448933</v>
+        <v>11581758838.768354</v>
       </c>
       <c r="D59" s="118">
-        <v>11999028758.746204</v>
+        <v>11999021064.065624</v>
       </c>
       <c r="E59" s="118">
-        <v>12428050579.710793</v>
+        <v>12428042885.030212</v>
       </c>
       <c r="F59" s="118">
-        <v>12869059448.655319</v>
+        <v>12869051753.974739</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18461,19 +18461,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>11020389766.48513</v>
+        <v>11020382071.80455</v>
       </c>
       <c r="C60" s="118">
-        <v>11500716625.064341</v>
+        <v>11500708930.38376</v>
       </c>
       <c r="D60" s="118">
-        <v>11999028758.746204</v>
+        <v>11999021064.065624</v>
       </c>
       <c r="E60" s="118">
-        <v>12515851131.448608</v>
+        <v>12515843436.768028</v>
       </c>
       <c r="F60" s="118">
-        <v>13051719019.3536</v>
+        <v>13051711324.673019</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18487,19 +18487,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>10880768787.650427</v>
+        <v>10880761092.969847</v>
       </c>
       <c r="C61" s="118">
-        <v>11427270941.493858</v>
+        <v>11427263246.813278</v>
       </c>
       <c r="D61" s="118">
-        <v>11999028758.746202</v>
+        <v>11999021064.065622</v>
       </c>
       <c r="E61" s="118">
-        <v>12597021435.572351</v>
+        <v>12597013740.891773</v>
       </c>
       <c r="F61" s="118">
-        <v>13222257016.71034</v>
+        <v>13222249322.02976</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18513,19 +18513,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>10755525255.148823</v>
+        <v>10755517560.468241</v>
       </c>
       <c r="C62" s="118">
-        <v>11360716042.880791</v>
+        <v>11360708348.200212</v>
       </c>
       <c r="D62" s="118">
-        <v>11999028758.746202</v>
+        <v>11999021064.065622</v>
       </c>
       <c r="E62" s="118">
-        <v>12672062174.396137</v>
+        <v>12672054479.715557</v>
       </c>
       <c r="F62" s="118">
-        <v>13381477847.194443</v>
+        <v>13381470152.513863</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18539,19 +18539,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>10643178653.911682</v>
+        <v>10643170959.231102</v>
       </c>
       <c r="C63" s="118">
-        <v>11300405425.373299</v>
+        <v>11300397730.692722</v>
       </c>
       <c r="D63" s="118">
-        <v>11999028758.746201</v>
+        <v>11999021064.06562</v>
       </c>
       <c r="E63" s="118">
-        <v>12741436221.272125</v>
+        <v>12741428526.591545</v>
       </c>
       <c r="F63" s="118">
-        <v>13530132535.609802</v>
+        <v>13530124840.929222</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18565,19 +18565,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>10542400924.655483</v>
+        <v>10542393229.974903</v>
       </c>
       <c r="C64" s="118">
-        <v>11245753241.087334</v>
+        <v>11245745546.406755</v>
       </c>
       <c r="D64" s="118">
-        <v>11999028758.746201</v>
+        <v>11999021064.06562</v>
       </c>
       <c r="E64" s="118">
-        <v>12805571495.729563</v>
+        <v>12805563801.048983</v>
       </c>
       <c r="F64" s="118">
-        <v>13668922267.585697</v>
+        <v>13668914572.905117</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18591,19 +18591,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>10452000764.773493</v>
+        <v>10451993070.092913</v>
       </c>
       <c r="C65" s="118">
-        <v>11196228607.272131</v>
+        <v>11196220912.591553</v>
       </c>
       <c r="D65" s="118">
-        <v>11999028758.746201</v>
+        <v>11999021064.06562</v>
       </c>
       <c r="E65" s="118">
-        <v>12864863603.008293</v>
+        <v>12864855908.327713</v>
       </c>
       <c r="F65" s="118">
-        <v>13798501696.98196</v>
+        <v>13798494002.30138</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18617,19 +18617,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>10121883060.674732</v>
+        <v>10121875365.994154</v>
       </c>
       <c r="C66" s="281">
-        <v>11010174632.840477</v>
+        <v>11010166938.159901</v>
       </c>
       <c r="D66" s="118">
-        <v>11999028758.746201</v>
+        <v>11999021064.06562</v>
       </c>
       <c r="E66" s="118">
-        <v>13100553293.969763</v>
+        <v>13100545599.289183</v>
       </c>
       <c r="F66" s="118">
-        <v>14328272312.779261</v>
+        <v>14328264618.098677</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18652,19 +18652,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>9930152224.5198059</v>
+        <v>9930144529.8392277</v>
       </c>
       <c r="C67" s="281">
-        <v>10896488446.918255</v>
+        <v>10896480752.237675</v>
       </c>
       <c r="D67" s="118">
-        <v>11999028758.746199</v>
+        <v>11999021064.065619</v>
       </c>
       <c r="E67" s="118">
-        <v>13259715601.77289</v>
+        <v>13259707907.092308</v>
       </c>
       <c r="F67" s="118">
-        <v>14704093704.691502</v>
+        <v>14704086010.010921</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18687,19 +18687,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>9818795841.3987427</v>
+        <v>9818788146.7181625</v>
       </c>
       <c r="C68" s="281">
-        <v>10827021783.230883</v>
+        <v>10827014088.550304</v>
       </c>
       <c r="D68" s="118">
-        <v>11999028758.746197</v>
+        <v>11999021064.065619</v>
       </c>
       <c r="E68" s="118">
-        <v>13367198623.715324</v>
+        <v>13367190929.03474</v>
       </c>
       <c r="F68" s="118">
-        <v>14970702901.968874</v>
+        <v>14970695207.288296</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18722,19 +18722,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>9754120568.9674206</v>
+        <v>9754112874.2868423</v>
       </c>
       <c r="C69" s="281">
-        <v>10784574960.648979</v>
+        <v>10784567265.968397</v>
       </c>
       <c r="D69" s="118">
-        <v>11999028758.746197</v>
+        <v>11999021064.065617</v>
       </c>
       <c r="E69" s="118">
-        <v>13439782391.601925</v>
+        <v>13439774696.921341</v>
       </c>
       <c r="F69" s="118">
-        <v>15159836531.93926</v>
+        <v>15159828837.25868</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18831,23 +18831,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>17.193043635054881</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>17.193043635054881</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>17.193043635054881</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>17.193043635054881</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>17.193043635054881</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18862,23 +18862,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>16.975528298619871</v>
+        <v>16.956172026448034</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>17.084285966837371</v>
+        <v>17.064804812922272</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>17.193043635054885</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>17.301801303272388</v>
+        <v>17.28207038587076</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>17.410558971489898</v>
+        <v>17.390703172345006</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>16.780411566623243</v>
+        <v>16.761279338585776</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>16.985732107308468</v>
+        <v>16.96636411854287</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>17.193043635054885</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>17.402346149862488</v>
+        <v>17.38249978114672</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>17.613639651731287</v>
+        <v>17.593550663793479</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18924,23 +18924,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>16.605386946617116</v>
+        <v>16.586455691807735</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>16.896424719726205</v>
+        <v>16.87715927878487</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>17.193043635054885</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>17.495298365016716</v>
+        <v>17.475345263278268</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>17.803243582025296</v>
+        <v>17.78293688006573</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18955,23 +18955,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>16.448385456817572</v>
+        <v>16.429634480052602</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>16.815496286127633</v>
+        <v>16.796323771818813</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>17.193043635054885</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>17.581231305342371</v>
+        <v>17.56117953051201</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>17.980265100469136</v>
+        <v>17.959755132329068</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18986,23 +18986,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>16.3075511684848</v>
+        <v>16.288961905663559</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>16.742160680395298</v>
+        <v>16.723072374201976</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>17.193043635054885</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>17.660675030494691</v>
+        <v>17.640532033858541</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>18.145539195492223</v>
+        <v>18.12483945023169</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -19017,23 +19017,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>16.181219266822449</v>
+        <v>16.162775065479334</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>16.675705531951341</v>
+        <v>16.656693533340949</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>17.193043635054885</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>17.73411957274077</v>
+        <v>17.713892242902016</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>18.299845444392489</v>
+        <v>18.27896851591651</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19049,23 +19049,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>16.067896371052104</v>
+        <v>16.049582293506305</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>16.615485305901441</v>
+        <v>16.596542455581304</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>17.193043635054885</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>17.802017959622731</v>
+        <v>17.781712664992551</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>18.443911690505324</v>
+        <v>18.422869336967786</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19080,23 +19080,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>15.966242881024698</v>
+        <v>15.948045527800517</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>16.560915032410001</v>
+        <v>16.542034842783092</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>17.193043635054877</v>
+        <v>17.173437599396511</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>17.864789008364856</v>
+        <v>17.844411636444658</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>18.578417476349802</v>
+        <v>18.557220675615199</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19112,23 +19112,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>15.875057141686613</v>
+        <v>15.856964493117069</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>16.511464624394876</v>
+        <v>16.492641216540314</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>17.193043635054877</v>
+        <v>17.173437599396511</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>17.922819909261474</v>
+        <v>17.902375902958742</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>18.70399724894602</v>
+        <v>18.682656250370684</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19144,23 +19144,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>15.793261238207144</v>
+        <v>15.775262512348387</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>16.466653728344554</v>
+        <v>16.447881774910698</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>17.193043635054877</v>
+        <v>17.173437599396511</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>17.97646861398054</v>
+        <v>17.955963005182291</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>18.821243352422581</v>
+        <v>18.799767725199601</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19176,23 +19176,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>15.494564024656016</v>
+        <v>15.476908279934573</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>16.298308307778374</v>
+        <v>16.279729658135746</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>17.193043635054877</v>
+        <v>17.173437599396511</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>18.189725440496748</v>
+        <v>18.168974958075378</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>19.300590581593234</v>
+        <v>19.278564540605512</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19208,23 +19208,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>15.321082064130294</v>
+        <v>15.303625521267538</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>16.195442734279585</v>
+        <v>16.176982200741783</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>17.193043635054877</v>
+        <v>17.173437599396511</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>18.333738734097437</v>
+        <v>18.312822887417589</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>19.640641421530944</v>
+        <v>19.61822491481896</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19240,23 +19240,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>15.220324543596217</v>
+        <v>15.202983696251922</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>16.132587883962611</v>
+        <v>16.11419952394056</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>17.193043635054874</v>
+        <v>17.173437599396511</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>18.430991558649534</v>
+        <v>18.409964040742583</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>19.881874846291552</v>
+        <v>19.8591813416344</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19272,23 +19272,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>15.161805041548801</v>
+        <v>15.14453138962668</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>16.094181135485037</v>
+        <v>16.075836876277041</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>17.193043635054874</v>
+        <v>17.173437599396511</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>18.496666828250596</v>
+        <v>18.475563898261978</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>20.053006801832062</v>
+        <v>20.030116793725668</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>17.803243582025296</v>
+        <v>17.78293688006573</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>17.495298365016716</v>
+        <v>17.475345263278268</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>17.193043635054885</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>16.896424719726205</v>
+        <v>16.87715927878487</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>16.605386946617116</v>
+        <v>16.586455691807735</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>1207974017.8034546</v>
+        <v>1207969521.4256642</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>1109910160.1840239</v>
+        <v>1109909448.4260702</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C14" s="252">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7246046132118273E-2</v>
+        <v>-7.7246733324975669E-2</v>
       </c>
       <c r="D14" s="465"/>
       <c r="E14" s="465"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>17.495298365016716</v>
+        <v>17.475345263278268</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>17.193043635054885</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>16.896424719726205</v>
+        <v>16.87715927878487</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>17.17933985221508</v>
+        <v>17.159749552019953</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19917,7 +19917,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>17.803243582025296</v>
+        <v>17.78293688006573</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19940,7 +19940,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>16.605386946617116</v>
+        <v>16.586455691807735</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.60285839447021494</v>
+        <v>0.60216615815734864</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.199999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.24164439429930151</v>
+        <v>0.23484614211405236</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20005,7 +20005,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>17.193043635054881</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20016,7 +20016,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.6021527305578262E-2</v>
+        <v>3.6021242322938081E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>17.244227766406713</v>
+        <v>17.224562958216211</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>17.245562328921746</v>
+        <v>17.225895988310622</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.36743184033758536</v>
+        <v>0.36743723848056592</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.60285839447021494</v>
+        <v>0.60216615815734864</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20265,15 +20265,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.103141383292539</v>
+        <v>1.1018746935843999</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>7.9466487402795929</v>
+        <v>7.9375866166894999</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>9.0497901235721319</v>
+        <v>9.0394613102739001</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.47519887546359563</v>
+        <v>0.47519938054729993</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20290,15 +20290,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2684164416096313</v>
+        <v>1.2669599736749177</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>9.9605647748197654</v>
+        <v>9.9492060408469136</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>11.228981216429396</v>
+        <v>11.216166014521832</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.34882667008699286</v>
+        <v>0.3488272508434439</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20336,15 +20336,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4544580469971957</v>
+        <v>1.4527879555048862</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>12.359979471086447</v>
+        <v>12.345884515439263</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>13.814437518083643</v>
+        <v>13.798672470944149</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19889497487412022</v>
+        <v>0.19889564081147804</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20361,15 +20361,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5748923352072874</v>
+        <v>1.5730839542122059</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>13.97821924282669</v>
+        <v>13.962278894324077</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>15.553111578033977</v>
+        <v>15.535362848536284</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>9.8068536978337728E-2</v>
+        <v>9.8069258057672193E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20488,7 +20488,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>10.199999999999999</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20506,14 +20506,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12585.1782</v>
+        <v>12770.254349999999</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.24164439429930151</v>
+        <v>0.23484614211405236</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20521,13 +20521,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.1164044342041017</v>
+        <v>1.1151225151062012</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>17.244227766406713</v>
+        <v>17.224562958216211</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20643,7 +20643,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>9.0497901235721319</v>
+        <v>9.0394613102739001</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>11.228981216429396</v>
+        <v>11.216166014521832</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>13.814437518083643</v>
+        <v>13.798672470944149</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>15.553111578033977</v>
+        <v>15.535362848536284</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20712,22 +20712,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>11594142.932626123</v>
+        <v>11593193.922021119</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-2562779.8968738765</v>
+        <v>-2563728.9074788801</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-389571879.39467466</v>
+        <v>-389571642.14202344</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20917,10 +20917,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20936,22 +20936,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>1207974017.8034546</v>
+        <v>1207969521.4256642</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>1109910160.1840239</v>
+        <v>1109909448.4260702</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.8457773478140262E-2</v>
+        <v>9.691937073038924E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20995,14 +20995,14 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.9103764163746568E-2</v>
+        <v>5.8180305135975718E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>0.74463624872544909</v>
+        <v>0.74378169198158484</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21022,11 +21022,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095716052324116</v>
+        <v>0.10095709903945535</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>8.8890951905778726E-2</v>
+        <v>8.8890660597833779E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21036,11 +21036,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639702816005058</v>
+        <v>0.12639695118316485</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>0.11129029474459018</v>
+        <v>0.11128993003090044</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21086,22 +21086,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21109,13 +21109,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25618943480625261</v>
+        <v>-0.2558952635193098</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>6702161592.7423134</v>
+        <v>6702319761.1764803</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0642521369365614</v>
+        <v>6.0574317672448155</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52801564128099832</v>
+        <v>0.5274093436761067</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>6.336078343411307</v>
+        <v>6.328945847401612</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21264,33 +21264,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21353,23 +21353,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.7420510758931296</v>
+        <v>1.740050753720191</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>17.193043635054881</v>
+        <v>17.173437599396518</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21413,13 +21413,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21464,7 +21464,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.8 HKD</v>
+        <v>17.78 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.5 HKD</v>
+        <v>17.48 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>17.19 HKD</v>
+        <v>17.17 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.9 HKD</v>
+        <v>16.88 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.61 HKD</v>
+        <v>16.59 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>17.244227766406713</v>
+        <v>17.224562958216211</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21583,13 +21583,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21602,22 +21602,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C136" s="410">
         <f>Scenarios!C58</f>
-        <v>0.60285839447021494</v>
+        <v>0.60216615815734864</v>
       </c>
       <c r="D136" s="347" t="str">
         <f>Market_currency</f>
@@ -21678,15 +21678,15 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>1.103141383292539</v>
+        <v>1.1018746935843999</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>7.9466487402795929</v>
+        <v>7.9375866166894999</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>9.0497901235721319</v>
+        <v>9.0394613102739001</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21699,15 +21699,15 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>1.2684164416096313</v>
+        <v>1.2669599736749177</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>9.9605647748197654</v>
+        <v>9.9492060408469136</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>11.228981216429396</v>
+        <v>11.216166014521832</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21739,15 +21739,15 @@
       </c>
       <c r="C144" s="413">
         <f>Scenarios!C66</f>
-        <v>1.4544580469971957</v>
+        <v>1.4527879555048862</v>
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>12.359979471086447</v>
+        <v>12.345884515439263</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>13.814437518083643</v>
+        <v>13.798672470944149</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21760,15 +21760,15 @@
       </c>
       <c r="C145" s="413">
         <f>Scenarios!C67</f>
-        <v>1.5748923352072874</v>
+        <v>1.5730839542122059</v>
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>13.97821924282669</v>
+        <v>13.962278894324077</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>15.553111578033977</v>
+        <v>15.535362848536284</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21786,13 +21786,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21800,13 +21800,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21843,22 +21843,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21882,12 +21882,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21902,15 +21905,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEB0904-D2F4-4AC3-8AE6-8D44E4B1BC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4DA0EC-11CC-491D-BA3E-56556929A758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4972,30 +4972,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5005,25 +5005,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5393,7 +5393,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.35</v>
+        <v>10.59</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12770.254349999999</v>
+        <v>13066.376190000001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.23484614211405236</v>
+        <v>0.22620514391839427</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.1151225151062012</v>
+        <v>1.1182475392341613</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>17.224562958216211</v>
+        <v>17.272500692925448</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>9.0394613102739001</v>
+        <v>9.0646403306357257</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>11.216166014521832</v>
+        <v>11.247406214854164</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>13.798672470944149</v>
+        <v>13.837103639723646</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>15.535362848536284</v>
+        <v>15.578629727559681</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C44" s="290">
         <f>Normalized_FCF!C46</f>
-        <v>11593193.922021119</v>
+        <v>11595507.391758157</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="C46" s="289">
         <f>Normalized_FCF!C10</f>
-        <v>-2563728.9074788801</v>
+        <v>-2561415.4377418421</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="C52" s="289">
         <f>Normalized_FCF!C12</f>
-        <v>-389571642.14202344</v>
+        <v>-389572220.50945771</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C60" s="289">
         <f>Normalized_FCF!G19</f>
-        <v>1207969521.4256642</v>
+        <v>1207980482.5612826</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C61" s="289">
         <f>Normalized_FCF!C19</f>
-        <v>1109909448.4260702</v>
+        <v>1109911183.5283732</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.691937073038924E-2</v>
+        <v>9.4988498088625667E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5894,14 +5894,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.8180305135975718E-2</v>
+        <v>5.7021120980778758E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="261">
         <f>Normalized_FCF!C90</f>
-        <v>0.74378169198158484</v>
+        <v>0.7458649029934451</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5921,11 +5921,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095709903945535</v>
+        <v>0.10095724892279394</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.8890660597833779E-2</v>
+        <v>8.8891370739650144E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5935,11 +5935,11 @@
       </c>
       <c r="C67" s="266">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639695118316485</v>
+        <v>0.1263971388351201</v>
       </c>
       <c r="D67" s="266">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128993003090044</v>
+        <v>0.11129081911905125</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.2558952635193098</v>
+        <v>-0.25661238550536569</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="C84" s="289">
         <f>DCF!F5</f>
-        <v>6702319761.1764803</v>
+        <v>6701934182.8869743</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0574317672448155</v>
+        <v>6.0740576850037149</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.5274093436761067</v>
+        <v>0.52888735788707653</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.328945847401612</v>
+        <v>6.3463326573854264</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.740050753720191</v>
+        <v>1.7449270794293288</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.78 HKD</v>
+        <v>17.83 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.3639110675551758E-2</v>
+        <v>2.3639555901009485E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.48 HKD</v>
+        <v>17.52 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.9814320896376947E-2</v>
+        <v>2.9814889128316445E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>17.17 HKD</v>
+        <v>17.22 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.6021242322938081E-2</v>
+        <v>3.6021937053017788E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.88 HKD</v>
+        <v>16.92 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.2258815242712591E-2</v>
+        <v>4.2259640017253727E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.59 HKD</v>
+        <v>16.63 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,17 +6445,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.8525915017963731E-2</v>
+        <v>4.8526873435919445E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>17.224562958216211</v>
+        <v>17.272500692925448</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.60216615815734864</v>
+        <v>0.60385367118644706</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,15 +6566,15 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>1.1018746935843999</v>
+        <v>1.104962591960402</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>7.9375866166894999</v>
+        <v>7.9596777386753237</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>9.0394613102739001</v>
+        <v>9.0646403306357257</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,15 +6587,15 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>1.2669599736749177</v>
+        <v>1.2705105077492085</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>9.9492060408469136</v>
+        <v>9.9768957071049567</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>11.216166014521832</v>
+        <v>11.247406214854164</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,15 +6634,15 @@
       </c>
       <c r="C144" s="337">
         <f>Scenarios!C66</f>
-        <v>1.4527879555048862</v>
+        <v>1.4568592547139514</v>
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>12.345884515439263</v>
+        <v>12.380244385009695</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>13.798672470944149</v>
+        <v>13.837103639723646</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,15 +6655,15 @@
       </c>
       <c r="C145" s="337">
         <f>Scenarios!C67</f>
-        <v>1.5730839542122059</v>
+        <v>1.5774923714449542</v>
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>13.962278894324077</v>
+        <v>14.001137356114727</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>15.535362848536284</v>
+        <v>15.578629727559681</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,18 +6777,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6805,6 +6793,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.66907350906372065</v>
+        <v>0.67094852354049672</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.66907350906372065</v>
+        <v>0.67094852354049672</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10216,11 +10216,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.544340018427304</v>
+        <v>13.582296735094307</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.740050753720191</v>
+        <v>1.7449270794293288</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6702319761.1764803</v>
+        <v>6701934182.8869743</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10478,11 +10478,11 @@
       </c>
       <c r="C73" s="289">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-985374251.66305745</v>
+        <v>-985567040.80781078</v>
       </c>
       <c r="D73" s="289">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-966099493.50175989</v>
+        <v>-966292282.6465131</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10494,11 +10494,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.762679493204903</v>
+        <v>8.7609654043450949</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9375046837909053</v>
+        <v>8.9357215236486169</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10511,7 +10511,7 @@
       <c r="C75" s="264"/>
       <c r="D75" s="265">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1932198987.0035198</v>
+        <v>1932584565.2930262</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10626,11 +10626,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-315734067.83592874</v>
+        <v>-316618882.3443259</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.2558952635193098</v>
+        <v>-0.25661238550536569</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10643,11 +10643,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7473907669.1291103</v>
+        <v>7494421408.1226683</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>6.0574317672448155</v>
+        <v>6.0740576850037149</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10660,11 +10660,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>650739272.01067114</v>
+        <v>652562906.54274845</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.5274093436761067</v>
+        <v>0.52888735788707653</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10677,11 +10677,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>7808912873.3038521</v>
+        <v>7830365432.3210907</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.328945847401612</v>
+        <v>6.3463326573854255</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11162,36 +11162,36 @@
       </c>
       <c r="C10" s="270">
         <f>C48</f>
-        <v>-2563728.9074788801</v>
+        <v>-2561415.4377418421</v>
       </c>
       <c r="E10" s="238"/>
       <c r="G10" s="270">
         <f>G48</f>
-        <v>42486248.885663263</v>
+        <v>42497210.021281652</v>
       </c>
       <c r="H10" s="270">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40959103.495800912</v>
+        <v>40970844.175385371</v>
       </c>
       <c r="I10" s="270">
         <f t="shared" si="6"/>
-        <v>17718159.818674952</v>
+        <v>17725881.834332384</v>
       </c>
       <c r="J10" s="270">
         <f t="shared" si="6"/>
-        <v>5072638.4504996203</v>
+        <v>5077539.5960290581</v>
       </c>
       <c r="K10" s="270">
         <f t="shared" si="6"/>
-        <v>-4695094.1127822921</v>
+        <v>-4691608.1294307746</v>
       </c>
       <c r="L10" s="270">
         <f t="shared" si="6"/>
-        <v>-6418066.4468276501</v>
+        <v>-6415467.8019388579</v>
       </c>
       <c r="M10" s="270">
         <f t="shared" si="6"/>
-        <v>7539175.8343284996</v>
+        <v>7540783.3601573715</v>
       </c>
       <c r="N10" s="270">
         <f t="shared" si="6"/>
@@ -11217,36 +11217,36 @@
       </c>
       <c r="C11" s="271">
         <f>SUM(C8:C10)</f>
-        <v>1558286568.5680938</v>
+        <v>1558288882.0378308</v>
       </c>
       <c r="E11" s="238"/>
       <c r="G11" s="271">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1372039448.4256642</v>
+        <v>1372050409.5612826</v>
       </c>
       <c r="H11" s="271">
         <f t="shared" si="7"/>
-        <v>1481943771.8158007</v>
+        <v>1481955512.4953852</v>
       </c>
       <c r="I11" s="271">
         <f t="shared" si="7"/>
-        <v>1407245658.818675</v>
+        <v>1407253380.8343325</v>
       </c>
       <c r="J11" s="271">
         <f t="shared" si="7"/>
-        <v>1240526956.4504995</v>
+        <v>1240531857.596029</v>
       </c>
       <c r="K11" s="271">
         <f t="shared" si="7"/>
-        <v>1157460596.8872178</v>
+        <v>1157464082.8705692</v>
       </c>
       <c r="L11" s="271">
         <f t="shared" si="7"/>
-        <v>999267748.13317442</v>
+        <v>999270346.77806318</v>
       </c>
       <c r="M11" s="271">
         <f t="shared" si="7"/>
-        <v>939486482.60432756</v>
+        <v>939488090.1301564</v>
       </c>
       <c r="N11" s="271">
         <f t="shared" si="7"/>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C12" s="270">
         <f>-C11*C41</f>
-        <v>-389571642.14202344</v>
+        <v>-389572220.50945771</v>
       </c>
       <c r="E12" s="238"/>
       <c r="G12" s="270">
@@ -11384,38 +11384,38 @@
       </c>
       <c r="C14" s="273">
         <f>SUM(C11:C13)</f>
-        <v>1109909448.4260702</v>
+        <v>1109911183.5283732</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="246"/>
       <c r="F14" s="58"/>
       <c r="G14" s="271">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207969521.4256642</v>
+        <v>1207980482.5612826</v>
       </c>
       <c r="H14" s="271">
         <f t="shared" si="8"/>
-        <v>1497917714.8158007</v>
+        <v>1497929455.4953852</v>
       </c>
       <c r="I14" s="271">
         <f t="shared" si="8"/>
-        <v>1418681135.818675</v>
+        <v>1418688857.8343325</v>
       </c>
       <c r="J14" s="271">
         <f t="shared" si="8"/>
-        <v>1235074144.4504995</v>
+        <v>1235079045.596029</v>
       </c>
       <c r="K14" s="271">
         <f t="shared" si="8"/>
-        <v>1149290045.8872178</v>
+        <v>1149293531.8705692</v>
       </c>
       <c r="L14" s="271">
         <f t="shared" si="8"/>
-        <v>975095673.01317441</v>
+        <v>975098271.65806317</v>
       </c>
       <c r="M14" s="271">
         <f t="shared" si="8"/>
-        <v>950282328.97432756</v>
+        <v>950283936.5001564</v>
       </c>
       <c r="N14" s="271">
         <f t="shared" si="8"/>
@@ -11602,38 +11602,38 @@
       </c>
       <c r="C19" s="271">
         <f>C14+C17</f>
-        <v>1109909448.4260702</v>
+        <v>1109911183.5283732</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="235"/>
       <c r="F19" s="26"/>
       <c r="G19" s="275">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207969521.4256642</v>
+        <v>1207980482.5612826</v>
       </c>
       <c r="H19" s="275">
         <f t="shared" si="9"/>
-        <v>1497917714.8158007</v>
+        <v>1497929455.4953852</v>
       </c>
       <c r="I19" s="275">
         <f t="shared" si="9"/>
-        <v>1418681135.818675</v>
+        <v>1418688857.8343325</v>
       </c>
       <c r="J19" s="275">
         <f t="shared" si="9"/>
-        <v>1235074144.4504995</v>
+        <v>1235079045.596029</v>
       </c>
       <c r="K19" s="275">
         <f t="shared" si="9"/>
-        <v>1149290045.8872178</v>
+        <v>1149293531.8705692</v>
       </c>
       <c r="L19" s="275">
         <f t="shared" si="9"/>
-        <v>975095673.01317441</v>
+        <v>975098271.65806317</v>
       </c>
       <c r="M19" s="275">
         <f t="shared" si="9"/>
-        <v>950282328.97432756</v>
+        <v>950283936.5001564</v>
       </c>
       <c r="N19" s="275">
         <f t="shared" si="9"/>
@@ -12341,31 +12341,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.6721153404725254E-2</v>
+        <v>7.6720540489221986E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.398159042170554E-2</v>
+        <v>-4.3981241980907956E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.1261412521248157E-3</v>
+        <v>-8.1260966615835269E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3955610731765526E-3</v>
+        <v>4.3955437070086695E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.059031661184172E-3</v>
+        <v>7.0590104012010655E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4189788137521817E-2</v>
+        <v>2.4189725230952534E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491220544305328E-2</v>
+        <v>-1.1491200882072221E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12479,36 +12479,36 @@
       </c>
       <c r="C46" s="270">
         <f>BS!D75*C51</f>
-        <v>11593193.922021119</v>
+        <v>11595507.391758157</v>
       </c>
       <c r="E46" s="238"/>
       <c r="G46" s="278">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54928131.885663263</v>
+        <v>54939093.021281652</v>
       </c>
       <c r="H46" s="278">
         <f t="shared" si="17"/>
-        <v>58834560.495800912</v>
+        <v>58846301.175385371</v>
       </c>
       <c r="I46" s="278">
         <f t="shared" si="17"/>
-        <v>38696345.818674952</v>
+        <v>38704067.834332384</v>
       </c>
       <c r="J46" s="278">
         <f t="shared" si="17"/>
-        <v>24560481.45049962</v>
+        <v>24565382.596029058</v>
       </c>
       <c r="K46" s="278">
         <f t="shared" si="17"/>
-        <v>17468860.887217708</v>
+        <v>17472346.870569225</v>
       </c>
       <c r="L46" s="278">
         <f t="shared" si="17"/>
-        <v>13022255.55317235</v>
+        <v>13024854.198061142</v>
       </c>
       <c r="M46" s="278">
         <f t="shared" si="17"/>
-        <v>8055587.8343284996</v>
+        <v>8057195.3601573715</v>
       </c>
       <c r="N46" s="278">
         <f t="shared" si="17"/>
@@ -12591,36 +12591,36 @@
       </c>
       <c r="C48" s="271">
         <f>C45+C46</f>
-        <v>-2563728.9074788801</v>
+        <v>-2561415.4377418421</v>
       </c>
       <c r="E48" s="238"/>
       <c r="G48" s="271">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42486248.885663263</v>
+        <v>42497210.021281652</v>
       </c>
       <c r="H48" s="271">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40959103.495800912</v>
+        <v>40970844.175385371</v>
       </c>
       <c r="I48" s="271">
         <f t="shared" si="18"/>
-        <v>17718159.818674952</v>
+        <v>17725881.834332384</v>
       </c>
       <c r="J48" s="271">
         <f t="shared" si="18"/>
-        <v>5072638.4504996203</v>
+        <v>5077539.5960290581</v>
       </c>
       <c r="K48" s="271">
         <f t="shared" si="18"/>
-        <v>-4695094.1127822921</v>
+        <v>-4691608.1294307746</v>
       </c>
       <c r="L48" s="271">
         <f t="shared" si="18"/>
-        <v>-6418066.4468276501</v>
+        <v>-6415467.8019388579</v>
       </c>
       <c r="M48" s="271">
         <f t="shared" si="18"/>
-        <v>7539175.8343284996</v>
+        <v>7540783.3601573715</v>
       </c>
       <c r="N48" s="271">
         <f t="shared" si="18"/>
@@ -13556,38 +13556,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0795117156354825E-4</v>
+        <v>2.077635196083082E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="235"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.4461776381038661E-3</v>
+        <v>3.4470667262546692E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4510794573776567E-3</v>
+        <v>3.4520686884562551E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.6210127615176356E-3</v>
+        <v>1.6217192392813222E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8493900004422833E-4</v>
+        <v>4.8540754449802884E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2121055020435563E-4</v>
+        <v>5.2082356513930635E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.25823820402364E-4</v>
+        <v>7.2552993775457921E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.2091851569421081E-4</v>
+        <v>9.2111487671997754E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13613,38 +13613,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639695118316485</v>
+        <v>0.1263971388351201</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="235"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.11128993003090044</v>
+        <v>0.11129081911905125</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12486371212755144</v>
+        <v>0.12486470135863005</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12874718339152905</v>
+        <v>0.12874788986929273</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11859309660237341</v>
+        <v>0.11859356514682722</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12849171072013874</v>
+        <v>0.12849209770520378</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300791921738183</v>
+        <v>0.11300821310002961</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11475929413069767</v>
+        <v>0.11475949049172343</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1599237795791213E-2</v>
+        <v>3.1599284708780026E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="235"/>
@@ -13785,38 +13785,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.002783775474292E-2</v>
+        <v>9.0027978493709374E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="235"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.798176260396789E-2</v>
+        <v>9.79826516921187E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12620962406984465</v>
+        <v>0.12621061330092326</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12979340118958183</v>
+        <v>0.1297941076673455</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11807181340340055</v>
+        <v>0.11807228194785435</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758468366596556</v>
+        <v>0.12758507065103059</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11027428159365119</v>
+        <v>0.11027457547629896</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607801848906232</v>
+        <v>0.11607821485008808</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14008,38 +14008,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.002783775474292E-2</v>
+        <v>9.0027978493709374E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="235"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.798176260396789E-2</v>
+        <v>9.79826516921187E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12620962406984465</v>
+        <v>0.12621061330092326</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12979340118958183</v>
+        <v>0.1297941076673455</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11807181340340055</v>
+        <v>0.11807228194785435</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758468366596556</v>
+        <v>0.12758507065103059</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11027428159365119</v>
+        <v>0.11027457547629896</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607801848906232</v>
+        <v>0.11607821485008808</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14077,12 +14077,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.66907350906372065</v>
+        <v>0.67094852354049672</v>
       </c>
       <c r="E88" s="238"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.66907350906372065</v>
+        <v>0.67094852354049672</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14133,12 +14133,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>825530327.49669015</v>
+        <v>827843797.23372996</v>
       </c>
       <c r="E89" s="238"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>825530327.49669015</v>
+        <v>827843797.23372996</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.74378169198158484</v>
+        <v>0.7458649029934451</v>
       </c>
       <c r="E90" s="238"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.68340327537600998</v>
+        <v>0.68531222911685763</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14264,12 +14264,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8180305135975718E-2</v>
+        <v>5.7021120980778758E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.8180305135975718E-2</v>
+        <v>5.7021120980778758E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14401,38 +14401,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.13574472684159145</v>
+        <v>0.1357373396623951</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="235"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162276248492587E-2</v>
+        <v>-7.416221472737683E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.3081075453330406E-2</v>
+        <v>5.3083639860764364E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.1343934539280025</v>
+        <v>0.13439519688062318</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1766036603469585E-2</v>
+        <v>7.1767043102925143E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830877064688442</v>
+        <v>0.15830924694460147</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3631852757613627E-2</v>
+        <v>6.3632798835826287E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35103823701049364</v>
+        <v>0.35104054872961044</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -15012,31 +15012,31 @@
       <c r="E113" s="238"/>
       <c r="G113" s="254">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4673208227208359</v>
+        <v>1.4673075083479914</v>
       </c>
       <c r="H113" s="254">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5708661348526427</v>
+        <v>1.5708538224998201</v>
       </c>
       <c r="I113" s="254">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.4269458258721366</v>
+        <v>1.4269380589132654</v>
       </c>
       <c r="J113" s="254">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.6576572234138085</v>
+        <v>1.657650645357676</v>
       </c>
       <c r="K113" s="254">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.5825468048806917</v>
+        <v>1.5825420047737897</v>
       </c>
       <c r="L113" s="254">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3992581009038745</v>
+        <v>1.3992543718695631</v>
       </c>
       <c r="M113" s="254">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.0454264397847586</v>
+        <v>1.045424671313316</v>
       </c>
       <c r="N113" s="254">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15120,36 +15120,36 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639695118316485</v>
+        <v>0.1263971388351201</v>
       </c>
       <c r="E116" s="238"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.11128993003090044</v>
+        <v>0.11129081911905125</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12486371212755144</v>
+        <v>0.12486470135863005</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12874718339152905</v>
+        <v>0.12874788986929273</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11859309660237341</v>
+        <v>0.11859356514682722</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12849171072013874</v>
+        <v>0.12849209770520378</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300791921738183</v>
+        <v>0.11300821310002961</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11475929413069767</v>
+        <v>0.11475949049172343</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15285,38 +15285,38 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.10095709903945535</v>
+        <v>0.10095724892279394</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="241"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.8890660597833779E-2</v>
+        <v>8.8891370739650144E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11047610844278136</v>
+        <v>0.11047698368826342</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11113899472609469</v>
+        <v>0.11113960458198734</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11166172209620981</v>
+        <v>0.11166216325578898</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11542114895818852</v>
+        <v>0.11542149657797339</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.10956923659468666</v>
+        <v>0.10956952153487129</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176340722195477</v>
+        <v>0.11176359845681248</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15406,50 +15406,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0031154870595287</v>
+        <v>1.0059281947585459</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0917403546355007</v>
+        <v>1.0948097867286377</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.35379013144119</v>
+        <v>1.3575946394665777</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2821775871508916</v>
+        <v>1.2857777657025218</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1162370080928425</v>
+        <v>1.1193695974582107</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0387069375683542</v>
+        <v>1.0416209737494557</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.88127330779219126</v>
+        <v>0.88374534708533181</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.85884746960656244</v>
+        <v>0.86125576436919493</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.62796649085606493</v>
+        <v>0.62972630684838105</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.51711911525095178</v>
+        <v>0.51856829208156641</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.48751643502724429</v>
+        <v>0.48888265317959873</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15463,50 +15463,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.691937073038924E-2</v>
+        <v>9.4988498088625667E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10548215986816432</v>
+        <v>0.10338147183462112</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.13080097888320677</v>
+        <v>0.1281959055209233</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12388189247834702</v>
+        <v>0.1214143310389539</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10784898628916353</v>
+        <v>0.10570062298944388</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.10035815821916466</v>
+        <v>9.8358921033942934E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.514717949683008E-2</v>
+        <v>8.3450929847528971E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.2980431846044686E-2</v>
+        <v>8.1327267645816326E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>6.0673090903967629E-2</v>
+        <v>5.9464240495597835E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.996319954115476E-2</v>
+        <v>4.8967732963320722E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.7103037200699936E-2</v>
+        <v>4.6164556485325657E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15520,43 +15520,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1255778961050999</v>
+        <v>0.12273193811971519</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12751118813855106</v>
+        <v>0.12462141616940542</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10894341568067514</v>
+        <v>0.1064744430873454</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10205601441290009</v>
+        <v>9.9743130233570898E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7335175395312307E-2</v>
+        <v>9.5129279069072939E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8069132633211797E-2</v>
+        <v>8.6073231610362802E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.256836405611608E-2</v>
+        <v>7.0923755238980299E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1766806328332849E-2</v>
+        <v>7.0140363125424446E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9336370037923329E-2</v>
+        <v>4.8218265334514301E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8152509977219052E-2</v>
+        <v>4.7061234963571029E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="C4" s="279">
         <f>Normalized_FCF!C19</f>
-        <v>1109909448.4260702</v>
+        <v>1109911183.5283732</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="F5" s="279">
         <f>BS!D66</f>
-        <v>6702319761.1764803</v>
+        <v>6701934182.8869743</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C6" s="287">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>11999021064.065624</v>
+        <v>11999039821.92836</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="I6" s="309">
         <f>I7+I8</f>
-        <v>-2563728.9074788801</v>
+        <v>-2561415.4377418421</v>
       </c>
       <c r="J6" s="309"/>
       <c r="N6" s="135"/>
@@ -16404,14 +16404,14 @@
       </c>
       <c r="C7" s="279">
         <f>F7</f>
-        <v>7002739849.2264805</v>
+        <v>7002354270.9369745</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>427</v>
       </c>
       <c r="F7" s="287">
         <f>SUM(F4:F6)</f>
-        <v>7002739849.2264805</v>
+        <v>7002354270.9369745</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="C8" s="287">
         <f>C6+C7</f>
-        <v>19001760913.292107</v>
+        <v>19001394092.865334</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.328945847401612</v>
+        <v>6.3463326573854264</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="I8" s="317">
         <f>Normalized_FCF!C10</f>
-        <v>-2563728.9074788801</v>
+        <v>-2561415.4377418421</v>
       </c>
       <c r="J8" s="317"/>
       <c r="N8" s="308"/>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1151225151062012</v>
+        <v>1.1182475392341613</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>21189291421.077</v>
+        <v>21248262186.365189</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>17.225895988310622</v>
+        <v>17.273837458709117</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>1561019745.0314069</v>
+        <v>1561022058.5011439</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16723,11 +16723,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>1111856357.574496</v>
+        <v>1111858092.6767986</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>1.7541153029976275E-3</v>
+        <v>1.7541125608233621E-3</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>1017717489.7707057</v>
+        <v>1017719077.9650329</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>1563757707.5101323</v>
+        <v>1563760020.9798694</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16772,11 +16772,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>1113806675.919992</v>
+        <v>1113808411.0222945</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>1.7541099911058122E-3</v>
+        <v>1.7541072537419211E-3</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>933183229.4623667</v>
+        <v>933184683.18715143</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>1566500464.384974</v>
+        <v>1566502777.8547111</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16821,11 +16821,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>1115760409.4323404</v>
+        <v>1115762144.5346429</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>1.7541046885309886E-3</v>
+        <v>1.75410195596859E-3</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>855670600.03700233</v>
+        <v>855671930.67753756</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>1566500464.384974</v>
+        <v>1566502777.8547111</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>12062274696.565842</v>
+        <v>12062293454.428572</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18285,7 +18285,7 @@
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>9250492973.3729973</v>
+        <v>9250507358.6760807</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18298,7 +18298,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>12057064292.643072</v>
+        <v>12057083050.505802</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18322,7 +18322,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>12057064292.643072</v>
+        <v>12057083050.505802</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18357,19 +18357,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>11758624902.961479</v>
+        <v>11758643660.824207</v>
       </c>
       <c r="C56" s="118">
-        <v>11878822983.513548</v>
+        <v>11878841741.37628</v>
       </c>
       <c r="D56" s="118">
-        <v>11999021064.065624</v>
+        <v>11999039821.92836</v>
       </c>
       <c r="E56" s="118">
-        <v>12119219144.617697</v>
+        <v>12119237902.480429</v>
       </c>
       <c r="F56" s="118">
-        <v>12239417225.169775</v>
+        <v>12239435983.032503</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18383,19 +18383,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>11542983495.289108</v>
+        <v>11543002253.15184</v>
       </c>
       <c r="C57" s="118">
-        <v>11769902068.413733</v>
+        <v>11769920826.276463</v>
       </c>
       <c r="D57" s="118">
-        <v>11999021064.065624</v>
+        <v>11999039821.92836</v>
       </c>
       <c r="E57" s="118">
-        <v>12230340482.244785</v>
+        <v>12230359240.107519</v>
       </c>
       <c r="F57" s="118">
-        <v>12463860322.951221</v>
+        <v>12463879080.813951</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18409,19 +18409,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>11349547724.562405</v>
+        <v>11349566482.425138</v>
       </c>
       <c r="C58" s="118">
-        <v>11671200278.071556</v>
+        <v>11671219035.934288</v>
       </c>
       <c r="D58" s="118">
-        <v>11999021064.065622</v>
+        <v>11999039821.928358</v>
       </c>
       <c r="E58" s="118">
-        <v>12333070506.046488</v>
+        <v>12333089263.909218</v>
       </c>
       <c r="F58" s="118">
-        <v>12673409027.516045</v>
+        <v>12673427785.378778</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18435,19 +18435,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>11176030969.127926</v>
+        <v>11176049726.990656</v>
       </c>
       <c r="C59" s="118">
-        <v>11581758838.768354</v>
+        <v>11581777596.631086</v>
       </c>
       <c r="D59" s="118">
-        <v>11999021064.065624</v>
+        <v>11999039821.928358</v>
       </c>
       <c r="E59" s="118">
-        <v>12428042885.030212</v>
+        <v>12428061642.892944</v>
       </c>
       <c r="F59" s="118">
-        <v>12869051753.974739</v>
+        <v>12869070511.837473</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18461,19 +18461,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>11020382071.80455</v>
+        <v>11020400829.667282</v>
       </c>
       <c r="C60" s="118">
-        <v>11500708930.38376</v>
+        <v>11500727688.246494</v>
       </c>
       <c r="D60" s="118">
-        <v>11999021064.065624</v>
+        <v>11999039821.928358</v>
       </c>
       <c r="E60" s="118">
-        <v>12515843436.768028</v>
+        <v>12515862194.63076</v>
       </c>
       <c r="F60" s="118">
-        <v>13051711324.673019</v>
+        <v>13051730082.535749</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18487,19 +18487,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>10880761092.969847</v>
+        <v>10880779850.832577</v>
       </c>
       <c r="C61" s="118">
-        <v>11427263246.813278</v>
+        <v>11427282004.676014</v>
       </c>
       <c r="D61" s="118">
-        <v>11999021064.065622</v>
+        <v>11999039821.928356</v>
       </c>
       <c r="E61" s="118">
-        <v>12597013740.891773</v>
+        <v>12597032498.754503</v>
       </c>
       <c r="F61" s="118">
-        <v>13222249322.02976</v>
+        <v>13222268079.89249</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18513,19 +18513,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>10755517560.468241</v>
+        <v>10755536318.330971</v>
       </c>
       <c r="C62" s="118">
-        <v>11360708348.200212</v>
+        <v>11360727106.062943</v>
       </c>
       <c r="D62" s="118">
-        <v>11999021064.065622</v>
+        <v>11999039821.928358</v>
       </c>
       <c r="E62" s="118">
-        <v>12672054479.715557</v>
+        <v>12672073237.578289</v>
       </c>
       <c r="F62" s="118">
-        <v>13381470152.513863</v>
+        <v>13381488910.376596</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18539,19 +18539,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>10643170959.231102</v>
+        <v>10643189717.093834</v>
       </c>
       <c r="C63" s="118">
-        <v>11300397730.692722</v>
+        <v>11300416488.55545</v>
       </c>
       <c r="D63" s="118">
-        <v>11999021064.06562</v>
+        <v>11999039821.928356</v>
       </c>
       <c r="E63" s="118">
-        <v>12741428526.591545</v>
+        <v>12741447284.454277</v>
       </c>
       <c r="F63" s="118">
-        <v>13530124840.929222</v>
+        <v>13530143598.791956</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18565,19 +18565,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>10542393229.974903</v>
+        <v>10542411987.837633</v>
       </c>
       <c r="C64" s="118">
-        <v>11245745546.406755</v>
+        <v>11245764304.269485</v>
       </c>
       <c r="D64" s="118">
-        <v>11999021064.06562</v>
+        <v>11999039821.928356</v>
       </c>
       <c r="E64" s="118">
-        <v>12805563801.048983</v>
+        <v>12805582558.911715</v>
       </c>
       <c r="F64" s="118">
-        <v>13668914572.905117</v>
+        <v>13668933330.767853</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18591,19 +18591,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>10451993070.092913</v>
+        <v>10452011827.955643</v>
       </c>
       <c r="C65" s="118">
-        <v>11196220912.591553</v>
+        <v>11196239670.454285</v>
       </c>
       <c r="D65" s="118">
-        <v>11999021064.06562</v>
+        <v>11999039821.928356</v>
       </c>
       <c r="E65" s="118">
-        <v>12864855908.327713</v>
+        <v>12864874666.190445</v>
       </c>
       <c r="F65" s="118">
-        <v>13798494002.30138</v>
+        <v>13798512760.164116</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18617,19 +18617,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>10121875365.994154</v>
+        <v>10121894123.856884</v>
       </c>
       <c r="C66" s="281">
-        <v>11010166938.159901</v>
+        <v>11010185696.022633</v>
       </c>
       <c r="D66" s="118">
-        <v>11999021064.06562</v>
+        <v>11999039821.928356</v>
       </c>
       <c r="E66" s="118">
-        <v>13100545599.289183</v>
+        <v>13100564357.151915</v>
       </c>
       <c r="F66" s="118">
-        <v>14328264618.098677</v>
+        <v>14328283375.961411</v>
       </c>
       <c r="G66" s="299"/>
       <c r="H66" s="299"/>
@@ -18652,19 +18652,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>9930144529.8392277</v>
+        <v>9930163287.7019558</v>
       </c>
       <c r="C67" s="281">
-        <v>10896480752.237675</v>
+        <v>10896499510.10041</v>
       </c>
       <c r="D67" s="118">
-        <v>11999021064.065619</v>
+        <v>11999039821.928356</v>
       </c>
       <c r="E67" s="118">
-        <v>13259707907.092308</v>
+        <v>13259726664.955042</v>
       </c>
       <c r="F67" s="118">
-        <v>14704086010.010921</v>
+        <v>14704104767.87365</v>
       </c>
       <c r="G67" s="299"/>
       <c r="H67" s="299"/>
@@ -18687,19 +18687,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>9818788146.7181625</v>
+        <v>9818806904.5808907</v>
       </c>
       <c r="C68" s="281">
-        <v>10827014088.550304</v>
+        <v>10827032846.41304</v>
       </c>
       <c r="D68" s="118">
-        <v>11999021064.065619</v>
+        <v>11999039821.928356</v>
       </c>
       <c r="E68" s="118">
-        <v>13367190929.03474</v>
+        <v>13367209686.897474</v>
       </c>
       <c r="F68" s="118">
-        <v>14970695207.288296</v>
+        <v>14970713965.151024</v>
       </c>
       <c r="G68" s="299"/>
       <c r="H68" s="299"/>
@@ -18722,19 +18722,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>9754112874.2868423</v>
+        <v>9754131632.1495705</v>
       </c>
       <c r="C69" s="281">
-        <v>10784567265.968397</v>
+        <v>10784586023.831135</v>
       </c>
       <c r="D69" s="118">
-        <v>11999021064.065617</v>
+        <v>11999039821.928358</v>
       </c>
       <c r="E69" s="118">
-        <v>13439774696.921341</v>
+        <v>13439793454.784075</v>
       </c>
       <c r="F69" s="118">
-        <v>15159828837.25868</v>
+        <v>15159847595.121408</v>
       </c>
       <c r="G69" s="299"/>
       <c r="H69" s="299"/>
@@ -18831,23 +18831,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18862,23 +18862,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>16.956172026448034</v>
+        <v>17.003357621256814</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>17.064804812922272</v>
+        <v>17.112294840718665</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>17.28207038587076</v>
+        <v>17.330169279642362</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>17.390703172345006</v>
+        <v>17.439106499104209</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>16.761279338585776</v>
+        <v>16.807918765288651</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>16.96636411854287</v>
+        <v>17.013578275714337</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>17.38249978114672</v>
+        <v>17.430880118687185</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>17.593550663793479</v>
+        <v>17.642522451234345</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18924,23 +18924,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>16.586455691807735</v>
+        <v>16.63260519197167</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>16.87715927878487</v>
+        <v>16.924123447930089</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>17.475345263278268</v>
+        <v>17.523985791396807</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>17.78293688006573</v>
+        <v>17.832439404252863</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18955,23 +18955,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>16.429634480052602</v>
+        <v>16.47534450377886</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>16.796323771818813</v>
+        <v>16.843061407191968</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>17.56117953051201</v>
+        <v>17.610060600949875</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>17.959755132329068</v>
+        <v>18.009753172746127</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18986,23 +18986,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>16.288961905663559</v>
+        <v>16.334277707962887</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>16.723072374201976</v>
+        <v>16.769604729543691</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>17.640532033858541</v>
+        <v>17.689635482092758</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>18.12483945023169</v>
+        <v>18.175300123650594</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -19017,23 +19017,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>16.162775065479334</v>
+        <v>16.20773724123551</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>16.656693533340949</v>
+        <v>16.703039868333811</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>17.173437599396518</v>
+        <v>17.221232060180512</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>17.713892242902016</v>
+        <v>17.763201276101274</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>18.27896851591651</v>
+        <v>18.329861121291373</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -19049,23 +19049,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>16.049582293506305</v>
+        <v>16.094227257351921</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>16.596542455581304</v>
+        <v>16.642720222935381</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>17.781712664992551</v>
+        <v>17.831211758434097</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>18.422869336967786</v>
+        <v>18.474165210621901</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -19080,23 +19080,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>15.948045527800517</v>
+        <v>15.992405944577625</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>16.542034842783092</v>
+        <v>16.58805985776884</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>17.173437599396511</v>
+        <v>17.221232060180512</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>17.844411636444658</v>
+        <v>17.89408643775322</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>18.557220675615199</v>
+        <v>18.608893056038045</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -19112,23 +19112,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>15.856964493117069</v>
+        <v>15.901069664011205</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>16.492641216540314</v>
+        <v>16.538527810615641</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>17.173437599396511</v>
+        <v>17.221232060180512</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>17.902375902958742</v>
+        <v>17.952213143576856</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>18.682656250370684</v>
+        <v>18.734680151987209</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -19144,23 +19144,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>15.775262512348387</v>
+        <v>15.819138721260549</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>16.447881774910698</v>
+        <v>16.493642934934478</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>17.173437599396511</v>
+        <v>17.221232060180512</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>17.955963005182291</v>
+        <v>18.005950418525934</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>18.799767725199601</v>
+        <v>18.85211982051641</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19176,23 +19176,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>15.476908279934573</v>
+        <v>15.519948379663804</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>16.279729658135746</v>
+        <v>16.325019587944929</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>17.173437599396511</v>
+        <v>17.221232060180512</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>18.168974958075378</v>
+        <v>18.219559317031113</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>19.278564540605512</v>
+        <v>19.332258418175176</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19208,23 +19208,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>15.303625521267538</v>
+        <v>15.346180012649292</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>16.176982200741783</v>
+        <v>16.221984190634871</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>17.173437599396511</v>
+        <v>17.221232060180512</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>18.312822887417589</v>
+        <v>18.363810366428623</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>19.61822491481896</v>
+        <v>19.672870658080821</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19240,23 +19240,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>15.202983696251922</v>
+        <v>15.245256148550796</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>16.11419952394056</v>
+        <v>16.159025571390405</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>17.173437599396511</v>
+        <v>17.221232060180512</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>18.409964040742583</v>
+        <v>18.461223748539105</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>19.8591813416344</v>
+        <v>19.914502342222146</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19272,23 +19272,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>15.14453138962668</v>
+        <v>15.186640034930303</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>16.075836876277041</v>
+        <v>16.120555416078236</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>17.173437599396511</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>18.475563898261978</v>
+        <v>18.527007443381095</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>20.030116793725668</v>
+        <v>20.085916824558858</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>17.78293688006573</v>
+        <v>17.832439404252863</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>17.475345263278268</v>
+        <v>17.523985791396807</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>16.87715927878487</v>
+        <v>16.924123447930089</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>16.586455691807735</v>
+        <v>16.63260519197167</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="C8" s="452">
         <f>Normalized_FCF!G19</f>
-        <v>1207969521.4256642</v>
+        <v>1207980482.5612826</v>
       </c>
       <c r="D8" s="465"/>
       <c r="E8" s="465"/>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="C9" s="452">
         <f>Normalized_FCF!C19</f>
-        <v>1109909448.4260702</v>
+        <v>1109911183.5283732</v>
       </c>
       <c r="D9" s="465"/>
       <c r="E9" s="465"/>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C14" s="252">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7246733324975669E-2</v>
+        <v>-7.7245058113006304E-2</v>
       </c>
       <c r="D14" s="465"/>
       <c r="E14" s="465"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>17.475345263278268</v>
+        <v>17.523985791396807</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="F23" s="331">
         <v>0.55000000000000004</v>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>16.87715927878487</v>
+        <v>16.924123447930089</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>17.159749552019953</v>
+        <v>17.207505653361167</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19917,7 +19917,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>17.78293688006573</v>
+        <v>17.832439404252863</v>
       </c>
       <c r="F29" s="331">
         <v>0.15</v>
@@ -19940,7 +19940,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>16.586455691807735</v>
+        <v>16.63260519197167</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.60216615815734864</v>
+        <v>0.60385367118644706</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.35</v>
+        <v>10.59</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.23484614211405236</v>
+        <v>0.22620514391839427</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20005,7 +20005,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20016,7 +20016,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.6021242322938081E-2</v>
+        <v>3.6021937053017788E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20025,7 +20025,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>17.224562958216211</v>
+        <v>17.272500692925448</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>17.225895988310622</v>
+        <v>17.273837458709117</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.36743723848056592</v>
+        <v>0.3674240788992868</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.60216615815734864</v>
+        <v>0.60385367118644706</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20265,15 +20265,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.1018746935843999</v>
+        <v>1.104962591960402</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>7.9375866166894999</v>
+        <v>7.9596777386753237</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>9.0394613102739001</v>
+        <v>9.0646403306357257</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.47519938054729993</v>
+        <v>0.47519814925533832</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20290,15 +20290,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2669599736749177</v>
+        <v>1.2705105077492085</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>9.9492060408469136</v>
+        <v>9.9768957071049567</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>11.216166014521832</v>
+        <v>11.247406214854164</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.3488272508434439</v>
+        <v>0.34882583507662379</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20336,15 +20336,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4527879555048862</v>
+        <v>1.4568592547139514</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>12.345884515439263</v>
+        <v>12.380244385009695</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>13.798672470944149</v>
+        <v>13.837103639723646</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.19889564081147804</v>
+        <v>0.19889401739082802</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20361,15 +20361,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5730839542122059</v>
+        <v>1.5774923714449542</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>13.962278894324077</v>
+        <v>14.001137356114727</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>15.535362848536284</v>
+        <v>15.578629727559681</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>9.8069258057672193E-2</v>
+        <v>9.80675002120307E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20488,7 +20488,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>10.35</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20506,14 +20506,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12770.254349999999</v>
+        <v>13066.376190000001</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.23484614211405236</v>
+        <v>0.22620514391839427</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20521,13 +20521,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.1151225151062012</v>
+        <v>1.1182475392341613</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>17.224562958216211</v>
+        <v>17.272500692925448</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20643,7 +20643,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>9.0394613102739001</v>
+        <v>9.0646403306357257</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>11.216166014521832</v>
+        <v>11.247406214854164</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>13.798672470944149</v>
+        <v>13.837103639723646</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>15.535362848536284</v>
+        <v>15.578629727559681</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20712,22 +20712,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C44" s="380">
         <f>Normalized_FCF!C46</f>
-        <v>11593193.922021119</v>
+        <v>11595507.391758157</v>
       </c>
       <c r="D44" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="C46" s="377">
         <f>Normalized_FCF!C10</f>
-        <v>-2563728.9074788801</v>
+        <v>-2561415.4377418421</v>
       </c>
       <c r="D46" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="C52" s="377">
         <f>Normalized_FCF!C12</f>
-        <v>-389571642.14202344</v>
+        <v>-389572220.50945771</v>
       </c>
       <c r="D52" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20917,10 +20917,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20936,22 +20936,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="C60" s="377">
         <f>Normalized_FCF!G19</f>
-        <v>1207969521.4256642</v>
+        <v>1207980482.5612826</v>
       </c>
       <c r="D60" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C61" s="377">
         <f>Normalized_FCF!C19</f>
-        <v>1109909448.4260702</v>
+        <v>1109911183.5283732</v>
       </c>
       <c r="D61" s="347" t="str">
         <f>Reporting_currency</f>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>9.691937073038924E-2</v>
+        <v>9.4988498088625667E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20995,14 +20995,14 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>5.8180305135975718E-2</v>
+        <v>5.7021120980778758E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="384">
         <f>Normalized_FCF!C90</f>
-        <v>0.74378169198158484</v>
+        <v>0.7458649029934451</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21022,11 +21022,11 @@
       </c>
       <c r="C66" s="382">
         <f>Normalized_FCF!C119</f>
-        <v>0.10095709903945535</v>
+        <v>0.10095724892279394</v>
       </c>
       <c r="D66" s="382">
         <f>Normalized_FCF!G119</f>
-        <v>8.8890660597833779E-2</v>
+        <v>8.8891370739650144E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21036,11 +21036,11 @@
       </c>
       <c r="C67" s="387">
         <f>Normalized_FCF!C116</f>
-        <v>0.12639695118316485</v>
+        <v>0.1263971388351201</v>
       </c>
       <c r="D67" s="387">
         <f>Normalized_FCF!G116</f>
-        <v>0.11128993003090044</v>
+        <v>0.11129081911905125</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21086,22 +21086,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21109,13 +21109,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.2558952635193098</v>
+        <v>-0.25661238550536569</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21172,7 +21172,7 @@
       </c>
       <c r="C84" s="377">
         <f>DCF!F5</f>
-        <v>6702319761.1764803</v>
+        <v>6701934182.8869743</v>
       </c>
       <c r="D84" s="347" t="str">
         <f>Reporting_currency</f>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0574317672448155</v>
+        <v>6.0740576850037149</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.5274093436761067</v>
+        <v>0.52888735788707653</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>6.328945847401612</v>
+        <v>6.3463326573854264</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21264,33 +21264,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21353,23 +21353,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>1.740050753720191</v>
+        <v>1.7449270794293288</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>17.173437599396518</v>
+        <v>17.221232060180515</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21413,13 +21413,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21464,7 +21464,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>17.78 HKD</v>
+        <v>17.83 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>17.48 HKD</v>
+        <v>17.52 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>17.17 HKD</v>
+        <v>17.22 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>16.88 HKD</v>
+        <v>16.92 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>16.59 HKD</v>
+        <v>16.63 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>17.224562958216211</v>
+        <v>17.272500692925448</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21583,13 +21583,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21602,22 +21602,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="C136" s="410">
         <f>Scenarios!C58</f>
-        <v>0.60216615815734864</v>
+        <v>0.60385367118644706</v>
       </c>
       <c r="D136" s="347" t="str">
         <f>Market_currency</f>
@@ -21678,15 +21678,15 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>1.1018746935843999</v>
+        <v>1.104962591960402</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>7.9375866166894999</v>
+        <v>7.9596777386753237</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>9.0394613102739001</v>
+        <v>9.0646403306357257</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21699,15 +21699,15 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>1.2669599736749177</v>
+        <v>1.2705105077492085</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>9.9492060408469136</v>
+        <v>9.9768957071049567</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>11.216166014521832</v>
+        <v>11.247406214854164</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21739,15 +21739,15 @@
       </c>
       <c r="C144" s="413">
         <f>Scenarios!C66</f>
-        <v>1.4527879555048862</v>
+        <v>1.4568592547139514</v>
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>12.345884515439263</v>
+        <v>12.380244385009695</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>13.798672470944149</v>
+        <v>13.837103639723646</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21760,15 +21760,15 @@
       </c>
       <c r="C145" s="413">
         <f>Scenarios!C67</f>
-        <v>1.5730839542122059</v>
+        <v>1.5774923714449542</v>
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>13.962278894324077</v>
+        <v>14.001137356114727</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>15.535362848536284</v>
+        <v>15.578629727559681</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21786,13 +21786,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21800,13 +21800,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21843,22 +21843,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21882,15 +21882,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21905,12 +21902,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1881B4E7-9DCF-4EC2-97D6-2B97C2E37F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4CAC596-702E-4F24-A1BF-EC70A61AC9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4991,30 +4991,30 @@
     <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5024,6 +5024,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5033,16 +5042,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5412,7 +5412,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.6</v>
+        <v>10.64</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>13078.714599999999</v>
+        <v>13128.068240000001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.28883385555917185</v>
+        <v>0.28734146037901681</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1192569189071655</v>
+        <v>1.1197439579010011</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>20.305918071385427</v>
+        <v>20.314702954364844</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>10.463525911566618</v>
+        <v>10.468055497634923</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>13.000707476246722</v>
+        <v>13.006335132146024</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>16.012652097665903</v>
+        <v>16.019583271014266</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>18.03895025042959</v>
+        <v>18.046758358580664</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
-        <v>11596254.64017323</v>
+        <v>11596615.197380746</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
-        <v>-2560668.1893267687</v>
+        <v>-2560307.6321192533</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
-        <v>-389572407.32156146</v>
+        <v>-389572497.46086335</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="C60" s="285">
         <f>Normalized_FCF!G19</f>
-        <v>1207984022.9971426</v>
+        <v>1207985731.304101</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
-        <v>1109911743.9646845</v>
+        <v>1109912014.3825901</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.4984594190073643E-2</v>
+        <v>9.4668708997100268E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,14 +5913,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.7018748699044282E-2</v>
+        <v>5.6829110645351559E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
-        <v>0.7465377766785446</v>
+        <v>0.74686244685569758</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5940,11 +5940,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
-        <v>0.10095729733496263</v>
+        <v>0.10095732069447201</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.889160011474774E-2</v>
+        <v>8.8891710791255046E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5954,11 +5954,11 @@
       </c>
       <c r="C67" s="263">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639719944651426</v>
+        <v>0.12639722869231071</v>
       </c>
       <c r="D67" s="263">
         <f>Normalized_FCF!G116</f>
-        <v>0.1112911062936362</v>
+        <v>0.11129124485915784</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25684401519081762</v>
+        <v>-0.25695577956646554</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
-        <v>6701809641.4844618</v>
+        <v>6701749548.6165428</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0794274225205953</v>
+        <v>6.0820183187534989</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52936475500142721</v>
+        <v>0.52959510540024335</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.3519481623312055</v>
+        <v>6.3546576445872764</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7465021277643842</v>
+        <v>1.7472621093420444</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>20.239350899086805</v>
+        <v>20.248106799472058</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>21.03 HKD</v>
+        <v>21.04 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>1.7419931184969917E-2</v>
+        <v>1.7419971063331381E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>20.63 HKD</v>
+        <v>20.64 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.4148400391622624E-2</v>
+        <v>2.4148459168348249E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>20.24 HKD</v>
+        <v>20.25 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.0925671305294427E-2</v>
+        <v>3.0925749606575102E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>19.85 HKD</v>
+        <v>19.86 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>3.7750978920530344E-2</v>
+        <v>3.7751077387165391E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.4623484065741272E-2</v>
+        <v>4.4623603353063084E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>20.305918071385427</v>
+        <v>20.314702954364844</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.60439873620986939</v>
+        <v>0.6046617372665406</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6585,15 +6585,15 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>1.1059599800525939</v>
+        <v>1.1064412329506623</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>9.3575659315140243</v>
+        <v>9.3616142646842615</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>10.463525911566618</v>
+        <v>10.468055497634923</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6606,15 +6606,15 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>1.2716573267100075</v>
+        <v>1.2722106819713797</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>11.729050149536715</v>
+        <v>11.734124450174644</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>13.000707476246722</v>
+        <v>13.006335132146024</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6653,15 +6653,15 @@
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
-        <v>1.4581742802932998</v>
+        <v>1.4588087974647501</v>
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>14.554477817372602</v>
+        <v>14.560774473549516</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>16.012652097665903</v>
+        <v>16.019583271014266</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6674,15 +6674,15 @@
       </c>
       <c r="C145" s="333">
         <f>Scenarios!C67</f>
-        <v>1.5789162858093413</v>
+        <v>1.5796033432545096</v>
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>16.460033964620248</v>
+        <v>16.467155015326156</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>18.03895025042959</v>
+        <v>18.046758358580664</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.6715541513442993</v>
+        <v>0.6718463747406006</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8869,7 +8869,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.6715541513442993</v>
+        <v>0.6718463747406006</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10235,11 +10235,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.594556716678085</v>
+        <v>13.600472319354365</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7465021277643842</v>
+        <v>1.7472621093420444</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6701809641.4844618</v>
+        <v>6701749548.6165428</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10497,11 +10497,11 @@
       </c>
       <c r="C73" s="285">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-985629311.5090667</v>
+        <v>-985659357.94302642</v>
       </c>
       <c r="D73" s="285">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-966354553.34776914</v>
+        <v>-966384599.78172874</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10513,11 +10513,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7604118986274404</v>
+        <v>8.7601448498387793</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9351457167218751</v>
+        <v>8.9348679088328034</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10530,7 +10530,7 @@
       <c r="C75" s="261"/>
       <c r="D75" s="262">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1932709106.6955383</v>
+        <v>1932769199.5634575</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10645,11 +10645,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-316904676.54705358</v>
+        <v>-317042576.01606739</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.25684401519081762</v>
+        <v>-0.25695577956646554</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10662,11 +10662,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7501046810.430234</v>
+        <v>7504243564.4291353</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>6.0794274225205953</v>
+        <v>6.0820183187534989</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10679,11 +10679,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>653151938.67571592</v>
+        <v>653436154.44214165</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.52936475500142721</v>
+        <v>0.52959510540024335</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10696,11 +10696,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>7837294072.558897</v>
+        <v>7840637142.8552094</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.3519481623312046</v>
+        <v>6.3546576445872773</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11181,36 +11181,36 @@
       </c>
       <c r="C10" s="266">
         <f>C48</f>
-        <v>-2560668.1893267687</v>
+        <v>-2560307.6321192533</v>
       </c>
       <c r="E10" s="237"/>
       <c r="G10" s="266">
         <f>G48</f>
-        <v>42500750.457141742</v>
+        <v>42502458.764100112</v>
       </c>
       <c r="H10" s="266">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40974636.403168134</v>
+        <v>40976466.203047305</v>
       </c>
       <c r="I10" s="266">
         <f t="shared" si="6"/>
-        <v>17728376.03767933</v>
+        <v>17729579.523662858</v>
       </c>
       <c r="J10" s="266">
         <f t="shared" si="6"/>
-        <v>5079122.6611412913</v>
+        <v>5079886.5109195858</v>
       </c>
       <c r="K10" s="266">
         <f t="shared" si="6"/>
-        <v>-4690482.1602889709</v>
+        <v>-4689938.865340028</v>
       </c>
       <c r="L10" s="266">
         <f t="shared" si="6"/>
-        <v>-6414628.4422345143</v>
+        <v>-6414223.4401160832</v>
       </c>
       <c r="M10" s="266">
         <f t="shared" si="6"/>
-        <v>7541302.5893949894</v>
+        <v>7541553.1243445445</v>
       </c>
       <c r="N10" s="266">
         <f t="shared" si="6"/>
@@ -11236,36 +11236,36 @@
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
-        <v>1558289629.2862458</v>
+        <v>1558289989.8434534</v>
       </c>
       <c r="E11" s="237"/>
       <c r="G11" s="267">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1372053949.9971426</v>
+        <v>1372055658.304101</v>
       </c>
       <c r="H11" s="267">
         <f t="shared" si="7"/>
-        <v>1481959304.7231679</v>
+        <v>1481961134.523047</v>
       </c>
       <c r="I11" s="267">
         <f t="shared" si="7"/>
-        <v>1407255875.0376794</v>
+        <v>1407257078.5236628</v>
       </c>
       <c r="J11" s="267">
         <f t="shared" si="7"/>
-        <v>1240533440.6611414</v>
+        <v>1240534204.5109196</v>
       </c>
       <c r="K11" s="267">
         <f t="shared" si="7"/>
-        <v>1157465208.839711</v>
+        <v>1157465752.13466</v>
       </c>
       <c r="L11" s="267">
         <f t="shared" si="7"/>
-        <v>999271186.13776755</v>
+        <v>999271591.13988602</v>
       </c>
       <c r="M11" s="267">
         <f t="shared" si="7"/>
-        <v>939488609.35939407</v>
+        <v>939488859.89434361</v>
       </c>
       <c r="N11" s="267">
         <f t="shared" si="7"/>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
-        <v>-389572407.32156146</v>
+        <v>-389572497.46086335</v>
       </c>
       <c r="E12" s="237"/>
       <c r="G12" s="266">
@@ -11403,38 +11403,38 @@
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
-        <v>1109911743.9646845</v>
+        <v>1109912014.3825901</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="243"/>
       <c r="F14" s="58"/>
       <c r="G14" s="267">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207984022.9971426</v>
+        <v>1207985731.304101</v>
       </c>
       <c r="H14" s="267">
         <f t="shared" si="8"/>
-        <v>1497933247.7231679</v>
+        <v>1497935077.523047</v>
       </c>
       <c r="I14" s="267">
         <f t="shared" si="8"/>
-        <v>1418691352.0376794</v>
+        <v>1418692555.5236628</v>
       </c>
       <c r="J14" s="267">
         <f t="shared" si="8"/>
-        <v>1235080628.6611414</v>
+        <v>1235081392.5109196</v>
       </c>
       <c r="K14" s="267">
         <f t="shared" si="8"/>
-        <v>1149294657.839711</v>
+        <v>1149295201.13466</v>
       </c>
       <c r="L14" s="267">
         <f t="shared" si="8"/>
-        <v>975099111.01776755</v>
+        <v>975099516.01988602</v>
       </c>
       <c r="M14" s="267">
         <f t="shared" si="8"/>
-        <v>950284455.72939408</v>
+        <v>950284706.26434362</v>
       </c>
       <c r="N14" s="267">
         <f t="shared" si="8"/>
@@ -11621,38 +11621,38 @@
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
-        <v>1109911743.9646845</v>
+        <v>1109912014.3825901</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="234"/>
       <c r="F19" s="26"/>
       <c r="G19" s="271">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207984022.9971426</v>
+        <v>1207985731.304101</v>
       </c>
       <c r="H19" s="271">
         <f t="shared" si="9"/>
-        <v>1497933247.7231679</v>
+        <v>1497935077.523047</v>
       </c>
       <c r="I19" s="271">
         <f t="shared" si="9"/>
-        <v>1418691352.0376794</v>
+        <v>1418692555.5236628</v>
       </c>
       <c r="J19" s="271">
         <f t="shared" si="9"/>
-        <v>1235080628.6611414</v>
+        <v>1235081392.5109196</v>
       </c>
       <c r="K19" s="271">
         <f t="shared" si="9"/>
-        <v>1149294657.839711</v>
+        <v>1149295201.13466</v>
       </c>
       <c r="L19" s="271">
         <f t="shared" si="9"/>
-        <v>975099111.01776755</v>
+        <v>975099516.01988602</v>
       </c>
       <c r="M19" s="271">
         <f t="shared" si="9"/>
-        <v>950284455.72939408</v>
+        <v>950284706.26434362</v>
       </c>
       <c r="N19" s="271">
         <f t="shared" si="9"/>
@@ -12360,31 +12360,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.6720342520218851E-2</v>
+        <v>7.672024699793141E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.3981129436057885E-2</v>
+        <v>-4.3981075131890625E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.126082258987772E-3</v>
+        <v>-8.1260753095637843E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.395538097783102E-3</v>
+        <v>4.3955353912629681E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.0590035342751115E-3</v>
+        <v>7.0590002208976241E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4189704912263372E-2</v>
+        <v>2.4189695108240299E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491194531204936E-2</v>
+        <v>-1.1491191466830289E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12498,36 +12498,36 @@
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
-        <v>11596254.64017323</v>
+        <v>11596615.197380746</v>
       </c>
       <c r="E46" s="237"/>
       <c r="G46" s="274">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54942633.457141742</v>
+        <v>54944341.764100112</v>
       </c>
       <c r="H46" s="274">
         <f t="shared" si="17"/>
-        <v>58850093.403168134</v>
+        <v>58851923.203047305</v>
       </c>
       <c r="I46" s="274">
         <f t="shared" si="17"/>
-        <v>38706562.03767933</v>
+        <v>38707765.523662858</v>
       </c>
       <c r="J46" s="274">
         <f t="shared" si="17"/>
-        <v>24566965.661141291</v>
+        <v>24567729.510919586</v>
       </c>
       <c r="K46" s="274">
         <f t="shared" si="17"/>
-        <v>17473472.839711029</v>
+        <v>17474016.134659972</v>
       </c>
       <c r="L46" s="274">
         <f t="shared" si="17"/>
-        <v>13025693.557765486</v>
+        <v>13026098.559883917</v>
       </c>
       <c r="M46" s="274">
         <f t="shared" si="17"/>
-        <v>8057714.5893949894</v>
+        <v>8057965.1243445445</v>
       </c>
       <c r="N46" s="274">
         <f t="shared" si="17"/>
@@ -12610,36 +12610,36 @@
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
-        <v>-2560668.1893267687</v>
+        <v>-2560307.6321192533</v>
       </c>
       <c r="E48" s="237"/>
       <c r="G48" s="267">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42500750.457141742</v>
+        <v>42502458.764100112</v>
       </c>
       <c r="H48" s="267">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40974636.403168134</v>
+        <v>40976466.203047305</v>
       </c>
       <c r="I48" s="267">
         <f t="shared" si="18"/>
-        <v>17728376.03767933</v>
+        <v>17729579.523662858</v>
       </c>
       <c r="J48" s="267">
         <f t="shared" si="18"/>
-        <v>5079122.6611412913</v>
+        <v>5079886.5109195858</v>
       </c>
       <c r="K48" s="267">
         <f t="shared" si="18"/>
-        <v>-4690482.1602889709</v>
+        <v>-4689938.865340028</v>
       </c>
       <c r="L48" s="267">
         <f t="shared" si="18"/>
-        <v>-6414628.4422345143</v>
+        <v>-6414223.4401160832</v>
       </c>
       <c r="M48" s="267">
         <f t="shared" si="18"/>
-        <v>7541302.5893949894</v>
+        <v>7541553.1243445445</v>
       </c>
       <c r="N48" s="267">
         <f t="shared" si="18"/>
@@ -13575,38 +13575,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0770290821413537E-4</v>
+        <v>2.0767366241770978E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="234"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.4473539008396279E-3</v>
+        <v>3.4474924663612581E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4523882091068996E-3</v>
+        <v>3.4525423820314792E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.6219474308935774E-3</v>
+        <v>1.622057536353601E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8555888388876652E-4</v>
+        <v>4.8563190713914894E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2069856934969802E-4</v>
+        <v>5.2063825723401732E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.254350139527854E-4</v>
+        <v>7.2538921196751364E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.2117830113523451E-4</v>
+        <v>9.2120890425140321E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13632,38 +13632,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639719944651426</v>
+        <v>0.12639722869231071</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="234"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.1112911062936362</v>
+        <v>0.11129124485915784</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12486502087928068</v>
+        <v>0.12486517505220526</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.128748118060905</v>
+        <v>0.128748228166365</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11859371648621796</v>
+        <v>0.11859378950946833</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12849222270099336</v>
+        <v>0.12849228301310905</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300830802383141</v>
+        <v>0.11300835382581668</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11475955391613869</v>
+        <v>0.11475958451925486</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13689,7 +13689,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1599299861628564E-2</v>
+        <v>3.1599307173077677E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="234"/>
@@ -13804,38 +13804,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.0028023952254996E-2</v>
+        <v>9.0028045886602306E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="234"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.7982938866703645E-2</v>
+        <v>9.7983077432225271E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12621093282157389</v>
+        <v>0.12621108699449846</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12979433585895778</v>
+        <v>0.12979444596441778</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11807243328724511</v>
+        <v>0.11807250631049547</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758519564682019</v>
+        <v>0.12758525595893588</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11027467040010076</v>
+        <v>0.11027471620208604</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607827827450334</v>
+        <v>0.11607830887761951</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14027,38 +14027,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.0028023952254996E-2</v>
+        <v>9.0028045886602306E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="234"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.7982938866703645E-2</v>
+        <v>9.7983077432225271E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12621093282157389</v>
+        <v>0.12621108699449846</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12979433585895778</v>
+        <v>0.12979444596441778</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11807243328724511</v>
+        <v>0.11807250631049547</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758519564682019</v>
+        <v>0.12758525595893588</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11027467040010076</v>
+        <v>0.11027471620208604</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607827827450334</v>
+        <v>0.11607830887761951</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14096,12 +14096,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.6715541513442993</v>
+        <v>0.6718463747406006</v>
       </c>
       <c r="E88" s="237"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.6715541513442993</v>
+        <v>0.6718463747406006</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14152,12 +14152,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>828591045.64880157</v>
+        <v>828951602.8563174</v>
       </c>
       <c r="E89" s="237"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>828591045.64880157</v>
+        <v>828951602.8563174</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.7465377766785446</v>
+        <v>0.74686244685569758</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.68592881186704369</v>
+        <v>0.68622631987665039</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14283,12 +14283,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.7018748699044282E-2</v>
+        <v>5.6829110645351559E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.7018748699044282E-2</v>
+        <v>5.6829110645351559E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14420,38 +14420,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.13573495363610966</v>
+        <v>0.1357338023513881</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="234"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162194856326247E-2</v>
+        <v>-7.4162185268318748E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.3084468155791598E-2</v>
+        <v>5.3084867818007586E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.13439575984963659</v>
+        <v>0.13439603148909041</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1767368199949111E-2</v>
+        <v>7.1767525063320736E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830940078775924</v>
+        <v>0.15830947501901793</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3633104417452513E-2</v>
+        <v>6.3633251864493312E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.351041295412577</v>
+        <v>0.35104165569694801</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -15031,31 +15031,31 @@
       <c r="E113" s="237"/>
       <c r="G113" s="251">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4673032078704842</v>
+        <v>1.467301132842431</v>
       </c>
       <c r="H113" s="251">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5708498456633908</v>
+        <v>1.5708479267946089</v>
       </c>
       <c r="I113" s="251">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.426935550211371</v>
+        <v>1.4269343397328025</v>
       </c>
       <c r="J113" s="251">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.6576485206632678</v>
+        <v>1.6576474954721652</v>
       </c>
       <c r="K113" s="251">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.582540454350275</v>
+        <v>1.582539706251584</v>
       </c>
       <c r="L113" s="251">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3992531673994508</v>
+        <v>1.3992525862274905</v>
       </c>
       <c r="M113" s="251">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.0454241001000841</v>
+        <v>1.0454238244823957</v>
       </c>
       <c r="N113" s="251">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15143,39 +15143,39 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639719944651426</v>
+        <v>0.12639722869231071</v>
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
-        <v>0.12639719944651426</v>
+        <v>0.12639722869231071</v>
       </c>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.1112911062936362</v>
+        <v>0.11129124485915784</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12486502087928068</v>
+        <v>0.12486517505220526</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.128748118060905</v>
+        <v>0.128748228166365</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11859371648621796</v>
+        <v>0.11859378950946833</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12849222270099336</v>
+        <v>0.12849228301310905</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300830802383141</v>
+        <v>0.11300835382581668</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11475955391613869</v>
+        <v>0.11475958451925486</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15317,41 +15317,41 @@
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
-        <v>0.10095729733496263</v>
+        <v>0.10095732069447201</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
         <f>C11/C104</f>
-        <v>0.10095729733496263</v>
+        <v>0.10095732069447201</v>
       </c>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.889160011474774E-2</v>
+        <v>8.8891710791255046E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11047726639168021</v>
+        <v>0.11047740279980425</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11113980156483172</v>
+        <v>0.11113989661164997</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11166230574989257</v>
+        <v>0.11166237450517533</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11542160885881679</v>
+        <v>0.11542166303580338</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.10956961357026641</v>
+        <v>0.1095696579785574</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176366022548058</v>
+        <v>0.11176369002967693</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15441,50 +15441,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0068366984147807</v>
+        <v>1.0072750637291468</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0958012220933364</v>
+        <v>1.0962796047938019</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3588235044671368</v>
+        <v>1.3594164502431021</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2869406281376077</v>
+        <v>1.2875017260463479</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1203814259999418</v>
+        <v>1.1208696475316164</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0425622082992378</v>
+        <v>1.0430163670320174</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.88454381612125266</v>
+        <v>0.88492908844450613</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.86203364291270457</v>
+        <v>0.8624089798646879</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63029472565672828</v>
+        <v>0.63056899522238219</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.51903637475085629</v>
+        <v>0.51926223080718481</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.48932394027864462</v>
+        <v>0.48953686711921818</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15498,50 +15498,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.4984594190073643E-2</v>
+        <v>9.4668708997100268E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10337747378239023</v>
+        <v>0.10303379744302649</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.12819089664784311</v>
+        <v>0.12776470397021636</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12140949322052903</v>
+        <v>0.12100580132014548</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10569636094339074</v>
+        <v>0.1053448916853023</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.8354925311248856E-2</v>
+        <v>9.8027854044362525E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.3447529822759686E-2</v>
+        <v>8.3170027109446057E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.1323928576670243E-2</v>
+        <v>8.1053475551192466E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.9461766571389463E-2</v>
+        <v>5.9264003310374264E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.8965695731212858E-2</v>
+        <v>4.8802841241276762E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.6162635875343833E-2</v>
+        <v>4.6009104052558099E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15555,43 +15555,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12261615327243244</v>
+        <v>0.12215519029020526</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1245038487956607</v>
+        <v>0.12403578921372213</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10637399549952714</v>
+        <v>0.10597409326080712</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9649032940897719E-2</v>
+        <v>9.9274412516307878E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5039534466177591E-2</v>
+        <v>9.4682242983222031E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5992030448466233E-2</v>
+        <v>8.5668752138509593E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0856846035924667E-2</v>
+        <v>7.0590466915488856E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0074192971532542E-2</v>
+        <v>6.9810756155850084E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8172776404953439E-2</v>
+        <v>4.7991675741776922E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.701683757209596E-2</v>
+        <v>4.6840082543629438E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
-        <v>1109911743.9646845</v>
+        <v>1109912014.3825901</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16385,7 +16385,7 @@
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
-        <v>6701809641.4844618</v>
+        <v>6701749548.6165428</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>15309127502.961166</v>
+        <v>15309131232.863312</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
-        <v>-2560668.1893267687</v>
+        <v>-2560307.6321192533</v>
       </c>
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
@@ -16439,14 +16439,14 @@
       </c>
       <c r="C7" s="275">
         <f>F7</f>
-        <v>7002229729.534462</v>
+        <v>7002169636.666543</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>424</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
-        <v>7002229729.534462</v>
+        <v>7002169636.666543</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16469,7 +16469,7 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>22311357232.495628</v>
+        <v>22311300869.529854</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16480,7 +16480,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.3519481623312055</v>
+        <v>6.3546576445872764</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16492,7 +16492,7 @@
       </c>
       <c r="I8" s="313">
         <f>Normalized_FCF!C10</f>
-        <v>-2560668.1893267687</v>
+        <v>-2560307.6321192533</v>
       </c>
       <c r="J8" s="313"/>
       <c r="N8" s="304"/>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1192569189071655</v>
+        <v>1.1197439579010011</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16530,7 +16530,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>24972140952.680161</v>
+        <v>24982944341.567406</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>20.239350899086805</v>
+        <v>20.248106799472058</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16642,14 +16642,14 @@
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
-        <v>0.12639719944651426</v>
+        <v>0.12639722869231071</v>
       </c>
       <c r="E17" s="308" t="s">
         <v>549</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
-        <v>0.12639719944651426</v>
+        <v>0.12639722869231071</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>412</v>
@@ -16675,7 +16675,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>20.307598147338574</v>
+        <v>20.316383761804069</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16742,11 +16742,11 @@
       </c>
       <c r="E21" s="299">
         <f>$C$17</f>
-        <v>0.12639719944651426</v>
+        <v>0.12639722869231071</v>
       </c>
       <c r="F21" s="277">
         <f>C21*E21</f>
-        <v>1561018321.8102365</v>
+        <v>1561018682.9988096</v>
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16754,15 +16754,15 @@
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>1111855290.1586182</v>
+        <v>1111855561.0500479</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
-        <v>1.7510817454648997E-3</v>
+        <v>1.7510817454651217E-3</v>
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>9.0028023952254982E-2</v>
+        <v>9.002804588660232E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>1036694909.2388048</v>
+        <v>1036695161.8182265</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16791,11 +16791,11 @@
       </c>
       <c r="E22" s="299">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>0.12639719944651426</v>
+        <v>0.12639722869231071</v>
       </c>
       <c r="F22" s="277">
         <f t="shared" ref="F22:F50" si="7">IF(A22="", 0,C22*E22)</f>
-        <v>1563751792.497895</v>
+        <v>1563752154.3189387</v>
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
@@ -16803,7 +16803,7 @@
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>1113802239.6608138</v>
+        <v>1113802511.0265965</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
@@ -16811,7 +16811,7 @@
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
-        <v>9.0028023952254982E-2</v>
+        <v>9.002804588660232E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16819,7 +16819,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>968307922.39626074</v>
+        <v>968308158.3139379</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16840,11 +16840,11 @@
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
-        <v>0.12639719944651426</v>
+        <v>0.12639722869231071</v>
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>1566490049.7161765</v>
+        <v>1566490412.1707983</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>1115752598.430742</v>
+        <v>1115752870.2717085</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
@@ -16860,7 +16860,7 @@
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>9.0028023952254982E-2</v>
+        <v>9.002804588660232E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16868,7 +16868,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>904432175.96564853</v>
+        <v>904432396.320696</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -18292,11 +18292,11 @@
       </c>
       <c r="E51" s="301">
         <f>F17</f>
-        <v>0.12639719944651426</v>
+        <v>0.12639722869231071</v>
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>1566490049.7161765</v>
+        <v>1566490412.1707983</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>15389691012.837822</v>
+        <v>15389694762.368395</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
@@ -18317,7 +18317,7 @@
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>12474926565.043428</v>
+        <v>12474929604.423395</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18330,7 +18330,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>15384361572.644142</v>
+        <v>15384365320.876255</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18354,7 +18354,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>15384361572.644142</v>
+        <v>15384365320.876255</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18389,19 +18389,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>15002944952.901939</v>
+        <v>15002948608.206045</v>
       </c>
       <c r="C56" s="118">
-        <v>15156036227.931549</v>
+        <v>15156039920.534681</v>
       </c>
       <c r="D56" s="118">
-        <v>15309127502.961166</v>
+        <v>15309131232.863316</v>
       </c>
       <c r="E56" s="118">
-        <v>15462218777.990774</v>
+        <v>15462222545.191944</v>
       </c>
       <c r="F56" s="118">
-        <v>15615310053.020384</v>
+        <v>15615313857.520582</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18415,19 +18415,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>14723169755.645029</v>
+        <v>14723173342.784958</v>
       </c>
       <c r="C57" s="118">
-        <v>15014721204.827295</v>
+        <v>15014724863.000559</v>
       </c>
       <c r="D57" s="118">
-        <v>15309127502.961166</v>
+        <v>15309131232.863316</v>
       </c>
       <c r="E57" s="118">
-        <v>15606388650.046635</v>
+        <v>15606392452.373224</v>
       </c>
       <c r="F57" s="118">
-        <v>15906504646.083706</v>
+        <v>15906508521.530293</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18441,19 +18441,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>14467524353.955727</v>
+        <v>14467527878.81044</v>
       </c>
       <c r="C58" s="118">
-        <v>14884276568.115677</v>
+        <v>14884280194.507519</v>
       </c>
       <c r="D58" s="118">
-        <v>15309127502.961166</v>
+        <v>15309131232.863316</v>
       </c>
       <c r="E58" s="118">
-        <v>15742157014.406933</v>
+        <v>15742160849.812002</v>
       </c>
       <c r="F58" s="118">
-        <v>16183444958.367702</v>
+        <v>16183448901.287775</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18467,19 +18467,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>14233927623.274593</v>
+        <v>14233931091.216005</v>
       </c>
       <c r="C59" s="118">
-        <v>14763866134.228022</v>
+        <v>14763869731.283176</v>
       </c>
       <c r="D59" s="118">
-        <v>15309127502.961166</v>
+        <v>15309131232.863316</v>
       </c>
       <c r="E59" s="118">
-        <v>15870013469.422216</v>
+        <v>15870017335.978125</v>
       </c>
       <c r="F59" s="118">
-        <v>16446828751.868559</v>
+        <v>16446832758.959225</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18493,19 +18493,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>14020477929.971554</v>
+        <v>14020481345.908276</v>
       </c>
       <c r="C60" s="118">
-        <v>14652718041.408653</v>
+        <v>14652721611.383787</v>
       </c>
       <c r="D60" s="118">
-        <v>15309127502.961166</v>
+        <v>15309131232.863316</v>
       </c>
       <c r="E60" s="118">
-        <v>15990419082.07065</v>
+        <v>15990422977.962074</v>
       </c>
       <c r="F60" s="118">
-        <v>16697319632.400848</v>
+        <v>16697323700.520889</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18519,19 +18519,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>13825437650.776237</v>
+        <v>13825441019.193518</v>
       </c>
       <c r="C61" s="118">
-        <v>14550119801.88308</v>
+        <v>14550123346.861271</v>
       </c>
       <c r="D61" s="118">
-        <v>15309127502.961166</v>
+        <v>15309131232.863314</v>
       </c>
       <c r="E61" s="118">
-        <v>16103808050.625349</v>
+        <v>16103811974.142757</v>
       </c>
       <c r="F61" s="118">
-        <v>16935548721.578407</v>
+        <v>16935552847.74037</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18545,19 +18545,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>13647219027.362335</v>
+        <v>13647222352.358589</v>
       </c>
       <c r="C62" s="118">
-        <v>14455413734.628704</v>
+        <v>14455417256.532793</v>
       </c>
       <c r="D62" s="118">
-        <v>15309127502.961166</v>
+        <v>15309131232.863316</v>
       </c>
       <c r="E62" s="118">
-        <v>16210589270.429777</v>
+        <v>16210593219.963264</v>
       </c>
       <c r="F62" s="118">
-        <v>17162116246.950073</v>
+        <v>17162120428.312748</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18571,19 +18571,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>13484371240.932846</v>
+        <v>13484374526.25301</v>
       </c>
       <c r="C63" s="118">
-        <v>14367992749.470821</v>
+        <v>14367996250.075741</v>
       </c>
       <c r="D63" s="118">
-        <v>15309127502.961166</v>
+        <v>15309131232.863316</v>
       </c>
       <c r="E63" s="118">
-        <v>16311147808.427414</v>
+        <v>16311151782.460899</v>
       </c>
       <c r="F63" s="118">
-        <v>17377593054.296555</v>
+        <v>17377597288.157806</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18597,19 +18597,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>13335568601.58469</v>
+        <v>13335571850.650711</v>
       </c>
       <c r="C64" s="118">
-        <v>14287296455.478928</v>
+        <v>14287299936.423073</v>
       </c>
       <c r="D64" s="118">
-        <v>15309127502.961166</v>
+        <v>15309131232.863316</v>
       </c>
       <c r="E64" s="118">
-        <v>16405846291.763189</v>
+        <v>16405850288.868925</v>
       </c>
       <c r="F64" s="118">
-        <v>17582522045.8988</v>
+        <v>17582526329.688766</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18623,19 +18623,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>13199599756.30619</v>
+        <v>13199602972.244883</v>
       </c>
       <c r="C65" s="118">
-        <v>14212807568.71718</v>
+        <v>14212811031.51292</v>
       </c>
       <c r="D65" s="118">
-        <v>15309127502.961166</v>
+        <v>15309131232.863316</v>
       </c>
       <c r="E65" s="118">
-        <v>16495026215.464012</v>
+        <v>16495030234.297466</v>
       </c>
       <c r="F65" s="118">
-        <v>17777419548.401634</v>
+        <v>17777423879.676254</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18649,19 +18649,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>12676695011.58423</v>
+        <v>12676698100.122879</v>
       </c>
       <c r="C66" s="277">
-        <v>13917989722.054935</v>
+        <v>13917993113.021519</v>
       </c>
       <c r="D66" s="118">
-        <v>15309127502.961166</v>
+        <v>15309131232.863314</v>
       </c>
       <c r="E66" s="118">
-        <v>16868769803.201134</v>
+        <v>16868773913.09314</v>
       </c>
       <c r="F66" s="118">
-        <v>18617804538.205452</v>
+        <v>18617809074.230721</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18684,19 +18684,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>12343601282.423637</v>
+        <v>12343604289.807627</v>
       </c>
       <c r="C67" s="277">
-        <v>13720409604.948877</v>
+        <v>13720412947.77722</v>
       </c>
       <c r="D67" s="118">
-        <v>15309127502.961166</v>
+        <v>15309131232.863312</v>
       </c>
       <c r="E67" s="118">
-        <v>17145587668.2901</v>
+        <v>17145591845.625763</v>
       </c>
       <c r="F67" s="118">
-        <v>19271676388.971382</v>
+        <v>19271681084.305401</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18719,19 +18719,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>12131418406.81193</v>
+        <v>12131421362.499874</v>
       </c>
       <c r="C68" s="277">
-        <v>13587995970.165207</v>
+        <v>13587999280.732405</v>
       </c>
       <c r="D68" s="118">
-        <v>15309127502.961166</v>
+        <v>15309131232.863314</v>
       </c>
       <c r="E68" s="118">
-        <v>17350616284.021999</v>
+        <v>17350620511.31065</v>
       </c>
       <c r="F68" s="118">
-        <v>19780429403.853138</v>
+        <v>19780434223.13929</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18754,19 +18754,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>11996256532.65624</v>
+        <v>11996259455.413467</v>
       </c>
       <c r="C69" s="277">
-        <v>13499255407.939442</v>
+        <v>13499258696.885969</v>
       </c>
       <c r="D69" s="118">
-        <v>15309127502.961166</v>
+        <v>15309131232.863312</v>
       </c>
       <c r="E69" s="118">
-        <v>17502473293.884514</v>
+        <v>17502477558.171478</v>
       </c>
       <c r="F69" s="118">
-        <v>20176270928.225365</v>
+        <v>20176275843.953991</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18863,23 +18863,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>20.239350899086805</v>
+        <v>20.248106799472058</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>20.239350899086805</v>
+        <v>20.248106799472058</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>20.239350899086805</v>
+        <v>20.248106799472058</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>20.239350899086805</v>
+        <v>20.248106799472058</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>20.239350899086805</v>
+        <v>20.248106799472058</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18894,23 +18894,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>19.961602844351685</v>
+        <v>19.970237816374368</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>20.100476871719241</v>
+        <v>20.109172307923217</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>20.239350899086801</v>
+        <v>20.248106799472065</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>20.378224926454358</v>
+        <v>20.387041291020907</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>20.517098953821911</v>
+        <v>20.525975782569763</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18925,23 +18925,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>19.707809750048277</v>
+        <v>19.716334223427289</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>19.972285461841498</v>
+        <v>19.98092508495505</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>20.239350899086801</v>
+        <v>20.248106799472065</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>20.509006061784177</v>
+        <v>20.517879366978335</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>20.781250949933629</v>
+        <v>20.790242787473865</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18956,23 +18956,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>19.475905570638165</v>
+        <v>19.484329075559565</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>19.853954929646662</v>
+        <v>19.86254303298443</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>20.239350899086801</v>
+        <v>20.248106799472065</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>20.632165918831376</v>
+        <v>20.641092846434741</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>21.032472428753163</v>
+        <v>21.041573645284757</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18987,23 +18987,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>19.264002450990695</v>
+        <v>19.272333695689753</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>19.74472674608219</v>
+        <v>19.75326729270386</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>20.239350899086801</v>
+        <v>20.248106799472065</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>20.748148628031995</v>
+        <v>20.757126053195556</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>21.271396352665445</v>
+        <v>21.28060159397204</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -19018,23 +19018,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>19.07037535797949</v>
+        <v>19.078622299631554</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>19.643900730484223</v>
+        <v>19.652397378598724</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>20.239350899086801</v>
+        <v>20.248106799472065</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>20.857372438095052</v>
+        <v>20.866397418070541</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>21.498624699882722</v>
+        <v>21.507928873842463</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -19049,23 +19049,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>18.893448037558997</v>
+        <v>18.901617947056234</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>19.550830562239938</v>
+        <v>19.559286688655515</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>20.239350899086801</v>
+        <v>20.248106799472065</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>20.960231224261662</v>
+        <v>20.969300987789637</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>21.714729981152299</v>
+        <v>21.724128244908041</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19081,23 +19081,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>18.731780183002275</v>
+        <v>18.739879704143586</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>19.464919637706757</v>
+        <v>19.473338359477172</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>20.239350899086801</v>
+        <v>20.248106799472065</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>21.057095908670316</v>
+        <v>21.066207845986646</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>21.920256682219868</v>
+        <v>21.929744429977404</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19112,23 +19112,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>18.584055709840882</v>
+        <v>18.592090913416875</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>19.385617245829977</v>
+        <v>19.394001440235623</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>20.239350899086801</v>
+        <v>20.248106799472065</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>21.148315797950243</v>
+        <v>21.15746745137497</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>22.115722635682733</v>
+        <v>22.125295487106307</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19144,23 +19144,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>18.449072042057054</v>
+        <v>18.457048475270327</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>19.312415037943712</v>
+        <v>19.320767360935733</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>20.239350899086801</v>
+        <v>20.248106799472065</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>21.234219842866555</v>
+        <v>21.24340889794113</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>22.30162032568937</v>
+        <v>22.311274114865263</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19176,23 +19176,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>18.32573032231052</v>
+        <v>18.333653053933624</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>19.244843769125623</v>
+        <v>19.253166672351213</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>20.239350899086801</v>
+        <v>20.248106799472065</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>21.315117824559298</v>
+        <v>21.324342101700406</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>22.478418128772606</v>
+        <v>22.488148893712939</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19208,23 +19208,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>17.851386583158199</v>
+        <v>17.859102790880595</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>18.977405002952327</v>
+        <v>18.985611466363011</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>20.239350899086801</v>
+        <v>20.248106799472065</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>21.654152673030019</v>
+        <v>21.663524562110741</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>23.240758425766831</v>
+        <v>23.250821105052829</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19240,23 +19240,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>17.549226530924905</v>
+        <v>17.556811181577025</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>18.798173713742901</v>
+        <v>18.806302141876802</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>20.239350899086801</v>
+        <v>20.248106799472062</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>21.905263076054343</v>
+        <v>21.914744295765281</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>23.833906645876556</v>
+        <v>23.844227575190967</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19272,23 +19272,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>17.356748609051646</v>
+        <v>17.364249456992898</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>18.678057039966241</v>
+        <v>18.686133170658511</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>20.239350899086801</v>
+        <v>20.248106799472065</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>22.091251138318352</v>
+        <v>22.100813335128667</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>24.295412894997217</v>
+        <v>24.305934758914329</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19304,23 +19304,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>17.234138918806945</v>
+        <v>17.241586383875386</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>18.597557617221412</v>
+        <v>18.605598699375218</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>20.239350899086801</v>
+        <v>20.248106799472062</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>22.229005523991361</v>
+        <v>22.238627697503642</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>24.65449349366785</v>
+        <v>24.665171697217563</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19367,7 +19367,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>21.032472428753163</v>
+        <v>21.041573645284757</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19395,7 +19395,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>20.632165918831376</v>
+        <v>20.641092846434741</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19423,7 +19423,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>20.239350899086801</v>
+        <v>20.248106799472065</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19451,7 +19451,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>19.853954929646662</v>
+        <v>19.86254303298443</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>19.475905570638165</v>
+        <v>19.484329075559565</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C8" s="447">
         <f>Normalized_FCF!G19</f>
-        <v>1207984022.9971426</v>
+        <v>1207985731.304101</v>
       </c>
       <c r="D8" s="469"/>
       <c r="E8" s="469"/>
@@ -19701,7 +19701,7 @@
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
-        <v>1109911743.9646845</v>
+        <v>1109912014.3825901</v>
       </c>
       <c r="D9" s="469"/>
       <c r="E9" s="469"/>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C14" s="249">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7244517025759296E-2</v>
+        <v>-7.7244255944825979E-2</v>
       </c>
       <c r="D14" s="469"/>
       <c r="E14" s="469"/>
@@ -19839,7 +19839,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>20.632165918831376</v>
+        <v>20.641092846434741</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19863,7 +19863,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>20.239350899086801</v>
+        <v>20.248106799472065</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19886,7 +19886,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>19.853954929646662</v>
+        <v>19.86254303298443</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19902,7 +19902,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>20.221564910675681</v>
+        <v>20.23031306724269</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19949,7 +19949,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>21.032472428753163</v>
+        <v>21.041573645284757</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>19.475905570638165</v>
+        <v>19.484329075559565</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.60439873620986939</v>
+        <v>0.6046617372665406</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -20017,7 +20017,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.6</v>
+        <v>10.64</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20028,7 +20028,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.28883385555917185</v>
+        <v>0.28734146037901681</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20037,7 +20037,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>20.239350899086805</v>
+        <v>20.248106799472058</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20048,7 +20048,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.0925671305294396E-2</v>
+        <v>3.0925749606575206E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20057,7 +20057,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>20.305918071385427</v>
+        <v>20.314702954364844</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20095,7 +20095,7 @@
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639719944651426</v>
+        <v>0.12639722869231071</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>401</v>
@@ -20160,7 +20160,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>20.307598147338574</v>
+        <v>20.316383761804069</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20227,7 +20227,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.31281265589671636</v>
+        <v>0.31281075873284708</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20261,7 +20261,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.60439873620986939</v>
+        <v>0.6046617372665406</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20301,15 +20301,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.1059599800525939</v>
+        <v>1.1064412329506623</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>9.3575659315140243</v>
+        <v>9.3616142646842615</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>10.463525911566618</v>
+        <v>10.468055497634923</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20317,7 +20317,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.48470559790588597</v>
+        <v>0.48470546081079946</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20326,15 +20326,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2716573267100075</v>
+        <v>1.2722106819713797</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>11.729050149536715</v>
+        <v>11.734124450174644</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>13.000707476246722</v>
+        <v>13.006335132146024</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.35975771050869243</v>
+        <v>0.35975755287371969</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20372,15 +20372,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4581742802932998</v>
+        <v>1.4588087974647501</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>14.554477817372602</v>
+        <v>14.560774473549516</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>16.012652097665903</v>
+        <v>16.019583271014266</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20388,7 +20388,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.21142929655416487</v>
+        <v>0.2114291157985021</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20397,15 +20397,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5789162858093413</v>
+        <v>1.5796033432545096</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>16.460033964620248</v>
+        <v>16.467155015326156</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>18.03895025042959</v>
+        <v>18.046758358580664</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20413,7 +20413,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.11164074497820364</v>
+        <v>0.11164054925533062</v>
       </c>
     </row>
   </sheetData>
@@ -20524,7 +20524,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>10.6</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20542,14 +20542,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>13078.714599999999</v>
+        <v>13128.068240000001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.28883385555917185</v>
+        <v>0.28734146037901681</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20557,13 +20557,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20601,7 +20601,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1192569189071655</v>
+        <v>1.1197439579010011</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20627,7 +20627,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>20.305918071385427</v>
+        <v>20.314702954364844</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20679,7 +20679,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>10.463525911566618</v>
+        <v>10.468055497634923</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20695,7 +20695,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>13.000707476246722</v>
+        <v>13.006335132146024</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>16.012652097665903</v>
+        <v>16.019583271014266</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20727,7 +20727,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>18.03895025042959</v>
+        <v>18.046758358580664</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20748,22 +20748,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20872,7 +20872,7 @@
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
-        <v>11596254.64017323</v>
+        <v>11596615.197380746</v>
       </c>
       <c r="D44" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
-        <v>-2560668.1893267687</v>
+        <v>-2560307.6321192533</v>
       </c>
       <c r="D46" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20942,7 +20942,7 @@
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
-        <v>-389572407.32156146</v>
+        <v>-389572497.46086335</v>
       </c>
       <c r="D52" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20953,10 +20953,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20972,22 +20972,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C60" s="373">
         <f>Normalized_FCF!G19</f>
-        <v>1207984022.9971426</v>
+        <v>1207985731.304101</v>
       </c>
       <c r="D60" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21008,7 +21008,7 @@
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
-        <v>1109911743.9646845</v>
+        <v>1109912014.3825901</v>
       </c>
       <c r="D61" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21021,7 +21021,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>9.4984594190073643E-2</v>
+        <v>9.4668708997100268E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21031,14 +21031,14 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.7018748699044282E-2</v>
+        <v>5.6829110645351559E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
-        <v>0.7465377766785446</v>
+        <v>0.74686244685569758</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21058,11 +21058,11 @@
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
-        <v>0.10095729733496263</v>
+        <v>0.10095732069447201</v>
       </c>
       <c r="D66" s="378">
         <f>Normalized_FCF!G119</f>
-        <v>8.889160011474774E-2</v>
+        <v>8.8891710791255046E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21072,11 +21072,11 @@
       </c>
       <c r="C67" s="383">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639719944651426</v>
+        <v>0.12639722869231071</v>
       </c>
       <c r="D67" s="383">
         <f>Normalized_FCF!G116</f>
-        <v>0.1112911062936362</v>
+        <v>0.11129124485915784</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21122,22 +21122,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21145,13 +21145,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21172,7 +21172,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25684401519081762</v>
+        <v>-0.25695577956646554</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21208,7 +21208,7 @@
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
-        <v>6701809641.4844618</v>
+        <v>6701749548.6165428</v>
       </c>
       <c r="D84" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0794274225205953</v>
+        <v>6.0820183187534989</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21265,7 +21265,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52936475500142721</v>
+        <v>0.52959510540024335</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21278,7 +21278,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.3519481623312055</v>
+        <v>6.3546576445872764</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21300,33 +21300,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21389,23 +21389,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21423,7 +21423,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.7465021277643842</v>
+        <v>1.7472621093420444</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21437,7 +21437,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>20.239350899086805</v>
+        <v>20.248106799472058</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21449,13 +21449,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21500,7 +21500,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>21.03 HKD</v>
+        <v>21.04 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>20.63 HKD</v>
+        <v>20.64 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>20.24 HKD</v>
+        <v>20.25 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>19.85 HKD</v>
+        <v>19.86 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21611,7 +21611,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>20.305918071385427</v>
+        <v>20.314702954364844</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21619,13 +21619,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21638,22 +21638,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="C136" s="406">
         <f>Scenarios!C58</f>
-        <v>0.60439873620986939</v>
+        <v>0.6046617372665406</v>
       </c>
       <c r="D136" s="343" t="str">
         <f>Market_currency</f>
@@ -21714,15 +21714,15 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>1.1059599800525939</v>
+        <v>1.1064412329506623</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>9.3575659315140243</v>
+        <v>9.3616142646842615</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>10.463525911566618</v>
+        <v>10.468055497634923</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21735,15 +21735,15 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>1.2716573267100075</v>
+        <v>1.2722106819713797</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>11.729050149536715</v>
+        <v>11.734124450174644</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>13.000707476246722</v>
+        <v>13.006335132146024</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21775,15 +21775,15 @@
       </c>
       <c r="C144" s="409">
         <f>Scenarios!C66</f>
-        <v>1.4581742802932998</v>
+        <v>1.4588087974647501</v>
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>14.554477817372602</v>
+        <v>14.560774473549516</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>16.012652097665903</v>
+        <v>16.019583271014266</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21796,15 +21796,15 @@
       </c>
       <c r="C145" s="409">
         <f>Scenarios!C67</f>
-        <v>1.5789162858093413</v>
+        <v>1.5796033432545096</v>
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>16.460033964620248</v>
+        <v>16.467155015326156</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>18.03895025042959</v>
+        <v>18.046758358580664</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21822,13 +21822,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21836,13 +21836,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21879,22 +21879,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21918,12 +21918,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21938,15 +21941,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4CAC596-702E-4F24-A1BF-EC70A61AC9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC71DC42-238D-42A1-B804-2C099AEE0445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3249,10 +3249,10 @@
     <t>FCFE Margin</t>
   </si>
   <si>
-    <t>Long-term Projection</t>
-  </si>
-  <si>
     <t>FCFE and TV</t>
+  </si>
+  <si>
+    <t>Sales/Total Assets g Projection</t>
   </si>
   <si>
     <t>新华文轩</t>
@@ -4985,12 +4985,10 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5412,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.64</v>
+        <v>10.57</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5429,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>13128.068240000001</v>
+        <v>13041.69937</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.28734146037901681</v>
+        <v>0.29058822043182098</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5487,7 +5485,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1197439579010011</v>
+        <v>1.1204719901561737</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5509,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>20.314702954364844</v>
+        <v>20.327834629345425</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5559,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>10.468055497634923</v>
+        <v>10.474826343883192</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5574,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>13.006335132146024</v>
+        <v>13.014747377846154</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5589,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>16.019583271014266</v>
+        <v>16.029944020097382</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5604,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>18.046758358580664</v>
+        <v>18.0584299534876</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5754,7 +5752,7 @@
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
-        <v>11596615.197380746</v>
+        <v>11597154.163008198</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5784,7 +5782,7 @@
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
-        <v>-2560307.6321192533</v>
+        <v>-2559768.6664918009</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5824,7 +5822,7 @@
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
-        <v>-389572497.46086335</v>
+        <v>-389572632.20227021</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5877,7 +5875,7 @@
       </c>
       <c r="C60" s="285">
         <f>Normalized_FCF!G19</f>
-        <v>1207985731.304101</v>
+        <v>1207988284.9036756</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5890,7 +5888,7 @@
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
-        <v>1109912014.3825901</v>
+        <v>1109912418.6068106</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5903,7 +5901,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.4668708997100268E-2</v>
+        <v>9.5357647902554368E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,14 +5911,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6829110645351559E-2</v>
+        <v>5.7242656072311618E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
-        <v>0.74686244685569758</v>
+        <v>0.74734776778600887</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5940,11 +5938,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
-        <v>0.10095732069447201</v>
+        <v>0.10095735561257201</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.8891710791255046E-2</v>
+        <v>8.8891876231945069E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5954,11 +5952,11 @@
       </c>
       <c r="C67" s="263">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639722869231071</v>
+        <v>0.12639727240930954</v>
       </c>
       <c r="D67" s="263">
         <f>Normalized_FCF!G116</f>
-        <v>0.11129124485915784</v>
+        <v>0.11129145198871108</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -6058,7 +6056,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25695577956646554</v>
+        <v>-0.25712284641630861</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6101,7 +6099,7 @@
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
-        <v>6701749548.6165428</v>
+        <v>6701659721.0119677</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6129,7 +6127,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0820183187534989</v>
+        <v>6.0858911358527941</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6164,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52959510540024335</v>
+        <v>0.52993943618782413</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6181,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.3546576445872764</v>
+        <v>6.3587077256243099</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6306,7 +6304,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7472621093420444</v>
+        <v>1.748398139739767</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6317,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>20.248106799472058</v>
+        <v>20.261195150865689</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6368,7 +6366,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>21.04 HKD</v>
+        <v>21.06 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6374,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>1.7419971063331381E-2</v>
+        <v>1.742003067439182E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6388,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>20.64 HKD</v>
+        <v>20.65 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6396,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.4148459168348249E-2</v>
+        <v>2.4148547029111289E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6410,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>20.25 HKD</v>
+        <v>20.26 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6418,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.0925749606575102E-2</v>
+        <v>3.0925866653090141E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6432,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>19.86 HKD</v>
+        <v>19.88 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6440,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>3.7751077387165391E-2</v>
+        <v>3.7751224577318894E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6454,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>19.48 HKD</v>
+        <v>19.5 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,7 +6462,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.4623603353063084E-2</v>
+        <v>4.4623781666467119E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6482,7 +6480,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>20.314702954364844</v>
+        <v>20.327834629345425</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6546,7 +6544,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.6046617372665406</v>
+        <v>0.60505487468433383</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6585,15 +6583,15 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>1.1064412329506623</v>
+        <v>1.1071606160742391</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>9.3616142646842615</v>
+        <v>9.3676657278089532</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>10.468055497634923</v>
+        <v>10.474826343883192</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6606,15 +6604,15 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>1.2722106819713797</v>
+        <v>1.2730378446502357</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>11.734124450174644</v>
+        <v>11.741709533195918</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>13.006335132146024</v>
+        <v>13.014747377846154</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6653,15 +6651,15 @@
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
-        <v>1.4588087974647501</v>
+        <v>1.4597572820278413</v>
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>14.560774473549516</v>
+        <v>14.570186738069541</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>16.019583271014266</v>
+        <v>16.029944020097382</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6674,15 +6672,15 @@
       </c>
       <c r="C145" s="333">
         <f>Scenarios!C67</f>
-        <v>1.5796033432545096</v>
+        <v>1.5806303657056273</v>
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>16.467155015326156</v>
+        <v>16.477799587781973</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>18.046758358580664</v>
+        <v>18.0584299534876</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -7493,7 +7491,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.6718463747406006</v>
+        <v>0.67228319409370418</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8869,7 +8867,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.6718463747406006</v>
+        <v>0.67228319409370418</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10235,11 +10233,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.600472319354365</v>
+        <v>13.609315039571076</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7472621093420444</v>
+        <v>1.748398139739767</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10430,7 +10428,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6701749548.6165428</v>
+        <v>6701659721.0119677</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10497,11 +10495,11 @@
       </c>
       <c r="C73" s="285">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-985659357.94302642</v>
+        <v>-985704271.74531412</v>
       </c>
       <c r="D73" s="285">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-966384599.78172874</v>
+        <v>-966429513.58401644</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10513,11 +10511,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7601448498387793</v>
+        <v>8.7597456921754961</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9348679088328034</v>
+        <v>8.9344526701784748</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10530,7 +10528,7 @@
       <c r="C75" s="261"/>
       <c r="D75" s="262">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1932769199.5634575</v>
+        <v>1932859027.1680329</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10645,11 +10643,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-317042576.01606739</v>
+        <v>-317248709.94514465</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.25695577956646554</v>
+        <v>-0.25712284641630861</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10662,11 +10660,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7504243564.4291353</v>
+        <v>7509022004.9517469</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>6.0820183187534989</v>
+        <v>6.0858911358527941</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10679,11 +10677,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>653436154.44214165</v>
+        <v>653861003.88542116</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.52959510540024335</v>
+        <v>0.52993943618782413</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10696,11 +10694,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>7840637142.8552094</v>
+        <v>7845634298.8920231</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.3546576445872773</v>
+        <v>6.3587077256243099</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10843,7 +10841,7 @@
       <c r="B4" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="459">
+      <c r="C4" s="458">
         <f>C100*C117</f>
         <v>12328513892</v>
       </c>
@@ -11181,36 +11179,36 @@
       </c>
       <c r="C10" s="266">
         <f>C48</f>
-        <v>-2560307.6321192533</v>
+        <v>-2559768.6664918009</v>
       </c>
       <c r="E10" s="237"/>
       <c r="G10" s="266">
         <f>G48</f>
-        <v>42502458.764100112</v>
+        <v>42505012.363674626</v>
       </c>
       <c r="H10" s="266">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40976466.203047305</v>
+        <v>40979201.411828145</v>
       </c>
       <c r="I10" s="266">
         <f t="shared" si="6"/>
-        <v>17729579.523662858</v>
+        <v>17731378.510244511</v>
       </c>
       <c r="J10" s="266">
         <f t="shared" si="6"/>
-        <v>5079886.5109195858</v>
+        <v>5081028.3235541806</v>
       </c>
       <c r="K10" s="266">
         <f t="shared" si="6"/>
-        <v>-4689938.865340028</v>
+        <v>-4689126.7409477085</v>
       </c>
       <c r="L10" s="266">
         <f t="shared" si="6"/>
-        <v>-6414223.4401160832</v>
+        <v>-6413618.0376547538</v>
       </c>
       <c r="M10" s="266">
         <f t="shared" si="6"/>
-        <v>7541553.1243445445</v>
+        <v>7541927.6272624489</v>
       </c>
       <c r="N10" s="266">
         <f t="shared" si="6"/>
@@ -11236,36 +11234,36 @@
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
-        <v>1558289989.8434534</v>
+        <v>1558290528.8090808</v>
       </c>
       <c r="E11" s="237"/>
       <c r="G11" s="267">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1372055658.304101</v>
+        <v>1372058211.9036756</v>
       </c>
       <c r="H11" s="267">
         <f t="shared" si="7"/>
-        <v>1481961134.523047</v>
+        <v>1481963869.7318277</v>
       </c>
       <c r="I11" s="267">
         <f t="shared" si="7"/>
-        <v>1407257078.5236628</v>
+        <v>1407258877.5102446</v>
       </c>
       <c r="J11" s="267">
         <f t="shared" si="7"/>
-        <v>1240534204.5109196</v>
+        <v>1240535346.3235543</v>
       </c>
       <c r="K11" s="267">
         <f t="shared" si="7"/>
-        <v>1157465752.13466</v>
+        <v>1157466564.2590523</v>
       </c>
       <c r="L11" s="267">
         <f t="shared" si="7"/>
-        <v>999271591.13988602</v>
+        <v>999272196.54234731</v>
       </c>
       <c r="M11" s="267">
         <f t="shared" si="7"/>
-        <v>939488859.89434361</v>
+        <v>939489234.3972615</v>
       </c>
       <c r="N11" s="267">
         <f t="shared" si="7"/>
@@ -11291,7 +11289,7 @@
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
-        <v>-389572497.46086335</v>
+        <v>-389572632.20227021</v>
       </c>
       <c r="E12" s="237"/>
       <c r="G12" s="266">
@@ -11403,38 +11401,38 @@
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
-        <v>1109912014.3825901</v>
+        <v>1109912418.6068106</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="243"/>
       <c r="F14" s="58"/>
       <c r="G14" s="267">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207985731.304101</v>
+        <v>1207988284.9036756</v>
       </c>
       <c r="H14" s="267">
         <f t="shared" si="8"/>
-        <v>1497935077.523047</v>
+        <v>1497937812.7318277</v>
       </c>
       <c r="I14" s="267">
         <f t="shared" si="8"/>
-        <v>1418692555.5236628</v>
+        <v>1418694354.5102446</v>
       </c>
       <c r="J14" s="267">
         <f t="shared" si="8"/>
-        <v>1235081392.5109196</v>
+        <v>1235082534.3235543</v>
       </c>
       <c r="K14" s="267">
         <f t="shared" si="8"/>
-        <v>1149295201.13466</v>
+        <v>1149296013.2590523</v>
       </c>
       <c r="L14" s="267">
         <f t="shared" si="8"/>
-        <v>975099516.01988602</v>
+        <v>975100121.42234731</v>
       </c>
       <c r="M14" s="267">
         <f t="shared" si="8"/>
-        <v>950284706.26434362</v>
+        <v>950285080.76726151</v>
       </c>
       <c r="N14" s="267">
         <f t="shared" si="8"/>
@@ -11621,38 +11619,38 @@
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
-        <v>1109912014.3825901</v>
+        <v>1109912418.6068106</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="234"/>
       <c r="F19" s="26"/>
       <c r="G19" s="271">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207985731.304101</v>
+        <v>1207988284.9036756</v>
       </c>
       <c r="H19" s="271">
         <f t="shared" si="9"/>
-        <v>1497935077.523047</v>
+        <v>1497937812.7318277</v>
       </c>
       <c r="I19" s="271">
         <f t="shared" si="9"/>
-        <v>1418692555.5236628</v>
+        <v>1418694354.5102446</v>
       </c>
       <c r="J19" s="271">
         <f t="shared" si="9"/>
-        <v>1235081392.5109196</v>
+        <v>1235082534.3235543</v>
       </c>
       <c r="K19" s="271">
         <f t="shared" si="9"/>
-        <v>1149295201.13466</v>
+        <v>1149296013.2590523</v>
       </c>
       <c r="L19" s="271">
         <f t="shared" si="9"/>
-        <v>975099516.01988602</v>
+        <v>975100121.42234731</v>
       </c>
       <c r="M19" s="271">
         <f t="shared" si="9"/>
-        <v>950284706.26434362</v>
+        <v>950285080.76726151</v>
       </c>
       <c r="N19" s="271">
         <f t="shared" si="9"/>
@@ -12360,31 +12358,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.672024699793141E-2</v>
+        <v>7.672010421041088E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.3981075131890625E-2</v>
+        <v>-4.3980993957561519E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.1260753095637843E-3</v>
+        <v>-8.1260649214961178E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3955353912629681E-3</v>
+        <v>4.3955313455275036E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.0590002208976241E-3</v>
+        <v>7.0589952680234413E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4189695108240299E-2</v>
+        <v>2.4189680453073261E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491191466830289E-2</v>
+        <v>-1.1491186886166056E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12498,36 +12496,36 @@
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
-        <v>11596615.197380746</v>
+        <v>11597154.163008198</v>
       </c>
       <c r="E46" s="237"/>
       <c r="G46" s="274">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54944341.764100112</v>
+        <v>54946895.363674626</v>
       </c>
       <c r="H46" s="274">
         <f t="shared" si="17"/>
-        <v>58851923.203047305</v>
+        <v>58854658.411828145</v>
       </c>
       <c r="I46" s="274">
         <f t="shared" si="17"/>
-        <v>38707765.523662858</v>
+        <v>38709564.510244511</v>
       </c>
       <c r="J46" s="274">
         <f t="shared" si="17"/>
-        <v>24567729.510919586</v>
+        <v>24568871.323554181</v>
       </c>
       <c r="K46" s="274">
         <f t="shared" si="17"/>
-        <v>17474016.134659972</v>
+        <v>17474828.259052292</v>
       </c>
       <c r="L46" s="274">
         <f t="shared" si="17"/>
-        <v>13026098.559883917</v>
+        <v>13026703.962345246</v>
       </c>
       <c r="M46" s="274">
         <f t="shared" si="17"/>
-        <v>8057965.1243445445</v>
+        <v>8058339.6272624489</v>
       </c>
       <c r="N46" s="274">
         <f t="shared" si="17"/>
@@ -12610,36 +12608,36 @@
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
-        <v>-2560307.6321192533</v>
+        <v>-2559768.6664918009</v>
       </c>
       <c r="E48" s="237"/>
       <c r="G48" s="267">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42502458.764100112</v>
+        <v>42505012.363674626</v>
       </c>
       <c r="H48" s="267">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40976466.203047305</v>
+        <v>40979201.411828145</v>
       </c>
       <c r="I48" s="267">
         <f t="shared" si="18"/>
-        <v>17729579.523662858</v>
+        <v>17731378.510244511</v>
       </c>
       <c r="J48" s="267">
         <f t="shared" si="18"/>
-        <v>5079886.5109195858</v>
+        <v>5081028.3235541806</v>
       </c>
       <c r="K48" s="267">
         <f t="shared" si="18"/>
-        <v>-4689938.865340028</v>
+        <v>-4689126.7409477085</v>
       </c>
       <c r="L48" s="267">
         <f t="shared" si="18"/>
-        <v>-6414223.4401160832</v>
+        <v>-6413618.0376547538</v>
       </c>
       <c r="M48" s="267">
         <f t="shared" si="18"/>
-        <v>7541553.1243445445</v>
+        <v>7541927.6272624489</v>
       </c>
       <c r="N48" s="267">
         <f t="shared" si="18"/>
@@ -13575,38 +13573,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0767366241770978E-4</v>
+        <v>2.0762994541887489E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="234"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.4474924663612581E-3</v>
+        <v>3.4476995959144942E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4525423820314792E-3</v>
+        <v>3.4527728417346848E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.622057536353601E-3</v>
+        <v>1.6222221234346806E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8563190713914894E-4</v>
+        <v>4.8574106324847182E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2063825723401732E-4</v>
+        <v>5.2054810189502152E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.2538921196751364E-4</v>
+        <v>7.2532074656114808E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.2120890425140321E-4</v>
+        <v>9.2125465018953474E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13632,38 +13630,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639722869231071</v>
+        <v>0.12639727240930954</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="234"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.11129124485915784</v>
+        <v>0.11129145198871108</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12486517505220526</v>
+        <v>0.12486540551190846</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.128748228166365</v>
+        <v>0.1287483927534461</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11859378950946833</v>
+        <v>0.11859389866557767</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12849228301310905</v>
+        <v>0.12849237316844805</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300835382581668</v>
+        <v>0.11300842229122304</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11475958451925486</v>
+        <v>0.11475963026519299</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13689,7 +13687,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1599307173077677E-2</v>
+        <v>3.1599318102327384E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="234"/>
@@ -13804,38 +13802,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.0028045886602306E-2</v>
+        <v>9.0028078674351433E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="234"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.7983077432225271E-2</v>
+        <v>9.7983284561778516E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12621108699449846</v>
+        <v>0.12621131745420167</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12979444596441778</v>
+        <v>0.12979461055149888</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11807250631049547</v>
+        <v>0.1180726154666048</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758525595893588</v>
+        <v>0.12758534611427488</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11027471620208604</v>
+        <v>0.1102747846674924</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607830887761951</v>
+        <v>0.11607835462355764</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14027,38 +14025,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.0028045886602306E-2</v>
+        <v>9.0028078674351433E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="234"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.7983077432225271E-2</v>
+        <v>9.7983284561778516E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12621108699449846</v>
+        <v>0.12621131745420167</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12979444596441778</v>
+        <v>0.12979461055149888</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11807250631049547</v>
+        <v>0.1180726154666048</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758525595893588</v>
+        <v>0.12758534611427488</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11027471620208604</v>
+        <v>0.1102747846674924</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607830887761951</v>
+        <v>0.11607835462355764</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14096,12 +14094,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.6718463747406006</v>
+        <v>0.67228319409370418</v>
       </c>
       <c r="E88" s="237"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.6718463747406006</v>
+        <v>0.67228319409370418</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14152,12 +14150,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>828951602.8563174</v>
+        <v>829490568.48377001</v>
       </c>
       <c r="E89" s="237"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>828951602.8563174</v>
+        <v>829490568.48377001</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14207,12 +14205,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.74686244685569758</v>
+        <v>0.74734776778600887</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.68622631987665039</v>
+        <v>0.68667103716979605</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14283,12 +14281,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6829110645351559E-2</v>
+        <v>5.7242656072311618E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.6829110645351559E-2</v>
+        <v>5.7242656072311618E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14420,38 +14418,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.1357338023513881</v>
+        <v>0.13573208140128057</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="234"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162185268318748E-2</v>
+        <v>-7.4162170936083904E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.3084867818007586E-2</v>
+        <v>5.3085465237038054E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.13439603148909041</v>
+        <v>0.13439643753867347</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1767525063320736E-2</v>
+        <v>7.1767759544465237E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830947501901793</v>
+        <v>0.15830958598076128</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3633251864493312E-2</v>
+        <v>6.3633472270110847E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35104165569694801</v>
+        <v>0.35104219425473615</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -14976,7 +14974,9 @@
         <v>303</v>
       </c>
       <c r="C112" s="151"/>
-      <c r="E112" s="237"/>
+      <c r="E112" s="451" t="s">
+        <v>553</v>
+      </c>
       <c r="G112" s="251">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.1052698089235498</v>
@@ -15028,34 +15028,37 @@
         <v>304</v>
       </c>
       <c r="C113" s="151"/>
-      <c r="E113" s="237"/>
+      <c r="E113" s="459">
+        <f>(Normalized_FCF!E117/Normalized_FCF!C117)^(1/DCF!C15)-1</f>
+        <v>0</v>
+      </c>
       <c r="G113" s="251">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.467301132842431</v>
+        <v>1.4672980310743136</v>
       </c>
       <c r="H113" s="251">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5708479267946089</v>
+        <v>1.570845058453209</v>
       </c>
       <c r="I113" s="251">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.4269343397328025</v>
+        <v>1.4269325302974423</v>
       </c>
       <c r="J113" s="251">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.6576474954721652</v>
+        <v>1.6576459630054663</v>
       </c>
       <c r="K113" s="251">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.582539706251584</v>
+        <v>1.5825385879851996</v>
       </c>
       <c r="L113" s="251">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3992525862274905</v>
+        <v>1.399251717484947</v>
       </c>
       <c r="M113" s="251">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.0454238244823957</v>
+        <v>1.0454234124857427</v>
       </c>
       <c r="N113" s="251">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15087,8 +15090,9 @@
         <v>327</v>
       </c>
       <c r="D115" s="52"/>
-      <c r="E115" s="451" t="s">
-        <v>552</v>
+      <c r="E115" s="451" t="str">
+        <f>DCF!F15&amp;"yrs Projection"</f>
+        <v>4yrs Projection</v>
       </c>
       <c r="F115" s="52"/>
       <c r="G115" s="22" t="str">
@@ -15143,39 +15147,39 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639722869231071</v>
+        <v>0.12639727240930954</v>
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
-        <v>0.12639722869231071</v>
+        <v>0.12639727240930954</v>
       </c>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.11129124485915784</v>
+        <v>0.11129145198871108</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12486517505220526</v>
+        <v>0.12486540551190846</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.128748228166365</v>
+        <v>0.1287483927534461</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11859378950946833</v>
+        <v>0.11859389866557767</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12849228301310905</v>
+        <v>0.12849237316844805</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300835382581668</v>
+        <v>0.11300842229122304</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11475958451925486</v>
+        <v>0.11475963026519299</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15202,7 +15206,7 @@
         <f>G117</f>
         <v>0.49405373744838704</v>
       </c>
-      <c r="E117" s="458">
+      <c r="E117" s="452">
         <f>C117</f>
         <v>0.49405373744838704</v>
       </c>
@@ -15317,41 +15321,41 @@
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
-        <v>0.10095732069447201</v>
+        <v>0.10095735561257201</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
         <f>C11/C104</f>
-        <v>0.10095732069447201</v>
+        <v>0.10095735561257201</v>
       </c>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.8891710791255046E-2</v>
+        <v>8.8891876231945069E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11047740279980425</v>
+        <v>0.11047760670445141</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11113989661164997</v>
+        <v>0.11114003868887648</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11166237450517533</v>
+        <v>0.11166247728147087</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11542166303580338</v>
+        <v>0.11542174402027119</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.1095696579785574</v>
+        <v>0.10956972436065134</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176369002967693</v>
+        <v>0.11176373458137925</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15441,50 +15445,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0072750637291468</v>
+        <v>1.0079303383299998</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0962796047938019</v>
+        <v>1.0969947000232319</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3594164502431021</v>
+        <v>1.3603027960343488</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2875017260463479</v>
+        <v>1.2883404643073313</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1208696475316164</v>
+        <v>1.1215994485842533</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0430163670320174</v>
+        <v>1.0436952502428809</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.88492908844450613</v>
+        <v>0.88550499914626279</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.8624089798646879</v>
+        <v>0.86297003881619583</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63056899522238219</v>
+        <v>0.63097897695471872</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.51926223080718481</v>
+        <v>0.51959984339285947</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.48953686711921818</v>
+        <v>0.48985515294415533</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15498,50 +15502,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.4668708997100268E-2</v>
+        <v>9.5357647902554368E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10303379744302649</v>
+        <v>0.10378379375811086</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.12776470397021636</v>
+        <v>0.12869468269009923</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12100580132014548</v>
+        <v>0.12188651507164913</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.1053448916853023</v>
+        <v>0.10611158453966446</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.8027854044362525E-2</v>
+        <v>9.8741272492230928E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.3170027109446057E-2</v>
+        <v>8.3775307393213122E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.1053475551192466E-2</v>
+        <v>8.164333385205258E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.9264003310374264E-2</v>
+        <v>5.969526745077755E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.8802841241276762E-2</v>
+        <v>4.9157979507366077E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.6009104052558099E-2</v>
+        <v>4.6343912293676001E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15555,43 +15559,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12215519029020526</v>
+        <v>0.12296416506033907</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12403578921372213</v>
+        <v>0.12485721828136268</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10597409326080712</v>
+        <v>0.10667590844796479</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9274412516307878E-2</v>
+        <v>9.9931858956813238E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4682242983222031E-2</v>
+        <v>9.5309277704965223E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5668752138509593E-2</v>
+        <v>8.6236094867903693E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0590466915488856E-2</v>
+        <v>7.1057953451353018E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9810756155850084E-2</v>
+        <v>7.0273079044299427E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7991675741776922E-2</v>
+        <v>4.8309501408941004E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6840082543629438E-2</v>
+        <v>4.7150281765772677E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16346,7 +16350,7 @@
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
-        <v>1109912014.3825901</v>
+        <v>1109912418.6068106</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16385,7 +16389,7 @@
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
-        <v>6701749548.6165428</v>
+        <v>6701659721.0119677</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16406,7 +16410,7 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>15309131232.863312</v>
+        <v>15309136808.369802</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16428,7 +16432,7 @@
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
-        <v>-2560307.6321192533</v>
+        <v>-2559768.6664918009</v>
       </c>
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
@@ -16439,14 +16443,14 @@
       </c>
       <c r="C7" s="275">
         <f>F7</f>
-        <v>7002169636.666543</v>
+        <v>7002079809.0619678</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>424</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
-        <v>7002169636.666543</v>
+        <v>7002079809.0619678</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16469,7 +16473,7 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>22311300869.529854</v>
+        <v>22311216617.43177</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16480,7 +16484,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.3546576445872764</v>
+        <v>6.3587077256243099</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16492,7 +16496,7 @@
       </c>
       <c r="I8" s="313">
         <f>Normalized_FCF!C10</f>
-        <v>-2560307.6321192533</v>
+        <v>-2559768.6664918009</v>
       </c>
       <c r="J8" s="313"/>
       <c r="N8" s="304"/>
@@ -16505,7 +16509,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1197439579010011</v>
+        <v>1.1204719901561737</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16530,7 +16534,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>24982944341.567406</v>
+        <v>24999093286.139271</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16552,7 +16556,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>20.248106799472058</v>
+        <v>20.261195150865689</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16642,14 +16646,14 @@
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
-        <v>0.12639722869231071</v>
+        <v>0.12639727240930954</v>
       </c>
       <c r="E17" s="308" t="s">
         <v>549</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
-        <v>0.12639722869231071</v>
+        <v>0.12639727240930954</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>412</v>
@@ -16675,7 +16679,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>20.316383761804069</v>
+        <v>20.329516530220264</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16709,7 +16713,7 @@
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="H20" s="121" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I20" s="121" t="s">
         <v>529</v>
@@ -16742,11 +16746,11 @@
       </c>
       <c r="E21" s="299">
         <f>$C$17</f>
-        <v>0.12639722869231071</v>
+        <v>0.12639727240930954</v>
       </c>
       <c r="F21" s="277">
         <f>C21*E21</f>
-        <v>1561018682.9988096</v>
+        <v>1561019222.9082098</v>
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16754,7 +16758,7 @@
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>1111855561.0500479</v>
+        <v>1111855965.9820981</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
@@ -16762,7 +16766,7 @@
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>9.002804588660232E-2</v>
+        <v>9.0028078674351447E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16770,7 +16774,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>1036695161.8182265</v>
+        <v>1036695539.3772476</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16791,11 +16795,11 @@
       </c>
       <c r="E22" s="299">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>0.12639722869231071</v>
+        <v>0.12639727240930954</v>
       </c>
       <c r="F22" s="277">
         <f t="shared" ref="F22:F50" si="7">IF(A22="", 0,C22*E22)</f>
-        <v>1563752154.3189387</v>
+        <v>1563752695.1737645</v>
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
@@ -16803,15 +16807,15 @@
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>1113802511.0265965</v>
+        <v>1113802916.667716</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
-        <v>1.7510817454651217E-3</v>
+        <v>1.7510817454653438E-3</v>
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
-        <v>9.002804588660232E-2</v>
+        <v>9.0028078674351461E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16819,7 +16823,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>968308158.3139379</v>
+        <v>968308510.966766</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16840,11 +16844,11 @@
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
-        <v>0.12639722869231071</v>
+        <v>0.12639727240930954</v>
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>1566490412.1707983</v>
+        <v>1566490953.9727051</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
@@ -16852,7 +16856,7 @@
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>1115752870.2717085</v>
+        <v>1115753276.6231387</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
@@ -16860,7 +16864,7 @@
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>9.002804588660232E-2</v>
+        <v>9.0028078674351461E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16868,7 +16872,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>904432396.320696</v>
+        <v>904432725.71030152</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -18292,11 +18296,11 @@
       </c>
       <c r="E51" s="301">
         <f>F17</f>
-        <v>0.12639722869231071</v>
+        <v>0.12639727240930954</v>
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>1566490412.1707983</v>
+        <v>1566490953.9727051</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
@@ -18304,7 +18308,7 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>15389694762.368395</v>
+        <v>15389700367.215706</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
@@ -18317,7 +18321,7 @@
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>12474929604.423395</v>
+        <v>12474934147.728296</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18330,7 +18334,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>15384365320.876255</v>
+        <v>15384370923.782612</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18354,7 +18358,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>15384365320.876255</v>
+        <v>15384370923.782612</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18389,19 +18393,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>15002948608.206045</v>
+        <v>15002954072.202408</v>
       </c>
       <c r="C56" s="118">
-        <v>15156039920.534681</v>
+        <v>15156045440.286104</v>
       </c>
       <c r="D56" s="118">
-        <v>15309131232.863316</v>
+        <v>15309136808.369802</v>
       </c>
       <c r="E56" s="118">
-        <v>15462222545.191944</v>
+        <v>15462228176.453503</v>
       </c>
       <c r="F56" s="118">
-        <v>15615313857.520582</v>
+        <v>15615319544.537201</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18415,19 +18419,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>14723173342.784958</v>
+        <v>14723178704.888611</v>
       </c>
       <c r="C57" s="118">
-        <v>15014724863.000559</v>
+        <v>15014730331.285772</v>
       </c>
       <c r="D57" s="118">
-        <v>15309131232.863316</v>
+        <v>15309136808.369802</v>
       </c>
       <c r="E57" s="118">
-        <v>15606392452.373224</v>
+        <v>15606398136.140715</v>
       </c>
       <c r="F57" s="118">
-        <v>15906508521.530293</v>
+        <v>15906514314.598501</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18441,19 +18445,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>14467527878.81044</v>
+        <v>14467533147.809334</v>
       </c>
       <c r="C58" s="118">
-        <v>14884280194.507519</v>
+        <v>14884285615.285458</v>
       </c>
       <c r="D58" s="118">
-        <v>15309131232.863316</v>
+        <v>15309136808.369802</v>
       </c>
       <c r="E58" s="118">
-        <v>15742160849.812002</v>
+        <v>15742166583.025642</v>
       </c>
       <c r="F58" s="118">
-        <v>16183448901.287775</v>
+        <v>16183454795.21624</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18467,19 +18471,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>14233931091.216005</v>
+        <v>14233936275.14016</v>
       </c>
       <c r="C59" s="118">
-        <v>14763869731.283176</v>
+        <v>14763875108.208246</v>
       </c>
       <c r="D59" s="118">
-        <v>15309131232.863316</v>
+        <v>15309136808.369801</v>
       </c>
       <c r="E59" s="118">
-        <v>15870017335.978125</v>
+        <v>15870023115.756435</v>
       </c>
       <c r="F59" s="118">
-        <v>16446832758.959225</v>
+        <v>16446838748.810734</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18493,19 +18497,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>14020481345.908276</v>
+        <v>14020486452.095135</v>
       </c>
       <c r="C60" s="118">
-        <v>14652721611.383787</v>
+        <v>14652726947.829285</v>
       </c>
       <c r="D60" s="118">
-        <v>15309131232.863316</v>
+        <v>15309136808.369801</v>
       </c>
       <c r="E60" s="118">
-        <v>15990422977.962074</v>
+        <v>15990428801.591496</v>
       </c>
       <c r="F60" s="118">
-        <v>16697323700.520889</v>
+        <v>16697329781.599901</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18519,19 +18523,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>13825441019.193518</v>
+        <v>13825446054.347698</v>
       </c>
       <c r="C61" s="118">
-        <v>14550123346.861271</v>
+        <v>14550128645.941008</v>
       </c>
       <c r="D61" s="118">
-        <v>15309131232.863314</v>
+        <v>15309136808.369801</v>
       </c>
       <c r="E61" s="118">
-        <v>16103811974.142757</v>
+        <v>16103817839.067867</v>
       </c>
       <c r="F61" s="118">
-        <v>16935552847.74037</v>
+        <v>16935559015.581207</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18545,19 +18549,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>13647222352.358589</v>
+        <v>13647227322.606451</v>
       </c>
       <c r="C62" s="118">
-        <v>14455417256.532793</v>
+        <v>14455422521.121065</v>
       </c>
       <c r="D62" s="118">
-        <v>15309131232.863316</v>
+        <v>15309136808.369802</v>
       </c>
       <c r="E62" s="118">
-        <v>16210593219.963264</v>
+        <v>16210599123.777554</v>
       </c>
       <c r="F62" s="118">
-        <v>17162120428.312748</v>
+        <v>17162126678.668329</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18571,19 +18575,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>13484374526.25301</v>
+        <v>13484379437.192535</v>
       </c>
       <c r="C63" s="118">
-        <v>14367996250.075741</v>
+        <v>14368001482.825729</v>
       </c>
       <c r="D63" s="118">
-        <v>15309131232.863316</v>
+        <v>15309136808.369801</v>
       </c>
       <c r="E63" s="118">
-        <v>16311151782.460899</v>
+        <v>16311157722.898096</v>
       </c>
       <c r="F63" s="118">
-        <v>17377597288.157806</v>
+        <v>17377603616.988941</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18597,19 +18601,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>13335571850.650711</v>
+        <v>13335576707.397072</v>
       </c>
       <c r="C64" s="118">
-        <v>14287299936.423073</v>
+        <v>14287305139.783884</v>
       </c>
       <c r="D64" s="118">
-        <v>15309131232.863316</v>
+        <v>15309136808.369801</v>
       </c>
       <c r="E64" s="118">
-        <v>16405850288.868925</v>
+        <v>16405856263.79483</v>
       </c>
       <c r="F64" s="118">
-        <v>17582526329.688766</v>
+        <v>17582532733.153999</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18623,19 +18627,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>13199602972.244883</v>
+        <v>13199607779.47208</v>
       </c>
       <c r="C65" s="118">
-        <v>14212811031.51292</v>
+        <v>14212816207.745258</v>
       </c>
       <c r="D65" s="118">
-        <v>15309131232.863316</v>
+        <v>15309136808.369801</v>
       </c>
       <c r="E65" s="118">
-        <v>16495030234.297466</v>
+        <v>16495036241.702244</v>
       </c>
       <c r="F65" s="118">
-        <v>17777423879.676254</v>
+        <v>17777430354.122169</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18649,19 +18653,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>12676698100.122879</v>
+        <v>12676702716.910824</v>
       </c>
       <c r="C66" s="277">
-        <v>13917993113.021519</v>
+        <v>13917998181.882694</v>
       </c>
       <c r="D66" s="118">
-        <v>15309131232.863314</v>
+        <v>15309136808.369801</v>
       </c>
       <c r="E66" s="118">
-        <v>16868773913.09314</v>
+        <v>16868780056.613434</v>
       </c>
       <c r="F66" s="118">
-        <v>18617809074.230721</v>
+        <v>18617815854.740582</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18684,19 +18688,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>12343604289.807627</v>
+        <v>12343608785.284527</v>
       </c>
       <c r="C67" s="277">
-        <v>13720412947.77722</v>
+        <v>13720417944.680717</v>
       </c>
       <c r="D67" s="118">
-        <v>15309131232.863312</v>
+        <v>15309136808.369799</v>
       </c>
       <c r="E67" s="118">
-        <v>17145591845.625763</v>
+        <v>17145598089.96172</v>
       </c>
       <c r="F67" s="118">
-        <v>19271681084.305401</v>
+        <v>19271688102.952076</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18719,19 +18723,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>12131421362.499874</v>
+        <v>12131425780.700848</v>
       </c>
       <c r="C68" s="277">
-        <v>13587999280.732405</v>
+        <v>13588004229.411533</v>
       </c>
       <c r="D68" s="118">
-        <v>15309131232.863314</v>
+        <v>15309136808.369799</v>
       </c>
       <c r="E68" s="118">
-        <v>17350620511.31065</v>
+        <v>17350626830.316982</v>
       </c>
       <c r="F68" s="118">
-        <v>19780434223.13929</v>
+        <v>19780441427.071228</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18754,19 +18758,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>11996259455.413467</v>
+        <v>11996263824.389174</v>
       </c>
       <c r="C69" s="277">
-        <v>13499258696.885969</v>
+        <v>13499263613.246235</v>
       </c>
       <c r="D69" s="118">
-        <v>15309131232.863312</v>
+        <v>15309136808.369799</v>
       </c>
       <c r="E69" s="118">
-        <v>17502477558.171478</v>
+        <v>17502483932.483364</v>
       </c>
       <c r="F69" s="118">
-        <v>20176275843.953991</v>
+        <v>20176283192.049404</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18863,23 +18867,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>20.248106799472058</v>
+        <v>20.261195150865689</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>20.248106799472058</v>
+        <v>20.261195150865689</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>20.248106799472058</v>
+        <v>20.261195150865689</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>20.248106799472058</v>
+        <v>20.261195150865689</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>20.248106799472058</v>
+        <v>20.261195150865689</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18894,23 +18898,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>19.970237816374368</v>
+        <v>19.983145402360858</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>20.109172307923217</v>
+        <v>20.122170276613275</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>20.248106799472065</v>
+        <v>20.261195150865685</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>20.387041291020907</v>
+        <v>20.400220025118102</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>20.525975782569763</v>
+        <v>20.539244899370516</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18925,23 +18929,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>19.716334223427289</v>
+        <v>19.729076634496309</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>19.98092508495505</v>
+        <v>19.993839623457205</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>20.248106799472065</v>
+        <v>20.261195150865685</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>20.517879366978335</v>
+        <v>20.531143216721773</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>20.790242787473865</v>
+        <v>20.803683821025459</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18956,23 +18960,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>19.484329075559565</v>
+        <v>19.496920557566458</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>19.86254303298443</v>
+        <v>19.875380559005443</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>20.248106799472065</v>
+        <v>20.261195150865685</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>20.641092846434741</v>
+        <v>20.654436851705182</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>21.041573645284757</v>
+        <v>21.055178180081899</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18987,23 +18991,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>19.272333695689753</v>
+        <v>19.284787265826367</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>19.75326729270386</v>
+        <v>19.766033730280736</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>20.248106799472065</v>
+        <v>20.261195150865685</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>20.757126053195556</v>
+        <v>20.770545542924996</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>21.28060159397204</v>
+        <v>21.294361626457267</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -19018,23 +19022,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>19.078622299631554</v>
+        <v>19.090949852394864</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>19.652397378598724</v>
+        <v>19.66509819607332</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>20.248106799472065</v>
+        <v>20.261195150865685</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>20.866397418070541</v>
+        <v>20.87988799339773</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>21.507928873842463</v>
+        <v>21.52183679224083</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -19049,23 +19053,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>18.901617947056234</v>
+        <v>18.913830351077497</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>19.559286688655515</v>
+        <v>19.571926933728008</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>20.248106799472065</v>
+        <v>20.261195150865685</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>20.969300987789637</v>
+        <v>20.982858506197228</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>21.724128244908041</v>
+        <v>21.738176810048966</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19081,23 +19085,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>18.739879704143586</v>
+        <v>18.751986890666288</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>19.473338359477172</v>
+        <v>19.485922691563111</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>20.248106799472065</v>
+        <v>20.261195150865685</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>21.066207845986646</v>
+        <v>21.079828406362722</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>21.929744429977404</v>
+        <v>21.943926757055319</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19112,23 +19116,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>18.592090913416875</v>
+        <v>18.604101957143691</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>19.394001440235623</v>
+        <v>19.406534160333965</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>20.248106799472065</v>
+        <v>20.261195150865685</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>21.15746745137497</v>
+        <v>21.171147379945143</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>22.125295487106307</v>
+        <v>22.139605028334078</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19144,23 +19148,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>18.457048475270327</v>
+        <v>18.468971668237263</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>19.320767360935733</v>
+        <v>19.333252439199381</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>20.248106799472065</v>
+        <v>20.261195150865685</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>21.24340889794113</v>
+        <v>21.257144735020432</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>22.311274114865263</v>
+        <v>22.32570464297681</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19176,23 +19180,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>18.333653053933624</v>
+        <v>18.345495973012749</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>19.253166672351213</v>
+        <v>19.265607773536683</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>20.248106799472065</v>
+        <v>20.261195150865685</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>21.324342101700406</v>
+        <v>21.338130589217208</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>22.488148893712939</v>
+        <v>22.502694486273402</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19208,23 +19212,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>17.859102790880595</v>
+        <v>17.87063699514546</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>18.985611466363011</v>
+        <v>18.997878511685165</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>20.248106799472065</v>
+        <v>20.261195150865685</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>21.663524562110741</v>
+        <v>21.677533702018696</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>23.250821105052829</v>
+        <v>23.265862847817804</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19240,23 +19244,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>17.556811181577025</v>
+        <v>17.568148732493903</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>18.806302141876802</v>
+        <v>18.818452538976175</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>20.248106799472062</v>
+        <v>20.261195150865682</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>21.914744295765281</v>
+        <v>21.928916864627876</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>23.844227575190967</v>
+        <v>23.859655353709101</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19272,23 +19276,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>17.364249456992898</v>
+        <v>17.375461738445892</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>18.686133170658511</v>
+        <v>18.698205392810962</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>20.248106799472065</v>
+        <v>20.261195150865682</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>22.100813335128667</v>
+        <v>22.115106949691572</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>24.305934758914329</v>
+        <v>24.321662897285911</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19304,23 +19308,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>17.241586383875386</v>
+        <v>17.252718867863745</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>18.605598699375218</v>
+        <v>18.617618530482336</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>20.248106799472062</v>
+        <v>20.261195150865682</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>22.238627697503642</v>
+        <v>22.253010966079191</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>24.665171697217563</v>
+        <v>24.681133534257803</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19367,7 +19371,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>21.041573645284757</v>
+        <v>21.055178180081899</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19395,7 +19399,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>20.641092846434741</v>
+        <v>20.654436851705182</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19423,7 +19427,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>20.248106799472065</v>
+        <v>20.261195150865685</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19451,7 +19455,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>19.86254303298443</v>
+        <v>19.875380559005443</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19479,7 +19483,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>19.484329075559565</v>
+        <v>19.496920557566458</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19688,7 +19692,7 @@
       </c>
       <c r="C8" s="447">
         <f>Normalized_FCF!G19</f>
-        <v>1207985731.304101</v>
+        <v>1207988284.9036756</v>
       </c>
       <c r="D8" s="469"/>
       <c r="E8" s="469"/>
@@ -19701,7 +19705,7 @@
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
-        <v>1109912014.3825901</v>
+        <v>1109912418.6068106</v>
       </c>
       <c r="D9" s="469"/>
       <c r="E9" s="469"/>
@@ -19757,7 +19761,7 @@
       </c>
       <c r="C14" s="249">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7244255944825979E-2</v>
+        <v>-7.7243865678597534E-2</v>
       </c>
       <c r="D14" s="469"/>
       <c r="E14" s="469"/>
@@ -19839,7 +19843,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>20.641092846434741</v>
+        <v>20.654436851705182</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19863,7 +19867,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>20.248106799472065</v>
+        <v>20.261195150865685</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19886,7 +19890,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>19.86254303298443</v>
+        <v>19.875380559005443</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19902,7 +19906,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>20.23031306724269</v>
+        <v>20.243389843068524</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19949,7 +19953,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>21.041573645284757</v>
+        <v>21.055178180081899</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19972,7 +19976,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>19.484329075559565</v>
+        <v>19.496920557566458</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19997,7 +20001,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.6046617372665406</v>
+        <v>0.60505487468433383</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -20017,7 +20021,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.64</v>
+        <v>10.57</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20028,7 +20032,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.28734146037901681</v>
+        <v>0.29058822043182098</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20037,7 +20041,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>20.248106799472058</v>
+        <v>20.261195150865689</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20048,7 +20052,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.0925749606575206E-2</v>
+        <v>3.0925866653090103E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20057,7 +20061,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>20.314702954364844</v>
+        <v>20.327834629345425</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20095,7 +20099,7 @@
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639722869231071</v>
+        <v>0.12639727240930954</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>401</v>
@@ -20160,7 +20164,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>20.316383761804069</v>
+        <v>20.329516530220264</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20227,7 +20231,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.31281075873284708</v>
+        <v>0.31280792280968422</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20261,7 +20265,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.6046617372665406</v>
+        <v>0.60505487468433383</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20301,15 +20305,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.1064412329506623</v>
+        <v>1.1071606160742391</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>9.3616142646842615</v>
+        <v>9.3676657278089532</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>10.468055497634923</v>
+        <v>10.474826343883192</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20317,7 +20321,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.48470546081079946</v>
+        <v>0.48470525587798474</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20326,15 +20330,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2722106819713797</v>
+        <v>1.2730378446502357</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>11.734124450174644</v>
+        <v>11.741709533195918</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>13.006335132146024</v>
+        <v>13.014747377846154</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20342,7 +20346,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.35975755287371969</v>
+        <v>0.35975731723742177</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20372,15 +20376,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4588087974647501</v>
+        <v>1.4597572820278413</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>14.560774473549516</v>
+        <v>14.570186738069541</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>16.019583271014266</v>
+        <v>16.029944020097382</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20388,7 +20392,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.2114291157985021</v>
+        <v>0.21142884560087738</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20397,15 +20401,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5796033432545096</v>
+        <v>1.5806303657056273</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>16.467155015326156</v>
+        <v>16.477799587781973</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>18.046758358580664</v>
+        <v>18.0584299534876</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20413,7 +20417,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.11164054925533062</v>
+        <v>0.1116402566843836</v>
       </c>
     </row>
   </sheetData>
@@ -20524,7 +20528,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>10.64</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20542,14 +20546,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>13128.068240000001</v>
+        <v>13041.69937</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.28734146037901681</v>
+        <v>0.29058822043182098</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20601,7 +20605,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1197439579010011</v>
+        <v>1.1204719901561737</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20627,7 +20631,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>20.314702954364844</v>
+        <v>20.327834629345425</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20679,7 +20683,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>10.468055497634923</v>
+        <v>10.474826343883192</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20695,7 +20699,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>13.006335132146024</v>
+        <v>13.014747377846154</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20711,7 +20715,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>16.019583271014266</v>
+        <v>16.029944020097382</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20727,7 +20731,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>18.046758358580664</v>
+        <v>18.0584299534876</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20872,7 +20876,7 @@
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
-        <v>11596615.197380746</v>
+        <v>11597154.163008198</v>
       </c>
       <c r="D44" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20902,7 +20906,7 @@
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
-        <v>-2560307.6321192533</v>
+        <v>-2559768.6664918009</v>
       </c>
       <c r="D46" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20942,7 +20946,7 @@
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
-        <v>-389572497.46086335</v>
+        <v>-389572632.20227021</v>
       </c>
       <c r="D52" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20995,7 +20999,7 @@
       </c>
       <c r="C60" s="373">
         <f>Normalized_FCF!G19</f>
-        <v>1207985731.304101</v>
+        <v>1207988284.9036756</v>
       </c>
       <c r="D60" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21008,7 +21012,7 @@
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
-        <v>1109912014.3825901</v>
+        <v>1109912418.6068106</v>
       </c>
       <c r="D61" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21021,7 +21025,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>9.4668708997100268E-2</v>
+        <v>9.5357647902554368E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21031,14 +21035,14 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.6829110645351559E-2</v>
+        <v>5.7242656072311618E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
-        <v>0.74686244685569758</v>
+        <v>0.74734776778600887</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21058,11 +21062,11 @@
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
-        <v>0.10095732069447201</v>
+        <v>0.10095735561257201</v>
       </c>
       <c r="D66" s="378">
         <f>Normalized_FCF!G119</f>
-        <v>8.8891710791255046E-2</v>
+        <v>8.8891876231945069E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21072,11 +21076,11 @@
       </c>
       <c r="C67" s="383">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639722869231071</v>
+        <v>0.12639727240930954</v>
       </c>
       <c r="D67" s="383">
         <f>Normalized_FCF!G116</f>
-        <v>0.11129124485915784</v>
+        <v>0.11129145198871108</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21172,7 +21176,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25695577956646554</v>
+        <v>-0.25712284641630861</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21208,7 +21212,7 @@
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
-        <v>6701749548.6165428</v>
+        <v>6701659721.0119677</v>
       </c>
       <c r="D84" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21234,7 +21238,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0820183187534989</v>
+        <v>6.0858911358527941</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21265,7 +21269,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52959510540024335</v>
+        <v>0.52993943618782413</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21278,7 +21282,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.3546576445872764</v>
+        <v>6.3587077256243099</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21423,7 +21427,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.7472621093420444</v>
+        <v>1.748398139739767</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21437,7 +21441,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>20.248106799472058</v>
+        <v>20.261195150865689</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21500,7 +21504,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>21.04 HKD</v>
+        <v>21.06 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21523,7 +21527,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>20.64 HKD</v>
+        <v>20.65 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21545,7 +21549,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>20.25 HKD</v>
+        <v>20.26 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21567,7 +21571,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>19.86 HKD</v>
+        <v>19.88 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21589,7 +21593,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>19.48 HKD</v>
+        <v>19.5 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21611,7 +21615,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>20.314702954364844</v>
+        <v>20.327834629345425</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21675,7 +21679,7 @@
       </c>
       <c r="C136" s="406">
         <f>Scenarios!C58</f>
-        <v>0.6046617372665406</v>
+        <v>0.60505487468433383</v>
       </c>
       <c r="D136" s="343" t="str">
         <f>Market_currency</f>
@@ -21714,15 +21718,15 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>1.1064412329506623</v>
+        <v>1.1071606160742391</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>9.3616142646842615</v>
+        <v>9.3676657278089532</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>10.468055497634923</v>
+        <v>10.474826343883192</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21735,15 +21739,15 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>1.2722106819713797</v>
+        <v>1.2730378446502357</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>11.734124450174644</v>
+        <v>11.741709533195918</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>13.006335132146024</v>
+        <v>13.014747377846154</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21775,15 +21779,15 @@
       </c>
       <c r="C144" s="409">
         <f>Scenarios!C66</f>
-        <v>1.4588087974647501</v>
+        <v>1.4597572820278413</v>
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>14.560774473549516</v>
+        <v>14.570186738069541</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>16.019583271014266</v>
+        <v>16.029944020097382</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21796,15 +21800,15 @@
       </c>
       <c r="C145" s="409">
         <f>Scenarios!C67</f>
-        <v>1.5796033432545096</v>
+        <v>1.5806303657056273</v>
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>16.467155015326156</v>
+        <v>16.477799587781973</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>18.046758358580664</v>
+        <v>18.0584299534876</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC71DC42-238D-42A1-B804-2C099AEE0445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A3C953-86C7-4B1D-9CA9-CCE62A3BD9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="559">
   <si>
     <t>Sales</t>
   </si>
@@ -3265,6 +3265,9 @@
   </si>
   <si>
     <t>CNY</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -5436,7 +5439,7 @@
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.29058822043182098</v>
+        <v>0.2562155514672021</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5479,7 +5482,7 @@
         <v>320</v>
       </c>
       <c r="C16" s="417" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>354</v>
@@ -5509,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>20.327834629345425</v>
+        <v>18.634068549575694</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5559,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>10.474826343883192</v>
+        <v>9.694288979934008</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5574,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>13.014747377846154</v>
+        <v>12.036398739712014</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5589,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>16.029944020097382</v>
+        <v>14.815919579086488</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5604,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>18.0584299534876</v>
+        <v>16.685458433405557</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -6239,7 +6242,7 @@
       </c>
       <c r="C101" s="211">
         <f>E25+C103</f>
-        <v>7.2499999999999995E-2</v>
+        <v>8.249999999999999E-2</v>
       </c>
     </row>
     <row r="102" spans="2:6">
@@ -6257,7 +6260,7 @@
       </c>
       <c r="C103" s="263">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="104" spans="2:6">
@@ -6317,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>20.261195150865689</v>
+        <v>18.57604515992734</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6366,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>21.06 HKD</v>
+        <v>19.27 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6374,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>1.742003067439182E-2</v>
+        <v>2.0666330686671047E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6388,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>20.65 HKD</v>
+        <v>18.92 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6396,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.4148547029111289E-2</v>
+        <v>2.7102841007406443E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6410,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>20.26 HKD</v>
+        <v>18.58 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6418,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.0925866653090141E-2</v>
+        <v>3.3578775508990591E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6432,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>19.88 HKD</v>
+        <v>18.24 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6440,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>3.7751224577318894E-2</v>
+        <v>4.0093189146888197E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6454,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>19.5 HKD</v>
+        <v>17.91 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6462,7 +6465,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.4623781666467119E-2</v>
+        <v>4.6645066717110807E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6480,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>20.327834629345425</v>
+        <v>18.634068549575694</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6587,11 +6590,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>9.3676657278089532</v>
+        <v>8.5871283638597689</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>10.474826343883192</v>
+        <v>9.694288979934008</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6608,11 +6611,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>11.741709533195918</v>
+        <v>10.763360895061778</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>13.014747377846154</v>
+        <v>12.036398739712014</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6655,11 +6658,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>14.570186738069541</v>
+        <v>13.356162297058647</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>16.029944020097382</v>
+        <v>14.815919579086488</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6676,11 +6679,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>16.477799587781973</v>
+        <v>15.10482806769993</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>18.0584299534876</v>
+        <v>16.685458433405557</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -16382,7 +16385,7 @@
       </c>
       <c r="C5" s="188">
         <f>Equity_Cost</f>
-        <v>7.2499999999999995E-2</v>
+        <v>8.249999999999999E-2</v>
       </c>
       <c r="E5" s="135" t="s">
         <v>432</v>
@@ -16410,7 +16413,7 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>15309136808.369802</v>
+        <v>13453483861.900736</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16473,7 +16476,7 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>22311216617.43177</v>
+        <v>20455563670.962704</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16534,7 +16537,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>24999093286.139271</v>
+        <v>22919886136.169907</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16556,7 +16559,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>20.261195150865689</v>
+        <v>18.57604515992734</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16679,7 +16682,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>20.329516530220264</v>
+        <v>18.635557324692481</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16770,11 +16773,11 @@
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.93240093240093236</v>
+        <v>0.92378752886836024</v>
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>1036695539.3772476</v>
+        <v>1027118675.272146</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16819,11 +16822,11 @@
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
-        <v>0.86937149874212816</v>
+        <v>0.85338339849271161</v>
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>968308510.966766</v>
+        <v>950500918.27698994</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16868,11 +16871,11 @@
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
-        <v>0.81060279602995633</v>
+        <v>0.78834494087086515</v>
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>904432725.71030152</v>
+        <v>879598450.88594234</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -18308,7 +18311,7 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>15389700367.215706</v>
+        <v>13524282140.886532</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
@@ -18317,11 +18320,11 @@
       <c r="J51" s="454"/>
       <c r="K51" s="119">
         <f>1/(1+Equity_Cost)^C15</f>
-        <v>0.81060279602995633</v>
+        <v>0.78834494087086515</v>
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>12474934147.728296</v>
+        <v>10661799404.678091</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18334,7 +18337,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>15384370923.782612</v>
+        <v>13519017449.113169</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18358,7 +18361,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>15384370923.782612</v>
+        <v>13519017449.113169</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18393,19 +18396,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>15002954072.202408</v>
+        <v>13184414184.662722</v>
       </c>
       <c r="C56" s="118">
-        <v>15156045440.286104</v>
+        <v>13318949023.281729</v>
       </c>
       <c r="D56" s="118">
-        <v>15309136808.369802</v>
+        <v>13453483861.900736</v>
       </c>
       <c r="E56" s="118">
-        <v>15462228176.453503</v>
+        <v>13588018700.519743</v>
       </c>
       <c r="F56" s="118">
-        <v>15615319544.537201</v>
+        <v>13722553539.138752</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18419,19 +18422,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>14723178704.888611</v>
+        <v>12940822236.678192</v>
       </c>
       <c r="C57" s="118">
-        <v>15014730331.285772</v>
+        <v>13195910233.228321</v>
       </c>
       <c r="D57" s="118">
-        <v>15309136808.369802</v>
+        <v>13453483861.900736</v>
       </c>
       <c r="E57" s="118">
-        <v>15606398136.140715</v>
+        <v>13713543122.695446</v>
       </c>
       <c r="F57" s="118">
-        <v>15906514314.598501</v>
+        <v>13976088015.61245</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18445,19 +18448,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>14467533147.809334</v>
+        <v>12720295577.070946</v>
       </c>
       <c r="C58" s="118">
-        <v>14884285615.285458</v>
+        <v>13083385150.408108</v>
       </c>
       <c r="D58" s="118">
-        <v>15309136808.369802</v>
+        <v>13453483861.900734</v>
       </c>
       <c r="E58" s="118">
-        <v>15742166583.025642</v>
+        <v>13830660597.427511</v>
       </c>
       <c r="F58" s="118">
-        <v>16183454795.21624</v>
+        <v>14214984242.867107</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18471,19 +18474,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>14233936275.14016</v>
+        <v>12520650194.701345</v>
       </c>
       <c r="C59" s="118">
-        <v>14763875108.208246</v>
+        <v>12980475374.895863</v>
       </c>
       <c r="D59" s="118">
-        <v>15309136808.369801</v>
+        <v>13453483861.900738</v>
       </c>
       <c r="E59" s="118">
-        <v>15870023115.756435</v>
+        <v>13939934176.623249</v>
       </c>
       <c r="F59" s="118">
-        <v>16446838748.810734</v>
+        <v>14440087385.407297</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18497,19 +18500,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>14020486452.095135</v>
+        <v>12339908878.56073</v>
       </c>
       <c r="C60" s="118">
-        <v>14652726947.829285</v>
+        <v>12886359275.351175</v>
       </c>
       <c r="D60" s="118">
-        <v>15309136808.369801</v>
+        <v>13453483861.900738</v>
       </c>
       <c r="E60" s="118">
-        <v>15990428801.591496</v>
+        <v>14041889202.016037</v>
       </c>
       <c r="F60" s="118">
-        <v>16697329781.599901</v>
+        <v>14652193810.710752</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18523,19 +18526,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>13825446054.347698</v>
+        <v>12176281636.234821</v>
       </c>
       <c r="C61" s="118">
-        <v>14550128645.941008</v>
+        <v>12800285429.116308</v>
       </c>
       <c r="D61" s="118">
-        <v>15309136808.369801</v>
+        <v>13453483861.900738</v>
       </c>
       <c r="E61" s="118">
-        <v>16103817839.067867</v>
+        <v>14137015830.788986</v>
       </c>
       <c r="F61" s="118">
-        <v>16935559015.581207</v>
+        <v>14852053906.608696</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18549,19 +18552,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>13647227322.606451</v>
+        <v>12028147966.507896</v>
       </c>
       <c r="C62" s="118">
-        <v>14455422521.121065</v>
+        <v>12721566622.859943</v>
       </c>
       <c r="D62" s="118">
-        <v>15309136808.369802</v>
+        <v>13453483861.900738</v>
       </c>
       <c r="E62" s="118">
-        <v>16210599123.777554</v>
+        <v>14225771392.045961</v>
       </c>
       <c r="F62" s="118">
-        <v>17162126678.668329</v>
+        <v>15040374735.999834</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18575,19 +18578,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>13484379437.192535</v>
+        <v>11894040810.542645</v>
       </c>
       <c r="C63" s="118">
-        <v>14368001482.825729</v>
+        <v>12649574365.867977</v>
       </c>
       <c r="D63" s="118">
-        <v>15309136808.369801</v>
+        <v>13453483861.900738</v>
       </c>
       <c r="E63" s="118">
-        <v>16311157722.898096</v>
+        <v>14308582585.458939</v>
       </c>
       <c r="F63" s="118">
-        <v>17377603616.988941</v>
+        <v>15217822538.289864</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18601,19 +18604,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>13335576707.397072</v>
+        <v>11772632022.694195</v>
       </c>
       <c r="C64" s="118">
-        <v>14287305139.783884</v>
+        <v>12583733872.17556</v>
       </c>
       <c r="D64" s="118">
-        <v>15309136808.369801</v>
+        <v>13453483861.900738</v>
       </c>
       <c r="E64" s="118">
-        <v>16405856263.79483</v>
+        <v>14385847532.661808</v>
       </c>
       <c r="F64" s="118">
-        <v>17582532733.153999</v>
+        <v>15385025086.406105</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18627,19 +18630,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>13199607779.47208</v>
+        <v>11662719217.066961</v>
       </c>
       <c r="C65" s="118">
-        <v>14212816207.745258</v>
+        <v>12523519471.47764</v>
       </c>
       <c r="D65" s="118">
-        <v>15309136808.369801</v>
+        <v>13453483861.900738</v>
       </c>
       <c r="E65" s="118">
-        <v>16495036241.702244</v>
+        <v>14457937691.252937</v>
       </c>
       <c r="F65" s="118">
-        <v>17777430354.122169</v>
+        <v>15542573907.725796</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18653,19 +18656,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>12676702716.910824</v>
+        <v>11250905154.704868</v>
       </c>
       <c r="C66" s="277">
-        <v>13917998181.882694</v>
+        <v>12291378727.807941</v>
       </c>
       <c r="D66" s="118">
-        <v>15309136808.369801</v>
+        <v>13453483861.900736</v>
       </c>
       <c r="E66" s="118">
-        <v>16868780056.613434</v>
+        <v>14752116437.765316</v>
       </c>
       <c r="F66" s="118">
-        <v>18617815854.740582</v>
+        <v>16203932160.360241</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18688,19 +18691,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>12343608785.284527</v>
+        <v>11000471883.787712</v>
       </c>
       <c r="C67" s="277">
-        <v>13720417944.680717</v>
+        <v>12142857743.350838</v>
       </c>
       <c r="D67" s="118">
-        <v>15309136808.369799</v>
+        <v>13453483861.900738</v>
       </c>
       <c r="E67" s="118">
-        <v>17145598089.96172</v>
+        <v>14960123766.570484</v>
       </c>
       <c r="F67" s="118">
-        <v>19271688102.952076</v>
+        <v>16695177123.937071</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18723,19 +18726,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>12131425780.700848</v>
+        <v>10848177853.752569</v>
       </c>
       <c r="C68" s="277">
-        <v>13588004229.411533</v>
+        <v>12047835721.471331</v>
       </c>
       <c r="D68" s="118">
-        <v>15309136808.369799</v>
+        <v>13453483861.900738</v>
       </c>
       <c r="E68" s="118">
-        <v>17350626830.316982</v>
+        <v>15107201179.026726</v>
       </c>
       <c r="F68" s="118">
-        <v>19780441427.071228</v>
+        <v>17060065009.252363</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18758,19 +18761,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>11996263824.389174</v>
+        <v>10755564474.150871</v>
       </c>
       <c r="C69" s="277">
-        <v>13499263613.246235</v>
+        <v>11987041722.057211</v>
       </c>
       <c r="D69" s="118">
-        <v>15309136808.369799</v>
+        <v>13453483861.90074</v>
       </c>
       <c r="E69" s="118">
-        <v>17502483932.483364</v>
+        <v>15211196386.21044</v>
       </c>
       <c r="F69" s="118">
-        <v>20176283192.049404</v>
+        <v>17331097139.292805</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18867,23 +18870,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>20.261195150865689</v>
+        <v>18.57604515992734</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>20.261195150865689</v>
+        <v>18.57604515992734</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>20.261195150865689</v>
+        <v>18.57604515992734</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>20.261195150865689</v>
+        <v>18.57604515992734</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>20.261195150865689</v>
+        <v>18.57604515992734</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18898,23 +18901,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>19.983145402360858</v>
+        <v>18.33169841124128</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>20.122170276613275</v>
+        <v>18.453871785584308</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>20.261195150865685</v>
+        <v>18.57604515992734</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>20.400220025118102</v>
+        <v>18.698218534270367</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>20.539244899370516</v>
+        <v>18.820391908613399</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18929,23 +18932,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>19.729076634496309</v>
+        <v>18.110488421668681</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>19.993839623457205</v>
+        <v>18.342138168402233</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>20.261195150865685</v>
+        <v>18.57604515992734</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>20.531143216721773</v>
+        <v>18.812209396244004</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>20.803683821025459</v>
+        <v>19.05063087735223</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18960,23 +18963,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>19.496920557566458</v>
+        <v>17.910224412632971</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>19.875380559005443</v>
+        <v>18.239952227515158</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>20.261195150865685</v>
+        <v>18.576045159927332</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>20.654436851705182</v>
+        <v>18.918565766307168</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>21.055178180081899</v>
+        <v>19.26757660309228</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18991,23 +18994,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>19.284787265826367</v>
+        <v>17.728923046485182</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>19.766033730280736</v>
+        <v>18.146498110676173</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>20.261195150865685</v>
+        <v>18.576045159927343</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>20.770545542924996</v>
+        <v>19.017798961470028</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>21.294361626457267</v>
+        <v>19.471996594089838</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -19022,23 +19025,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>19.090949852394864</v>
+        <v>17.564788784291331</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>19.66509819607332</v>
+        <v>18.06102968049548</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>20.261195150865685</v>
+        <v>18.576045159927343</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>20.87988799339773</v>
+        <v>19.110386053492643</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>21.52183679224083</v>
+        <v>19.66461404519146</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -19053,23 +19056,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>18.913830351077497</v>
+        <v>17.416196103506145</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>19.571926933728008</v>
+        <v>17.982864557281729</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>20.261195150865685</v>
+        <v>18.576045159927343</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>20.982858506197228</v>
+        <v>19.196772162446777</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>21.738176810048966</v>
+        <v>19.846110396344944</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19085,23 +19088,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>18.751986890666288</v>
+        <v>17.281673399423472</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>19.485922691563111</v>
+        <v>17.911378670924584</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>20.261195150865685</v>
+        <v>18.576045159927343</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>21.079828406362722</v>
+        <v>19.277372596667256</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>21.943926757055319</v>
+        <v>20.017127743390272</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19116,23 +19119,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>18.604101957143691</v>
+        <v>17.159888410969884</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>19.406534160333965</v>
+        <v>17.84600127832082</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>20.261195150865685</v>
+        <v>18.576045159927343</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>21.171147379945143</v>
+        <v>19.352574849381053</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>22.139605028334078</v>
+        <v>20.178271109659303</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19148,23 +19151,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>18.468971668237263</v>
+        <v>17.049635026503815</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>19.333252439199381</v>
+        <v>17.786210406563104</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>20.261195150865685</v>
+        <v>18.576045159927343</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>21.257144735020432</v>
+        <v>19.422740461612868</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>22.32570464297681</v>
+        <v>20.330110586420883</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19180,23 +19183,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>18.345495973012749</v>
+        <v>16.949821338950233</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>19.265607773536683</v>
+        <v>17.731528685509858</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>20.261195150865685</v>
+        <v>18.576045159927343</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>21.338130589217208</v>
+        <v>19.488206760323379</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>22.502694486273402</v>
+        <v>20.473183349743575</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19212,23 +19215,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>17.87063699514546</v>
+        <v>16.575845987159241</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>18.997878511685165</v>
+        <v>17.520717729271638</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>20.261195150865685</v>
+        <v>18.57604515992734</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>21.677533702018696</v>
+        <v>19.755355481727818</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>23.265862847817804</v>
+        <v>21.07377402353017</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19244,23 +19247,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>17.568148732493903</v>
+        <v>16.348423275913731</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>18.818452538976175</v>
+        <v>17.385843298097274</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>20.261195150865682</v>
+        <v>18.576045159927343</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>21.928916864627876</v>
+        <v>19.944250473605539</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>23.859655353709101</v>
+        <v>21.519881927217217</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19276,23 +19279,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>17.375461738445892</v>
+        <v>16.210122477899741</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>18.698205392810962</v>
+        <v>17.29955218444163</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>20.261195150865682</v>
+        <v>18.576045159927343</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>22.115106949691572</v>
+        <v>20.077813972501961</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>24.321662897285911</v>
+        <v>21.851242819782062</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19308,23 +19311,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>17.252718867863745</v>
+        <v>16.126018693248877</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>18.617618530482336</v>
+        <v>17.244344119939729</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>20.261195150865682</v>
+        <v>18.576045159927343</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>22.253010966079191</v>
+        <v>20.172253788296572</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>24.681133534257803</v>
+        <v>22.097371705224099</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19371,7 +19374,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>21.055178180081899</v>
+        <v>19.26757660309228</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19399,7 +19402,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>20.654436851705182</v>
+        <v>18.918565766307168</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19427,7 +19430,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>20.261195150865685</v>
+        <v>18.576045159927332</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19455,7 +19458,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>19.875380559005443</v>
+        <v>18.239952227515158</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19483,7 +19486,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>19.496920557566458</v>
+        <v>17.910224412632971</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19843,7 +19846,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>20.654436851705182</v>
+        <v>18.918565766307168</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19867,7 +19870,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>20.261195150865685</v>
+        <v>18.576045159927332</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19890,7 +19893,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>19.875380559005443</v>
+        <v>18.239952227515158</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19906,7 +19909,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>20.243389843068524</v>
+        <v>18.560526048100257</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19953,7 +19956,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>21.055178180081899</v>
+        <v>19.26757660309228</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19976,7 +19979,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>19.496920557566458</v>
+        <v>17.910224412632971</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -20032,7 +20035,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.29058822043182098</v>
+        <v>0.2562155514672021</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20041,7 +20044,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>20.261195150865689</v>
+        <v>18.57604515992734</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20052,7 +20055,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.0925866653090103E-2</v>
+        <v>3.3578775508990376E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20061,7 +20064,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>20.327834629345425</v>
+        <v>18.634068549575694</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20164,7 +20167,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>20.329516530220264</v>
+        <v>18.635557324692481</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20231,7 +20234,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.31280792280968422</v>
+        <v>0.34124097529785574</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20309,11 +20312,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>9.3676657278089532</v>
+        <v>8.5871283638597689</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>10.474826343883192</v>
+        <v>9.694288979934008</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20321,7 +20324,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.48470525587798474</v>
+        <v>0.47975457135716337</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20334,11 +20337,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>11.741709533195918</v>
+        <v>10.763360895061778</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>13.014747377846154</v>
+        <v>12.036398739712014</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20346,7 +20349,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.35975731723742177</v>
+        <v>0.35406491031793008</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20380,11 +20383,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>14.570186738069541</v>
+        <v>13.356162297058647</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>16.029944020097382</v>
+        <v>14.815919579086488</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20392,7 +20395,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.21142884560087738</v>
+        <v>0.204901520048135</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20405,11 +20408,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>16.477799587781973</v>
+        <v>15.10482806769993</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>18.0584299534876</v>
+        <v>16.685458433405557</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20417,7 +20420,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.1116402566843836</v>
+        <v>0.10457244541018429</v>
       </c>
     </row>
   </sheetData>
@@ -20553,7 +20556,7 @@
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.29058822043182098</v>
+        <v>0.2562155514672021</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20598,7 +20601,7 @@
       </c>
       <c r="C16" s="358" t="str">
         <f>Thesis!C16</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="D16" s="351" t="s">
         <v>369</v>
@@ -20631,7 +20634,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>20.327834629345425</v>
+        <v>18.634068549575694</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20683,7 +20686,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>10.474826343883192</v>
+        <v>9.694288979934008</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20699,7 +20702,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>13.014747377846154</v>
+        <v>12.036398739712014</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20715,7 +20718,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>16.029944020097382</v>
+        <v>14.815919579086488</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20731,7 +20734,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>18.0584299534876</v>
+        <v>16.685458433405557</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -21348,7 +21351,7 @@
       </c>
       <c r="C101" s="368">
         <f>E25+C103</f>
-        <v>7.2499999999999995E-2</v>
+        <v>8.249999999999999E-2</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -21368,7 +21371,7 @@
       </c>
       <c r="C103" s="383">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -21441,7 +21444,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>20.261195150865689</v>
+        <v>18.57604515992734</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21504,7 +21507,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>21.06 HKD</v>
+        <v>19.27 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21527,7 +21530,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>20.65 HKD</v>
+        <v>18.92 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21549,7 +21552,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>20.26 HKD</v>
+        <v>18.58 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21571,7 +21574,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>19.88 HKD</v>
+        <v>18.24 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21593,7 +21596,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>19.5 HKD</v>
+        <v>17.91 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21615,7 +21618,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>20.327834629345425</v>
+        <v>18.634068549575694</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21722,11 +21725,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>9.3676657278089532</v>
+        <v>8.5871283638597689</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>10.474826343883192</v>
+        <v>9.694288979934008</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21743,11 +21746,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>11.741709533195918</v>
+        <v>10.763360895061778</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>13.014747377846154</v>
+        <v>12.036398739712014</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21783,11 +21786,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>14.570186738069541</v>
+        <v>13.356162297058647</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>16.029944020097382</v>
+        <v>14.815919579086488</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21804,11 +21807,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>16.477799587781973</v>
+        <v>15.10482806769993</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>18.0584299534876</v>
+        <v>16.685458433405557</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A3C953-86C7-4B1D-9CA9-CCE62A3BD9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A48172-CB25-4BE1-A007-3FD2497E6F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.57</v>
+        <v>10.75</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>13041.69937</v>
+        <v>13263.79075</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.2562155514672021</v>
+        <v>0.24857571240316154</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1204719901561737</v>
+        <v>1.1197497097015381</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>18.634068549575694</v>
+        <v>18.622133071257309</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>9.694288979934008</v>
+        <v>9.6880750598555032</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>12.036398739712014</v>
+        <v>12.028683972910242</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>14.815919579086488</v>
+        <v>14.806423709871549</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>16.685458433405557</v>
+        <v>16.674764592822669</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
-        <v>11597154.163008198</v>
+        <v>11596619.455465142</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
-        <v>-2559768.6664918009</v>
+        <v>-2560303.3740348574</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
-        <v>-389572632.20227021</v>
+        <v>-389572498.52538443</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="C60" s="285">
         <f>Normalized_FCF!G19</f>
-        <v>1207988284.9036756</v>
+        <v>1207985751.4787502</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
-        <v>1109912418.6068106</v>
+        <v>1109912017.5761533</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.5357647902554368E-2</v>
+        <v>9.3700487507701824E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,14 +5914,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.7242656072311618E-2</v>
+        <v>5.6247892394309815E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
-        <v>0.74734776778600887</v>
+        <v>0.7468662811228971</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5941,11 +5941,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
-        <v>0.10095735561257201</v>
+        <v>0.10095732097034157</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.8891876231945069E-2</v>
+        <v>8.8891712098315062E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5955,11 +5955,11 @@
       </c>
       <c r="C67" s="263">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639727240930954</v>
+        <v>0.12639722903769574</v>
       </c>
       <c r="D67" s="263">
         <f>Normalized_FCF!G116</f>
-        <v>0.11129145198871108</v>
+        <v>0.11129124649557967</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25712284641630861</v>
+        <v>-0.25695709947391437</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
-        <v>6701659721.0119677</v>
+        <v>6701748838.9358101</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0858911358527941</v>
+        <v>6.0820489162631111</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52993943618782413</v>
+        <v>0.52959782577697778</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.3587077256243099</v>
+        <v>6.354689642566175</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.748398139739767</v>
+        <v>1.7472710845216537</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>18.57604515992734</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>19.27 HKD</v>
+        <v>19.26 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.0666330686671047E-2</v>
+        <v>2.0666251924560203E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>18.92 HKD</v>
+        <v>18.91 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.7102841007406443E-2</v>
+        <v>2.7102732808888481E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>18.58 HKD</v>
+        <v>18.56 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.3578775508990591E-2</v>
+        <v>3.3578636971898473E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>18.24 HKD</v>
+        <v>18.23 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.0093189146888197E-2</v>
+        <v>4.0093019351629719E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>17.91 HKD</v>
+        <v>17.9 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.6645066717110807E-2</v>
+        <v>4.6644864727009072E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>18.634068549575694</v>
+        <v>18.622133071257309</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.60505487468433383</v>
+        <v>0.60466484323883052</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6586,15 +6586,15 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>1.1071606160742391</v>
+        <v>1.1064469164189523</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>8.5871283638597689</v>
+        <v>8.58162814343655</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>9.694288979934008</v>
+        <v>9.6880750598555032</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6607,15 +6607,15 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>1.2730378446502357</v>
+        <v>1.272217216949338</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>10.763360895061778</v>
+        <v>10.756466755960904</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>12.036398739712014</v>
+        <v>12.028683972910242</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6654,15 +6654,15 @@
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
-        <v>1.4597572820278413</v>
+        <v>1.4588162909432056</v>
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>13.356162297058647</v>
+        <v>13.347607418928343</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>14.815919579086488</v>
+        <v>14.806423709871549</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6675,15 +6675,15 @@
       </c>
       <c r="C145" s="333">
         <f>Scenarios!C67</f>
-        <v>1.5806303657056273</v>
+        <v>1.5796114572195761</v>
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>15.10482806769993</v>
+        <v>15.095153135603093</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>16.685458433405557</v>
+        <v>16.674764592822669</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,18 +6797,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6825,6 +6813,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.67228319409370418</v>
+        <v>0.67184982582092279</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.67228319409370418</v>
+        <v>0.67184982582092279</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10236,11 +10236,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.609315039571076</v>
+        <v>13.600542181043224</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.748398139739767</v>
+        <v>1.7472710845216537</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6701659721.0119677</v>
+        <v>6701748838.9358101</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C73" s="285">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-985704271.74531412</v>
+        <v>-985659712.78339279</v>
       </c>
       <c r="D73" s="285">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-966429513.58401644</v>
+        <v>-966384954.62209511</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10514,11 +10514,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7597456921754961</v>
+        <v>8.7601416961611278</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9344526701784748</v>
+        <v>8.9348646280989854</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10531,7 +10531,7 @@
       <c r="C75" s="261"/>
       <c r="D75" s="262">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1932859027.1680329</v>
+        <v>1932769909.2441902</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10646,11 +10646,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-317248709.94514465</v>
+        <v>-317044204.57199401</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.25712284641630861</v>
+        <v>-0.25695709947391437</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10663,11 +10663,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7509022004.9517469</v>
+        <v>7504281316.8909931</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>6.0858911358527941</v>
+        <v>6.0820489162631111</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10680,11 +10680,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>653861003.88542116</v>
+        <v>653439510.95449209</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.52993943618782413</v>
+        <v>0.52959782577697778</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10697,11 +10697,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>7845634298.8920231</v>
+        <v>7840676623.2734909</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.3587077256243099</v>
+        <v>6.354689642566175</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11182,36 +11182,36 @@
       </c>
       <c r="C10" s="266">
         <f>C48</f>
-        <v>-2559768.6664918009</v>
+        <v>-2560303.3740348574</v>
       </c>
       <c r="E10" s="237"/>
       <c r="G10" s="266">
         <f>G48</f>
-        <v>42505012.363674626</v>
+        <v>42502478.938749373</v>
       </c>
       <c r="H10" s="266">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40979201.411828145</v>
+        <v>40976487.812495545</v>
       </c>
       <c r="I10" s="266">
         <f t="shared" si="6"/>
-        <v>17731378.510244511</v>
+        <v>17729593.736511134</v>
       </c>
       <c r="J10" s="266">
         <f t="shared" si="6"/>
-        <v>5081028.3235541806</v>
+        <v>5079895.5317816101</v>
       </c>
       <c r="K10" s="266">
         <f t="shared" si="6"/>
-        <v>-4689126.7409477085</v>
+        <v>-4689932.4491716772</v>
       </c>
       <c r="L10" s="266">
         <f t="shared" si="6"/>
-        <v>-6413618.0376547538</v>
+        <v>-6414218.657149151</v>
       </c>
       <c r="M10" s="266">
         <f t="shared" si="6"/>
-        <v>7541927.6272624489</v>
+        <v>7541556.083095436</v>
       </c>
       <c r="N10" s="266">
         <f t="shared" si="6"/>
@@ -11237,36 +11237,36 @@
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
-        <v>1558290528.8090808</v>
+        <v>1558289994.1015377</v>
       </c>
       <c r="E11" s="237"/>
       <c r="G11" s="267">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1372058211.9036756</v>
+        <v>1372055678.4787502</v>
       </c>
       <c r="H11" s="267">
         <f t="shared" si="7"/>
-        <v>1481963869.7318277</v>
+        <v>1481961156.1324952</v>
       </c>
       <c r="I11" s="267">
         <f t="shared" si="7"/>
-        <v>1407258877.5102446</v>
+        <v>1407257092.7365112</v>
       </c>
       <c r="J11" s="267">
         <f t="shared" si="7"/>
-        <v>1240535346.3235543</v>
+        <v>1240534213.5317817</v>
       </c>
       <c r="K11" s="267">
         <f t="shared" si="7"/>
-        <v>1157466564.2590523</v>
+        <v>1157465758.5508282</v>
       </c>
       <c r="L11" s="267">
         <f t="shared" si="7"/>
-        <v>999272196.54234731</v>
+        <v>999271595.92285287</v>
       </c>
       <c r="M11" s="267">
         <f t="shared" si="7"/>
-        <v>939489234.3972615</v>
+        <v>939488862.85309446</v>
       </c>
       <c r="N11" s="267">
         <f t="shared" si="7"/>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
-        <v>-389572632.20227021</v>
+        <v>-389572498.52538443</v>
       </c>
       <c r="E12" s="237"/>
       <c r="G12" s="266">
@@ -11404,38 +11404,38 @@
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
-        <v>1109912418.6068106</v>
+        <v>1109912017.5761533</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="243"/>
       <c r="F14" s="58"/>
       <c r="G14" s="267">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207988284.9036756</v>
+        <v>1207985751.4787502</v>
       </c>
       <c r="H14" s="267">
         <f t="shared" si="8"/>
-        <v>1497937812.7318277</v>
+        <v>1497935099.1324952</v>
       </c>
       <c r="I14" s="267">
         <f t="shared" si="8"/>
-        <v>1418694354.5102446</v>
+        <v>1418692569.7365112</v>
       </c>
       <c r="J14" s="267">
         <f t="shared" si="8"/>
-        <v>1235082534.3235543</v>
+        <v>1235081401.5317817</v>
       </c>
       <c r="K14" s="267">
         <f t="shared" si="8"/>
-        <v>1149296013.2590523</v>
+        <v>1149295207.5508282</v>
       </c>
       <c r="L14" s="267">
         <f t="shared" si="8"/>
-        <v>975100121.42234731</v>
+        <v>975099520.80285287</v>
       </c>
       <c r="M14" s="267">
         <f t="shared" si="8"/>
-        <v>950285080.76726151</v>
+        <v>950284709.22309446</v>
       </c>
       <c r="N14" s="267">
         <f t="shared" si="8"/>
@@ -11622,38 +11622,38 @@
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
-        <v>1109912418.6068106</v>
+        <v>1109912017.5761533</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="234"/>
       <c r="F19" s="26"/>
       <c r="G19" s="271">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207988284.9036756</v>
+        <v>1207985751.4787502</v>
       </c>
       <c r="H19" s="271">
         <f t="shared" si="9"/>
-        <v>1497937812.7318277</v>
+        <v>1497935099.1324952</v>
       </c>
       <c r="I19" s="271">
         <f t="shared" si="9"/>
-        <v>1418694354.5102446</v>
+        <v>1418692569.7365112</v>
       </c>
       <c r="J19" s="271">
         <f t="shared" si="9"/>
-        <v>1235082534.3235543</v>
+        <v>1235081401.5317817</v>
       </c>
       <c r="K19" s="271">
         <f t="shared" si="9"/>
-        <v>1149296013.2590523</v>
+        <v>1149295207.5508282</v>
       </c>
       <c r="L19" s="271">
         <f t="shared" si="9"/>
-        <v>975100121.42234731</v>
+        <v>975099520.80285287</v>
       </c>
       <c r="M19" s="271">
         <f t="shared" si="9"/>
-        <v>950285080.76726151</v>
+        <v>950284709.22309446</v>
       </c>
       <c r="N19" s="271">
         <f t="shared" si="9"/>
@@ -12361,31 +12361,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.672010421041088E-2</v>
+        <v>7.6720245869840109E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.3980993957561519E-2</v>
+        <v>-4.3981074490573709E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.1260649214961178E-3</v>
+        <v>-8.1260752274930122E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3955313455275036E-3</v>
+        <v>4.3955353592997071E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.0589952680234413E-3</v>
+        <v>7.0590001817675404E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4189680453073261E-2</v>
+        <v>2.4189694992457454E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491186886166056E-2</v>
+        <v>-1.1491191430640854E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12499,36 +12499,36 @@
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
-        <v>11597154.163008198</v>
+        <v>11596619.455465142</v>
       </c>
       <c r="E46" s="237"/>
       <c r="G46" s="274">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54946895.363674626</v>
+        <v>54944361.938749373</v>
       </c>
       <c r="H46" s="274">
         <f t="shared" si="17"/>
-        <v>58854658.411828145</v>
+        <v>58851944.812495545</v>
       </c>
       <c r="I46" s="274">
         <f t="shared" si="17"/>
-        <v>38709564.510244511</v>
+        <v>38707779.736511134</v>
       </c>
       <c r="J46" s="274">
         <f t="shared" si="17"/>
-        <v>24568871.323554181</v>
+        <v>24567738.53178161</v>
       </c>
       <c r="K46" s="274">
         <f t="shared" si="17"/>
-        <v>17474828.259052292</v>
+        <v>17474022.550828323</v>
       </c>
       <c r="L46" s="274">
         <f t="shared" si="17"/>
-        <v>13026703.962345246</v>
+        <v>13026103.342850849</v>
       </c>
       <c r="M46" s="274">
         <f t="shared" si="17"/>
-        <v>8058339.6272624489</v>
+        <v>8057968.083095436</v>
       </c>
       <c r="N46" s="274">
         <f t="shared" si="17"/>
@@ -12611,36 +12611,36 @@
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
-        <v>-2559768.6664918009</v>
+        <v>-2560303.3740348574</v>
       </c>
       <c r="E48" s="237"/>
       <c r="G48" s="267">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42505012.363674626</v>
+        <v>42502478.938749373</v>
       </c>
       <c r="H48" s="267">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40979201.411828145</v>
+        <v>40976487.812495545</v>
       </c>
       <c r="I48" s="267">
         <f t="shared" si="18"/>
-        <v>17731378.510244511</v>
+        <v>17729593.736511134</v>
       </c>
       <c r="J48" s="267">
         <f t="shared" si="18"/>
-        <v>5081028.3235541806</v>
+        <v>5079895.5317816101</v>
       </c>
       <c r="K48" s="267">
         <f t="shared" si="18"/>
-        <v>-4689126.7409477085</v>
+        <v>-4689932.4491716772</v>
       </c>
       <c r="L48" s="267">
         <f t="shared" si="18"/>
-        <v>-6413618.0376547538</v>
+        <v>-6414218.657149151</v>
       </c>
       <c r="M48" s="267">
         <f t="shared" si="18"/>
-        <v>7541927.6272624489</v>
+        <v>7541556.083095436</v>
       </c>
       <c r="N48" s="267">
         <f t="shared" si="18"/>
@@ -13576,38 +13576,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0762994541887489E-4</v>
+        <v>2.0767331703265907E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="234"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.4476995959144942E-3</v>
+        <v>3.4474941027830878E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4527728417346848E-3</v>
+        <v>3.4525442027725731E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.6222221234346806E-3</v>
+        <v>1.6220588366696986E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8574106324847182E-4</v>
+        <v>4.8563276952424739E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2054810189502152E-4</v>
+        <v>5.2063754496402747E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.2532074656114808E-4</v>
+        <v>7.2538867105829117E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.2125465018953474E-4</v>
+        <v>9.2120926566603776E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13633,38 +13633,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639727240930954</v>
+        <v>0.12639722903769574</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="234"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.11129145198871108</v>
+        <v>0.11129124649557967</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12486540551190846</v>
+        <v>0.12486517687294635</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.1287483927534461</v>
+        <v>0.1287482294666811</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11859389866557767</v>
+        <v>0.11859379037185344</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12849237316844805</v>
+        <v>0.12849228372537905</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300842229122304</v>
+        <v>0.11300835436672589</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11475963026519299</v>
+        <v>0.11475958488066949</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1599318102327384E-2</v>
+        <v>3.1599307259423934E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="234"/>
@@ -13805,38 +13805,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.0028078674351433E-2</v>
+        <v>9.0028046145641097E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="234"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.7983284561778516E-2</v>
+        <v>9.7983079068647103E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12621131745420167</v>
+        <v>0.12621108881523954</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12979461055149888</v>
+        <v>0.12979444726473388</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.1180726154666048</v>
+        <v>0.11807250717288058</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758534611427488</v>
+        <v>0.12758525667120588</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.1102747846674924</v>
+        <v>0.11027471674299524</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607835462355764</v>
+        <v>0.11607830923903414</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14028,38 +14028,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.0028078674351433E-2</v>
+        <v>9.0028046145641097E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="234"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.7983284561778516E-2</v>
+        <v>9.7983079068647103E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12621131745420167</v>
+        <v>0.12621108881523954</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12979461055149888</v>
+        <v>0.12979444726473388</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.1180726154666048</v>
+        <v>0.11807250717288058</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758534611427488</v>
+        <v>0.12758525667120588</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.1102747846674924</v>
+        <v>0.11027471674299524</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607835462355764</v>
+        <v>0.11607830923903414</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.67228319409370418</v>
+        <v>0.67184982582092279</v>
       </c>
       <c r="E88" s="237"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.67228319409370418</v>
+        <v>0.67184982582092279</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14153,12 +14153,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>829490568.48377001</v>
+        <v>828955860.94071317</v>
       </c>
       <c r="E89" s="237"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>829490568.48377001</v>
+        <v>828955860.94071317</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.74734776778600887</v>
+        <v>0.7468662811228971</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.68667103716979605</v>
+        <v>0.68622983336181798</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14284,12 +14284,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.7242656072311618E-2</v>
+        <v>5.6247892394309815E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.7242656072311618E-2</v>
+        <v>5.6247892394309815E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14421,38 +14421,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.13573208140128057</v>
+        <v>0.13573378875503983</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="234"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162170936083904E-2</v>
+        <v>-7.416218515508699E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.3085465237038054E-2</v>
+        <v>5.308487253790739E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.13439643753867347</v>
+        <v>0.13439603469707784</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1767759544465237E-2</v>
+        <v>7.1767526915834656E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830958598076128</v>
+        <v>0.15830947589566868</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3633472270110847E-2</v>
+        <v>6.3633253605803075E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35104219425473615</v>
+        <v>0.35104165995181025</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -15037,31 +15037,31 @@
       </c>
       <c r="G113" s="251">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4672980310743136</v>
+        <v>1.4673011083369387</v>
       </c>
       <c r="H113" s="251">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.570845058453209</v>
+        <v>1.5708479041333088</v>
       </c>
       <c r="I113" s="251">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.4269325302974423</v>
+        <v>1.4269343254373859</v>
       </c>
       <c r="J113" s="251">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.6576459630054663</v>
+        <v>1.6576474833649393</v>
       </c>
       <c r="K113" s="251">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.5825385879851996</v>
+        <v>1.5825396974167425</v>
       </c>
       <c r="L113" s="251">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.399251717484947</v>
+        <v>1.3992525793640078</v>
       </c>
       <c r="M113" s="251">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.0454234124857427</v>
+        <v>1.0454238212274252</v>
       </c>
       <c r="N113" s="251">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15150,39 +15150,39 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639727240930954</v>
+        <v>0.12639722903769574</v>
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
-        <v>0.12639727240930954</v>
+        <v>0.12639722903769574</v>
       </c>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.11129145198871108</v>
+        <v>0.11129124649557967</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12486540551190846</v>
+        <v>0.12486517687294635</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.1287483927534461</v>
+        <v>0.1287482294666811</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11859389866557767</v>
+        <v>0.11859379037185344</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12849237316844805</v>
+        <v>0.12849228372537905</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300842229122304</v>
+        <v>0.11300835436672589</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11475963026519299</v>
+        <v>0.11475958488066949</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15324,41 +15324,41 @@
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
-        <v>0.10095735561257201</v>
+        <v>0.10095732097034157</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
         <f>C11/C104</f>
-        <v>0.10095735561257201</v>
+        <v>0.10095732097034157</v>
       </c>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.8891876231945069E-2</v>
+        <v>8.8891712098315062E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11047760670445141</v>
+        <v>0.1104774044107478</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11114003868887648</v>
+        <v>0.11113989773412754</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11166247728147087</v>
+        <v>0.11166237531715686</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11542174402027119</v>
+        <v>0.11542166367561912</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.10956972436065134</v>
+        <v>0.10956965850300746</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176373458137925</v>
+        <v>0.11176369038165652</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15448,50 +15448,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0079303383299998</v>
+        <v>1.0072802407077948</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0969947000232319</v>
+        <v>1.0962852543738819</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3603027960343488</v>
+        <v>1.3594234527831026</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2883404643073313</v>
+        <v>1.287508352468582</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1215994485842533</v>
+        <v>1.1208754133012124</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0436952502428809</v>
+        <v>1.0430217305280087</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.88550499914626279</v>
+        <v>0.88493363840973305</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.86297003881619583</v>
+        <v>0.86241341249510317</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63097897695471872</v>
+        <v>0.63057223427275588</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.51959984339285947</v>
+        <v>0.51926489810693388</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.48985515294415533</v>
+        <v>0.48953938172837974</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15505,50 +15505,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.5357647902554368E-2</v>
+        <v>9.3700487507701824E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10378379375811086</v>
+        <v>0.10198002366268669</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.12869468269009923</v>
+        <v>0.12645799560773047</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12188651507164913</v>
+        <v>0.11976821883428669</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10611158453966446</v>
+        <v>0.10426748030708953</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.8741272492230928E-2</v>
+        <v>9.7025277258419418E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.3775307393213122E-2</v>
+        <v>8.2319408224161214E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.164333385205258E-2</v>
+        <v>8.0224503487916571E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.969526745077755E-2</v>
+        <v>5.8657882257930782E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.9157979507366077E-2</v>
+        <v>4.8303711451807806E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.6343912293676001E-2</v>
+        <v>4.5538547137523699E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15562,43 +15562,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12296416506033907</v>
+        <v>0.12090523020351478</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12485721828136268</v>
+        <v>0.12276658578920963</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10667590844796479</v>
+        <v>0.10488970719023143</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9931858956813238E-2</v>
+        <v>9.8258581318466598E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5309277704965223E-2</v>
+        <v>9.3713401427114637E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6236094867903693E-2</v>
+        <v>8.4792141651510888E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1057953451353018E-2</v>
+        <v>6.9868145858679204E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0273079044299427E-2</v>
+        <v>6.9096413534720458E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8309501408941004E-2</v>
+        <v>4.7500598129535485E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7150281765772677E-2</v>
+        <v>4.6360788675741137E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
-        <v>1109912418.6068106</v>
+        <v>1109912017.5761533</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
-        <v>6701659721.0119677</v>
+        <v>6701748838.9358101</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16413,7 +16413,7 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>13453483861.900736</v>
+        <v>13453479000.923071</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16435,7 +16435,7 @@
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
-        <v>-2559768.6664918009</v>
+        <v>-2560303.3740348574</v>
       </c>
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
@@ -16446,14 +16446,14 @@
       </c>
       <c r="C7" s="275">
         <f>F7</f>
-        <v>7002079809.0619678</v>
+        <v>7002168926.9858103</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>424</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
-        <v>7002079809.0619678</v>
+        <v>7002168926.9858103</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>20455563670.962704</v>
+        <v>20455647927.908882</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.3587077256243099</v>
+        <v>6.354689642566175</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="I8" s="313">
         <f>Normalized_FCF!C10</f>
-        <v>-2559768.6664918009</v>
+        <v>-2560303.3740348574</v>
       </c>
       <c r="J8" s="313"/>
       <c r="N8" s="304"/>
@@ -16512,7 +16512,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1204719901561737</v>
+        <v>1.1197497097015381</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16537,7 +16537,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>22919886136.169907</v>
+        <v>22905205829.032841</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>18.57604515992734</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16649,14 +16649,14 @@
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
-        <v>0.12639727240930954</v>
+        <v>0.12639722903769574</v>
       </c>
       <c r="E17" s="308" t="s">
         <v>549</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
-        <v>0.12639727240930954</v>
+        <v>0.12639722903769574</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>412</v>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>18.635557324692481</v>
+        <v>18.623620886139907</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16749,11 +16749,11 @@
       </c>
       <c r="E21" s="299">
         <f>$C$17</f>
-        <v>0.12639727240930954</v>
+        <v>0.12639722903769574</v>
       </c>
       <c r="F21" s="277">
         <f>C21*E21</f>
-        <v>1561019222.9082098</v>
+        <v>1561018687.2643497</v>
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16761,15 +16761,15 @@
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>1111855965.9820981</v>
+        <v>1111855564.249203</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
-        <v>1.7510817454651217E-3</v>
+        <v>1.7510817454648997E-3</v>
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>9.0028078674351447E-2</v>
+        <v>9.0028046145641069E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>1027118675.272146</v>
+        <v>1027118304.1563076</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16798,11 +16798,11 @@
       </c>
       <c r="E22" s="299">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>0.12639727240930954</v>
+        <v>0.12639722903769574</v>
       </c>
       <c r="F22" s="277">
         <f t="shared" ref="F22:F50" si="7">IF(A22="", 0,C22*E22)</f>
-        <v>1563752695.1737645</v>
+        <v>1563752158.5919483</v>
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
@@ -16810,7 +16810,7 @@
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>1113802916.667716</v>
+        <v>1113802514.2313538</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
@@ -16818,7 +16818,7 @@
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
-        <v>9.0028078674351461E-2</v>
+        <v>9.0028046145641083E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16826,7 +16826,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>950500918.27698994</v>
+        <v>950500574.84447944</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16847,11 +16847,11 @@
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
-        <v>0.12639727240930954</v>
+        <v>0.12639722903769574</v>
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>1566490953.9727051</v>
+        <v>1566490416.4512904</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
@@ -16859,15 +16859,15 @@
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>1115753276.6231387</v>
+        <v>1115752873.4820776</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
-        <v>1.7510817454651217E-3</v>
+        <v>1.7510817454653438E-3</v>
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>9.0028078674351461E-2</v>
+        <v>9.0028046145641097E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>879598450.88594234</v>
+        <v>879598133.07172632</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -18299,11 +18299,11 @@
       </c>
       <c r="E51" s="301">
         <f>F17</f>
-        <v>0.12639727240930954</v>
+        <v>0.12639722903769574</v>
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>1566490953.9727051</v>
+        <v>1566490416.4512904</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
@@ -18311,7 +18311,7 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>13524282140.886532</v>
+        <v>13524277254.328215</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>10661799404.678091</v>
+        <v>10661795552.384563</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18337,7 +18337,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>13519017449.113169</v>
+        <v>13519012564.457077</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18361,7 +18361,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>13519017449.113169</v>
+        <v>13519012564.457077</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18396,19 +18396,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>13184414184.662722</v>
+        <v>13184409420.904608</v>
       </c>
       <c r="C56" s="118">
-        <v>13318949023.281729</v>
+        <v>13318944210.913837</v>
       </c>
       <c r="D56" s="118">
-        <v>13453483861.900736</v>
+        <v>13453479000.923069</v>
       </c>
       <c r="E56" s="118">
-        <v>13588018700.519743</v>
+        <v>13588013790.932301</v>
       </c>
       <c r="F56" s="118">
-        <v>13722553539.138752</v>
+        <v>13722548580.941534</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18422,19 +18422,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>12940822236.678192</v>
+        <v>12940817560.934086</v>
       </c>
       <c r="C57" s="118">
-        <v>13195910233.228321</v>
+        <v>13195905465.316486</v>
       </c>
       <c r="D57" s="118">
-        <v>13453483861.900736</v>
+        <v>13453479000.923071</v>
       </c>
       <c r="E57" s="118">
-        <v>13713543122.695446</v>
+        <v>13713538167.753849</v>
       </c>
       <c r="F57" s="118">
-        <v>13976088015.61245</v>
+        <v>13976082965.808815</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18448,19 +18448,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>12720295577.070946</v>
+        <v>12720290981.006962</v>
       </c>
       <c r="C58" s="118">
-        <v>13083385150.408108</v>
+        <v>13083380423.153542</v>
       </c>
       <c r="D58" s="118">
-        <v>13453483861.900734</v>
+        <v>13453479000.923069</v>
       </c>
       <c r="E58" s="118">
-        <v>13830660597.427511</v>
+        <v>13830655600.169331</v>
       </c>
       <c r="F58" s="118">
-        <v>14214984242.867107</v>
+        <v>14214979106.746113</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18474,19 +18474,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>12520650194.701345</v>
+        <v>12520645670.772703</v>
       </c>
       <c r="C59" s="118">
-        <v>12980475374.895863</v>
+        <v>12980470684.824387</v>
       </c>
       <c r="D59" s="118">
-        <v>13453483861.900738</v>
+        <v>13453479000.923073</v>
       </c>
       <c r="E59" s="118">
-        <v>13939934176.623249</v>
+        <v>13939929139.882624</v>
       </c>
       <c r="F59" s="118">
-        <v>14440087385.407297</v>
+        <v>14440082167.952618</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18500,19 +18500,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>12339908878.56073</v>
+        <v>12339904419.937071</v>
       </c>
       <c r="C60" s="118">
-        <v>12886359275.351175</v>
+        <v>12886354619.285482</v>
       </c>
       <c r="D60" s="118">
-        <v>13453483861.900738</v>
+        <v>13453479000.923073</v>
       </c>
       <c r="E60" s="118">
-        <v>14041889202.016037</v>
+        <v>14041884128.43729</v>
       </c>
       <c r="F60" s="118">
-        <v>14652193810.710752</v>
+        <v>14652188516.61834</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18526,19 +18526,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>12176281636.234821</v>
+        <v>12176277236.732527</v>
       </c>
       <c r="C61" s="118">
-        <v>12800285429.116308</v>
+        <v>12800280804.150597</v>
       </c>
       <c r="D61" s="118">
-        <v>13453483861.900738</v>
+        <v>13453479000.923073</v>
       </c>
       <c r="E61" s="118">
-        <v>14137015830.788986</v>
+        <v>14137010722.839333</v>
       </c>
       <c r="F61" s="118">
-        <v>14852053906.608696</v>
+        <v>14852048540.303356</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18552,19 +18552,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>12028147966.507896</v>
+        <v>12028143620.528873</v>
       </c>
       <c r="C62" s="118">
-        <v>12721566622.859943</v>
+        <v>12721562026.336702</v>
       </c>
       <c r="D62" s="118">
-        <v>13453483861.900738</v>
+        <v>13453479000.923073</v>
       </c>
       <c r="E62" s="118">
-        <v>14225771392.045961</v>
+        <v>14225766252.027382</v>
       </c>
       <c r="F62" s="118">
-        <v>15040374735.999834</v>
+        <v>15040369301.650898</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18578,19 +18578,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>11894040810.542645</v>
+        <v>11894036513.018871</v>
       </c>
       <c r="C63" s="118">
-        <v>12649574365.867977</v>
+        <v>12649569795.356794</v>
       </c>
       <c r="D63" s="118">
-        <v>13453483861.900738</v>
+        <v>13453479000.923073</v>
       </c>
       <c r="E63" s="118">
-        <v>14308582585.458939</v>
+        <v>14308577415.519234</v>
       </c>
       <c r="F63" s="118">
-        <v>15217822538.289864</v>
+        <v>15217817039.825954</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18604,19 +18604,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>11772632022.694195</v>
+        <v>11772627769.037529</v>
       </c>
       <c r="C64" s="118">
-        <v>12583733872.17556</v>
+        <v>12583729325.45369</v>
       </c>
       <c r="D64" s="118">
-        <v>13453483861.900738</v>
+        <v>13453479000.923073</v>
       </c>
       <c r="E64" s="118">
-        <v>14385847532.661808</v>
+        <v>14385842334.804934</v>
       </c>
       <c r="F64" s="118">
-        <v>15385025086.406105</v>
+        <v>15385019527.529003</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18630,19 +18630,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>11662719217.066961</v>
+        <v>11662715003.123703</v>
       </c>
       <c r="C65" s="118">
-        <v>12523519471.47764</v>
+        <v>12523514946.512281</v>
       </c>
       <c r="D65" s="118">
-        <v>13453483861.900738</v>
+        <v>13453479000.923073</v>
       </c>
       <c r="E65" s="118">
-        <v>14457937691.252937</v>
+        <v>14457932467.348637</v>
       </c>
       <c r="F65" s="118">
-        <v>15542573907.725796</v>
+        <v>15542568291.923569</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18656,19 +18656,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>11250905154.704868</v>
+        <v>11250901089.55719</v>
       </c>
       <c r="C66" s="277">
-        <v>12291378727.807941</v>
+        <v>12291374286.71907</v>
       </c>
       <c r="D66" s="118">
-        <v>13453483861.900736</v>
+        <v>13453479000.923077</v>
       </c>
       <c r="E66" s="118">
-        <v>14752116437.765316</v>
+        <v>14752111107.569118</v>
       </c>
       <c r="F66" s="118">
-        <v>16203932160.360241</v>
+        <v>16203926305.597778</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18691,19 +18691,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>11000471883.787712</v>
+        <v>11000467909.125927</v>
       </c>
       <c r="C67" s="277">
-        <v>12142857743.350838</v>
+        <v>12142853355.92518</v>
       </c>
       <c r="D67" s="118">
-        <v>13453483861.900738</v>
+        <v>13453479000.923077</v>
       </c>
       <c r="E67" s="118">
-        <v>14960123766.570484</v>
+        <v>14960118361.217623</v>
       </c>
       <c r="F67" s="118">
-        <v>16695177123.937071</v>
+        <v>16695171091.679256</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18726,19 +18726,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>10848177853.752569</v>
+        <v>10848173934.117262</v>
       </c>
       <c r="C68" s="277">
-        <v>12047835721.471331</v>
+        <v>12047831368.37878</v>
       </c>
       <c r="D68" s="118">
-        <v>13453483861.900738</v>
+        <v>13453479000.923077</v>
       </c>
       <c r="E68" s="118">
-        <v>15107201179.026726</v>
+        <v>15107195720.532238</v>
       </c>
       <c r="F68" s="118">
-        <v>17060065009.252363</v>
+        <v>17060058845.154211</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18761,19 +18761,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>10755564474.150871</v>
+        <v>10755560587.978386</v>
       </c>
       <c r="C69" s="277">
-        <v>11987041722.057211</v>
+        <v>11987037390.930586</v>
       </c>
       <c r="D69" s="118">
-        <v>13453483861.90074</v>
+        <v>13453479000.923079</v>
       </c>
       <c r="E69" s="118">
-        <v>15211196386.21044</v>
+        <v>15211190890.140671</v>
       </c>
       <c r="F69" s="118">
-        <v>17331097139.292805</v>
+        <v>17331090877.266029</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18870,23 +18870,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>18.57604515992734</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>18.57604515992734</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>18.57604515992734</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>18.57604515992734</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>18.57604515992734</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18901,23 +18901,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>18.33169841124128</v>
+        <v>18.319957956428464</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>18.453871785584308</v>
+        <v>18.442052531059709</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>18.57604515992734</v>
+        <v>18.564147105690957</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>18.698218534270367</v>
+        <v>18.686241680322205</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>18.820391908613399</v>
+        <v>18.80833625495346</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18932,23 +18932,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>18.110488421668681</v>
+        <v>18.09889064347027</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>18.342138168402233</v>
+        <v>18.330390980126747</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>18.57604515992734</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>18.812209396244004</v>
+        <v>18.800159020162912</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>19.05063087735223</v>
+        <v>19.038426723542599</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18963,23 +18963,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>17.910224412632971</v>
+        <v>17.898755801254076</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>18.239952227515158</v>
+        <v>18.22827094740283</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>18.576045159927332</v>
+        <v>18.564147105690957</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>18.918565766307168</v>
+        <v>18.906446792208278</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>19.26757660309228</v>
+        <v>19.255232523044608</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>17.728923046485182</v>
+        <v>17.717571371349344</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>18.146498110676173</v>
+        <v>18.134877106851633</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>18.576045159927343</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>19.017798961470028</v>
+        <v>19.005615983677856</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>19.471996594089838</v>
+        <v>19.459520666686217</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -19025,23 +19025,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>17.564788784291331</v>
+        <v>17.553542972913654</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>18.06102968049548</v>
+        <v>18.049463802329054</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>18.576045159927343</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>19.110386053492643</v>
+        <v>19.09814335862869</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>19.66461404519146</v>
+        <v>19.652013882865855</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -19056,23 +19056,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>17.416196103506145</v>
+        <v>17.405046131835615</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>17.982864557281729</v>
+        <v>17.971349094266838</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>18.576045159927343</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>19.196772162446777</v>
+        <v>19.184473750037778</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>19.846110396344944</v>
+        <v>19.833393172014326</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19088,23 +19088,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>17.281673399423472</v>
+        <v>17.270610192568654</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>17.911378670924584</v>
+        <v>17.89990931506906</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>18.576045159927343</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>19.277372596667256</v>
+        <v>19.265022198373284</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>20.017127743390272</v>
+        <v>20.004300215830895</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19119,23 +19119,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>17.159888410969884</v>
+        <v>17.148903753324671</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>17.84600127832082</v>
+        <v>17.834574089751928</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>18.576045159927343</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>19.352574849381053</v>
+        <v>19.340175946935737</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>20.178271109659303</v>
+        <v>20.165339647417881</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19151,23 +19151,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>17.049635026503815</v>
+        <v>17.038721480383234</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>17.786210406563104</v>
+        <v>17.774821782071587</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>18.576045159927343</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>19.422740461612868</v>
+        <v>19.410296303562138</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>20.330110586420883</v>
+        <v>20.317081190345096</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19183,23 +19183,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>16.949821338950233</v>
+        <v>16.938972170930477</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>17.731528685509858</v>
+        <v>17.720175329781952</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>18.576045159927343</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>19.488206760323379</v>
+        <v>19.475720377643125</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>20.473183349743575</v>
+        <v>20.460061674211861</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19215,23 +19215,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>16.575845987159241</v>
+        <v>16.565238026768338</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>17.520717729271638</v>
+        <v>17.50950034296163</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>18.57604515992734</v>
+        <v>18.564147105690964</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>19.755355481727818</v>
+        <v>19.742696792746269</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>21.07377402353017</v>
+        <v>21.060264977409343</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19247,23 +19247,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>16.348423275913731</v>
+        <v>16.33796199923518</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>17.385843298097274</v>
+        <v>17.374712903460868</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>18.576045159927343</v>
+        <v>18.564147105690964</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>19.944250473605539</v>
+        <v>19.931469950623764</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>21.519881927217217</v>
+        <v>21.506085149220077</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19279,23 +19279,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>16.210122477899741</v>
+        <v>16.199750402842092</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>17.29955218444163</v>
+        <v>17.288477446079934</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>18.576045159927343</v>
+        <v>18.564147105690964</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>20.077813972501961</v>
+        <v>20.06494730337522</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>21.851242819782062</v>
+        <v>21.837232319744665</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19311,23 +19311,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>16.126018693248877</v>
+        <v>16.115700863676594</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>17.244344119939729</v>
+        <v>17.233304989824052</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>18.576045159927343</v>
+        <v>18.564147105690967</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>20.172253788296572</v>
+        <v>20.159326207123272</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>22.097371705224099</v>
+        <v>22.083202456315767</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>19.26757660309228</v>
+        <v>19.255232523044608</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19402,7 +19402,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>18.918565766307168</v>
+        <v>18.906446792208278</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>18.576045159927332</v>
+        <v>18.564147105690957</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19458,7 +19458,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>18.239952227515158</v>
+        <v>18.22827094740283</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19486,7 +19486,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>17.910224412632971</v>
+        <v>17.898755801254076</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C8" s="447">
         <f>Normalized_FCF!G19</f>
-        <v>1207988284.9036756</v>
+        <v>1207985751.4787502</v>
       </c>
       <c r="D8" s="469"/>
       <c r="E8" s="469"/>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
-        <v>1109912418.6068106</v>
+        <v>1109912017.5761533</v>
       </c>
       <c r="D9" s="469"/>
       <c r="E9" s="469"/>
@@ -19764,7 +19764,7 @@
       </c>
       <c r="C14" s="249">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7243865678597534E-2</v>
+        <v>-7.7244252861532914E-2</v>
       </c>
       <c r="D14" s="469"/>
       <c r="E14" s="469"/>
@@ -19846,7 +19846,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>18.918565766307168</v>
+        <v>18.906446792208278</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>18.576045159927332</v>
+        <v>18.564147105690957</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>18.239952227515158</v>
+        <v>18.22827094740283</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19909,7 +19909,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>18.560526048100257</v>
+        <v>18.54863800342239</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>19.26757660309228</v>
+        <v>19.255232523044608</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>17.910224412632971</v>
+        <v>17.898755801254076</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -20004,7 +20004,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.60505487468433383</v>
+        <v>0.60466484323883052</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -20024,7 +20024,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.57</v>
+        <v>10.75</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20035,7 +20035,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.2562155514672021</v>
+        <v>0.24857571240316154</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20044,7 +20044,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>18.57604515992734</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.3578775508990376E-2</v>
+        <v>3.3578636971898314E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20064,7 +20064,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>18.634068549575694</v>
+        <v>18.622133071257309</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639727240930954</v>
+        <v>0.12639722903769574</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>401</v>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>18.635557324692481</v>
+        <v>18.623620886139907</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20234,7 +20234,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.34124097529785574</v>
+        <v>0.3412439175603596</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.60505487468433383</v>
+        <v>0.60466484323883052</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20308,15 +20308,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.1071606160742391</v>
+        <v>1.1064469164189523</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>8.5871283638597689</v>
+        <v>8.58162814343655</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>9.694288979934008</v>
+        <v>9.6880750598555032</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20324,7 +20324,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.47975457135716337</v>
+        <v>0.47975481526287933</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20333,15 +20333,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2730378446502357</v>
+        <v>1.272217216949338</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>10.763360895061778</v>
+        <v>10.756466755960904</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>12.036398739712014</v>
+        <v>12.028683972910242</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20349,7 +20349,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.35406491031793008</v>
+        <v>0.35406519076613485</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20379,15 +20379,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4597572820278413</v>
+        <v>1.4588162909432056</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>13.356162297058647</v>
+        <v>13.347607418928343</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>14.815919579086488</v>
+        <v>14.806423709871549</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.204901520048135</v>
+        <v>0.20490184163033343</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20404,15 +20404,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5806303657056273</v>
+        <v>1.5796114572195761</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>15.10482806769993</v>
+        <v>15.095153135603093</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>16.685458433405557</v>
+        <v>16.674764592822669</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20420,7 +20420,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.10457244541018429</v>
+        <v>0.10457279362053018</v>
       </c>
     </row>
   </sheetData>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>10.57</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20549,14 +20549,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>13041.69937</v>
+        <v>13263.79075</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.2562155514672021</v>
+        <v>0.24857571240316154</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20564,13 +20564,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20608,7 +20608,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1204719901561737</v>
+        <v>1.1197497097015381</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>18.634068549575694</v>
+        <v>18.622133071257309</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20686,7 +20686,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>9.694288979934008</v>
+        <v>9.6880750598555032</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>12.036398739712014</v>
+        <v>12.028683972910242</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20718,7 +20718,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>14.815919579086488</v>
+        <v>14.806423709871549</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>16.685458433405557</v>
+        <v>16.674764592822669</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20755,22 +20755,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
-        <v>11597154.163008198</v>
+        <v>11596619.455465142</v>
       </c>
       <c r="D44" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20909,7 +20909,7 @@
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
-        <v>-2559768.6664918009</v>
+        <v>-2560303.3740348574</v>
       </c>
       <c r="D46" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
-        <v>-389572632.20227021</v>
+        <v>-389572498.52538443</v>
       </c>
       <c r="D52" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20960,10 +20960,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20979,22 +20979,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21002,7 +21002,7 @@
       </c>
       <c r="C60" s="373">
         <f>Normalized_FCF!G19</f>
-        <v>1207988284.9036756</v>
+        <v>1207985751.4787502</v>
       </c>
       <c r="D60" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
-        <v>1109912418.6068106</v>
+        <v>1109912017.5761533</v>
       </c>
       <c r="D61" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21028,7 +21028,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>9.5357647902554368E-2</v>
+        <v>9.3700487507701824E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21038,14 +21038,14 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.7242656072311618E-2</v>
+        <v>5.6247892394309815E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
-        <v>0.74734776778600887</v>
+        <v>0.7468662811228971</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21065,11 +21065,11 @@
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
-        <v>0.10095735561257201</v>
+        <v>0.10095732097034157</v>
       </c>
       <c r="D66" s="378">
         <f>Normalized_FCF!G119</f>
-        <v>8.8891876231945069E-2</v>
+        <v>8.8891712098315062E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21079,11 +21079,11 @@
       </c>
       <c r="C67" s="383">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639727240930954</v>
+        <v>0.12639722903769574</v>
       </c>
       <c r="D67" s="383">
         <f>Normalized_FCF!G116</f>
-        <v>0.11129145198871108</v>
+        <v>0.11129124649557967</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21129,22 +21129,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21152,13 +21152,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25712284641630861</v>
+        <v>-0.25695709947391437</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,7 +21215,7 @@
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
-        <v>6701659721.0119677</v>
+        <v>6701748838.9358101</v>
       </c>
       <c r="D84" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0858911358527941</v>
+        <v>6.0820489162631111</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21272,7 +21272,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52993943618782413</v>
+        <v>0.52959782577697778</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,7 +21285,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.3587077256243099</v>
+        <v>6.354689642566175</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21307,33 +21307,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21396,23 +21396,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.748398139739767</v>
+        <v>1.7472710845216537</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21444,7 +21444,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>18.57604515992734</v>
+        <v>18.56414710569096</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21456,13 +21456,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>19.27 HKD</v>
+        <v>19.26 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21530,7 +21530,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>18.92 HKD</v>
+        <v>18.91 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21552,7 +21552,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>18.58 HKD</v>
+        <v>18.56 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>18.24 HKD</v>
+        <v>18.23 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21596,7 +21596,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>17.91 HKD</v>
+        <v>17.9 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21618,7 +21618,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>18.634068549575694</v>
+        <v>18.622133071257309</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21626,13 +21626,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21645,22 +21645,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="C136" s="406">
         <f>Scenarios!C58</f>
-        <v>0.60505487468433383</v>
+        <v>0.60466484323883052</v>
       </c>
       <c r="D136" s="343" t="str">
         <f>Market_currency</f>
@@ -21721,15 +21721,15 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>1.1071606160742391</v>
+        <v>1.1064469164189523</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>8.5871283638597689</v>
+        <v>8.58162814343655</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>9.694288979934008</v>
+        <v>9.6880750598555032</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21742,15 +21742,15 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>1.2730378446502357</v>
+        <v>1.272217216949338</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>10.763360895061778</v>
+        <v>10.756466755960904</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>12.036398739712014</v>
+        <v>12.028683972910242</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21782,15 +21782,15 @@
       </c>
       <c r="C144" s="409">
         <f>Scenarios!C66</f>
-        <v>1.4597572820278413</v>
+        <v>1.4588162909432056</v>
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>13.356162297058647</v>
+        <v>13.347607418928343</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>14.815919579086488</v>
+        <v>14.806423709871549</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21803,15 +21803,15 @@
       </c>
       <c r="C145" s="409">
         <f>Scenarios!C67</f>
-        <v>1.5806303657056273</v>
+        <v>1.5796114572195761</v>
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>15.10482806769993</v>
+        <v>15.095153135603093</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>16.685458433405557</v>
+        <v>16.674764592822669</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21829,13 +21829,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21843,13 +21843,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21886,22 +21886,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21925,15 +21925,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21948,12 +21945,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A48172-CB25-4BE1-A007-3FD2497E6F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94D98A2-5D18-45A7-A802-90E11AB3B390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2498,6 +2498,9 @@
     <t xml:space="preserve">Taxes = </t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -3265,9 +3268,6 @@
   </si>
   <si>
     <t>CNY</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5354,7 +5354,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F3" s="429">
         <v>45965</v>
@@ -5362,13 +5362,13 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C4" s="420" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E4" s="430" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F4" s="431" t="s">
         <v>324</v>
@@ -5379,13 +5379,13 @@
         <v>349</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E5" s="433" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F5" s="432" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5393,7 +5393,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
@@ -5435,11 +5435,11 @@
         <v>13263.79075</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.24857571240316154</v>
+        <v>0.24857571240316212</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5467,7 +5467,7 @@
         <v>319</v>
       </c>
       <c r="C15" s="417" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>353</v>
@@ -5482,18 +5482,18 @@
         <v>320</v>
       </c>
       <c r="C16" s="417" t="s">
-        <v>558</v>
+        <v>497</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1197497097015381</v>
+        <v>1.1197497097015401</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C17" s="456">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>274</v>
       </c>
       <c r="E17" s="224" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>18.622133071257309</v>
+        <v>18.622133071257338</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,13 +5562,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>9.6880750598555032</v>
+        <v>9.6880750598555174</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5577,13 +5577,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>12.028683972910242</v>
+        <v>12.028683972910262</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>14.806423709871549</v>
+        <v>14.80642370987157</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>16.674764592822669</v>
+        <v>16.674764592822694</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.3700487507701824E-2</v>
+        <v>9.3700487507701991E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,14 +5914,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6247892394309815E-2</v>
+        <v>5.6247892394309919E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
-        <v>0.7468662811228971</v>
+        <v>0.74686628112289843</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25695709947391437</v>
+        <v>-0.25695709947391487</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0820489162631111</v>
+        <v>6.0820489162631217</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52959782577697778</v>
+        <v>0.52959782577697867</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.354689642566175</v>
+        <v>6.3546896425661865</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7472710845216537</v>
+        <v>1.7472710845216568</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6355,7 +6355,7 @@
         <v>124</v>
       </c>
       <c r="F117" s="342" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="118" spans="2:6">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.0666251924560203E-2</v>
+        <v>2.0666251924560241E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.7102732808888481E-2</v>
+        <v>2.710273280888845E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.3578636971898473E-2</v>
+        <v>3.357863697189839E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.0093019351629719E-2</v>
+        <v>4.0093019351629663E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.6644864727009072E-2</v>
+        <v>4.6644864727008975E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>18.622133071257309</v>
+        <v>18.622133071257338</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.60466484323883052</v>
+        <v>0.60466484323883163</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6586,19 +6586,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>1.1064469164189523</v>
+        <v>1.1064469164189545</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>8.58162814343655</v>
+        <v>8.5816281434365624</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>9.6880750598555032</v>
+        <v>9.6880750598555174</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6607,19 +6607,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>1.272217216949338</v>
+        <v>1.2722172169493406</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>10.756466755960904</v>
+        <v>10.756466755960922</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>12.028683972910242</v>
+        <v>12.028683972910262</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6654,15 +6654,15 @@
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
-        <v>1.4588162909432056</v>
+        <v>1.4588162909432085</v>
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>13.347607418928343</v>
+        <v>13.347607418928362</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>14.806423709871549</v>
+        <v>14.80642370987157</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6675,15 +6675,15 @@
       </c>
       <c r="C145" s="333">
         <f>Scenarios!C67</f>
-        <v>1.5796114572195761</v>
+        <v>1.579611457219579</v>
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>15.095153135603093</v>
+        <v>15.095153135603116</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>16.674764592822669</v>
+        <v>16.674764592822694</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,6 +6797,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6813,18 +6825,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.67184982582092279</v>
+        <v>0.67184982582092401</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -7512,7 +7512,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.67184982582092279</v>
+        <v>0.67184982582092401</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10236,11 +10236,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.600542181043224</v>
+        <v>13.600542181043249</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7472710845216537</v>
+        <v>1.7472710845216568</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10646,11 +10646,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-317044204.57199401</v>
+        <v>-317044204.5719946</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.25695709947391437</v>
+        <v>-0.25695709947391487</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10663,11 +10663,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7504281316.8909931</v>
+        <v>7504281316.8910065</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>6.0820489162631111</v>
+        <v>6.0820489162631217</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10680,11 +10680,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>653439510.95449209</v>
+        <v>653439510.95449317</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.52959782577697778</v>
+        <v>0.52959782577697867</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10697,11 +10697,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>7840676623.2734909</v>
+        <v>7840676623.2735052</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.354689642566175</v>
+        <v>6.3546896425661856</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -13923,7 +13923,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="235" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.67184982582092279</v>
+        <v>0.67184982582092401</v>
       </c>
       <c r="E88" s="237"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.67184982582092279</v>
+        <v>0.67184982582092401</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14153,12 +14153,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>828955860.94071317</v>
+        <v>828955860.94071472</v>
       </c>
       <c r="E89" s="237"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>828955860.94071317</v>
+        <v>828955860.94071472</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.7468662811228971</v>
+        <v>0.74686628112289843</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.68622983336181798</v>
+        <v>0.6862298333618192</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14284,12 +14284,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6247892394309815E-2</v>
+        <v>5.6247892394309919E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.6247892394309815E-2</v>
+        <v>5.6247892394309919E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="C112" s="151"/>
       <c r="E112" s="451" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G112" s="251">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
@@ -15448,50 +15448,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0072802407077948</v>
+        <v>1.0072802407077965</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0962852543738819</v>
+        <v>1.0962852543738839</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3594234527831026</v>
+        <v>1.3594234527831051</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.287508352468582</v>
+        <v>1.2875083524685842</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1208754133012124</v>
+        <v>1.1208754133012144</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0430217305280087</v>
+        <v>1.0430217305280107</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.88493363840973305</v>
+        <v>0.8849336384097346</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.86241341249510317</v>
+        <v>0.86241341249510473</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63057223427275588</v>
+        <v>0.63057223427275699</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.51926489810693388</v>
+        <v>0.51926489810693488</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.48953938172837974</v>
+        <v>0.48953938172838063</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15505,50 +15505,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.3700487507701824E-2</v>
+        <v>9.3700487507701991E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10198002366268669</v>
+        <v>0.10198002366268688</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.12645799560773047</v>
+        <v>0.12645799560773072</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.11976821883428669</v>
+        <v>0.1197682188342869</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10426748030708953</v>
+        <v>0.10426748030708971</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.7025277258419418E-2</v>
+        <v>9.7025277258419598E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.2319408224161214E-2</v>
+        <v>8.2319408224161353E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.0224503487916571E-2</v>
+        <v>8.0224503487916723E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.8657882257930782E-2</v>
+        <v>5.8657882257930886E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.8303711451807806E-2</v>
+        <v>4.8303711451807896E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.5538547137523699E-2</v>
+        <v>4.5538547137523783E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.354689642566175</v>
+        <v>6.3546896425661865</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16512,7 +16512,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1197497097015381</v>
+        <v>1.1197497097015401</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16537,7 +16537,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>22905205829.032841</v>
+        <v>22905205829.032879</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16595,7 +16595,7 @@
         <v>399</v>
       </c>
       <c r="F14" s="309" t="str">
-        <f>IF(ROUND(F17,2)=ROUND(C17,2),"I","II")</f>
+        <f>IF(ROUND(F17,4)=ROUND(C17,4),"I","II")</f>
         <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
@@ -16645,14 +16645,14 @@
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
         <v>0.12639722903769574</v>
       </c>
       <c r="E17" s="308" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>18.623620886139907</v>
+        <v>18.623620886139943</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16706,26 +16706,26 @@
         <v>102</v>
       </c>
       <c r="E20" s="121" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F20" s="121" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G20" s="121" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="H20" s="121" t="s">
+        <v>553</v>
+      </c>
+      <c r="I20" s="121" t="s">
+        <v>530</v>
+      </c>
+      <c r="J20" s="121" t="s">
         <v>552</v>
       </c>
-      <c r="I20" s="121" t="s">
-        <v>529</v>
-      </c>
-      <c r="J20" s="121" t="s">
-        <v>551</v>
-      </c>
       <c r="K20" s="121" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L20" s="122" t="s">
         <v>419</v>
@@ -18870,23 +18870,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18901,23 +18901,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>18.319957956428464</v>
+        <v>18.319957956428496</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>18.442052531059709</v>
+        <v>18.442052531059744</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690957</v>
+        <v>18.564147105690989</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>18.686241680322205</v>
+        <v>18.686241680322237</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>18.80833625495346</v>
+        <v>18.808336254953492</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18932,23 +18932,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>18.09889064347027</v>
+        <v>18.098890643470302</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>18.330390980126747</v>
+        <v>18.330390980126779</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>18.800159020162912</v>
+        <v>18.800159020162944</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>19.038426723542599</v>
+        <v>19.038426723542631</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18963,23 +18963,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>17.898755801254076</v>
+        <v>17.898755801254108</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>18.22827094740283</v>
+        <v>18.228270947402862</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690957</v>
+        <v>18.564147105690989</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>18.906446792208278</v>
+        <v>18.90644679220831</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>19.255232523044608</v>
+        <v>19.25523252304464</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>17.717571371349344</v>
+        <v>17.717571371349376</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>18.134877106851633</v>
+        <v>18.134877106851665</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>19.005615983677856</v>
+        <v>19.005615983677892</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>19.459520666686217</v>
+        <v>19.459520666686252</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -19025,23 +19025,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>17.553542972913654</v>
+        <v>17.553542972913686</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>18.049463802329054</v>
+        <v>18.049463802329086</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>19.09814335862869</v>
+        <v>19.098143358628725</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>19.652013882865855</v>
+        <v>19.652013882865887</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -19056,23 +19056,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>17.405046131835615</v>
+        <v>17.405046131835643</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>17.971349094266838</v>
+        <v>17.97134909426687</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>19.184473750037778</v>
+        <v>19.184473750037814</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>19.833393172014326</v>
+        <v>19.833393172014361</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19088,23 +19088,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>17.270610192568654</v>
+        <v>17.270610192568686</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>17.89990931506906</v>
+        <v>17.899909315069092</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>19.265022198373284</v>
+        <v>19.26502219837332</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>20.004300215830895</v>
+        <v>20.004300215830931</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19119,23 +19119,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>17.148903753324671</v>
+        <v>17.148903753324703</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>17.834574089751928</v>
+        <v>17.83457408975196</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>19.340175946935737</v>
+        <v>19.340175946935769</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>20.165339647417881</v>
+        <v>20.165339647417916</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19151,23 +19151,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>17.038721480383234</v>
+        <v>17.038721480383263</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>17.774821782071587</v>
+        <v>17.774821782071619</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>19.410296303562138</v>
+        <v>19.410296303562173</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>20.317081190345096</v>
+        <v>20.317081190345132</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19183,23 +19183,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>16.938972170930477</v>
+        <v>16.938972170930505</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>17.720175329781952</v>
+        <v>17.720175329781984</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>19.475720377643125</v>
+        <v>19.47572037764316</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>20.460061674211861</v>
+        <v>20.460061674211897</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19215,23 +19215,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>16.565238026768338</v>
+        <v>16.565238026768366</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>17.50950034296163</v>
+        <v>17.509500342961662</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690964</v>
+        <v>18.564147105690996</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>19.742696792746269</v>
+        <v>19.742696792746305</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>21.060264977409343</v>
+        <v>21.060264977409382</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19247,23 +19247,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>16.33796199923518</v>
+        <v>16.337961999235208</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>17.374712903460868</v>
+        <v>17.3747129034609</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690964</v>
+        <v>18.564147105690996</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>19.931469950623764</v>
+        <v>19.9314699506238</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>21.506085149220077</v>
+        <v>21.506085149220116</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19279,23 +19279,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>16.199750402842092</v>
+        <v>16.19975040284212</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>17.288477446079934</v>
+        <v>17.288477446079966</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690964</v>
+        <v>18.564147105690996</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>20.06494730337522</v>
+        <v>20.064947303375256</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>21.837232319744665</v>
+        <v>21.837232319744704</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19311,23 +19311,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>16.115700863676594</v>
+        <v>16.115700863676622</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>17.233304989824052</v>
+        <v>17.233304989824084</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690967</v>
+        <v>18.564147105690999</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>20.159326207123272</v>
+        <v>20.159326207123307</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>22.083202456315767</v>
+        <v>22.083202456315806</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>19.255232523044608</v>
+        <v>19.25523252304464</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19402,7 +19402,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>18.906446792208278</v>
+        <v>18.90644679220831</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>18.564147105690957</v>
+        <v>18.564147105690989</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19458,7 +19458,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>18.22827094740283</v>
+        <v>18.228270947402862</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19486,7 +19486,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>17.898755801254076</v>
+        <v>17.898755801254108</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19631,7 +19631,7 @@
         <v>125</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E3" s="97"/>
     </row>
@@ -19797,7 +19797,7 @@
         <v>3</v>
       </c>
       <c r="E18" s="450" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F18" s="319"/>
     </row>
@@ -19846,7 +19846,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>18.906446792208278</v>
+        <v>18.90644679220831</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>18.564147105690957</v>
+        <v>18.564147105690989</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>18.22827094740283</v>
+        <v>18.228270947402862</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19909,7 +19909,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>18.54863800342239</v>
+        <v>18.548638003422422</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>19.255232523044608</v>
+        <v>19.25523252304464</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>17.898755801254076</v>
+        <v>17.898755801254108</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -20004,7 +20004,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.60466484323883052</v>
+        <v>0.60466484323883163</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -20035,7 +20035,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.24857571240316154</v>
+        <v>0.24857571240316212</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20044,7 +20044,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.3578636971898314E-2</v>
+        <v>3.3578636971898279E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20064,7 +20064,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>18.622133071257309</v>
+        <v>18.622133071257338</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20098,7 +20098,7 @@
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>18.623620886139907</v>
+        <v>18.623620886139943</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20234,7 +20234,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.3412439175603596</v>
+        <v>0.34124391756035966</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.60466484323883052</v>
+        <v>0.60466484323883163</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20308,19 +20308,19 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.1064469164189523</v>
+        <v>1.1064469164189545</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>8.58162814343655</v>
+        <v>8.5816281434365624</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>9.6880750598555032</v>
+        <v>9.6880750598555174</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
@@ -20333,23 +20333,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.272217216949338</v>
+        <v>1.2722172169493406</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>10.756466755960904</v>
+        <v>10.756466755960922</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>12.028683972910242</v>
+        <v>12.028683972910262</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.35406519076613485</v>
+        <v>0.35406519076613474</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20379,15 +20379,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4588162909432056</v>
+        <v>1.4588162909432085</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>13.347607418928343</v>
+        <v>13.347607418928362</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>14.806423709871549</v>
+        <v>14.80642370987157</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.20490184163033343</v>
+        <v>0.20490184163033354</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20404,15 +20404,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5796114572195761</v>
+        <v>1.579611457219579</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>15.095153135603093</v>
+        <v>15.095153135603116</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>16.674764592822669</v>
+        <v>16.674764592822694</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20464,7 +20464,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F3" s="436">
         <f>Thesis!F3</f>
@@ -20473,7 +20473,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C4" s="423" t="str">
         <f>Thesis!C4</f>
@@ -20481,7 +20481,7 @@
       </c>
       <c r="D4" s="349"/>
       <c r="E4" s="434" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F4" s="437" t="str">
         <f>Thesis!F4</f>
@@ -20497,7 +20497,7 @@
         <v>0811.HK</v>
       </c>
       <c r="E5" s="438" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F5" s="439" t="str">
         <f>Thesis!F5</f>
@@ -20552,11 +20552,11 @@
         <v>13263.79075</v>
       </c>
       <c r="D10" s="343" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.24857571240316154</v>
+        <v>0.24857571240316212</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20564,13 +20564,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
-        <v>497</v>
-      </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="B12" s="471" t="s">
+        <v>498</v>
+      </c>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20608,12 +20608,12 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1197497097015381</v>
+        <v>1.1197497097015401</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C17" s="424">
         <f>Terminal_Growth</f>
@@ -20634,7 +20634,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>18.622133071257309</v>
+        <v>18.622133071257338</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20686,14 +20686,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>9.6880750598555032</v>
+        <v>9.6880750598555174</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20702,14 +20702,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>12.028683972910242</v>
+        <v>12.028683972910262</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20718,7 +20718,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>14.806423709871549</v>
+        <v>14.80642370987157</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>16.674764592822669</v>
+        <v>16.674764592822694</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20755,22 +20755,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
-        <v>498</v>
-      </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="B29" s="471" t="s">
+        <v>499</v>
+      </c>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
-        <v>499</v>
-      </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="B30" s="472" t="s">
+        <v>500</v>
+      </c>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20783,7 +20783,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="470" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C33" s="470"/>
       <c r="D33" s="470"/>
@@ -20809,7 +20809,7 @@
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="470" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C36" s="470"/>
       <c r="D36" s="470"/>
@@ -20844,7 +20844,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="470" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C40" s="470"/>
       <c r="D40" s="470"/>
@@ -20866,7 +20866,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="470" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C43" s="470"/>
       <c r="D43" s="470"/>
@@ -20918,7 +20918,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20936,7 +20936,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="470" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C51" s="470"/>
       <c r="D51" s="470"/>
@@ -20958,12 +20958,12 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
-        <v>506</v>
-      </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+        <v>507</v>
+      </c>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20979,22 +20979,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
-        <v>507</v>
-      </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="B57" s="471" t="s">
+        <v>508</v>
+      </c>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
-        <v>508</v>
-      </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="B58" s="471" t="s">
+        <v>509</v>
+      </c>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21028,7 +21028,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>9.3700487507701824E-2</v>
+        <v>9.3700487507701991E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21038,14 +21038,14 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.6247892394309815E-2</v>
+        <v>5.6247892394309919E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
-        <v>0.7468662811228971</v>
+        <v>0.74686628112289843</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21129,22 +21129,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
-        <v>509</v>
-      </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="B73" s="471" t="s">
+        <v>510</v>
+      </c>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21152,13 +21152,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
-        <v>510</v>
-      </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="B77" s="471" t="s">
+        <v>511</v>
+      </c>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25695709947391437</v>
+        <v>-0.25695709947391487</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21206,7 +21206,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0820489162631111</v>
+        <v>6.0820489162631217</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21250,7 +21250,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="343" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -21272,7 +21272,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52959782577697778</v>
+        <v>0.52959782577697867</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,7 +21285,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.354689642566175</v>
+        <v>6.3546896425661865</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21307,33 +21307,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
-        <v>513</v>
-      </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="B96" s="471" t="s">
+        <v>514</v>
+      </c>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
-        <v>514</v>
-      </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="B97" s="472" t="s">
+        <v>515</v>
+      </c>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
-        <v>515</v>
-      </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="B98" s="472" t="s">
+        <v>516</v>
+      </c>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21377,7 +21377,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C104" s="368">
         <v>0</v>
@@ -21396,23 +21396,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
-        <v>516</v>
-      </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="B107" s="471" t="s">
+        <v>517</v>
+      </c>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
-        <v>535</v>
-      </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="B108" s="471" t="s">
+        <v>536</v>
+      </c>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.7472710845216537</v>
+        <v>1.7472710845216568</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21444,7 +21444,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>18.56414710569096</v>
+        <v>18.564147105690992</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21456,13 +21456,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
-        <v>517</v>
-      </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="B114" s="471" t="s">
+        <v>518</v>
+      </c>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21605,7 +21605,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="470" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C124" s="470"/>
       <c r="D124" s="470"/>
@@ -21618,7 +21618,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>18.622133071257309</v>
+        <v>18.622133071257338</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21626,13 +21626,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
-        <v>519</v>
-      </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="B127" s="475" t="s">
+        <v>520</v>
+      </c>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21645,22 +21645,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
-        <v>520</v>
-      </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="B131" s="476" t="s">
+        <v>521</v>
+      </c>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
-        <v>521</v>
-      </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="B132" s="471" t="s">
+        <v>522</v>
+      </c>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="C136" s="406">
         <f>Scenarios!C58</f>
-        <v>0.60466484323883052</v>
+        <v>0.60466484323883163</v>
       </c>
       <c r="D136" s="343" t="str">
         <f>Market_currency</f>
@@ -21721,19 +21721,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>1.1064469164189523</v>
+        <v>1.1064469164189545</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>8.58162814343655</v>
+        <v>8.5816281434365624</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>9.6880750598555032</v>
+        <v>9.6880750598555174</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21742,19 +21742,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>1.272217216949338</v>
+        <v>1.2722172169493406</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>10.756466755960904</v>
+        <v>10.756466755960922</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>12.028683972910242</v>
+        <v>12.028683972910262</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21782,15 +21782,15 @@
       </c>
       <c r="C144" s="409">
         <f>Scenarios!C66</f>
-        <v>1.4588162909432056</v>
+        <v>1.4588162909432085</v>
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>13.347607418928343</v>
+        <v>13.347607418928362</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>14.806423709871549</v>
+        <v>14.80642370987157</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21803,15 +21803,15 @@
       </c>
       <c r="C145" s="409">
         <f>Scenarios!C67</f>
-        <v>1.5796114572195761</v>
+        <v>1.579611457219579</v>
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>15.095153135603093</v>
+        <v>15.095153135603116</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>16.674764592822669</v>
+        <v>16.674764592822694</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21829,13 +21829,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
-        <v>522</v>
-      </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="B149" s="477" t="s">
+        <v>523</v>
+      </c>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21843,13 +21843,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
-        <v>523</v>
-      </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="B152" s="473" t="s">
+        <v>524</v>
+      </c>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21868,7 +21868,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="343" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
@@ -21882,30 +21882,30 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="165" spans="2:6">
@@ -21925,12 +21925,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21945,15 +21948,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94D98A2-5D18-45A7-A802-90E11AB3B390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253C35C1-D231-4D5F-BCC1-C79542D72FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.75</v>
+        <v>10.85</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>13263.79075</v>
+        <v>13387.174849999999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.24857571240316212</v>
+        <v>0.24453329278037109</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1197497097015401</v>
+        <v>1.1196808250427246</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>18.622133071257338</v>
+        <v>18.620994766784168</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,13 +5562,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>9.6880750598555174</v>
+        <v>9.6874824292833566</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5577,13 +5577,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>12.028683972910262</v>
+        <v>12.027948204380639</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>14.80642370987157</v>
+        <v>14.80551807498469</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>16.674764592822694</v>
+        <v>16.67374470564285</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
-        <v>11596619.455465142</v>
+        <v>11596568.459835352</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
-        <v>-2560303.3740348574</v>
+        <v>-2560354.3696646467</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
-        <v>-389572498.52538443</v>
+        <v>-389572485.77647698</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="C60" s="285">
         <f>Normalized_FCF!G19</f>
-        <v>1207985751.4787502</v>
+        <v>1207985509.863308</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
-        <v>1109912017.5761533</v>
+        <v>1109911979.3294311</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.3700487507701991E-2</v>
+        <v>9.2831174214504319E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,14 +5914,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.6247892394309919E-2</v>
+        <v>5.5726050278624088E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
-        <v>0.74686628112289843</v>
+        <v>0.74682036120712814</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5941,11 +5941,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
-        <v>0.10095732097034157</v>
+        <v>0.10095731766647505</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.8891712098315062E-2</v>
+        <v>8.8891696444715382E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5955,11 +5955,11 @@
       </c>
       <c r="C67" s="263">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639722903769574</v>
+        <v>0.12639722490129859</v>
       </c>
       <c r="D67" s="263">
         <f>Normalized_FCF!G116</f>
-        <v>0.11129124649557967</v>
+        <v>0.11129122689748014</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25695709947391487</v>
+        <v>-0.25694129201089511</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
-        <v>6701748838.9358101</v>
+        <v>6701757338.2074413</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0820489162631217</v>
+        <v>6.0816824742249942</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52959782577697867</v>
+        <v>0.52956524602703814</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.3546896425661865</v>
+        <v>6.3543064282411379</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7472710845216568</v>
+        <v>1.7471635960610905</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>19.26 HKD</v>
+        <v>19.25 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.0666251924560241E-2</v>
+        <v>2.0666244412966515E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.710273280888845E-2</v>
+        <v>2.710272248992621E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.357863697189839E-2</v>
+        <v>3.3578623759527394E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.0093019351629663E-2</v>
+        <v>4.0093003158148392E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.6644864727008975E-2</v>
+        <v>4.6644845463086483E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>18.622133071257338</v>
+        <v>18.620994766784168</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.60466484323883163</v>
+        <v>0.60462764552307136</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6586,19 +6586,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>1.1064469164189545</v>
+        <v>1.1063788501201428</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>8.5816281434365624</v>
+        <v>8.581103579163214</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>9.6880750598555174</v>
+        <v>9.6874824292833566</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6607,19 +6607,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>1.2722172169493406</v>
+        <v>1.2721389528085512</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>10.756466755960922</v>
+        <v>10.755809251572087</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>12.028683972910262</v>
+        <v>12.027948204380639</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6654,15 +6654,15 @@
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
-        <v>1.4588162909432085</v>
+        <v>1.4587265476178874</v>
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>13.347607418928362</v>
+        <v>13.346791527366802</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>14.80642370987157</v>
+        <v>14.80551807498469</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6675,15 +6675,15 @@
       </c>
       <c r="C145" s="333">
         <f>Scenarios!C67</f>
-        <v>1.579611457219579</v>
+        <v>1.5795142828284194</v>
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>15.095153135603116</v>
+        <v>15.094230422814432</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>16.674764592822694</v>
+        <v>16.67374470564285</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,18 +6797,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6825,6 +6813,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.67184982582092401</v>
+        <v>0.67180849502563478</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.67184982582092401</v>
+        <v>0.67180849502563478</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10236,11 +10236,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.600542181043249</v>
+        <v>13.59970550415043</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7472710845216568</v>
+        <v>1.7471635960610905</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6701748838.9358101</v>
+        <v>6701757338.2074413</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C73" s="285">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-985659712.78339279</v>
+        <v>-985655463.14757693</v>
       </c>
       <c r="D73" s="285">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-966384954.62209511</v>
+        <v>-966380704.98627937</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10514,11 +10514,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7601416961611278</v>
+        <v>8.7601794653546197</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9348646280989854</v>
+        <v>8.9349039189504431</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10531,7 +10531,7 @@
       <c r="C75" s="261"/>
       <c r="D75" s="262">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1932769909.2441902</v>
+        <v>1932761409.9725587</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10646,11 +10646,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-317044204.5719946</v>
+        <v>-317024700.67601484</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.25695709947391487</v>
+        <v>-0.25694129201089511</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10663,11 +10663,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7504281316.8910065</v>
+        <v>7503829185.6802416</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>6.0820489162631217</v>
+        <v>6.0816824742249942</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10680,11 +10680,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>653439510.95449317</v>
+        <v>653399312.72324681</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.52959782577697867</v>
+        <v>0.52956524602703814</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10697,11 +10697,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>7840676623.2735052</v>
+        <v>7840203797.7274733</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.3546896425661856</v>
+        <v>6.3543064282411379</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11182,36 +11182,36 @@
       </c>
       <c r="C10" s="266">
         <f>C48</f>
-        <v>-2560303.3740348574</v>
+        <v>-2560354.3696646467</v>
       </c>
       <c r="E10" s="237"/>
       <c r="G10" s="266">
         <f>G48</f>
-        <v>42502478.938749373</v>
+        <v>42502237.323306948</v>
       </c>
       <c r="H10" s="266">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40976487.812495545</v>
+        <v>40976229.013627343</v>
       </c>
       <c r="I10" s="266">
         <f t="shared" si="6"/>
-        <v>17729593.736511134</v>
+        <v>17729423.520732909</v>
       </c>
       <c r="J10" s="266">
         <f t="shared" si="6"/>
-        <v>5079895.5317816101</v>
+        <v>5079787.496219717</v>
       </c>
       <c r="K10" s="266">
         <f t="shared" si="6"/>
-        <v>-4689932.4491716772</v>
+        <v>-4690009.2904260047</v>
       </c>
       <c r="L10" s="266">
         <f t="shared" si="6"/>
-        <v>-6414218.657149151</v>
+        <v>-6414275.9388721753</v>
       </c>
       <c r="M10" s="266">
         <f t="shared" si="6"/>
-        <v>7541556.083095436</v>
+        <v>7541520.6485311836</v>
       </c>
       <c r="N10" s="266">
         <f t="shared" si="6"/>
@@ -11237,36 +11237,36 @@
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
-        <v>1558289994.1015377</v>
+        <v>1558289943.1059079</v>
       </c>
       <c r="E11" s="237"/>
       <c r="G11" s="267">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1372055678.4787502</v>
+        <v>1372055436.863308</v>
       </c>
       <c r="H11" s="267">
         <f t="shared" si="7"/>
-        <v>1481961156.1324952</v>
+        <v>1481960897.333627</v>
       </c>
       <c r="I11" s="267">
         <f t="shared" si="7"/>
-        <v>1407257092.7365112</v>
+        <v>1407256922.5207329</v>
       </c>
       <c r="J11" s="267">
         <f t="shared" si="7"/>
-        <v>1240534213.5317817</v>
+        <v>1240534105.4962196</v>
       </c>
       <c r="K11" s="267">
         <f t="shared" si="7"/>
-        <v>1157465758.5508282</v>
+        <v>1157465681.709574</v>
       </c>
       <c r="L11" s="267">
         <f t="shared" si="7"/>
-        <v>999271595.92285287</v>
+        <v>999271538.64112985</v>
       </c>
       <c r="M11" s="267">
         <f t="shared" si="7"/>
-        <v>939488862.85309446</v>
+        <v>939488827.41853023</v>
       </c>
       <c r="N11" s="267">
         <f t="shared" si="7"/>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
-        <v>-389572498.52538443</v>
+        <v>-389572485.77647698</v>
       </c>
       <c r="E12" s="237"/>
       <c r="G12" s="266">
@@ -11404,38 +11404,38 @@
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
-        <v>1109912017.5761533</v>
+        <v>1109911979.3294311</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="243"/>
       <c r="F14" s="58"/>
       <c r="G14" s="267">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207985751.4787502</v>
+        <v>1207985509.863308</v>
       </c>
       <c r="H14" s="267">
         <f t="shared" si="8"/>
-        <v>1497935099.1324952</v>
+        <v>1497934840.333627</v>
       </c>
       <c r="I14" s="267">
         <f t="shared" si="8"/>
-        <v>1418692569.7365112</v>
+        <v>1418692399.5207329</v>
       </c>
       <c r="J14" s="267">
         <f t="shared" si="8"/>
-        <v>1235081401.5317817</v>
+        <v>1235081293.4962196</v>
       </c>
       <c r="K14" s="267">
         <f t="shared" si="8"/>
-        <v>1149295207.5508282</v>
+        <v>1149295130.709574</v>
       </c>
       <c r="L14" s="267">
         <f t="shared" si="8"/>
-        <v>975099520.80285287</v>
+        <v>975099463.52112985</v>
       </c>
       <c r="M14" s="267">
         <f t="shared" si="8"/>
-        <v>950284709.22309446</v>
+        <v>950284673.78853023</v>
       </c>
       <c r="N14" s="267">
         <f t="shared" si="8"/>
@@ -11622,38 +11622,38 @@
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
-        <v>1109912017.5761533</v>
+        <v>1109911979.3294311</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="234"/>
       <c r="F19" s="26"/>
       <c r="G19" s="271">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207985751.4787502</v>
+        <v>1207985509.863308</v>
       </c>
       <c r="H19" s="271">
         <f t="shared" si="9"/>
-        <v>1497935099.1324952</v>
+        <v>1497934840.333627</v>
       </c>
       <c r="I19" s="271">
         <f t="shared" si="9"/>
-        <v>1418692569.7365112</v>
+        <v>1418692399.5207329</v>
       </c>
       <c r="J19" s="271">
         <f t="shared" si="9"/>
-        <v>1235081401.5317817</v>
+        <v>1235081293.4962196</v>
       </c>
       <c r="K19" s="271">
         <f t="shared" si="9"/>
-        <v>1149295207.5508282</v>
+        <v>1149295130.709574</v>
       </c>
       <c r="L19" s="271">
         <f t="shared" si="9"/>
-        <v>975099520.80285287</v>
+        <v>975099463.52112985</v>
       </c>
       <c r="M19" s="271">
         <f t="shared" si="9"/>
-        <v>950284709.22309446</v>
+        <v>950284673.78853023</v>
       </c>
       <c r="N19" s="271">
         <f t="shared" si="9"/>
@@ -12361,31 +12361,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.6720245869840109E-2</v>
+        <v>7.6720259380078565E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.3981074490573709E-2</v>
+        <v>-4.3981082171108542E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.1260752274930122E-3</v>
+        <v>-8.1260762103883156E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3955353592997071E-3</v>
+        <v>4.3955357420978353E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.0590001817675404E-3</v>
+        <v>7.0590006503969223E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4189694992457454E-2</v>
+        <v>2.4189696379094974E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491191430640854E-2</v>
+        <v>-1.1491191864052459E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12499,36 +12499,36 @@
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
-        <v>11596619.455465142</v>
+        <v>11596568.459835352</v>
       </c>
       <c r="E46" s="237"/>
       <c r="G46" s="274">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54944361.938749373</v>
+        <v>54944120.323306948</v>
       </c>
       <c r="H46" s="274">
         <f t="shared" si="17"/>
-        <v>58851944.812495545</v>
+        <v>58851686.013627343</v>
       </c>
       <c r="I46" s="274">
         <f t="shared" si="17"/>
-        <v>38707779.736511134</v>
+        <v>38707609.520732909</v>
       </c>
       <c r="J46" s="274">
         <f t="shared" si="17"/>
-        <v>24567738.53178161</v>
+        <v>24567630.496219717</v>
       </c>
       <c r="K46" s="274">
         <f t="shared" si="17"/>
-        <v>17474022.550828323</v>
+        <v>17473945.709573995</v>
       </c>
       <c r="L46" s="274">
         <f t="shared" si="17"/>
-        <v>13026103.342850849</v>
+        <v>13026046.061127825</v>
       </c>
       <c r="M46" s="274">
         <f t="shared" si="17"/>
-        <v>8057968.083095436</v>
+        <v>8057932.6485311836</v>
       </c>
       <c r="N46" s="274">
         <f t="shared" si="17"/>
@@ -12611,36 +12611,36 @@
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
-        <v>-2560303.3740348574</v>
+        <v>-2560354.3696646467</v>
       </c>
       <c r="E48" s="237"/>
       <c r="G48" s="267">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42502478.938749373</v>
+        <v>42502237.323306948</v>
       </c>
       <c r="H48" s="267">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40976487.812495545</v>
+        <v>40976229.013627343</v>
       </c>
       <c r="I48" s="267">
         <f t="shared" si="18"/>
-        <v>17729593.736511134</v>
+        <v>17729423.520732909</v>
       </c>
       <c r="J48" s="267">
         <f t="shared" si="18"/>
-        <v>5079895.5317816101</v>
+        <v>5079787.496219717</v>
       </c>
       <c r="K48" s="267">
         <f t="shared" si="18"/>
-        <v>-4689932.4491716772</v>
+        <v>-4690009.2904260047</v>
       </c>
       <c r="L48" s="267">
         <f t="shared" si="18"/>
-        <v>-6414218.657149151</v>
+        <v>-6414275.9388721753</v>
       </c>
       <c r="M48" s="267">
         <f t="shared" si="18"/>
-        <v>7541556.083095436</v>
+        <v>7541520.6485311836</v>
       </c>
       <c r="N48" s="267">
         <f t="shared" si="18"/>
@@ -13576,38 +13576,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0767331703265907E-4</v>
+        <v>2.0767745342981415E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="234"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.4474941027830878E-3</v>
+        <v>3.4474745046835487E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4525442027725731E-3</v>
+        <v>3.4525223972304247E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.6220588366696986E-3</v>
+        <v>1.6220432638364283E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8563276952424739E-4</v>
+        <v>4.8562244143604143E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2063754496402747E-4</v>
+        <v>5.2064607524510045E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.2538867105829117E-4</v>
+        <v>7.2539514909017021E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.2120926566603776E-4</v>
+        <v>9.2120493729553254E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13633,38 +13633,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639722903769574</v>
+        <v>0.12639722490129859</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="234"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.11129124649557967</v>
+        <v>0.11129122689748014</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12486517687294635</v>
+        <v>0.1248651550674042</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.1287482294666811</v>
+        <v>0.12874821389384783</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11859379037185344</v>
+        <v>0.11859378004376522</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12849228372537905</v>
+        <v>0.12849227519509798</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300835436672589</v>
+        <v>0.11300834788869402</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11475958488066949</v>
+        <v>0.11475958055229898</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1599307259423934E-2</v>
+        <v>3.1599306225324648E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="234"/>
@@ -13805,38 +13805,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.0028046145641097E-2</v>
+        <v>9.0028043043343234E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="234"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.7983079068647103E-2</v>
+        <v>9.798305947054757E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12621108881523954</v>
+        <v>0.12621106700969739</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12979444726473388</v>
+        <v>0.12979443169190061</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11807250717288058</v>
+        <v>0.11807249684479236</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758525667120588</v>
+        <v>0.12758524814092481</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11027471674299524</v>
+        <v>0.11027471026496337</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607830923903414</v>
+        <v>0.11607830491066363</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14028,38 +14028,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.0028046145641097E-2</v>
+        <v>9.0028043043343234E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="234"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.7983079068647103E-2</v>
+        <v>9.798305947054757E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12621108881523954</v>
+        <v>0.12621106700969739</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12979444726473388</v>
+        <v>0.12979443169190061</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11807250717288058</v>
+        <v>0.11807249684479236</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758525667120588</v>
+        <v>0.12758524814092481</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11027471674299524</v>
+        <v>0.11027471026496337</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607830923903414</v>
+        <v>0.11607830491066363</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.67184982582092401</v>
+        <v>0.67180849502563478</v>
       </c>
       <c r="E88" s="237"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.67184982582092401</v>
+        <v>0.67180849502563478</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14153,12 +14153,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>828955860.94071472</v>
+        <v>828904865.31092429</v>
       </c>
       <c r="E89" s="237"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>828955860.94071472</v>
+        <v>828904865.31092429</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.74686628112289843</v>
+        <v>0.74682036120712814</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.6862298333618192</v>
+        <v>0.6861877551865011</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14284,12 +14284,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.6247892394309919E-2</v>
+        <v>5.5726050278624088E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.6247892394309919E-2</v>
+        <v>5.5726050278624088E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14421,38 +14421,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.13573378875503983</v>
+        <v>0.13573395158752155</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="234"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.416218515508699E-2</v>
+        <v>-7.4162186511171124E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.308487253790739E-2</v>
+        <v>5.308481601147963E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.13439603469707784</v>
+        <v>0.13439599627760601</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1767526915834656E-2</v>
+        <v>7.1767504729776332E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830947589566868</v>
+        <v>0.15830946539672897</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3633253605803075E-2</v>
+        <v>6.3633232751545199E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35104165995181025</v>
+        <v>0.35104160899476922</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -15037,31 +15037,31 @@
       </c>
       <c r="G113" s="251">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4673011083369387</v>
+        <v>1.4673014018194377</v>
       </c>
       <c r="H113" s="251">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5708479041333088</v>
+        <v>1.5708481755293993</v>
       </c>
       <c r="I113" s="251">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.4269343254373859</v>
+        <v>1.4269344966420365</v>
       </c>
       <c r="J113" s="251">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.6576474833649393</v>
+        <v>1.6576476283633927</v>
       </c>
       <c r="K113" s="251">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.5825396974167425</v>
+        <v>1.5825398032244955</v>
       </c>
       <c r="L113" s="251">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3992525793640078</v>
+        <v>1.3992526615623904</v>
       </c>
       <c r="M113" s="251">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.0454238212274252</v>
+        <v>1.0454238602095729</v>
       </c>
       <c r="N113" s="251">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15150,39 +15150,39 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639722903769574</v>
+        <v>0.12639722490129859</v>
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
-        <v>0.12639722903769574</v>
+        <v>0.12639722490129859</v>
       </c>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.11129124649557967</v>
+        <v>0.11129122689748014</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12486517687294635</v>
+        <v>0.1248651550674042</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.1287482294666811</v>
+        <v>0.12874821389384783</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11859379037185344</v>
+        <v>0.11859378004376522</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12849228372537905</v>
+        <v>0.12849227519509798</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300835436672589</v>
+        <v>0.11300834788869402</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11475958488066949</v>
+        <v>0.11475958055229898</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15324,41 +15324,41 @@
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
-        <v>0.10095732097034157</v>
+        <v>0.10095731766647505</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
         <f>C11/C104</f>
-        <v>0.10095732097034157</v>
+        <v>0.10095731766647505</v>
       </c>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.8891712098315062E-2</v>
+        <v>8.8891696444715382E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.1104774044107478</v>
+        <v>0.1104773851177811</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11113989773412754</v>
+        <v>0.11113988429112248</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11166237531715686</v>
+        <v>0.11166236559271127</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11542166367561912</v>
+        <v>0.11542165601306381</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.10956965850300746</v>
+        <v>0.10956965222209358</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176369038165652</v>
+        <v>0.11176368616628174</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15448,50 +15448,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0072802407077965</v>
+        <v>1.0072182402273719</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0962852543738839</v>
+        <v>1.0962175939390935</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3594234527831051</v>
+        <v>1.3593395890434807</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2875083524685842</v>
+        <v>1.2874289931824414</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1208754133012144</v>
+        <v>1.1208063613518133</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0430217305280107</v>
+        <v>1.0429574962823263</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.8849336384097346</v>
+        <v>0.88487914716244387</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.86241341249510473</v>
+        <v>0.862360326470751</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63057223427275699</v>
+        <v>0.6305334427885172</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.51926489810693488</v>
+        <v>0.51923295401708058</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.48953938172838063</v>
+        <v>0.48950926629008673</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15505,50 +15505,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.3700487507701991E-2</v>
+        <v>9.2831174214504319E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10198002366268688</v>
+        <v>0.1010338796257229</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.12645799560773072</v>
+        <v>0.12528475475055123</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.1197682188342869</v>
+        <v>0.11865705006289783</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10426748030708971</v>
+        <v>0.10330012547021321</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.7025277258419598E-2</v>
+        <v>9.6125114864730535E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.2319408224161353E-2</v>
+        <v>8.1555681766123864E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.0224503487916723E-2</v>
+        <v>7.9480214421267376E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.8657882257930886E-2</v>
+        <v>5.811368136299698E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.8303711451807896E-2</v>
+        <v>4.7855571798809275E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.5538547137523783E-2</v>
+        <v>4.5116061409224584E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15562,43 +15562,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12090523020351478</v>
+        <v>0.11979089628458837</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12276658578920963</v>
+        <v>0.12163509651926299</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10488970719023143</v>
+        <v>0.10392298177833989</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8258581318466598E-2</v>
+        <v>9.7352972274056759E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3713401427114637E-2</v>
+        <v>9.2849683441611278E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4792141651510888E-2</v>
+        <v>8.4010647258409413E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9868145858679204E-2</v>
+        <v>6.9224199813898754E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9096413534720458E-2</v>
+        <v>6.8459580230252989E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7500598129535485E-2</v>
+        <v>4.7062804598387693E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6360788675741137E-2</v>
+        <v>4.5933500300849507E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
-        <v>1109912017.5761533</v>
+        <v>1109911979.3294311</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
-        <v>6701748838.9358101</v>
+        <v>6701757338.2074413</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16413,7 +16413,7 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>13453479000.923071</v>
+        <v>13453478537.326439</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16435,7 +16435,7 @@
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
-        <v>-2560303.3740348574</v>
+        <v>-2560354.3696646467</v>
       </c>
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
@@ -16446,14 +16446,14 @@
       </c>
       <c r="C7" s="275">
         <f>F7</f>
-        <v>7002168926.9858103</v>
+        <v>7002177426.2574415</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>424</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
-        <v>7002168926.9858103</v>
+        <v>7002177426.2574415</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>20455647927.908882</v>
+        <v>20455655963.583881</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.3546896425661865</v>
+        <v>6.3543064282411379</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="I8" s="313">
         <f>Normalized_FCF!C10</f>
-        <v>-2560303.3740348574</v>
+        <v>-2560354.3696646467</v>
       </c>
       <c r="J8" s="313"/>
       <c r="N8" s="304"/>
@@ -16512,7 +16512,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1197497097015401</v>
+        <v>1.1196808250427246</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16537,7 +16537,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>22905205829.032879</v>
+        <v>22903805746.09573</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16649,14 +16649,14 @@
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
-        <v>0.12639722903769574</v>
+        <v>0.12639722490129859</v>
       </c>
       <c r="E17" s="308" t="s">
         <v>550</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
-        <v>0.12639722903769574</v>
+        <v>0.12639722490129859</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>412</v>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>18.623620886139943</v>
+        <v>18.622482490088245</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16749,11 +16749,11 @@
       </c>
       <c r="E21" s="299">
         <f>$C$17</f>
-        <v>0.12639722903769574</v>
+        <v>0.12639722490129859</v>
       </c>
       <c r="F21" s="277">
         <f>C21*E21</f>
-        <v>1561018687.2643497</v>
+        <v>1561018636.1794226</v>
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16761,15 +16761,15 @@
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>1111855564.249203</v>
+        <v>1111855525.9355078</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
-        <v>1.7510817454648997E-3</v>
+        <v>1.7510817454651217E-3</v>
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>9.0028046145641069E-2</v>
+        <v>9.0028043043343234E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>1027118304.1563076</v>
+        <v>1027118268.7625937</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16798,11 +16798,11 @@
       </c>
       <c r="E22" s="299">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>0.12639722903769574</v>
+        <v>0.12639722490129859</v>
       </c>
       <c r="F22" s="277">
         <f t="shared" ref="F22:F50" si="7">IF(A22="", 0,C22*E22)</f>
-        <v>1563752158.5919483</v>
+        <v>1563752107.4175673</v>
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
@@ -16810,15 +16810,15 @@
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>1113802514.2313538</v>
+        <v>1113802475.8505681</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
-        <v>1.7510817454653438E-3</v>
+        <v>1.7510817454651217E-3</v>
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
-        <v>9.0028046145641083E-2</v>
+        <v>9.0028043043343234E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16826,7 +16826,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>950500574.84447944</v>
+        <v>950500542.09095407</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16847,11 +16847,11 @@
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
-        <v>0.12639722903769574</v>
+        <v>0.12639722490129859</v>
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>1566490416.4512904</v>
+        <v>1566490365.1872988</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
@@ -16859,15 +16859,15 @@
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>1115752873.4820776</v>
+        <v>1115752835.0340838</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
-        <v>1.7510817454653438E-3</v>
+        <v>1.7510817454651217E-3</v>
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>9.0028046145641097E-2</v>
+        <v>9.0028043043343234E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>879598133.07172632</v>
+        <v>879598102.76144505</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -18299,11 +18299,11 @@
       </c>
       <c r="E51" s="301">
         <f>F17</f>
-        <v>0.12639722903769574</v>
+        <v>0.12639722490129859</v>
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>1566490416.4512904</v>
+        <v>1566490365.1872988</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
@@ -18311,7 +18311,7 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>13524277254.328215</v>
+        <v>13524276788.291927</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>10661795552.384563</v>
+        <v>10661795184.987213</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18337,7 +18337,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>13519012564.457077</v>
+        <v>13519012098.602207</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18361,7 +18361,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>13519012564.457077</v>
+        <v>13519012098.602207</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18396,19 +18396,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>13184409420.904608</v>
+        <v>13184408966.579908</v>
       </c>
       <c r="C56" s="118">
-        <v>13318944210.913837</v>
+        <v>13318943751.953176</v>
       </c>
       <c r="D56" s="118">
-        <v>13453479000.923069</v>
+        <v>13453478537.326439</v>
       </c>
       <c r="E56" s="118">
-        <v>13588013790.932301</v>
+        <v>13588013322.699701</v>
       </c>
       <c r="F56" s="118">
-        <v>13722548580.941534</v>
+        <v>13722548108.072968</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18422,19 +18422,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>12940817560.934086</v>
+        <v>12940817115.003374</v>
       </c>
       <c r="C57" s="118">
-        <v>13195905465.316486</v>
+        <v>13195905010.59564</v>
       </c>
       <c r="D57" s="118">
-        <v>13453479000.923071</v>
+        <v>13453478537.326439</v>
       </c>
       <c r="E57" s="118">
-        <v>13713538167.753849</v>
+        <v>13713537695.195776</v>
       </c>
       <c r="F57" s="118">
-        <v>13976082965.808815</v>
+        <v>13976082484.20365</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18448,19 +18448,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>12720290981.006962</v>
+        <v>12720290542.675426</v>
       </c>
       <c r="C58" s="118">
-        <v>13083380423.153542</v>
+        <v>13083379972.310226</v>
       </c>
       <c r="D58" s="118">
-        <v>13453479000.923069</v>
+        <v>13453478537.326439</v>
       </c>
       <c r="E58" s="118">
-        <v>13830655600.169331</v>
+        <v>13830655123.57548</v>
       </c>
       <c r="F58" s="118">
-        <v>14214979106.746113</v>
+        <v>14214978616.908764</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18474,19 +18474,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>12520645670.772703</v>
+        <v>12520645239.320795</v>
       </c>
       <c r="C59" s="118">
-        <v>12980470684.824387</v>
+        <v>12980470237.52726</v>
       </c>
       <c r="D59" s="118">
-        <v>13453479000.923073</v>
+        <v>13453478537.326441</v>
       </c>
       <c r="E59" s="118">
-        <v>13939929139.882624</v>
+        <v>13939928659.523289</v>
       </c>
       <c r="F59" s="118">
-        <v>14440082167.952618</v>
+        <v>14440081670.358393</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18500,19 +18500,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>12339904419.937071</v>
+        <v>12339903994.713367</v>
       </c>
       <c r="C60" s="118">
-        <v>12886354619.285482</v>
+        <v>12886354175.231525</v>
       </c>
       <c r="D60" s="118">
-        <v>13453479000.923073</v>
+        <v>13453478537.326441</v>
       </c>
       <c r="E60" s="118">
-        <v>14041884128.43729</v>
+        <v>14041883644.564667</v>
       </c>
       <c r="F60" s="118">
-        <v>14652188516.61834</v>
+        <v>14652188011.715086</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18526,19 +18526,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>12176277236.732527</v>
+        <v>12176276817.147293</v>
       </c>
       <c r="C61" s="118">
-        <v>12800280804.150597</v>
+        <v>12800280363.062675</v>
       </c>
       <c r="D61" s="118">
-        <v>13453479000.923073</v>
+        <v>13453478537.326443</v>
       </c>
       <c r="E61" s="118">
-        <v>14137010722.839333</v>
+        <v>14137010235.688717</v>
       </c>
       <c r="F61" s="118">
-        <v>14852048540.303356</v>
+        <v>14852048028.513077</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18552,19 +18552,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>12028143620.528873</v>
+        <v>12028143206.04821</v>
       </c>
       <c r="C62" s="118">
-        <v>12721562026.336702</v>
+        <v>12721561587.961372</v>
       </c>
       <c r="D62" s="118">
-        <v>13453479000.923073</v>
+        <v>13453478537.326441</v>
       </c>
       <c r="E62" s="118">
-        <v>14225766252.027382</v>
+        <v>14225765761.818317</v>
       </c>
       <c r="F62" s="118">
-        <v>15040369301.650898</v>
+        <v>15040368783.371235</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18578,19 +18578,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>11894036513.018871</v>
+        <v>11894036103.159437</v>
       </c>
       <c r="C63" s="118">
-        <v>12649569795.356794</v>
+        <v>12649569359.462261</v>
       </c>
       <c r="D63" s="118">
-        <v>13453479000.923073</v>
+        <v>13453478537.326443</v>
       </c>
       <c r="E63" s="118">
-        <v>14308577415.519234</v>
+        <v>14308576922.456562</v>
       </c>
       <c r="F63" s="118">
-        <v>15217817039.825954</v>
+        <v>15217816515.431576</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18604,19 +18604,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>11772627769.037529</v>
+        <v>11772627363.361748</v>
       </c>
       <c r="C64" s="118">
-        <v>12583729325.45369</v>
+        <v>12583728891.827967</v>
       </c>
       <c r="D64" s="118">
-        <v>13453479000.923073</v>
+        <v>13453478537.326441</v>
       </c>
       <c r="E64" s="118">
-        <v>14385842334.804934</v>
+        <v>14385841839.079773</v>
       </c>
       <c r="F64" s="118">
-        <v>15385019527.529003</v>
+        <v>15385018997.372955</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18630,19 +18630,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>11662715003.123703</v>
+        <v>11662714601.235432</v>
       </c>
       <c r="C65" s="118">
-        <v>12523514946.512281</v>
+        <v>12523514514.961502</v>
       </c>
       <c r="D65" s="118">
-        <v>13453479000.923073</v>
+        <v>13453478537.326441</v>
       </c>
       <c r="E65" s="118">
-        <v>14457932467.348637</v>
+        <v>14457931969.139301</v>
       </c>
       <c r="F65" s="118">
-        <v>15542568291.923569</v>
+        <v>15542567756.338509</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18656,19 +18656,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>11250901089.55719</v>
+        <v>11250900701.859715</v>
       </c>
       <c r="C66" s="277">
-        <v>12291374286.71907</v>
+        <v>12291373863.167679</v>
       </c>
       <c r="D66" s="118">
-        <v>13453479000.923077</v>
+        <v>13453478537.326443</v>
       </c>
       <c r="E66" s="118">
-        <v>14752111107.569118</v>
+        <v>14752110599.222614</v>
       </c>
       <c r="F66" s="118">
-        <v>16203926305.597778</v>
+        <v>16203925747.222828</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18691,19 +18691,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>11000467909.125927</v>
+        <v>11000467530.058189</v>
       </c>
       <c r="C67" s="277">
-        <v>12142853355.92518</v>
+        <v>12142852937.491709</v>
       </c>
       <c r="D67" s="118">
-        <v>13453479000.923077</v>
+        <v>13453478537.326443</v>
       </c>
       <c r="E67" s="118">
-        <v>14960118361.217623</v>
+        <v>14960117845.703346</v>
       </c>
       <c r="F67" s="118">
-        <v>16695171091.679256</v>
+        <v>16695170516.376385</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18726,19 +18726,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>10848173934.117262</v>
+        <v>10848173560.297461</v>
       </c>
       <c r="C68" s="277">
-        <v>12047831368.37878</v>
+        <v>12047830953.219692</v>
       </c>
       <c r="D68" s="118">
-        <v>13453479000.923077</v>
+        <v>13453478537.326443</v>
       </c>
       <c r="E68" s="118">
-        <v>15107195720.532238</v>
+        <v>15107195199.949789</v>
       </c>
       <c r="F68" s="118">
-        <v>17060058845.154211</v>
+        <v>17060058257.277586</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18761,19 +18761,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>10755560587.978386</v>
+        <v>10755560217.349972</v>
       </c>
       <c r="C69" s="277">
-        <v>11987037390.930586</v>
+        <v>11987036977.866417</v>
       </c>
       <c r="D69" s="118">
-        <v>13453479000.923079</v>
+        <v>13453478537.326443</v>
       </c>
       <c r="E69" s="118">
-        <v>15211190890.140671</v>
+        <v>15211190365.97463</v>
       </c>
       <c r="F69" s="118">
-        <v>17331090877.266029</v>
+        <v>17331090280.049847</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18870,23 +18870,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18901,23 +18901,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>18.319957956428496</v>
+        <v>18.318838251548101</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>18.442052531059744</v>
+        <v>18.440925310969604</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690989</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>18.686241680322237</v>
+        <v>18.685099429812599</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>18.808336254953492</v>
+        <v>18.807186489234105</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18932,23 +18932,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>18.098890643470302</v>
+        <v>18.097784545805709</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>18.330390980126779</v>
+        <v>18.329270633069108</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>18.800159020162944</v>
+        <v>18.799009757771692</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>19.038426723542631</v>
+        <v>19.037262795210882</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18963,23 +18963,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>17.898755801254108</v>
+        <v>17.897662022362251</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>18.228270947402862</v>
+        <v>18.227156886074663</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690989</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>18.90644679220831</v>
+        <v>18.905290987553382</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>19.25523252304464</v>
+        <v>19.254055249803312</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>17.717571371349376</v>
+        <v>17.716488744787572</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>18.134877106851665</v>
+        <v>18.133768794135165</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>19.005615983677892</v>
+        <v>19.004454074924755</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>19.459520666686252</v>
+        <v>19.458330819026667</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -19025,23 +19025,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>17.553542972913686</v>
+        <v>17.552470442687632</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>18.049463802329086</v>
+        <v>18.048360747003436</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>19.098143358628725</v>
+        <v>19.09697575459689</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>19.652013882865887</v>
+        <v>19.650812186793711</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -19056,23 +19056,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>17.405046131835643</v>
+        <v>17.403982741941267</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>17.97134909426687</v>
+        <v>17.970250847086195</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690992</v>
+        <v>18.563012370391107</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>19.184473750037814</v>
+        <v>19.183300832166271</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>19.833393172014361</v>
+        <v>19.832180311618085</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19088,23 +19088,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>17.270610192568686</v>
+        <v>17.269555077524231</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>17.899909315069092</v>
+        <v>17.898815465175741</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>19.26502219837332</v>
+        <v>19.263844322554327</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>20.004300215830931</v>
+        <v>20.003076835702021</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19119,23 +19119,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>17.148903753324703</v>
+        <v>17.147856129599344</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>17.83457408975196</v>
+        <v>17.833484261396201</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690992</v>
+        <v>18.563012370391107</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>19.340175946935769</v>
+        <v>19.338993445225867</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>20.165339647417916</v>
+        <v>20.164106354931228</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19151,23 +19151,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>17.038721480383263</v>
+        <v>17.037680638637323</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>17.774821782071619</v>
+        <v>17.773735631611675</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>19.410296303562173</v>
+        <v>19.409109485778526</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>20.317081190345132</v>
+        <v>20.315838557807705</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19183,23 +19183,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>16.938972170930505</v>
+        <v>16.937937468990409</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>17.720175329781984</v>
+        <v>17.719092542940384</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>19.47572037764316</v>
+        <v>19.474529532853062</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>20.460061674211897</v>
+        <v>20.458810240887622</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19215,23 +19215,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>16.565238026768366</v>
+        <v>16.564226329048498</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>17.509500342961662</v>
+        <v>17.508430523663616</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690996</v>
+        <v>18.563012370391107</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>19.742696792746305</v>
+        <v>19.74148951492662</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>21.060264977409382</v>
+        <v>21.058976600152679</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19247,23 +19247,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>16.337961999235208</v>
+        <v>16.336964290892208</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>17.3747129034609</v>
+        <v>17.373651380648447</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690996</v>
+        <v>18.563012370391107</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>19.9314699506238</v>
+        <v>19.930251053369911</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>21.506085149220116</v>
+        <v>21.504769330677739</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19279,23 +19279,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>16.19975040284212</v>
+        <v>16.198761201749662</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>17.288477446079966</v>
+        <v>17.287421231263814</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690996</v>
+        <v>18.563012370391107</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>20.064947303375256</v>
+        <v>20.063720190274712</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>21.837232319744704</v>
+        <v>21.835896118311016</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19311,23 +19311,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>16.115700863676622</v>
+        <v>16.114716836032031</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>17.233304989824084</v>
+        <v>17.232252171003065</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>18.564147105690999</v>
+        <v>18.563012370391107</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>20.159326207123307</v>
+        <v>20.158093284778094</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>22.083202456315806</v>
+        <v>22.081851114838646</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>19.25523252304464</v>
+        <v>19.254055249803312</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19402,7 +19402,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>18.90644679220831</v>
+        <v>18.905290987553382</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>18.564147105690989</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19458,7 +19458,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>18.228270947402862</v>
+        <v>18.227156886074663</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19486,7 +19486,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>17.898755801254108</v>
+        <v>17.897662022362251</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C8" s="447">
         <f>Normalized_FCF!G19</f>
-        <v>1207985751.4787502</v>
+        <v>1207985509.863308</v>
       </c>
       <c r="D8" s="469"/>
       <c r="E8" s="469"/>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
-        <v>1109912017.5761533</v>
+        <v>1109911979.3294311</v>
       </c>
       <c r="D9" s="469"/>
       <c r="E9" s="469"/>
@@ -19764,7 +19764,7 @@
       </c>
       <c r="C14" s="249">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7244252861532914E-2</v>
+        <v>-7.7244289787642528E-2</v>
       </c>
       <c r="D14" s="469"/>
       <c r="E14" s="469"/>
@@ -19846,7 +19846,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>18.90644679220831</v>
+        <v>18.905290987553382</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>18.564147105690989</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>18.228270947402862</v>
+        <v>18.227156886074663</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19909,7 +19909,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>18.548638003422422</v>
+        <v>18.547504222744447</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>19.25523252304464</v>
+        <v>19.254055249803312</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>17.898755801254108</v>
+        <v>17.897662022362251</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -20004,7 +20004,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.60466484323883163</v>
+        <v>0.60462764552307136</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -20024,7 +20024,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.75</v>
+        <v>10.85</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20035,7 +20035,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.24857571240316212</v>
+        <v>0.24453329278037109</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20044,7 +20044,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.3578636971898279E-2</v>
+        <v>3.3578623759527394E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20064,7 +20064,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>18.622133071257338</v>
+        <v>18.620994766784168</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639722903769574</v>
+        <v>0.12639722490129859</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>401</v>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>18.623620886139943</v>
+        <v>18.622482490088245</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20234,7 +20234,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.34124391756035966</v>
+        <v>0.34124419816581697</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.60466484323883163</v>
+        <v>0.60462764552307136</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20308,23 +20308,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.1064469164189545</v>
+        <v>1.1063788501201428</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>8.5816281434365624</v>
+        <v>8.581103579163214</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>9.6880750598555174</v>
+        <v>9.6874824292833566</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.47975481526287933</v>
+        <v>0.47975483852432355</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20333,23 +20333,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2722172169493406</v>
+        <v>1.2721389528085512</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>10.756466755960922</v>
+        <v>10.755809251572087</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>12.028683972910262</v>
+        <v>12.027948204380639</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.35406519076613474</v>
+        <v>0.3540652175126594</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20379,15 +20379,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4588162909432085</v>
+        <v>1.4587265476178874</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>13.347607418928362</v>
+        <v>13.346791527366802</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>14.80642370987157</v>
+        <v>14.80551807498469</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.20490184163033354</v>
+        <v>0.20490187229983359</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20404,15 +20404,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.579611457219579</v>
+        <v>1.5795142828284194</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>15.095153135603116</v>
+        <v>15.094230422814432</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>16.674764592822694</v>
+        <v>16.67374470564285</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20420,7 +20420,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.10457279362053018</v>
+        <v>0.1045728268295737</v>
       </c>
     </row>
   </sheetData>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>10.75</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20549,14 +20549,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>13263.79075</v>
+        <v>13387.174849999999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.24857571240316212</v>
+        <v>0.24453329278037109</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20564,13 +20564,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20608,7 +20608,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1197497097015401</v>
+        <v>1.1196808250427246</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>18.622133071257338</v>
+        <v>18.620994766784168</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20686,14 +20686,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>9.6880750598555174</v>
+        <v>9.6874824292833566</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20702,14 +20702,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>12.028683972910262</v>
+        <v>12.027948204380639</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20718,7 +20718,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>14.80642370987157</v>
+        <v>14.80551807498469</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>16.674764592822694</v>
+        <v>16.67374470564285</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20755,22 +20755,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
-        <v>11596619.455465142</v>
+        <v>11596568.459835352</v>
       </c>
       <c r="D44" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20909,7 +20909,7 @@
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
-        <v>-2560303.3740348574</v>
+        <v>-2560354.3696646467</v>
       </c>
       <c r="D46" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
-        <v>-389572498.52538443</v>
+        <v>-389572485.77647698</v>
       </c>
       <c r="D52" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20960,10 +20960,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20979,22 +20979,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21002,7 +21002,7 @@
       </c>
       <c r="C60" s="373">
         <f>Normalized_FCF!G19</f>
-        <v>1207985751.4787502</v>
+        <v>1207985509.863308</v>
       </c>
       <c r="D60" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
-        <v>1109912017.5761533</v>
+        <v>1109911979.3294311</v>
       </c>
       <c r="D61" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21028,7 +21028,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>9.3700487507701991E-2</v>
+        <v>9.2831174214504319E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21038,14 +21038,14 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.6247892394309919E-2</v>
+        <v>5.5726050278624088E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
-        <v>0.74686628112289843</v>
+        <v>0.74682036120712814</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21065,11 +21065,11 @@
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
-        <v>0.10095732097034157</v>
+        <v>0.10095731766647505</v>
       </c>
       <c r="D66" s="378">
         <f>Normalized_FCF!G119</f>
-        <v>8.8891712098315062E-2</v>
+        <v>8.8891696444715382E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21079,11 +21079,11 @@
       </c>
       <c r="C67" s="383">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639722903769574</v>
+        <v>0.12639722490129859</v>
       </c>
       <c r="D67" s="383">
         <f>Normalized_FCF!G116</f>
-        <v>0.11129124649557967</v>
+        <v>0.11129122689748014</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21129,22 +21129,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21152,13 +21152,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25695709947391487</v>
+        <v>-0.25694129201089511</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,7 +21215,7 @@
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
-        <v>6701748838.9358101</v>
+        <v>6701757338.2074413</v>
       </c>
       <c r="D84" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0820489162631217</v>
+        <v>6.0816824742249942</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21272,7 +21272,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52959782577697867</v>
+        <v>0.52956524602703814</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,7 +21285,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.3546896425661865</v>
+        <v>6.3543064282411379</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21307,33 +21307,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21396,23 +21396,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.7472710845216568</v>
+        <v>1.7471635960610905</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21444,7 +21444,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>18.564147105690992</v>
+        <v>18.563012370391103</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21456,13 +21456,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>19.26 HKD</v>
+        <v>19.25 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21618,7 +21618,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>18.622133071257338</v>
+        <v>18.620994766784168</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21626,13 +21626,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21645,22 +21645,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="C136" s="406">
         <f>Scenarios!C58</f>
-        <v>0.60466484323883163</v>
+        <v>0.60462764552307136</v>
       </c>
       <c r="D136" s="343" t="str">
         <f>Market_currency</f>
@@ -21721,19 +21721,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>1.1064469164189545</v>
+        <v>1.1063788501201428</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>8.5816281434365624</v>
+        <v>8.581103579163214</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>9.6880750598555174</v>
+        <v>9.6874824292833566</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21742,19 +21742,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>1.2722172169493406</v>
+        <v>1.2721389528085512</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>10.756466755960922</v>
+        <v>10.755809251572087</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>12.028683972910262</v>
+        <v>12.027948204380639</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21782,15 +21782,15 @@
       </c>
       <c r="C144" s="409">
         <f>Scenarios!C66</f>
-        <v>1.4588162909432085</v>
+        <v>1.4587265476178874</v>
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>13.347607418928362</v>
+        <v>13.346791527366802</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>14.80642370987157</v>
+        <v>14.80551807498469</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21803,15 +21803,15 @@
       </c>
       <c r="C145" s="409">
         <f>Scenarios!C67</f>
-        <v>1.579611457219579</v>
+        <v>1.5795142828284194</v>
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>15.095153135603116</v>
+        <v>15.094230422814432</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>16.674764592822694</v>
+        <v>16.67374470564285</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21829,13 +21829,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21843,13 +21843,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21886,22 +21886,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21925,15 +21925,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21948,12 +21945,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253C35C1-D231-4D5F-BCC1-C79542D72FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF77D3C-4E40-49A1-9914-29B1F118885E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.85</v>
+        <v>10.69</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>13387.174849999999</v>
+        <v>13189.76029</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.24453329278037109</v>
+        <v>0.25169595174628212</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1196808250427246</v>
+        <v>1.1215249683380129</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>18.620994766784168</v>
+        <v>18.65146853674332</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>9.6874824292833566</v>
+        <v>9.7033478758444449</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>12.027948204380639</v>
+        <v>12.047645627751585</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>14.80551807498469</v>
+        <v>14.829763026691854</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>16.67374470564285</v>
+        <v>16.701048329677697</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
-        <v>11596568.459835352</v>
+        <v>11597933.687599914</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
-        <v>-2560354.3696646467</v>
+        <v>-2558989.1419000849</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
-        <v>-389572485.77647698</v>
+        <v>-389572827.08341813</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="C60" s="285">
         <f>Normalized_FCF!G19</f>
-        <v>1207985509.863308</v>
+        <v>1207991978.2628887</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
-        <v>1109911979.3294311</v>
+        <v>1109913003.2502544</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.2831174214504319E-2</v>
+        <v>9.4375873288004258E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,14 +5914,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.5726050278624088E-2</v>
+        <v>5.665327248854321E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
-        <v>0.74682036120712814</v>
+        <v>0.74804970357508505</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5941,11 +5941,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
-        <v>0.10095731766647505</v>
+        <v>0.10095740611582539</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.8891696444715382E-2</v>
+        <v>8.8892115514525943E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5955,11 +5955,11 @@
       </c>
       <c r="C67" s="263">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639722490129859</v>
+        <v>0.12639733563871405</v>
       </c>
       <c r="D67" s="263">
         <f>Normalized_FCF!G116</f>
-        <v>0.11129122689748014</v>
+        <v>0.1112917515673339</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25694129201089511</v>
+        <v>-0.25736448096827186</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
-        <v>6701757338.2074413</v>
+        <v>6701529800.2466812</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0816824742249942</v>
+        <v>6.091492337374028</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52956524602703814</v>
+        <v>0.53043745369196915</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.3543064282411379</v>
+        <v>6.3645653100977251</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7471635960610905</v>
+        <v>1.7500412197189974</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>18.563012370391103</v>
+        <v>18.593390588264583</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>19.25 HKD</v>
+        <v>19.29 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.0666244412966515E-2</v>
+        <v>2.0666445511321369E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>18.91 HKD</v>
+        <v>18.94 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.710272248992621E-2</v>
+        <v>2.7102998746432419E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>18.56 HKD</v>
+        <v>18.59 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.3578623759527394E-2</v>
+        <v>3.357897747764374E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>18.23 HKD</v>
+        <v>18.26 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.0093003158148392E-2</v>
+        <v>4.0093436685824935E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>17.9 HKD</v>
+        <v>17.93 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.6644845463086483E-2</v>
+        <v>4.6645361191894899E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>18.620994766784168</v>
+        <v>18.65146853674332</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.60462764552307136</v>
+        <v>0.60562348290252688</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6586,15 +6586,15 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>1.1063788501201428</v>
+        <v>1.1082010847184887</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>8.581103579163214</v>
+        <v>8.5951467911259556</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>9.6874824292833566</v>
+        <v>9.7033478758444449</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6607,15 +6607,15 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>1.2721389528085512</v>
+        <v>1.2742341985857637</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>10.755809251572087</v>
+        <v>10.773411429165821</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>12.027948204380639</v>
+        <v>12.047645627751585</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6654,15 +6654,15 @@
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
-        <v>1.4587265476178874</v>
+        <v>1.4611291079924882</v>
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>13.346791527366802</v>
+        <v>13.368633918699366</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>14.80551807498469</v>
+        <v>14.829763026691854</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6675,15 +6675,15 @@
       </c>
       <c r="C145" s="333">
         <f>Scenarios!C67</f>
-        <v>1.5795142828284194</v>
+        <v>1.5821157837288018</v>
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>15.094230422814432</v>
+        <v>15.118932545948894</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>16.67374470564285</v>
+        <v>16.701048329677697</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,6 +6797,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6813,18 +6825,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.67180849502563478</v>
+        <v>0.67291498100280767</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.67180849502563478</v>
+        <v>0.67291498100280767</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10236,11 +10236,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.59970550415043</v>
+        <v>13.622104571065252</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7471635960610905</v>
+        <v>1.7500412197189974</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6701757338.2074413</v>
+        <v>6701529800.2466812</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C73" s="285">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-985655463.14757693</v>
+        <v>-985769232.12795699</v>
       </c>
       <c r="D73" s="285">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-966380704.98627937</v>
+        <v>-966494473.96665943</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10514,11 +10514,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7601794653546197</v>
+        <v>8.7591684410162269</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9349039189504431</v>
+        <v>8.9338521644541338</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10531,7 +10531,7 @@
       <c r="C75" s="261"/>
       <c r="D75" s="262">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1932761409.9725587</v>
+        <v>1932988947.9333189</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10646,11 +10646,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-317024700.67601484</v>
+        <v>-317546848.56237352</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.25694129201089511</v>
+        <v>-0.25736448096827186</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10663,11 +10663,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7503829185.6802416</v>
+        <v>7515932997.0379086</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>6.0816824742249942</v>
+        <v>6.091492337374028</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10680,11 +10680,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>653399312.72324681</v>
+        <v>654475478.30075288</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.52956524602703814</v>
+        <v>0.53043745369196915</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10697,11 +10697,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>7840203797.7274733</v>
+        <v>7852861626.776288</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.3543064282411379</v>
+        <v>6.3645653100977251</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11182,36 +11182,36 @@
       </c>
       <c r="C10" s="266">
         <f>C48</f>
-        <v>-2560354.3696646467</v>
+        <v>-2558989.1419000849</v>
       </c>
       <c r="E10" s="237"/>
       <c r="G10" s="266">
         <f>G48</f>
-        <v>42502237.323306948</v>
+        <v>42508705.722887784</v>
       </c>
       <c r="H10" s="266">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40976229.013627343</v>
+        <v>40983157.438705444</v>
       </c>
       <c r="I10" s="266">
         <f t="shared" si="6"/>
-        <v>17729423.520732909</v>
+        <v>17733980.44663737</v>
       </c>
       <c r="J10" s="266">
         <f t="shared" si="6"/>
-        <v>5079787.496219717</v>
+        <v>5082679.7665822022</v>
       </c>
       <c r="K10" s="266">
         <f t="shared" si="6"/>
-        <v>-4690009.2904260047</v>
+        <v>-4687952.1374051124</v>
       </c>
       <c r="L10" s="266">
         <f t="shared" si="6"/>
-        <v>-6414275.9388721753</v>
+        <v>-6412742.4231768474</v>
       </c>
       <c r="M10" s="266">
         <f t="shared" si="6"/>
-        <v>7541520.6485311836</v>
+        <v>7542469.2837602021</v>
       </c>
       <c r="N10" s="266">
         <f t="shared" si="6"/>
@@ -11237,36 +11237,36 @@
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
-        <v>1558289943.1059079</v>
+        <v>1558291308.3336725</v>
       </c>
       <c r="E11" s="237"/>
       <c r="G11" s="267">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1372055436.863308</v>
+        <v>1372061905.2628887</v>
       </c>
       <c r="H11" s="267">
         <f t="shared" si="7"/>
-        <v>1481960897.333627</v>
+        <v>1481967825.7587051</v>
       </c>
       <c r="I11" s="267">
         <f t="shared" si="7"/>
-        <v>1407256922.5207329</v>
+        <v>1407261479.4466374</v>
       </c>
       <c r="J11" s="267">
         <f t="shared" si="7"/>
-        <v>1240534105.4962196</v>
+        <v>1240536997.7665823</v>
       </c>
       <c r="K11" s="267">
         <f t="shared" si="7"/>
-        <v>1157465681.709574</v>
+        <v>1157467738.8625948</v>
       </c>
       <c r="L11" s="267">
         <f t="shared" si="7"/>
-        <v>999271538.64112985</v>
+        <v>999273072.15682518</v>
       </c>
       <c r="M11" s="267">
         <f t="shared" si="7"/>
-        <v>939488827.41853023</v>
+        <v>939489776.05375922</v>
       </c>
       <c r="N11" s="267">
         <f t="shared" si="7"/>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
-        <v>-389572485.77647698</v>
+        <v>-389572827.08341813</v>
       </c>
       <c r="E12" s="237"/>
       <c r="G12" s="266">
@@ -11404,38 +11404,38 @@
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
-        <v>1109911979.3294311</v>
+        <v>1109913003.2502544</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="243"/>
       <c r="F14" s="58"/>
       <c r="G14" s="267">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207985509.863308</v>
+        <v>1207991978.2628887</v>
       </c>
       <c r="H14" s="267">
         <f t="shared" si="8"/>
-        <v>1497934840.333627</v>
+        <v>1497941768.7587051</v>
       </c>
       <c r="I14" s="267">
         <f t="shared" si="8"/>
-        <v>1418692399.5207329</v>
+        <v>1418696956.4466374</v>
       </c>
       <c r="J14" s="267">
         <f t="shared" si="8"/>
-        <v>1235081293.4962196</v>
+        <v>1235084185.7665823</v>
       </c>
       <c r="K14" s="267">
         <f t="shared" si="8"/>
-        <v>1149295130.709574</v>
+        <v>1149297187.8625948</v>
       </c>
       <c r="L14" s="267">
         <f t="shared" si="8"/>
-        <v>975099463.52112985</v>
+        <v>975100997.03682518</v>
       </c>
       <c r="M14" s="267">
         <f t="shared" si="8"/>
-        <v>950284673.78853023</v>
+        <v>950285622.42375922</v>
       </c>
       <c r="N14" s="267">
         <f t="shared" si="8"/>
@@ -11622,38 +11622,38 @@
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
-        <v>1109911979.3294311</v>
+        <v>1109913003.2502544</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="234"/>
       <c r="F19" s="26"/>
       <c r="G19" s="271">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207985509.863308</v>
+        <v>1207991978.2628887</v>
       </c>
       <c r="H19" s="271">
         <f t="shared" si="9"/>
-        <v>1497934840.333627</v>
+        <v>1497941768.7587051</v>
       </c>
       <c r="I19" s="271">
         <f t="shared" si="9"/>
-        <v>1418692399.5207329</v>
+        <v>1418696956.4466374</v>
       </c>
       <c r="J19" s="271">
         <f t="shared" si="9"/>
-        <v>1235081293.4962196</v>
+        <v>1235084185.7665823</v>
       </c>
       <c r="K19" s="271">
         <f t="shared" si="9"/>
-        <v>1149295130.709574</v>
+        <v>1149297187.8625948</v>
       </c>
       <c r="L19" s="271">
         <f t="shared" si="9"/>
-        <v>975099463.52112985</v>
+        <v>975100997.03682518</v>
       </c>
       <c r="M19" s="271">
         <f t="shared" si="9"/>
-        <v>950284673.78853023</v>
+        <v>950285622.42375922</v>
       </c>
       <c r="N19" s="271">
         <f t="shared" si="9"/>
@@ -12361,31 +12361,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.6720259380078565E-2</v>
+        <v>7.6719897692831288E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.3981082171108542E-2</v>
+        <v>-4.3980876552857338E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.1260762103883156E-3</v>
+        <v>-8.1260498969222498E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3955357420978353E-3</v>
+        <v>4.3955254940538204E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.0590006503969223E-3</v>
+        <v>7.0589881045228352E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4189696379094974E-2</v>
+        <v>2.4189659256830701E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491191864052459E-2</v>
+        <v>-1.1491180260999713E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12499,36 +12499,36 @@
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
-        <v>11596568.459835352</v>
+        <v>11597933.687599914</v>
       </c>
       <c r="E46" s="237"/>
       <c r="G46" s="274">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54944120.323306948</v>
+        <v>54950588.722887784</v>
       </c>
       <c r="H46" s="274">
         <f t="shared" si="17"/>
-        <v>58851686.013627343</v>
+        <v>58858614.438705444</v>
       </c>
       <c r="I46" s="274">
         <f t="shared" si="17"/>
-        <v>38707609.520732909</v>
+        <v>38712166.44663737</v>
       </c>
       <c r="J46" s="274">
         <f t="shared" si="17"/>
-        <v>24567630.496219717</v>
+        <v>24570522.766582202</v>
       </c>
       <c r="K46" s="274">
         <f t="shared" si="17"/>
-        <v>17473945.709573995</v>
+        <v>17476002.862594888</v>
       </c>
       <c r="L46" s="274">
         <f t="shared" si="17"/>
-        <v>13026046.061127825</v>
+        <v>13027579.576823153</v>
       </c>
       <c r="M46" s="274">
         <f t="shared" si="17"/>
-        <v>8057932.6485311836</v>
+        <v>8058881.2837602021</v>
       </c>
       <c r="N46" s="274">
         <f t="shared" si="17"/>
@@ -12611,36 +12611,36 @@
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
-        <v>-2560354.3696646467</v>
+        <v>-2558989.1419000849</v>
       </c>
       <c r="E48" s="237"/>
       <c r="G48" s="267">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42502237.323306948</v>
+        <v>42508705.722887784</v>
       </c>
       <c r="H48" s="267">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40976229.013627343</v>
+        <v>40983157.438705444</v>
       </c>
       <c r="I48" s="267">
         <f t="shared" si="18"/>
-        <v>17729423.520732909</v>
+        <v>17733980.44663737</v>
       </c>
       <c r="J48" s="267">
         <f t="shared" si="18"/>
-        <v>5079787.496219717</v>
+        <v>5082679.7665822022</v>
       </c>
       <c r="K48" s="267">
         <f t="shared" si="18"/>
-        <v>-4690009.2904260047</v>
+        <v>-4687952.1374051124</v>
       </c>
       <c r="L48" s="267">
         <f t="shared" si="18"/>
-        <v>-6414275.9388721753</v>
+        <v>-6412742.4231768474</v>
       </c>
       <c r="M48" s="267">
         <f t="shared" si="18"/>
-        <v>7541520.6485311836</v>
+        <v>7542469.2837602021</v>
       </c>
       <c r="N48" s="267">
         <f t="shared" si="18"/>
@@ -13576,38 +13576,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0767745342981415E-4</v>
+        <v>2.0756671601437855E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="234"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.4474745046835487E-3</v>
+        <v>3.4479991745373119E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4525223972304247E-3</v>
+        <v>3.4531061635587447E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.6220432638364283E-3</v>
+        <v>1.6224601714114821E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8562244143604143E-4</v>
+        <v>4.8589893949738127E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2064607524510045E-4</v>
+        <v>5.2041770711613053E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.2539514909017021E-4</v>
+        <v>7.2522172268054189E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.2120493729553254E-4</v>
+        <v>9.2132081411897319E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13633,38 +13633,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639722490129859</v>
+        <v>0.12639733563871403</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="234"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.11129122689748014</v>
+        <v>0.1112917515673339</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.1248651550674042</v>
+        <v>0.12486573883373253</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12874821389384783</v>
+        <v>0.12874863080142288</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11859378004376522</v>
+        <v>0.11859405654182657</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12849227519509798</v>
+        <v>0.12849250356322695</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300834788869402</v>
+        <v>0.11300852131510365</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11475958055229898</v>
+        <v>0.11475969642912243</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1599306225324648E-2</v>
+        <v>3.1599333909678506E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="234"/>
@@ -13805,38 +13805,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.0028043043343234E-2</v>
+        <v>9.0028126096404801E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="234"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.798305947054757E-2</v>
+        <v>9.7983584140401328E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12621106700969739</v>
+        <v>0.12621165077602572</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12979443169190061</v>
+        <v>0.12979484859947568</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11807249684479236</v>
+        <v>0.11807277334285371</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758524814092481</v>
+        <v>0.12758547650905377</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11027471026496337</v>
+        <v>0.110274883691373</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607830491066363</v>
+        <v>0.11607842078748708</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14028,38 +14028,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.0028043043343234E-2</v>
+        <v>9.0028126096404801E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="234"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.798305947054757E-2</v>
+        <v>9.7983584140401328E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12621106700969739</v>
+        <v>0.12621165077602572</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12979443169190061</v>
+        <v>0.12979484859947568</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11807249684479236</v>
+        <v>0.11807277334285371</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758524814092481</v>
+        <v>0.12758547650905377</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11027471026496337</v>
+        <v>0.110274883691373</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607830491066363</v>
+        <v>0.11607842078748708</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.67180849502563478</v>
+        <v>0.67291498100280767</v>
       </c>
       <c r="E88" s="237"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.67180849502563478</v>
+        <v>0.67291498100280767</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14153,12 +14153,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>828904865.31092429</v>
+        <v>830270093.07548523</v>
       </c>
       <c r="E89" s="237"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>828904865.31092429</v>
+        <v>830270093.07548523</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.74682036120712814</v>
+        <v>0.74804970357508505</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.6861877551865011</v>
+        <v>0.68731424381594541</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14284,12 +14284,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.5726050278624088E-2</v>
+        <v>5.665327248854321E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.5726050278624088E-2</v>
+        <v>5.665327248854321E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14421,38 +14421,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.13573395158752155</v>
+        <v>0.13572959234306703</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="234"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162186511171124E-2</v>
+        <v>-7.4162150206971811E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.308481601147963E-2</v>
+        <v>5.308632930210222E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.13439599627760601</v>
+        <v>0.1343970248208799</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1767504729776332E-2</v>
+        <v>7.1768098682056358E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830946539672897</v>
+        <v>0.15830974646832341</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3633232751545199E-2</v>
+        <v>6.3633791050053068E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35104160899476922</v>
+        <v>0.35104297318945554</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -15037,31 +15037,31 @@
       </c>
       <c r="G113" s="251">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4673014018194377</v>
+        <v>1.4672935449032138</v>
       </c>
       <c r="H113" s="251">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5708481755293993</v>
+        <v>1.5708409098905605</v>
       </c>
       <c r="I113" s="251">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.4269344966420365</v>
+        <v>1.426929913256739</v>
       </c>
       <c r="J113" s="251">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.6576476283633927</v>
+        <v>1.657643746550993</v>
       </c>
       <c r="K113" s="251">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.5825398032244955</v>
+        <v>1.5825369706007222</v>
       </c>
       <c r="L113" s="251">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3992526615623904</v>
+        <v>1.3992504609945264</v>
       </c>
       <c r="M113" s="251">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.0454238602095729</v>
+        <v>1.045422816601336</v>
       </c>
       <c r="N113" s="251">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15150,39 +15150,39 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639722490129859</v>
+        <v>0.12639733563871403</v>
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
-        <v>0.12639722490129859</v>
+        <v>0.12639733563871405</v>
       </c>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.11129122689748014</v>
+        <v>0.1112917515673339</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.1248651550674042</v>
+        <v>0.12486573883373253</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12874821389384783</v>
+        <v>0.12874863080142288</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11859378004376522</v>
+        <v>0.11859405654182657</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12849227519509798</v>
+        <v>0.12849250356322695</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300834788869402</v>
+        <v>0.11300852131510365</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11475958055229898</v>
+        <v>0.11475969642912243</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15324,41 +15324,41 @@
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
-        <v>0.10095731766647505</v>
+        <v>0.10095740611582539</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
         <f>C11/C104</f>
-        <v>0.10095731766647505</v>
+        <v>0.10095740611582539</v>
       </c>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.8891696444715382E-2</v>
+        <v>8.8892115514525943E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.1104773851177811</v>
+        <v>0.11047790161878122</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11113988429112248</v>
+        <v>0.11114024418007357</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11166236559271127</v>
+        <v>0.11166262593037485</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11542165601306381</v>
+        <v>0.11542186115090253</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.10956965222209358</v>
+        <v>0.10956982037136526</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176368616628174</v>
+        <v>0.11176379901804423</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15448,50 +15448,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0072182402273719</v>
+        <v>1.0088780854487656</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0962175939390935</v>
+        <v>1.0980289722694088</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3593395890434807</v>
+        <v>1.3615847542586879</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2874289931824414</v>
+        <v>1.2895535641626841</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1208063613518133</v>
+        <v>1.1226549874227283</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0429574962823263</v>
+        <v>1.0446771441608471</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.88487914716244387</v>
+        <v>0.88633795993818498</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.862360326470751</v>
+        <v>0.86378151852700258</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.6305334427885172</v>
+        <v>0.63157194768649028</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.51923295401708058</v>
+        <v>0.52008814412967963</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.48950926629008673</v>
+        <v>0.49031550071977426</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15505,50 +15505,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.2831174214504319E-2</v>
+        <v>9.4375873288004258E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.1010338796257229</v>
+        <v>0.10271552593726931</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.12528475475055123</v>
+        <v>0.12736994894842732</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.11865705006289783</v>
+        <v>0.12063176465506867</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10330012547021321</v>
+        <v>0.10501917562420283</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.6125114864730535E-2</v>
+        <v>9.7724709463128834E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.1555681766123864E-2</v>
+        <v>8.2912811968024788E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>7.9480214421267376E-2</v>
+        <v>8.0802761321515676E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.811368136299698E-2</v>
+        <v>5.9080631214826033E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.7855571798809275E-2</v>
+        <v>4.8651837617369471E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.5116061409224584E-2</v>
+        <v>4.5866744688472808E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15562,43 +15562,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11979089628458837</v>
+        <v>0.12158383766957755</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12163509651926299</v>
+        <v>0.12345564052703493</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10392298177833989</v>
+        <v>0.10547842397520933</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7352972274056759E-2</v>
+        <v>9.8810079436250309E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2849683441611278E-2</v>
+        <v>9.4239388712954383E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4010647258409413E-2</v>
+        <v>8.5268056384821531E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9224199813898754E-2</v>
+        <v>7.0260296349934651E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8459580230252989E-2</v>
+        <v>6.948423250685172E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7062804598387693E-2</v>
+        <v>4.7767205789757385E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5933500300849507E-2</v>
+        <v>4.6620998902171862E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
-        <v>1109911979.3294311</v>
+        <v>1109913003.2502544</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
-        <v>6701757338.2074413</v>
+        <v>6701529800.2466812</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16413,7 +16413,7 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>13453478537.326439</v>
+        <v>13453490948.487934</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16435,7 +16435,7 @@
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
-        <v>-2560354.3696646467</v>
+        <v>-2558989.1419000849</v>
       </c>
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
@@ -16446,14 +16446,14 @@
       </c>
       <c r="C7" s="275">
         <f>F7</f>
-        <v>7002177426.2574415</v>
+        <v>7001949888.2966814</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>424</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
-        <v>7002177426.2574415</v>
+        <v>7001949888.2966814</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>20455655963.583881</v>
+        <v>20455440836.784615</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.3543064282411379</v>
+        <v>6.3645653100977251</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="I8" s="313">
         <f>Normalized_FCF!C10</f>
-        <v>-2560354.3696646467</v>
+        <v>-2558989.1419000849</v>
       </c>
       <c r="J8" s="313"/>
       <c r="N8" s="304"/>
@@ -16512,7 +16512,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1196808250427246</v>
+        <v>1.1215249683380129</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16537,7 +16537,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>22903805746.09573</v>
+        <v>22941287636.81496</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>18.563012370391103</v>
+        <v>18.593390588264583</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16649,14 +16649,14 @@
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
-        <v>0.12639722490129859</v>
+        <v>0.12639733563871403</v>
       </c>
       <c r="E17" s="308" t="s">
         <v>550</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
-        <v>0.12639722490129859</v>
+        <v>0.12639733563871405</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>412</v>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>18.622482490088245</v>
+        <v>18.652958711740901</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16749,11 +16749,11 @@
       </c>
       <c r="E21" s="299">
         <f>$C$17</f>
-        <v>0.12639722490129859</v>
+        <v>0.12639733563871403</v>
       </c>
       <c r="F21" s="277">
         <f>C21*E21</f>
-        <v>1561018636.1794226</v>
+        <v>1561020003.7978127</v>
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16761,7 +16761,7 @@
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>1111855525.9355078</v>
+        <v>1111856551.6493003</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
@@ -16769,7 +16769,7 @@
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>9.0028043043343234E-2</v>
+        <v>9.0028126096404815E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>1027118268.7625937</v>
+        <v>1027119216.3042035</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16798,11 +16798,11 @@
       </c>
       <c r="E22" s="299">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>0.12639722490129859</v>
+        <v>0.12639733563871403</v>
       </c>
       <c r="F22" s="277">
         <f t="shared" ref="F22:F50" si="7">IF(A22="", 0,C22*E22)</f>
-        <v>1563752107.4175673</v>
+        <v>1563753477.430769</v>
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
@@ -16810,7 +16810,7 @@
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>1113802475.8505681</v>
+        <v>1113803503.3604693</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
@@ -16818,7 +16818,7 @@
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
-        <v>9.0028043043343234E-2</v>
+        <v>9.0028126096404815E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16826,7 +16826,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>950500542.09095407</v>
+        <v>950501418.95084572</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16847,11 +16847,11 @@
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
-        <v>0.12639722490129859</v>
+        <v>0.12639733563871403</v>
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>1566490365.1872988</v>
+        <v>1566491737.5995054</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
@@ -16859,15 +16859,15 @@
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>1115752835.0340838</v>
+        <v>1115753864.3432388</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
-        <v>1.7510817454651217E-3</v>
+        <v>1.7510817454648997E-3</v>
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>9.0028043043343234E-2</v>
+        <v>9.0028126096404815E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>879598102.76144505</v>
+        <v>879598914.21210992</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -18299,11 +18299,11 @@
       </c>
       <c r="E51" s="301">
         <f>F17</f>
-        <v>0.12639722490129859</v>
+        <v>0.12639733563871405</v>
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>1566490365.1872988</v>
+        <v>1566491737.5995059</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
@@ -18311,7 +18311,7 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>13524276788.291927</v>
+        <v>13524289264.766537</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>10661795184.987213</v>
+        <v>10661805020.752851</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18337,7 +18337,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>13519012098.602207</v>
+        <v>13519024570.220011</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18361,7 +18361,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>13519012098.602207</v>
+        <v>13519024570.220011</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18396,19 +18396,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>13184408966.579908</v>
+        <v>13184421129.518175</v>
       </c>
       <c r="C56" s="118">
-        <v>13318943751.953176</v>
+        <v>13318956039.003057</v>
       </c>
       <c r="D56" s="118">
-        <v>13453478537.326439</v>
+        <v>13453490948.487934</v>
       </c>
       <c r="E56" s="118">
-        <v>13588013322.699701</v>
+        <v>13588025857.972816</v>
       </c>
       <c r="F56" s="118">
-        <v>13722548108.072968</v>
+        <v>13722560767.457695</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18422,19 +18422,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>12940817115.003374</v>
+        <v>12940829053.222229</v>
       </c>
       <c r="C57" s="118">
-        <v>13195905010.59564</v>
+        <v>13195917184.13929</v>
       </c>
       <c r="D57" s="118">
-        <v>13453478537.326439</v>
+        <v>13453490948.487936</v>
       </c>
       <c r="E57" s="118">
-        <v>13713537695.195776</v>
+        <v>13713550346.268179</v>
       </c>
       <c r="F57" s="118">
-        <v>13976082484.20365</v>
+        <v>13976095377.480011</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18448,19 +18448,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>12720290542.675426</v>
+        <v>12720302277.453148</v>
       </c>
       <c r="C58" s="118">
-        <v>13083379972.310226</v>
+        <v>13083392042.046787</v>
       </c>
       <c r="D58" s="118">
-        <v>13453478537.326439</v>
+        <v>13453490948.487936</v>
       </c>
       <c r="E58" s="118">
-        <v>13830655123.57548</v>
+        <v>13830667882.691561</v>
       </c>
       <c r="F58" s="118">
-        <v>14214978616.908764</v>
+        <v>14214991730.572626</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18474,19 +18474,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>12520645239.320795</v>
+        <v>12520656789.920864</v>
       </c>
       <c r="C59" s="118">
-        <v>12980470237.52726</v>
+        <v>12980482212.327087</v>
       </c>
       <c r="D59" s="118">
-        <v>13453478537.326441</v>
+        <v>13453490948.487936</v>
       </c>
       <c r="E59" s="118">
-        <v>13939928659.523289</v>
+        <v>13939941519.446865</v>
       </c>
       <c r="F59" s="118">
-        <v>14440081670.358393</v>
+        <v>14440094991.685305</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18500,19 +18500,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>12339903994.713367</v>
+        <v>12339915378.575241</v>
       </c>
       <c r="C60" s="118">
-        <v>12886354175.231525</v>
+        <v>12886366063.206989</v>
       </c>
       <c r="D60" s="118">
-        <v>13453478537.326441</v>
+        <v>13453490948.487936</v>
       </c>
       <c r="E60" s="118">
-        <v>14041883644.564667</v>
+        <v>14041896598.544199</v>
       </c>
       <c r="F60" s="118">
-        <v>14652188011.715086</v>
+        <v>14652201528.71526</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18526,19 +18526,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>12176276817.147293</v>
+        <v>12176288050.059109</v>
       </c>
       <c r="C61" s="118">
-        <v>12800280363.062675</v>
+        <v>12800292171.632957</v>
       </c>
       <c r="D61" s="118">
-        <v>13453478537.326443</v>
+        <v>13453490948.487938</v>
       </c>
       <c r="E61" s="118">
-        <v>14137010235.688717</v>
+        <v>14137023277.424849</v>
       </c>
       <c r="F61" s="118">
-        <v>14852048028.513077</v>
+        <v>14852061729.888985</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18552,19 +18552,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>12028143206.04821</v>
+        <v>12028154302.303165</v>
       </c>
       <c r="C62" s="118">
-        <v>12721561587.961372</v>
+        <v>12721573323.911663</v>
       </c>
       <c r="D62" s="118">
-        <v>13453478537.326441</v>
+        <v>13453490948.487938</v>
       </c>
       <c r="E62" s="118">
-        <v>14225765761.818317</v>
+        <v>14225778885.433582</v>
       </c>
       <c r="F62" s="118">
-        <v>15040368783.371235</v>
+        <v>15040382658.477619</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18578,19 +18578,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>11894036103.159437</v>
+        <v>11894047075.697321</v>
       </c>
       <c r="C63" s="118">
-        <v>12649569359.462261</v>
+        <v>12649581028.997969</v>
       </c>
       <c r="D63" s="118">
-        <v>13453478537.326443</v>
+        <v>13453490948.487938</v>
       </c>
       <c r="E63" s="118">
-        <v>14308576922.456562</v>
+        <v>14308590122.467136</v>
       </c>
       <c r="F63" s="118">
-        <v>15217816515.431576</v>
+        <v>15217830554.237814</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18604,19 +18604,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>11772627363.361748</v>
+        <v>11772638223.897112</v>
       </c>
       <c r="C64" s="118">
-        <v>12583728891.827967</v>
+        <v>12583740500.624241</v>
       </c>
       <c r="D64" s="118">
-        <v>13453478537.326441</v>
+        <v>13453490948.487938</v>
       </c>
       <c r="E64" s="118">
-        <v>14385841839.079773</v>
+        <v>14385855110.369114</v>
       </c>
       <c r="F64" s="118">
-        <v>15385018997.372955</v>
+        <v>15385033190.427555</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18630,19 +18630,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>11662714601.235432</v>
+        <v>11662725360.373596</v>
       </c>
       <c r="C65" s="118">
-        <v>12523514514.961502</v>
+        <v>12523526068.208546</v>
       </c>
       <c r="D65" s="118">
-        <v>13453478537.326441</v>
+        <v>13453490948.487938</v>
       </c>
       <c r="E65" s="118">
-        <v>14457931969.139301</v>
+        <v>14457945306.933544</v>
       </c>
       <c r="F65" s="118">
-        <v>15542567756.338509</v>
+        <v>15542582094.735672</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18656,19 +18656,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>11250900701.859715</v>
+        <v>11250911081.089531</v>
       </c>
       <c r="C66" s="277">
-        <v>12291373863.167679</v>
+        <v>12291385202.259321</v>
       </c>
       <c r="D66" s="118">
-        <v>13453478537.326443</v>
+        <v>13453490948.487938</v>
       </c>
       <c r="E66" s="118">
-        <v>14752110599.222614</v>
+        <v>14752124208.403801</v>
       </c>
       <c r="F66" s="118">
-        <v>16203925747.222828</v>
+        <v>16203940695.738838</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18691,19 +18691,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>11000467530.058189</v>
+        <v>11000477678.257307</v>
       </c>
       <c r="C67" s="277">
-        <v>12142852937.491709</v>
+        <v>12142864139.56918</v>
       </c>
       <c r="D67" s="118">
-        <v>13453478537.326443</v>
+        <v>13453490948.487938</v>
       </c>
       <c r="E67" s="118">
-        <v>14960117845.703346</v>
+        <v>14960131646.776283</v>
       </c>
       <c r="F67" s="118">
-        <v>16695170516.376385</v>
+        <v>16695185918.07766</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18726,19 +18726,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>10848173560.297461</v>
+        <v>10848183568.001682</v>
       </c>
       <c r="C68" s="277">
-        <v>12047830953.219692</v>
+        <v>12047842067.63707</v>
       </c>
       <c r="D68" s="118">
-        <v>13453478537.326443</v>
+        <v>13453490948.487938</v>
       </c>
       <c r="E68" s="118">
-        <v>15107195199.949789</v>
+        <v>15107209136.705166</v>
       </c>
       <c r="F68" s="118">
-        <v>17060058257.277586</v>
+        <v>17060073995.596687</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18761,19 +18761,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>10755560217.349972</v>
+        <v>10755570139.616131</v>
       </c>
       <c r="C69" s="277">
-        <v>11987036977.866417</v>
+        <v>11987048036.199871</v>
       </c>
       <c r="D69" s="118">
-        <v>13453478537.326443</v>
+        <v>13453490948.487938</v>
       </c>
       <c r="E69" s="118">
-        <v>15211190365.97463</v>
+        <v>15211204398.668079</v>
       </c>
       <c r="F69" s="118">
-        <v>17331090280.049847</v>
+        <v>17331106268.402588</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18870,23 +18870,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>18.563012370391103</v>
+        <v>18.593390588264583</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>18.563012370391103</v>
+        <v>18.593390588264583</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>18.563012370391103</v>
+        <v>18.593390588264583</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>18.563012370391103</v>
+        <v>18.593390588264583</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>18.563012370391103</v>
+        <v>18.593390588264583</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18901,23 +18901,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>18.318838251548101</v>
+        <v>18.348814082701246</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>18.440925310969604</v>
+        <v>18.471102335482918</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>18.563012370391103</v>
+        <v>18.593390588264583</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>18.685099429812599</v>
+        <v>18.715678841046252</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>18.807186489234105</v>
+        <v>18.83796709382792</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18932,23 +18932,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>18.097784545805709</v>
+        <v>18.127396091521504</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>18.329270633069108</v>
+        <v>18.359263656264581</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>18.563012370391103</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>18.799009757771692</v>
+        <v>18.829776887521533</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>19.037262795210882</v>
+        <v>19.068422554035408</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18963,23 +18963,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>17.897662022362251</v>
+        <v>17.926943776180952</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>18.227156886074663</v>
+        <v>18.256981630928639</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>18.563012370391103</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>18.905290987553382</v>
+        <v>18.936233263447647</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>19.254055249803312</v>
+        <v>19.28557227173669</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>17.716488744787572</v>
+        <v>17.74547193411745</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>18.133768794135165</v>
+        <v>18.163439640090225</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>18.563012370391103</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>19.004454074924755</v>
+        <v>19.035559766621212</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>19.458330819026667</v>
+        <v>19.490184476868613</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -19025,23 +19025,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>17.552470442687632</v>
+        <v>17.581183338069202</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>18.048360747003436</v>
+        <v>18.077890844773798</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>18.563012370391103</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>19.09697575459689</v>
+        <v>19.128233917388236</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>19.650812186793711</v>
+        <v>19.68298304429084</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -19056,23 +19056,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>17.403982741941267</v>
+        <v>17.432450937027827</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>17.970250847086195</v>
+        <v>17.999652223653008</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>18.563012370391107</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>19.183300832166271</v>
+        <v>19.214701254362552</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>19.832180311618085</v>
+        <v>19.864650054702548</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19088,23 +19088,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>17.269555077524231</v>
+        <v>17.297801742551577</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>17.898815465175741</v>
+        <v>17.928099119810433</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>18.563012370391103</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>19.263844322554327</v>
+        <v>19.295377476389387</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>20.003076835702021</v>
+        <v>20.035828207700177</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19119,23 +19119,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>17.147856129599344</v>
+        <v>17.175902240854828</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>17.833484261396201</v>
+        <v>17.862660253478658</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>18.563012370391107</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>19.338993445225867</v>
+        <v>19.370650441051843</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>20.164106354931228</v>
+        <v>20.197123095513199</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19151,23 +19151,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>17.037680638637323</v>
+        <v>17.065545186200957</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>17.773735631611675</v>
+        <v>17.802813160944286</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>18.563012370391103</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>19.409109485778526</v>
+        <v>19.440882029328129</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>20.315838557807705</v>
+        <v>20.349105345461716</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19183,23 +19183,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>16.937937468990409</v>
+        <v>16.965637644805309</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>17.719092542940384</v>
+        <v>17.748080023199226</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>18.563012370391103</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>19.474529532853062</v>
+        <v>19.506409885364199</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>20.458810240887622</v>
+        <v>20.492312638715749</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19215,23 +19215,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>16.564226329048498</v>
+        <v>16.591310647619117</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>17.508430523663616</v>
+        <v>17.537070843464022</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>18.563012370391107</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>19.74148951492662</v>
+        <v>19.773809804119647</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>21.058976600152679</v>
+        <v>21.093468042086318</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19247,23 +19247,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>16.336964290892208</v>
+        <v>16.363674093004555</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>17.373651380648447</v>
+        <v>17.402069591170502</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>18.563012370391107</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>19.930251053369911</v>
+        <v>19.96288241212568</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>21.504769330677739</v>
+        <v>21.539995416707317</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19279,23 +19279,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>16.198761201749662</v>
+        <v>16.225243252091904</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>17.287421231263814</v>
+        <v>17.315697338817831</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>18.563012370391107</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>20.063720190274712</v>
+        <v>20.096571499484362</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>21.835896118311016</v>
+        <v>21.87166788470477</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19311,23 +19311,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>16.114716836032031</v>
+        <v>16.141060385468261</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>17.232252171003065</v>
+        <v>17.260437362708473</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>18.563012370391107</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>20.158093284778094</v>
+        <v>20.191100116121564</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>22.081851114838646</v>
+        <v>22.118028202749976</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>19.254055249803312</v>
+        <v>19.28557227173669</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19402,7 +19402,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>18.905290987553382</v>
+        <v>18.936233263447647</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>18.563012370391103</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19458,7 +19458,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>18.227156886074663</v>
+        <v>18.256981630928639</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19486,7 +19486,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>17.897662022362251</v>
+        <v>17.926943776180952</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C8" s="447">
         <f>Normalized_FCF!G19</f>
-        <v>1207985509.863308</v>
+        <v>1207991978.2628887</v>
       </c>
       <c r="D8" s="469"/>
       <c r="E8" s="469"/>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
-        <v>1109911979.3294311</v>
+        <v>1109913003.2502544</v>
       </c>
       <c r="D9" s="469"/>
       <c r="E9" s="469"/>
@@ -19764,7 +19764,7 @@
       </c>
       <c r="C14" s="249">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7244289787642528E-2</v>
+        <v>-7.7243301225122574E-2</v>
       </c>
       <c r="D14" s="469"/>
       <c r="E14" s="469"/>
@@ -19846,7 +19846,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>18.905290987553382</v>
+        <v>18.936233263447647</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>18.563012370391103</v>
+        <v>18.593390588264587</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>18.227156886074663</v>
+        <v>18.256981630928639</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19909,7 +19909,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>18.547504222744447</v>
+        <v>18.577856883967211</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>19.254055249803312</v>
+        <v>19.28557227173669</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>17.897662022362251</v>
+        <v>17.926943776180952</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -20004,7 +20004,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.60462764552307136</v>
+        <v>0.60562348290252688</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -20024,7 +20024,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.85</v>
+        <v>10.69</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20035,7 +20035,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.24453329278037109</v>
+        <v>0.25169595174628212</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20044,7 +20044,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>18.563012370391103</v>
+        <v>18.593390588264583</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.3578623759527394E-2</v>
+        <v>3.3578977477643837E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20064,7 +20064,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>18.620994766784168</v>
+        <v>18.65146853674332</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639722490129859</v>
+        <v>0.12639733563871405</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>401</v>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>18.622482490088245</v>
+        <v>18.652958711740901</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20234,7 +20234,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.34124419816581697</v>
+        <v>0.34123668587058209</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.60462764552307136</v>
+        <v>0.60562348290252688</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20308,15 +20308,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.1063788501201428</v>
+        <v>1.1082010847184887</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>8.581103579163214</v>
+        <v>8.5951467911259556</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>9.6874824292833566</v>
+        <v>9.7033478758444449</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20324,7 +20324,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.47975483852432355</v>
+        <v>0.47975421577508026</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20333,15 +20333,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2721389528085512</v>
+        <v>1.2742341985857637</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>10.755809251572087</v>
+        <v>10.773411429165821</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>12.027948204380639</v>
+        <v>12.047645627751585</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20349,7 +20349,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.3540652175126594</v>
+        <v>0.35406450146176049</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20379,15 +20379,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4587265476178874</v>
+        <v>1.4611291079924882</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>13.346791527366802</v>
+        <v>13.368633918699366</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>14.80551807498469</v>
+        <v>14.829763026691854</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.20490187229983359</v>
+        <v>0.20490105122407498</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20404,15 +20404,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5795142828284194</v>
+        <v>1.5821157837288018</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>15.094230422814432</v>
+        <v>15.118932545948894</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>16.67374470564285</v>
+        <v>16.701048329677697</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20420,7 +20420,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.1045728268295737</v>
+        <v>0.10457193776582807</v>
       </c>
     </row>
   </sheetData>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>10.85</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20549,14 +20549,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>13387.174849999999</v>
+        <v>13189.76029</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.24453329278037109</v>
+        <v>0.25169595174628212</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20564,13 +20564,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20608,7 +20608,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1196808250427246</v>
+        <v>1.1215249683380129</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>18.620994766784168</v>
+        <v>18.65146853674332</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20686,7 +20686,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>9.6874824292833566</v>
+        <v>9.7033478758444449</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>12.027948204380639</v>
+        <v>12.047645627751585</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20718,7 +20718,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>14.80551807498469</v>
+        <v>14.829763026691854</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>16.67374470564285</v>
+        <v>16.701048329677697</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20755,22 +20755,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
-        <v>11596568.459835352</v>
+        <v>11597933.687599914</v>
       </c>
       <c r="D44" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20909,7 +20909,7 @@
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
-        <v>-2560354.3696646467</v>
+        <v>-2558989.1419000849</v>
       </c>
       <c r="D46" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
-        <v>-389572485.77647698</v>
+        <v>-389572827.08341813</v>
       </c>
       <c r="D52" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20960,10 +20960,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20979,22 +20979,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21002,7 +21002,7 @@
       </c>
       <c r="C60" s="373">
         <f>Normalized_FCF!G19</f>
-        <v>1207985509.863308</v>
+        <v>1207991978.2628887</v>
       </c>
       <c r="D60" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
-        <v>1109911979.3294311</v>
+        <v>1109913003.2502544</v>
       </c>
       <c r="D61" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21028,7 +21028,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>9.2831174214504319E-2</v>
+        <v>9.4375873288004258E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21038,14 +21038,14 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.5726050278624088E-2</v>
+        <v>5.665327248854321E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
-        <v>0.74682036120712814</v>
+        <v>0.74804970357508505</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21065,11 +21065,11 @@
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
-        <v>0.10095731766647505</v>
+        <v>0.10095740611582539</v>
       </c>
       <c r="D66" s="378">
         <f>Normalized_FCF!G119</f>
-        <v>8.8891696444715382E-2</v>
+        <v>8.8892115514525943E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21079,11 +21079,11 @@
       </c>
       <c r="C67" s="383">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639722490129859</v>
+        <v>0.12639733563871405</v>
       </c>
       <c r="D67" s="383">
         <f>Normalized_FCF!G116</f>
-        <v>0.11129122689748014</v>
+        <v>0.1112917515673339</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21129,22 +21129,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21152,13 +21152,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25694129201089511</v>
+        <v>-0.25736448096827186</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,7 +21215,7 @@
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
-        <v>6701757338.2074413</v>
+        <v>6701529800.2466812</v>
       </c>
       <c r="D84" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.0816824742249942</v>
+        <v>6.091492337374028</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21272,7 +21272,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.52956524602703814</v>
+        <v>0.53043745369196915</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,7 +21285,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.3543064282411379</v>
+        <v>6.3645653100977251</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21307,33 +21307,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21396,23 +21396,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.7471635960610905</v>
+        <v>1.7500412197189974</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21444,7 +21444,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>18.563012370391103</v>
+        <v>18.593390588264583</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21456,13 +21456,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>19.25 HKD</v>
+        <v>19.29 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21530,7 +21530,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>18.91 HKD</v>
+        <v>18.94 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21552,7 +21552,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>18.56 HKD</v>
+        <v>18.59 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>18.23 HKD</v>
+        <v>18.26 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21596,7 +21596,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>17.9 HKD</v>
+        <v>17.93 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21618,7 +21618,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>18.620994766784168</v>
+        <v>18.65146853674332</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21626,13 +21626,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21645,22 +21645,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="C136" s="406">
         <f>Scenarios!C58</f>
-        <v>0.60462764552307136</v>
+        <v>0.60562348290252688</v>
       </c>
       <c r="D136" s="343" t="str">
         <f>Market_currency</f>
@@ -21721,15 +21721,15 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>1.1063788501201428</v>
+        <v>1.1082010847184887</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>8.581103579163214</v>
+        <v>8.5951467911259556</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>9.6874824292833566</v>
+        <v>9.7033478758444449</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21742,15 +21742,15 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>1.2721389528085512</v>
+        <v>1.2742341985857637</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>10.755809251572087</v>
+        <v>10.773411429165821</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>12.027948204380639</v>
+        <v>12.047645627751585</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21782,15 +21782,15 @@
       </c>
       <c r="C144" s="409">
         <f>Scenarios!C66</f>
-        <v>1.4587265476178874</v>
+        <v>1.4611291079924882</v>
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>13.346791527366802</v>
+        <v>13.368633918699366</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>14.80551807498469</v>
+        <v>14.829763026691854</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21803,15 +21803,15 @@
       </c>
       <c r="C145" s="409">
         <f>Scenarios!C67</f>
-        <v>1.5795142828284194</v>
+        <v>1.5821157837288018</v>
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>15.094230422814432</v>
+        <v>15.118932545948894</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>16.67374470564285</v>
+        <v>16.701048329677697</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21829,13 +21829,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21843,13 +21843,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21886,22 +21886,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21925,12 +21925,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21945,15 +21948,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF77D3C-4E40-49A1-9914-29B1F118885E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89347DDA-4D96-4164-94C1-1DC40C68F9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>10.69</v>
+        <v>10.77</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>13189.76029</v>
+        <v>13288.467570000001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.25169595174628212</v>
+        <v>0.24912116807900339</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5447,13 +5447,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1215249683380129</v>
+        <v>1.1232618942260741</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>18.65146853674332</v>
+        <v>18.680169991712596</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>9.7033478758444449</v>
+        <v>9.718290643738694</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>12.047645627751585</v>
+        <v>12.066197514914851</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>14.829763026691854</v>
+        <v>14.852597969762343</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>16.701048329677697</v>
+        <v>16.726764060493078</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5631,22 +5631,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5658,13 +5658,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5684,13 +5684,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5719,13 +5719,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
-        <v>11597933.687599914</v>
+        <v>11599219.541824704</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
-        <v>-2558989.1419000849</v>
+        <v>-2557703.287675295</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5811,13 +5811,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
-        <v>-389572827.08341813</v>
+        <v>-389573148.5469743</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5833,7 +5833,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5855,22 +5855,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="C60" s="285">
         <f>Normalized_FCF!G19</f>
-        <v>1207991978.2628887</v>
+        <v>1207998070.5935199</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
-        <v>1109913003.2502544</v>
+        <v>1109913967.640923</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.4375873288004258E-2</v>
+        <v>9.3820002882418194E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5914,14 +5914,14 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.665327248854321E-2</v>
+        <v>5.6319537872059428E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
-        <v>0.74804970357508505</v>
+        <v>0.74920757062613996</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5941,11 +5941,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
-        <v>0.10095740611582539</v>
+        <v>0.10095748942278249</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>8.8892115514525943E-2</v>
+        <v>8.8892510219864065E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5955,11 +5955,11 @@
       </c>
       <c r="C67" s="263">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639733563871405</v>
+        <v>0.12639743993792121</v>
       </c>
       <c r="D67" s="263">
         <f>Normalized_FCF!G116</f>
-        <v>0.1112917515673339</v>
+        <v>0.11129224573319076</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -6005,13 +6005,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25736448096827186</v>
+        <v>-0.2577630659684112</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
-        <v>6701529800.2466812</v>
+        <v>6701315491.2092161</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.091492337374028</v>
+        <v>6.1007312388404973</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.53043745369196915</v>
+        <v>0.53125895171593207</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>6.3645653100977251</v>
+        <v>6.3742271245880184</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6205,31 +6205,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6279,22 +6279,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>1.7500412197189974</v>
+        <v>1.7527515400288598</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>18.593390588264583</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6328,13 +6328,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>19.29 HKD</v>
+        <v>19.32 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>2.0666445511321369E-2</v>
+        <v>2.0666634921696569E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>18.94 HKD</v>
+        <v>18.97 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.7102998746432419E-2</v>
+        <v>2.7103258946784007E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>18.59 HKD</v>
+        <v>18.62 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>3.357897747764374E-2</v>
+        <v>3.3579310637593417E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>18.26 HKD</v>
+        <v>18.29 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>4.0093436685824935E-2</v>
+        <v>4.0093845016902364E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>17.93 HKD</v>
+        <v>17.95 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6465,17 +6465,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.6645361191894899E-2</v>
+        <v>4.6645846946718673E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>18.65146853674332</v>
+        <v>18.680169991712596</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6510,22 +6510,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
-        <v>0.60562348290252688</v>
+        <v>0.60656142288208004</v>
       </c>
       <c r="D136" s="194" t="str">
         <f>Market_currency</f>
@@ -6586,15 +6586,15 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>1.1082010847184887</v>
+        <v>1.1099173756683709</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>8.5951467911259556</v>
+        <v>8.6083732680703235</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>9.7033478758444449</v>
+        <v>9.718290643738694</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6607,15 +6607,15 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>1.2742341985857637</v>
+        <v>1.2762076280050449</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>10.773411429165821</v>
+        <v>10.789989886909806</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>12.047645627751585</v>
+        <v>12.066197514914851</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6654,15 +6654,15 @@
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
-        <v>1.4611291079924882</v>
+        <v>1.4633919849191011</v>
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>13.368633918699366</v>
+        <v>13.389205984843242</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>14.829763026691854</v>
+        <v>14.852597969762343</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6675,15 +6675,15 @@
       </c>
       <c r="C145" s="333">
         <f>Scenarios!C67</f>
-        <v>1.5821157837288018</v>
+        <v>1.5845660348959618</v>
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>15.118932545948894</v>
+        <v>15.142198025597116</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>16.701048329677697</v>
+        <v>16.726764060493078</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6701,13 +6701,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6744,13 +6744,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6758,22 +6758,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6797,18 +6797,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6825,6 +6813,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="C25" s="37">
         <f>(0.19+0.41)*Exchange_Rate</f>
-        <v>0.67291498100280767</v>
+        <v>0.67395713653564449</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
-        <v>0.67291498100280767</v>
+        <v>0.67395713653564449</v>
       </c>
       <c r="D65" s="70">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -10236,11 +10236,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>13.622104571065252</v>
+        <v>13.643201369395497</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.7500412197189974</v>
+        <v>1.7527515400288598</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>6701529800.2466812</v>
+        <v>6701315491.2092161</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C73" s="285">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-985769232.12795699</v>
+        <v>-985876386.64668953</v>
       </c>
       <c r="D73" s="285">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-966494473.96665943</v>
+        <v>-966601628.48539197</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10514,11 +10514,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>8.7591684410162269</v>
+        <v>8.7582164104254687</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>8.9338521644541338</v>
+        <v>8.9328617847559233</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10531,7 +10531,7 @@
       <c r="C75" s="261"/>
       <c r="D75" s="262">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1932988947.9333189</v>
+        <v>1933203256.9707839</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10646,11 +10646,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-317546848.56237352</v>
+        <v>-318038639.07753044</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.25736448096827186</v>
+        <v>-0.2577630659684112</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10663,11 +10663,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>7515932997.0379086</v>
+        <v>7527332332.4621983</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>6.091492337374028</v>
+        <v>6.1007312388404973</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10680,11 +10680,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>654475478.30075288</v>
+        <v>655489076.24413741</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.53043745369196915</v>
+        <v>0.53125895171593207</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10697,11 +10697,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>7852861626.776288</v>
+        <v>7864782769.6288052</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>6.3645653100977251</v>
+        <v>6.3742271245880184</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11182,36 +11182,36 @@
       </c>
       <c r="C10" s="266">
         <f>C48</f>
-        <v>-2558989.1419000849</v>
+        <v>-2557703.287675295</v>
       </c>
       <c r="E10" s="237"/>
       <c r="G10" s="266">
         <f>G48</f>
-        <v>42508705.722887784</v>
+        <v>42514798.053519025</v>
       </c>
       <c r="H10" s="266">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>40983157.438705444</v>
+        <v>40989683.049221933</v>
       </c>
       <c r="I10" s="266">
         <f t="shared" si="6"/>
-        <v>17733980.44663737</v>
+        <v>17738272.435548246</v>
       </c>
       <c r="J10" s="266">
         <f t="shared" si="6"/>
-        <v>5082679.7665822022</v>
+        <v>5085403.8820458502</v>
       </c>
       <c r="K10" s="266">
         <f t="shared" si="6"/>
-        <v>-4687952.1374051124</v>
+        <v>-4686014.5860516876</v>
       </c>
       <c r="L10" s="266">
         <f t="shared" si="6"/>
-        <v>-6412742.4231768474</v>
+        <v>-6411298.0651826672</v>
       </c>
       <c r="M10" s="266">
         <f t="shared" si="6"/>
-        <v>7542469.2837602021</v>
+        <v>7543362.7658946011</v>
       </c>
       <c r="N10" s="266">
         <f t="shared" si="6"/>
@@ -11237,36 +11237,36 @@
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
-        <v>1558291308.3336725</v>
+        <v>1558292594.1878972</v>
       </c>
       <c r="E11" s="237"/>
       <c r="G11" s="267">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>1372061905.2628887</v>
+        <v>1372067997.5935199</v>
       </c>
       <c r="H11" s="267">
         <f t="shared" si="7"/>
-        <v>1481967825.7587051</v>
+        <v>1481974351.3692217</v>
       </c>
       <c r="I11" s="267">
         <f t="shared" si="7"/>
-        <v>1407261479.4466374</v>
+        <v>1407265771.4355483</v>
       </c>
       <c r="J11" s="267">
         <f t="shared" si="7"/>
-        <v>1240536997.7665823</v>
+        <v>1240539721.8820457</v>
       </c>
       <c r="K11" s="267">
         <f t="shared" si="7"/>
-        <v>1157467738.8625948</v>
+        <v>1157469676.4139483</v>
       </c>
       <c r="L11" s="267">
         <f t="shared" si="7"/>
-        <v>999273072.15682518</v>
+        <v>999274516.51481938</v>
       </c>
       <c r="M11" s="267">
         <f t="shared" si="7"/>
-        <v>939489776.05375922</v>
+        <v>939490669.53589368</v>
       </c>
       <c r="N11" s="267">
         <f t="shared" si="7"/>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
-        <v>-389572827.08341813</v>
+        <v>-389573148.5469743</v>
       </c>
       <c r="E12" s="237"/>
       <c r="G12" s="266">
@@ -11404,38 +11404,38 @@
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
-        <v>1109913003.2502544</v>
+        <v>1109913967.640923</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="243"/>
       <c r="F14" s="58"/>
       <c r="G14" s="267">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>1207991978.2628887</v>
+        <v>1207998070.5935199</v>
       </c>
       <c r="H14" s="267">
         <f t="shared" si="8"/>
-        <v>1497941768.7587051</v>
+        <v>1497948294.3692217</v>
       </c>
       <c r="I14" s="267">
         <f t="shared" si="8"/>
-        <v>1418696956.4466374</v>
+        <v>1418701248.4355483</v>
       </c>
       <c r="J14" s="267">
         <f t="shared" si="8"/>
-        <v>1235084185.7665823</v>
+        <v>1235086909.8820457</v>
       </c>
       <c r="K14" s="267">
         <f t="shared" si="8"/>
-        <v>1149297187.8625948</v>
+        <v>1149299125.4139483</v>
       </c>
       <c r="L14" s="267">
         <f t="shared" si="8"/>
-        <v>975100997.03682518</v>
+        <v>975102441.39481938</v>
       </c>
       <c r="M14" s="267">
         <f t="shared" si="8"/>
-        <v>950285622.42375922</v>
+        <v>950286515.90589368</v>
       </c>
       <c r="N14" s="267">
         <f t="shared" si="8"/>
@@ -11622,38 +11622,38 @@
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
-        <v>1109913003.2502544</v>
+        <v>1109913967.640923</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="234"/>
       <c r="F19" s="26"/>
       <c r="G19" s="271">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>1207991978.2628887</v>
+        <v>1207998070.5935199</v>
       </c>
       <c r="H19" s="271">
         <f t="shared" si="9"/>
-        <v>1497941768.7587051</v>
+        <v>1497948294.3692217</v>
       </c>
       <c r="I19" s="271">
         <f t="shared" si="9"/>
-        <v>1418696956.4466374</v>
+        <v>1418701248.4355483</v>
       </c>
       <c r="J19" s="271">
         <f t="shared" si="9"/>
-        <v>1235084185.7665823</v>
+        <v>1235086909.8820457</v>
       </c>
       <c r="K19" s="271">
         <f t="shared" si="9"/>
-        <v>1149297187.8625948</v>
+        <v>1149299125.4139483</v>
       </c>
       <c r="L19" s="271">
         <f t="shared" si="9"/>
-        <v>975100997.03682518</v>
+        <v>975102441.39481938</v>
       </c>
       <c r="M19" s="271">
         <f t="shared" si="9"/>
-        <v>950285622.42375922</v>
+        <v>950286515.90589368</v>
       </c>
       <c r="N19" s="271">
         <f t="shared" si="9"/>
@@ -12361,31 +12361,31 @@
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>7.6719897692831288E-2</v>
+        <v>7.671955703698656E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.3980876552857338E-2</v>
+        <v>-4.3980682890888557E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>-8.1260498969222498E-3</v>
+        <v>-8.1260251134614731E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>4.3955254940538204E-3</v>
+        <v>4.3955158418687622E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
-        <v>7.0589881045228352E-3</v>
+        <v>7.0589762880992734E-3</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="16"/>
-        <v>2.4189659256830701E-2</v>
+        <v>2.4189624292937251E-2</v>
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.1491180260999713E-2</v>
+        <v>-1.1491169332563061E-2</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
@@ -12499,36 +12499,36 @@
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
-        <v>11597933.687599914</v>
+        <v>11599219.541824704</v>
       </c>
       <c r="E46" s="237"/>
       <c r="G46" s="274">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>54950588.722887784</v>
+        <v>54956681.053519025</v>
       </c>
       <c r="H46" s="274">
         <f t="shared" si="17"/>
-        <v>58858614.438705444</v>
+        <v>58865140.049221933</v>
       </c>
       <c r="I46" s="274">
         <f t="shared" si="17"/>
-        <v>38712166.44663737</v>
+        <v>38716458.435548246</v>
       </c>
       <c r="J46" s="274">
         <f t="shared" si="17"/>
-        <v>24570522.766582202</v>
+        <v>24573246.88204585</v>
       </c>
       <c r="K46" s="274">
         <f t="shared" si="17"/>
-        <v>17476002.862594888</v>
+        <v>17477940.413948312</v>
       </c>
       <c r="L46" s="274">
         <f t="shared" si="17"/>
-        <v>13027579.576823153</v>
+        <v>13029023.934817333</v>
       </c>
       <c r="M46" s="274">
         <f t="shared" si="17"/>
-        <v>8058881.2837602021</v>
+        <v>8059774.7658946011</v>
       </c>
       <c r="N46" s="274">
         <f t="shared" si="17"/>
@@ -12611,36 +12611,36 @@
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
-        <v>-2558989.1419000849</v>
+        <v>-2557703.287675295</v>
       </c>
       <c r="E48" s="237"/>
       <c r="G48" s="267">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>42508705.722887784</v>
+        <v>42514798.053519025</v>
       </c>
       <c r="H48" s="267">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>40983157.438705444</v>
+        <v>40989683.049221933</v>
       </c>
       <c r="I48" s="267">
         <f t="shared" si="18"/>
-        <v>17733980.44663737</v>
+        <v>17738272.435548246</v>
       </c>
       <c r="J48" s="267">
         <f t="shared" si="18"/>
-        <v>5082679.7665822022</v>
+        <v>5085403.8820458502</v>
       </c>
       <c r="K48" s="267">
         <f t="shared" si="18"/>
-        <v>-4687952.1374051124</v>
+        <v>-4686014.5860516876</v>
       </c>
       <c r="L48" s="267">
         <f t="shared" si="18"/>
-        <v>-6412742.4231768474</v>
+        <v>-6411298.0651826672</v>
       </c>
       <c r="M48" s="267">
         <f t="shared" si="18"/>
-        <v>7542469.2837602021</v>
+        <v>7543362.7658946011</v>
       </c>
       <c r="N48" s="267">
         <f t="shared" si="18"/>
@@ -13576,38 +13576,38 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>2.0756671601437855E-4</v>
+        <v>2.0746241680718667E-4</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="234"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>3.4479991745373119E-3</v>
+        <v>3.4484933403941711E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.4531061635587447E-3</v>
+        <v>3.4536559900558653E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>1.6224601714114821E-3</v>
+        <v>1.6228528402251752E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>4.8589893949738127E-4</v>
+        <v>4.8615936212395669E-4</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
-        <v>5.2041770711613053E-4</v>
+        <v>5.2020261617594717E-4</v>
       </c>
       <c r="L76" s="6">
         <f t="shared" si="28"/>
-        <v>7.2522172268054189E-4</v>
+        <v>7.2505837918043162E-4</v>
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>9.2132081411897319E-4</v>
+        <v>9.2142995393200997E-4</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
@@ -13633,38 +13633,38 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.12639733563871403</v>
+        <v>0.12639743993792121</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="234"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>0.1112917515673339</v>
+        <v>0.11129224573319076</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12486573883373253</v>
+        <v>0.12486628866022965</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12874863080142288</v>
+        <v>0.12874902347023659</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11859405654182657</v>
+        <v>0.11859431696445313</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
-        <v>0.12849250356322695</v>
+        <v>0.12849271865416714</v>
       </c>
       <c r="L77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11300852131510365</v>
+        <v>0.11300868465860375</v>
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>0.11475969642912243</v>
+        <v>0.11475980556893547</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.1599333909678506E-2</v>
+        <v>3.1599359984480303E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="234"/>
@@ -13805,38 +13805,38 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>9.0028126096404801E-2</v>
+        <v>9.0028204320810198E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="234"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.7983584140401328E-2</v>
+        <v>9.7984078306258188E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12621165077602572</v>
+        <v>0.12621220060252286</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12979484859947568</v>
+        <v>0.12979524126828937</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11807277334285371</v>
+        <v>0.11807303376548027</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
-        <v>0.12758547650905377</v>
+        <v>0.12758569159999394</v>
       </c>
       <c r="L80" s="62">
         <f t="shared" si="32"/>
-        <v>0.110274883691373</v>
+        <v>0.11027504703487311</v>
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.11607842078748708</v>
+        <v>0.11607852992730013</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
@@ -14028,38 +14028,38 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>9.0028126096404801E-2</v>
+        <v>9.0028204320810198E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="234"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.7983584140401328E-2</v>
+        <v>9.7984078306258188E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12621165077602572</v>
+        <v>0.12621220060252286</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12979484859947568</v>
+        <v>0.12979524126828937</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11807277334285371</v>
+        <v>0.11807303376548027</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
-        <v>0.12758547650905377</v>
+        <v>0.12758569159999394</v>
       </c>
       <c r="L85" s="62">
         <f t="shared" si="35"/>
-        <v>0.110274883691373</v>
+        <v>0.11027504703487311</v>
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.11607842078748708</v>
+        <v>0.11607852992730013</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C88" s="110">
         <f>G88</f>
-        <v>0.67291498100280767</v>
+        <v>0.67395713653564449</v>
       </c>
       <c r="E88" s="237"/>
       <c r="G88" s="109">
         <f>Data!C65</f>
-        <v>0.67291498100280767</v>
+        <v>0.67395713653564449</v>
       </c>
       <c r="H88" s="109">
         <f>Data!D65</f>
@@ -14153,12 +14153,12 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>830270093.07548523</v>
+        <v>831555947.30027616</v>
       </c>
       <c r="E89" s="237"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>830270093.07548523</v>
+        <v>831555947.30027616</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.74804970357508505</v>
+        <v>0.74920757062613996</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.68731424381594541</v>
+        <v>0.68837522802640883</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
@@ -14284,12 +14284,12 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.665327248854321E-2</v>
+        <v>5.6319537872059428E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.665327248854321E-2</v>
+        <v>5.6319537872059428E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
@@ -14421,38 +14421,38 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.13572959234306703</v>
+        <v>0.13572548658010963</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="234"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>-7.4162150206971811E-2</v>
+        <v>-7.4162116013787527E-2</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>5.308632930210222E-2</v>
+        <v>5.3087754601935266E-2</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>0.1343970248208799</v>
+        <v>0.13439799356086679</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>7.1768098682056358E-2</v>
+        <v>7.1768658100369143E-2</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
-        <v>0.15830974646832341</v>
+        <v>0.15831001119779176</v>
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>6.3633791050053068E-2</v>
+        <v>6.3634316888382614E-2</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>0.35104297318945554</v>
+        <v>0.35104425807066475</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
@@ -15037,31 +15037,31 @@
       </c>
       <c r="G113" s="251">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4672935449032138</v>
+        <v>1.4672861448604271</v>
       </c>
       <c r="H113" s="251">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.5708409098905605</v>
+        <v>1.5708340667331566</v>
       </c>
       <c r="I113" s="251">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.426929913256739</v>
+        <v>1.4269255963736946</v>
       </c>
       <c r="J113" s="251">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.657643746550993</v>
+        <v>1.6576400904415105</v>
       </c>
       <c r="K113" s="251">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.5825369706007222</v>
+        <v>1.5825343026733032</v>
       </c>
       <c r="L113" s="251">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3992504609945264</v>
+        <v>1.399248388372714</v>
       </c>
       <c r="M113" s="251">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.045422816601336</v>
+        <v>1.0454218336697738</v>
       </c>
       <c r="N113" s="251">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -15150,39 +15150,39 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.12639733563871403</v>
+        <v>0.12639743993792121</v>
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
-        <v>0.12639733563871405</v>
+        <v>0.12639743993792121</v>
       </c>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>0.1112917515673339</v>
+        <v>0.11129224573319076</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12486573883373253</v>
+        <v>0.12486628866022965</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12874863080142288</v>
+        <v>0.12874902347023659</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11859405654182657</v>
+        <v>0.11859431696445313</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
-        <v>0.12849250356322695</v>
+        <v>0.12849271865416714</v>
       </c>
       <c r="L116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11300852131510365</v>
+        <v>0.11300868465860375</v>
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>0.11475969642912243</v>
+        <v>0.11475980556893547</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
@@ -15324,41 +15324,41 @@
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
-        <v>0.10095740611582539</v>
+        <v>0.10095748942278249</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
         <f>C11/C104</f>
-        <v>0.10095740611582539</v>
+        <v>0.10095748942278249</v>
       </c>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>8.8892115514525943E-2</v>
+        <v>8.8892510219864065E-2</v>
       </c>
       <c r="H119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11047790161878122</v>
+        <v>0.11047838809071681</v>
       </c>
       <c r="I119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11114024418007357</v>
+        <v>0.11114058314529257</v>
       </c>
       <c r="J119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11166262593037485</v>
+        <v>0.11166287113215968</v>
       </c>
       <c r="K119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11542186115090253</v>
+        <v>0.11542205436214789</v>
       </c>
       <c r="L119" s="99">
         <f t="shared" si="47"/>
-        <v>0.10956982037136526</v>
+        <v>0.1095699787445371</v>
       </c>
       <c r="M119" s="99">
         <f t="shared" si="47"/>
-        <v>0.11176379901804423</v>
+        <v>0.1117639053086716</v>
       </c>
       <c r="N119" s="99">
         <f t="shared" si="47"/>
@@ -15448,50 +15448,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0088780854487656</v>
+        <v>1.010441431043644</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0980289722694088</v>
+        <v>1.0997350558105299</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>1.3615847542586879</v>
+        <v>1.3636994058277274</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>1.2895535641626841</v>
+        <v>1.2915546262918887</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>1.1226549874227283</v>
+        <v>1.1243961433668803</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>1.0446771441608471</v>
+        <v>1.046296818345996</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.88633795993818498</v>
+        <v>0.88771196238868244</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.86378151852700258</v>
+        <v>0.86512008590568035</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63157194768649028</v>
+        <v>0.63255007452011369</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.52008814412967963</v>
+        <v>0.52089361399180079</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.49031550071977426</v>
+        <v>0.49107486115361276</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15505,50 +15505,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.4375873288004258E-2</v>
+        <v>9.3820002882418194E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10271552593726931</v>
+        <v>0.10211096154229618</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.12736994894842732</v>
+        <v>0.12662018624212884</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12063176465506867</v>
+        <v>0.11992150661948828</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.10501917562420283</v>
+        <v>0.10440075611577349</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>9.7724709463128834E-2</v>
+        <v>9.7149193903992195E-2</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>8.2912811968024788E-2</v>
+        <v>8.2424509042588898E-2</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>8.0802761321515676E-2</v>
+        <v>8.0326841773972174E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.9080631214826033E-2</v>
+        <v>5.8732597448478523E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.8651837617369471E-2</v>
+        <v>4.8365238067948076E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>4.5866744688472808E-2</v>
+        <v>4.5596551639146964E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15562,43 +15562,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12158383766957755</v>
+        <v>0.1206807079561545</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12345564052703493</v>
+        <v>0.12253860698551564</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10547842397520933</v>
+        <v>0.10469492593268225</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8810079436250309E-2</v>
+        <v>9.8076114129388658E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4239388712954383E-2</v>
+        <v>9.3539374683517404E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5268056384821531E-2</v>
+        <v>8.4634681778434737E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0260296349934651E-2</v>
+        <v>6.9738399998217404E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.948423250685172E-2</v>
+        <v>6.8968100789066386E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7767205789757385E-2</v>
+        <v>4.7412389033658908E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6620998902171862E-2</v>
+        <v>4.6274696217661761E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
-        <v>1109913003.2502544</v>
+        <v>1109913967.640923</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
-        <v>6701529800.2466812</v>
+        <v>6701315491.2092161</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16413,7 +16413,7 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>13453490948.487934</v>
+        <v>13453502638.071796</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16435,7 +16435,7 @@
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
-        <v>-2558989.1419000849</v>
+        <v>-2557703.287675295</v>
       </c>
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
@@ -16446,14 +16446,14 @@
       </c>
       <c r="C7" s="275">
         <f>F7</f>
-        <v>7001949888.2966814</v>
+        <v>7001735579.2592163</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>424</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
-        <v>7001949888.2966814</v>
+        <v>7001735579.2592163</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>20455440836.784615</v>
+        <v>20455238217.331013</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>6.3645653100977251</v>
+        <v>6.3742271245880184</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="I8" s="313">
         <f>Normalized_FCF!C10</f>
-        <v>-2558989.1419000849</v>
+        <v>-2557703.287675295</v>
       </c>
       <c r="J8" s="313"/>
       <c r="N8" s="304"/>
@@ -16512,7 +16512,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1215249683380129</v>
+        <v>1.1232618942260741</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16537,7 +16537,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>22941287636.81496</v>
+        <v>22976589626.844818</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>18.593390588264583</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16649,14 +16649,14 @@
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
-        <v>0.12639733563871403</v>
+        <v>0.12639743993792121</v>
       </c>
       <c r="E17" s="308" t="s">
         <v>550</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
-        <v>0.12639733563871405</v>
+        <v>0.12639743993792121</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>412</v>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>18.652958711740901</v>
+        <v>18.681662475867796</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16749,11 +16749,11 @@
       </c>
       <c r="E21" s="299">
         <f>$C$17</f>
-        <v>0.12639733563871403</v>
+        <v>0.12639743993792121</v>
       </c>
       <c r="F21" s="277">
         <f>C21*E21</f>
-        <v>1561020003.7978127</v>
+        <v>1561021291.9036732</v>
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16761,15 +16761,15 @@
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>1111856551.6493003</v>
+        <v>1111857517.7286956</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
-        <v>1.7510817454651217E-3</v>
+        <v>1.7510817454648997E-3</v>
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>9.0028126096404815E-2</v>
+        <v>9.0028204320810185E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>1027119216.3042035</v>
+        <v>1027120108.7563008</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16798,11 +16798,11 @@
       </c>
       <c r="E22" s="299">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>0.12639733563871403</v>
+        <v>0.12639743993792121</v>
       </c>
       <c r="F22" s="277">
         <f t="shared" ref="F22:F50" si="7">IF(A22="", 0,C22*E22)</f>
-        <v>1563753477.430769</v>
+        <v>1563754767.7922082</v>
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
@@ -16810,15 +16810,15 @@
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>1113803503.3604693</v>
+        <v>1113804471.1315489</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
-        <v>1.7510817454651217E-3</v>
+        <v>1.7510817454653438E-3</v>
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
-        <v>9.0028126096404815E-2</v>
+        <v>9.0028204320810226E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16826,7 +16826,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>950501418.95084572</v>
+        <v>950502244.8306185</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16847,11 +16847,11 @@
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
-        <v>0.12639733563871403</v>
+        <v>0.12639743993792121</v>
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>1566491737.5995054</v>
+        <v>1566493030.2204731</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
@@ -16859,7 +16859,7 @@
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>1115753864.3432388</v>
+        <v>1115754833.8089645</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
@@ -16867,7 +16867,7 @@
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>9.0028126096404815E-2</v>
+        <v>9.0028204320810198E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>879598914.21210992</v>
+        <v>879599678.48551011</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -18299,11 +18299,11 @@
       </c>
       <c r="E51" s="301">
         <f>F17</f>
-        <v>0.12639733563871405</v>
+        <v>0.12639743993792121</v>
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>1566491737.5995059</v>
+        <v>1566493030.2204731</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
@@ -18311,7 +18311,7 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>13524289264.766537</v>
+        <v>13524301015.866238</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>10661805020.752851</v>
+        <v>10661814284.672852</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18337,7 +18337,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>13519024570.220011</v>
+        <v>13519036316.745281</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18361,7 +18361,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>13519024570.220011</v>
+        <v>13519036316.745281</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18396,19 +18396,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>13184421129.518175</v>
+        <v>13184432585.310358</v>
       </c>
       <c r="C56" s="118">
-        <v>13318956039.003057</v>
+        <v>13318967611.691078</v>
       </c>
       <c r="D56" s="118">
-        <v>13453490948.487934</v>
+        <v>13453502638.071795</v>
       </c>
       <c r="E56" s="118">
-        <v>13588025857.972816</v>
+        <v>13588037664.452515</v>
       </c>
       <c r="F56" s="118">
-        <v>13722560767.457695</v>
+        <v>13722572690.833233</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18422,19 +18422,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>12940829053.222229</v>
+        <v>12940840297.360056</v>
       </c>
       <c r="C57" s="118">
-        <v>13195917184.13929</v>
+        <v>13195928649.920256</v>
       </c>
       <c r="D57" s="118">
-        <v>13453490948.487936</v>
+        <v>13453502638.071796</v>
       </c>
       <c r="E57" s="118">
-        <v>13713550346.268179</v>
+        <v>13713562261.814661</v>
       </c>
       <c r="F57" s="118">
-        <v>13976095377.480011</v>
+        <v>13976107521.148859</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18448,19 +18448,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>12720302277.453148</v>
+        <v>12720313329.977791</v>
       </c>
       <c r="C58" s="118">
-        <v>13083392042.046787</v>
+        <v>13083403410.055954</v>
       </c>
       <c r="D58" s="118">
-        <v>13453490948.487936</v>
+        <v>13453502638.071795</v>
       </c>
       <c r="E58" s="118">
-        <v>13830667882.691561</v>
+        <v>13830679900.000128</v>
       </c>
       <c r="F58" s="118">
-        <v>14214991730.572626</v>
+        <v>14215004081.815777</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18474,19 +18474,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>12520656789.920864</v>
+        <v>12520667668.975832</v>
       </c>
       <c r="C59" s="118">
-        <v>12980482212.327087</v>
+        <v>12980493490.919083</v>
       </c>
       <c r="D59" s="118">
-        <v>13453490948.487936</v>
+        <v>13453502638.071798</v>
       </c>
       <c r="E59" s="118">
-        <v>13939941519.446865</v>
+        <v>13939953631.702045</v>
       </c>
       <c r="F59" s="118">
-        <v>14440094991.685305</v>
+        <v>14440107538.518091</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18500,19 +18500,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>12339915378.575241</v>
+        <v>12339926100.586067</v>
       </c>
       <c r="C60" s="118">
-        <v>12886366063.206989</v>
+        <v>12886377260.022547</v>
       </c>
       <c r="D60" s="118">
-        <v>13453490948.487936</v>
+        <v>13453502638.071796</v>
       </c>
       <c r="E60" s="118">
-        <v>14041896598.544199</v>
+        <v>14041908799.386974</v>
       </c>
       <c r="F60" s="118">
-        <v>14652201528.71526</v>
+        <v>14652214259.844982</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18526,19 +18526,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>12176288050.059109</v>
+        <v>12176298629.89603</v>
       </c>
       <c r="C61" s="118">
-        <v>12800292171.632957</v>
+        <v>12800303293.659893</v>
       </c>
       <c r="D61" s="118">
-        <v>13453490948.487938</v>
+        <v>13453502638.071796</v>
       </c>
       <c r="E61" s="118">
-        <v>14137023277.424849</v>
+        <v>14137035560.922102</v>
       </c>
       <c r="F61" s="118">
-        <v>14852061729.888985</v>
+        <v>14852074634.674942</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18552,19 +18552,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>12028154302.303165</v>
+        <v>12028164753.428371</v>
       </c>
       <c r="C62" s="118">
-        <v>12721573323.911663</v>
+        <v>12721584377.540699</v>
       </c>
       <c r="D62" s="118">
-        <v>13453490948.487938</v>
+        <v>13453502638.071796</v>
       </c>
       <c r="E62" s="118">
-        <v>14225778885.433582</v>
+        <v>14225791246.049566</v>
       </c>
       <c r="F62" s="118">
-        <v>15040382658.477619</v>
+        <v>15040395726.893473</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18578,19 +18578,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>11894047075.697321</v>
+        <v>11894057410.2983</v>
       </c>
       <c r="C63" s="118">
-        <v>12649581028.997969</v>
+        <v>12649592020.073727</v>
       </c>
       <c r="D63" s="118">
-        <v>13453490948.487938</v>
+        <v>13453502638.0718</v>
       </c>
       <c r="E63" s="118">
-        <v>14308590122.467136</v>
+        <v>14308602555.036854</v>
       </c>
       <c r="F63" s="118">
-        <v>15217830554.237814</v>
+        <v>15217843776.836105</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18604,19 +18604,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>11772638223.897112</v>
+        <v>11772648453.007336</v>
       </c>
       <c r="C64" s="118">
-        <v>12583740500.624241</v>
+        <v>12583751434.49192</v>
       </c>
       <c r="D64" s="118">
-        <v>13453490948.487938</v>
+        <v>13453502638.071796</v>
       </c>
       <c r="E64" s="118">
-        <v>14385855110.369114</v>
+        <v>14385867610.07349</v>
       </c>
       <c r="F64" s="118">
-        <v>15385033190.427555</v>
+        <v>15385046558.306297</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18630,19 +18630,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>11662725360.373596</v>
+        <v>11662735493.981794</v>
       </c>
       <c r="C65" s="118">
-        <v>12523526068.208546</v>
+        <v>12523536949.756594</v>
       </c>
       <c r="D65" s="118">
-        <v>13453490948.487938</v>
+        <v>13453502638.071796</v>
       </c>
       <c r="E65" s="118">
-        <v>14457945306.933544</v>
+        <v>14457957869.276268</v>
       </c>
       <c r="F65" s="118">
-        <v>15542582094.735672</v>
+        <v>15542595599.506851</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18656,19 +18656,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>11250911081.089531</v>
+        <v>11250920856.877028</v>
       </c>
       <c r="C66" s="277">
-        <v>12291385202.259321</v>
+        <v>12291395882.102839</v>
       </c>
       <c r="D66" s="118">
-        <v>13453490948.487938</v>
+        <v>13453502638.0718</v>
       </c>
       <c r="E66" s="118">
-        <v>14752124208.403801</v>
+        <v>14752137026.355196</v>
       </c>
       <c r="F66" s="118">
-        <v>16203940695.738838</v>
+        <v>16203954775.15691</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18691,19 +18691,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>11000477678.257307</v>
+        <v>11000487236.446093</v>
       </c>
       <c r="C67" s="277">
-        <v>12142864139.56918</v>
+        <v>12142874690.36445</v>
       </c>
       <c r="D67" s="118">
-        <v>13453490948.487938</v>
+        <v>13453502638.0718</v>
       </c>
       <c r="E67" s="118">
-        <v>14960131646.776283</v>
+        <v>14960144645.462954</v>
       </c>
       <c r="F67" s="118">
-        <v>16695185918.07766</v>
+        <v>16695200424.333065</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18726,19 +18726,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>10848183568.001682</v>
+        <v>10848192993.863861</v>
       </c>
       <c r="C68" s="277">
-        <v>12047842067.63707</v>
+        <v>12047852535.868753</v>
       </c>
       <c r="D68" s="118">
-        <v>13453490948.487938</v>
+        <v>13453502638.0718</v>
       </c>
       <c r="E68" s="118">
-        <v>15107209136.705166</v>
+        <v>15107222263.18578</v>
       </c>
       <c r="F68" s="118">
-        <v>17060073995.596687</v>
+        <v>17060088818.899153</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18761,19 +18761,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>10755570139.616131</v>
+        <v>10755579485.007566</v>
       </c>
       <c r="C69" s="277">
-        <v>11987048036.199871</v>
+        <v>11987058451.608318</v>
       </c>
       <c r="D69" s="118">
-        <v>13453490948.487938</v>
+        <v>13453502638.0718</v>
       </c>
       <c r="E69" s="118">
-        <v>15211204398.668079</v>
+        <v>15211217615.50898</v>
       </c>
       <c r="F69" s="118">
-        <v>17331106268.402588</v>
+        <v>17331121327.201885</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18870,23 +18870,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>18.593390588264583</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>18.593390588264583</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>18.593390588264583</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>18.593390588264583</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>18.593390588264583</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18901,23 +18901,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>18.348814082701246</v>
+        <v>18.377046547894334</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>18.471102335482918</v>
+        <v>18.499524297111748</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>18.593390588264583</v>
+        <v>18.622002046329158</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>18.715678841046252</v>
+        <v>18.744479795546575</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>18.83796709382792</v>
+        <v>18.866957544763981</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18932,23 +18932,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>18.127396091521504</v>
+        <v>18.155285450004154</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>18.359263656264581</v>
+        <v>18.387512313993746</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>18.593390588264587</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>18.829776887521533</v>
+        <v>18.858754647010386</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>19.068422554035408</v>
+        <v>19.097770116037442</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18963,23 +18963,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>17.926943776180952</v>
+        <v>17.954522516117425</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>18.256981630928639</v>
+        <v>18.285071793636401</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>18.593390588264587</v>
+        <v>18.622002046329158</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>18.936233263447647</v>
+        <v>18.96537598648241</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>19.28557227173669</v>
+        <v>19.315256326382872</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>17.74547193411745</v>
+        <v>17.772769467425512</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>18.163439640090225</v>
+        <v>18.191384851231074</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>18.593390588264587</v>
+        <v>18.622002046329165</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>19.035559766621212</v>
+        <v>19.064856404835052</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>19.490184476868613</v>
+        <v>19.520185596177178</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -19025,23 +19025,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>17.581183338069202</v>
+        <v>17.60822629170443</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>18.077890844773798</v>
+        <v>18.105703490509342</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>18.593390588264587</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>19.128233917388236</v>
+        <v>19.157674162374242</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>19.68298304429084</v>
+        <v>19.713282921987982</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -19056,23 +19056,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>17.432450937027827</v>
+        <v>17.459263416686731</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>17.999652223653008</v>
+        <v>18.027343631743047</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>18.593390588264587</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>19.214701254362552</v>
+        <v>19.244275488115193</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>19.864650054702548</v>
+        <v>19.895231441458673</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19088,23 +19088,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>17.297801742551577</v>
+        <v>17.324405571405116</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>17.928099119810433</v>
+        <v>17.955679650053778</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>18.593390588264587</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>19.295377476389387</v>
+        <v>19.32507672506518</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>20.035828207700177</v>
+        <v>20.066674850105418</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19119,23 +19119,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>17.175902240854828</v>
+        <v>17.202317175676729</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>17.862660253478658</v>
+        <v>17.890139380425722</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>18.593390588264587</v>
+        <v>18.622002046329165</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>19.370650441051843</v>
+        <v>19.400466331826831</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>20.197123095513199</v>
+        <v>20.228219678576256</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19151,23 +19151,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>17.065545186200957</v>
+        <v>17.091789113031165</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>17.802813160944286</v>
+        <v>17.830199549541859</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>18.593390588264587</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>19.440882029328129</v>
+        <v>19.470806750144856</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>20.349105345461716</v>
+        <v>20.380437438428679</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19183,23 +19183,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>16.965637644805309</v>
+        <v>16.991726756086454</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>17.748080023199226</v>
+        <v>17.775381597971396</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>18.593390588264587</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>19.506409885364199</v>
+        <v>19.536436147374612</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>20.492312638715749</v>
+        <v>20.523866644017112</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19215,23 +19215,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>16.591310647619117</v>
+        <v>16.616819706195646</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>17.537070843464022</v>
+        <v>17.564045440897331</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>18.593390588264587</v>
+        <v>18.622002046329165</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>19.773809804119647</v>
+        <v>19.804250425893731</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>21.093468042086318</v>
+        <v>21.125953590718087</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19247,23 +19247,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>16.363674093004555</v>
+        <v>16.388830408657999</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>17.402069591170502</v>
+        <v>17.428834992253808</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>18.593390588264587</v>
+        <v>18.622002046329165</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>19.96288241212568</v>
+        <v>19.993616018585527</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>21.539995416707317</v>
+        <v>21.57317289889793</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19279,23 +19279,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>16.225243252091904</v>
+        <v>16.250185056945224</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>17.315697338817831</v>
+        <v>17.342328898476506</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>18.593390588264587</v>
+        <v>18.622002046329165</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>20.096571499484362</v>
+        <v>20.12751226897889</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>21.87166788470477</v>
+        <v>21.905359322644113</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19311,23 +19311,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>16.141060385468261</v>
+        <v>16.165871741543285</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>17.260437362708473</v>
+        <v>17.286983292159228</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>18.593390588264587</v>
+        <v>18.622002046329165</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>20.191100116121564</v>
+        <v>20.222187366046718</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>22.118028202749976</v>
+        <v>22.152101397735613</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>19.28557227173669</v>
+        <v>19.315256326382872</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19402,7 +19402,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>18.936233263447647</v>
+        <v>18.96537598648241</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>18.593390588264587</v>
+        <v>18.622002046329158</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19458,7 +19458,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>18.256981630928639</v>
+        <v>18.285071793636401</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19486,7 +19486,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>17.926943776180952</v>
+        <v>17.954522516117425</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C8" s="447">
         <f>Normalized_FCF!G19</f>
-        <v>1207991978.2628887</v>
+        <v>1207998070.5935199</v>
       </c>
       <c r="D8" s="469"/>
       <c r="E8" s="469"/>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
-        <v>1109913003.2502544</v>
+        <v>1109913967.640923</v>
       </c>
       <c r="D9" s="469"/>
       <c r="E9" s="469"/>
@@ -19764,7 +19764,7 @@
       </c>
       <c r="C14" s="249">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.7243301225122574E-2</v>
+        <v>-7.7242370143822403E-2</v>
       </c>
       <c r="D14" s="469"/>
       <c r="E14" s="469"/>
@@ -19846,7 +19846,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>18.936233263447647</v>
+        <v>18.96537598648241</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>18.593390588264587</v>
+        <v>18.622002046329158</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>18.256981630928639</v>
+        <v>18.285071793636401</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19909,7 +19909,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>18.577856883967211</v>
+        <v>18.606444271186618</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>19.28557227173669</v>
+        <v>19.315256326382872</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>17.926943776180952</v>
+        <v>17.954522516117425</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -20004,7 +20004,7 @@
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
-        <v>0.60562348290252688</v>
+        <v>0.60656142288208004</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -20024,7 +20024,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>10.69</v>
+        <v>10.77</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20035,7 +20035,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.25169595174628212</v>
+        <v>0.24912116807900339</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20044,7 +20044,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>18.593390588264583</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>3.3578977477643837E-2</v>
+        <v>3.3579310637593326E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20064,7 +20064,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>18.65146853674332</v>
+        <v>18.680169991712596</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639733563871405</v>
+        <v>0.12639743993792121</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>401</v>
@@ -20167,7 +20167,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>18.652958711740901</v>
+        <v>18.681662475867796</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20234,7 +20234,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.34123668587058209</v>
+        <v>0.34122961019176623</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="C58" s="155">
         <f>C33</f>
-        <v>0.60562348290252688</v>
+        <v>0.60656142288208004</v>
       </c>
       <c r="D58" t="str">
         <f>Market_currency</f>
@@ -20308,15 +20308,15 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>1.1082010847184887</v>
+        <v>1.1099173756683709</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>8.5951467911259556</v>
+        <v>8.6083732680703235</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>9.7033478758444449</v>
+        <v>9.718290643738694</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20324,7 +20324,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.47975421577508026</v>
+        <v>0.47975362922017384</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20333,15 +20333,15 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>1.2742341985857637</v>
+        <v>1.2762076280050449</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>10.773411429165821</v>
+        <v>10.789989886909806</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>12.047645627751585</v>
+        <v>12.066197514914851</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20349,7 +20349,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.35406450146176049</v>
+        <v>0.35406382702791328</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20379,15 +20379,15 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>1.4611291079924882</v>
+        <v>1.4633919849191011</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>13.368633918699366</v>
+        <v>13.389205984843242</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>14.829763026691854</v>
+        <v>14.852597969762343</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.20490105122407498</v>
+        <v>0.20490027786943821</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20404,15 +20404,15 @@
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>1.5821157837288018</v>
+        <v>1.5845660348959618</v>
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>15.118932545948894</v>
+        <v>15.142198025597116</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>16.701048329677697</v>
+        <v>16.726764060493078</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20420,7 +20420,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.10457193776582807</v>
+        <v>0.10457110037468287</v>
       </c>
     </row>
   </sheetData>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>10.69</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20549,14 +20549,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>13189.76029</v>
+        <v>13288.467570000001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.25169595174628212</v>
+        <v>0.24912116807900339</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20564,13 +20564,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20608,7 +20608,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1215249683380129</v>
+        <v>1.1232618942260741</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>18.65146853674332</v>
+        <v>18.680169991712596</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20686,7 +20686,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>9.7033478758444449</v>
+        <v>9.718290643738694</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>12.047645627751585</v>
+        <v>12.066197514914851</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20718,7 +20718,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>14.829763026691854</v>
+        <v>14.852597969762343</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>16.701048329677697</v>
+        <v>16.726764060493078</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20755,22 +20755,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
-        <v>11597933.687599914</v>
+        <v>11599219.541824704</v>
       </c>
       <c r="D44" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20909,7 +20909,7 @@
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
-        <v>-2558989.1419000849</v>
+        <v>-2557703.287675295</v>
       </c>
       <c r="D46" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
-        <v>-389572827.08341813</v>
+        <v>-389573148.5469743</v>
       </c>
       <c r="D52" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20960,10 +20960,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20979,22 +20979,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21002,7 +21002,7 @@
       </c>
       <c r="C60" s="373">
         <f>Normalized_FCF!G19</f>
-        <v>1207991978.2628887</v>
+        <v>1207998070.5935199</v>
       </c>
       <c r="D60" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
-        <v>1109913003.2502544</v>
+        <v>1109913967.640923</v>
       </c>
       <c r="D61" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21028,7 +21028,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>9.4375873288004258E-2</v>
+        <v>9.3820002882418194E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21038,14 +21038,14 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.665327248854321E-2</v>
+        <v>5.6319537872059428E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
-        <v>0.74804970357508505</v>
+        <v>0.74920757062613996</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21065,11 +21065,11 @@
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
-        <v>0.10095740611582539</v>
+        <v>0.10095748942278249</v>
       </c>
       <c r="D66" s="378">
         <f>Normalized_FCF!G119</f>
-        <v>8.8892115514525943E-2</v>
+        <v>8.8892510219864065E-2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -21079,11 +21079,11 @@
       </c>
       <c r="C67" s="383">
         <f>Normalized_FCF!E116</f>
-        <v>0.12639733563871405</v>
+        <v>0.12639743993792121</v>
       </c>
       <c r="D67" s="383">
         <f>Normalized_FCF!G116</f>
-        <v>0.1112917515673339</v>
+        <v>0.11129224573319076</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -21129,22 +21129,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21152,13 +21152,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.25736448096827186</v>
+        <v>-0.2577630659684112</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,7 +21215,7 @@
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
-        <v>6701529800.2466812</v>
+        <v>6701315491.2092161</v>
       </c>
       <c r="D84" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.091492337374028</v>
+        <v>6.1007312388404973</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21272,7 +21272,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.53043745369196915</v>
+        <v>0.53125895171593207</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21285,7 +21285,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>6.3645653100977251</v>
+        <v>6.3742271245880184</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21307,33 +21307,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21396,23 +21396,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>1.7500412197189974</v>
+        <v>1.7527515400288598</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21444,7 +21444,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>18.593390588264583</v>
+        <v>18.622002046329161</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21456,13 +21456,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>19.29 HKD</v>
+        <v>19.32 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21530,7 +21530,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>18.94 HKD</v>
+        <v>18.97 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21552,7 +21552,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>18.59 HKD</v>
+        <v>18.62 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>18.26 HKD</v>
+        <v>18.29 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21596,7 +21596,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>17.93 HKD</v>
+        <v>17.95 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21618,7 +21618,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>18.65146853674332</v>
+        <v>18.680169991712596</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21626,13 +21626,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21645,22 +21645,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="C136" s="406">
         <f>Scenarios!C58</f>
-        <v>0.60562348290252688</v>
+        <v>0.60656142288208004</v>
       </c>
       <c r="D136" s="343" t="str">
         <f>Market_currency</f>
@@ -21721,15 +21721,15 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>1.1082010847184887</v>
+        <v>1.1099173756683709</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>8.5951467911259556</v>
+        <v>8.6083732680703235</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>9.7033478758444449</v>
+        <v>9.718290643738694</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21742,15 +21742,15 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>1.2742341985857637</v>
+        <v>1.2762076280050449</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>10.773411429165821</v>
+        <v>10.789989886909806</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>12.047645627751585</v>
+        <v>12.066197514914851</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21782,15 +21782,15 @@
       </c>
       <c r="C144" s="409">
         <f>Scenarios!C66</f>
-        <v>1.4611291079924882</v>
+        <v>1.4633919849191011</v>
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>13.368633918699366</v>
+        <v>13.389205984843242</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>14.829763026691854</v>
+        <v>14.852597969762343</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21803,15 +21803,15 @@
       </c>
       <c r="C145" s="409">
         <f>Scenarios!C67</f>
-        <v>1.5821157837288018</v>
+        <v>1.5845660348959618</v>
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>15.118932545948894</v>
+        <v>15.142198025597116</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>16.701048329677697</v>
+        <v>16.726764060493078</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21829,13 +21829,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21843,13 +21843,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21886,22 +21886,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21925,15 +21925,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21948,12 +21945,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0811.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0811.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
